--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -9,11 +9,11 @@
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
     <sheet name="清单" sheetId="1" r:id="rId2"/>
-    <sheet name="已出手" sheetId="3" r:id="rId3"/>
+    <sheet name="已出售" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已出手!$C$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已出售!$C$1:$D$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="59">
   <si>
     <t>时间</t>
   </si>
@@ -119,6 +119,9 @@
     <t>中国西电</t>
   </si>
   <si>
+    <t>低于14补仓</t>
+  </si>
+  <si>
     <t>电魂网络</t>
   </si>
   <si>
@@ -161,7 +164,10 @@
     <t>黄河旋风</t>
   </si>
   <si>
-    <t>短期持有，升职5%以上可以考虑售出</t>
+    <t>短期持有，升值5%以上可以考虑售出</t>
+  </si>
+  <si>
+    <t>ST闻泰</t>
   </si>
   <si>
     <t>出手时间</t>
@@ -192,6 +198,12 @@
   </si>
   <si>
     <t>月度盈亏</t>
+  </si>
+  <si>
+    <t>月份盈亏</t>
+  </si>
+  <si>
+    <t>季度盈亏</t>
   </si>
   <si>
     <t>单次购入单次售出</t>
@@ -369,12 +381,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -569,7 +587,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -581,43 +599,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -779,7 +760,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -791,119 +772,119 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -913,6 +894,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -922,15 +906,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -949,9 +924,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -961,10 +933,25 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1498,8 +1485,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="2" width="8.875" customWidth="1"/>
@@ -1531,7 +1518,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>46096</v>
       </c>
       <c r="B2" s="2">
@@ -1556,7 +1543,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>46107</v>
       </c>
       <c r="B3" s="2">
@@ -1582,7 +1569,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>46101</v>
       </c>
       <c r="B4" s="2">
@@ -1608,7 +1595,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>46177</v>
       </c>
       <c r="B5" s="2">
@@ -1634,7 +1621,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>46182</v>
       </c>
       <c r="B6" s="2">
@@ -1660,7 +1647,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>46184</v>
       </c>
       <c r="B7" s="2">
@@ -1683,6 +1670,32 @@
       <c r="G7" s="2">
         <f t="shared" si="1"/>
         <v>293715</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4">
+        <v>46190</v>
+      </c>
+      <c r="B8" s="2">
+        <f>SUM(D8+C8)</f>
+        <v>282342</v>
+      </c>
+      <c r="C8" s="2">
+        <f>B7</f>
+        <v>281842</v>
+      </c>
+      <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>11873</v>
+      </c>
+      <c r="G8" s="2">
+        <f>SUM(B8+F8-E8)</f>
+        <v>294215</v>
       </c>
     </row>
   </sheetData>
@@ -1693,21 +1706,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
-    <col min="2" max="2" width="9.375" style="10"/>
-    <col min="3" max="3" width="9" style="9"/>
-    <col min="4" max="4" width="9" style="10"/>
+    <col min="1" max="1" width="9" style="8"/>
+    <col min="2" max="2" width="9.375" style="8"/>
+    <col min="3" max="3" width="9" style="7"/>
+    <col min="4" max="4" width="9" style="8"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="8" width="12.875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="9" style="9"/>
-    <col min="10" max="10" width="68.625" style="11" customWidth="1"/>
+    <col min="6" max="8" width="12.875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="9" style="7"/>
+    <col min="10" max="10" width="68.625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" spans="1:11">
+    <row r="1" s="7" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1720,2128 +1733,2147 @@
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>300323</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <v>1</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="12">
         <v>46182</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
         <v>16.6114</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>1600</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="5">
         <f>F2*G2</f>
         <v>26578.24</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="4">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5">
         <v>600740</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <v>1</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="12">
         <v>46182</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="5">
         <v>4.1541</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <v>1800</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <f t="shared" ref="H3:H16" si="0">F3*G3</f>
         <v>7477.38</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="15"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="16">
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" hidden="1" spans="1:11">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="15">
         <v>46182</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="13">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="13">
         <v>4300</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="13">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="2"/>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>601990</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>46182</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>9.9227</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>500</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="5">
         <f t="shared" si="0"/>
         <v>4961.35</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>600059</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>46182</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>10.9008</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>1000</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <f t="shared" si="0"/>
         <v>10900.8</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>1</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>46182</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>9.6507</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>1000</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="5">
         <f t="shared" si="0"/>
         <v>9650.7</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="J7" s="11"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>601179</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>1</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>46182</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>20.12</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>700</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <f t="shared" si="0"/>
         <v>14084</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="15"/>
+      <c r="J8" s="11" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>603258</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="4">
+        <v>29</v>
+      </c>
+      <c r="D9" s="5">
         <v>1</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>46182</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>20.6888</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <v>900</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <f t="shared" si="0"/>
         <v>18619.92</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="15"/>
+      <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="4">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>600422</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5">
         <v>1</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>46182</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>21.0619</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <v>600</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="5">
         <f t="shared" si="0"/>
         <v>12637.14</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="19" t="s">
-        <v>30</v>
+      <c r="J10" s="17" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>2</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>46188</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>8.5</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>600</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <f t="shared" si="0"/>
         <v>5100</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="20"/>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>600879</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="4">
+        <v>32</v>
+      </c>
+      <c r="D12" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>46182</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>26.2661</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>700</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <f t="shared" si="0"/>
         <v>18386.27</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="15"/>
+      <c r="J12" s="11"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <v>601066</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="4">
+        <v>33</v>
+      </c>
+      <c r="D13" s="5">
         <v>1</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>46182</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>27.6302</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <v>3400</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="5">
         <f t="shared" si="0"/>
         <v>93942.68</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="15" t="s">
-        <v>33</v>
+      <c r="J13" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="4">
+      <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>34</v>
+      <c r="B14" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="4">
+        <v>36</v>
+      </c>
+      <c r="D14" s="5">
         <v>1</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <v>46182</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>18.3681</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>1000</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="5">
         <f t="shared" si="0"/>
         <v>18368.1</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="15" t="s">
-        <v>36</v>
+      <c r="J14" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>300589</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="4">
+        <v>38</v>
+      </c>
+      <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <v>46182</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>22.8225</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <v>1200</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="5">
         <f t="shared" si="0"/>
         <v>27387</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="15" t="s">
-        <v>38</v>
+      <c r="J15" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="4">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <v>300129</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="4">
+        <v>40</v>
+      </c>
+      <c r="D16" s="5">
         <v>1</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <v>46182</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>14.9016</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>2300</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <f t="shared" si="0"/>
         <v>34273.68</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="4">
+      <c r="J16" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" hidden="1" spans="1:10">
+      <c r="A17" s="19">
         <v>15</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="19">
         <v>600172</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C17" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="19">
         <v>1</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="21">
         <v>46188</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="19">
         <v>12.2123</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="19">
         <v>600</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="19">
         <f t="shared" ref="H17:H48" si="1">F17*G17</f>
         <v>7327.38</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="15" t="s">
+      <c r="I17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="5">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5">
+        <v>600745</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>46189</v>
+      </c>
+      <c r="F18" s="5">
+        <v>18.6687</v>
+      </c>
+      <c r="G18" s="5">
+        <v>800</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="1"/>
+        <v>14934.96</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="5">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="11"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="5">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="5">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="5">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="5">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="11"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="5">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="11"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="5">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="11"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="5">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="5">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="5">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="11"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="5">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="11"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="5">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="11"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="5">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="11"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="5">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="5">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="11"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="5">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="5">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="5">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="5">
+        <v>35</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="5">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="5">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="5">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="5">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="11"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="5">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="5">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="5">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="4">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4">
+      <c r="B44" s="5"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="4">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4">
+      <c r="I44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="5">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="4">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4">
+      <c r="I45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="5">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="4">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4">
+      <c r="I46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="5">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="4">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4">
+      <c r="I47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="5">
+        <v>46</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="15"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="4">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="4">
-        <v>22</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="4">
-        <v>23</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="4">
-        <v>24</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="15"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="4">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="4">
-        <v>26</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="4">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="15"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="4">
-        <v>28</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="4">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="4">
-        <v>30</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="4">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="4">
-        <v>32</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="4">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="15"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="4">
-        <v>34</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="15"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="4">
-        <v>35</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="15"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="4">
-        <v>36</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="15"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="4">
-        <v>37</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="4">
-        <v>38</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="4">
-        <v>39</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="15"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="4">
-        <v>40</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="4">
-        <v>41</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="4">
-        <v>42</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="4">
-        <v>43</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="4">
-        <v>44</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="4">
-        <v>45</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="15"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="4">
-        <v>46</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="I48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J48" s="15"/>
+      <c r="J48" s="11"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="4">
+      <c r="A49" s="5">
         <v>47</v>
       </c>
-      <c r="B49" s="4"/>
+      <c r="B49" s="5"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="4"/>
+      <c r="D49" s="5"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4">
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5">
         <f t="shared" ref="H49:H80" si="2">F49*G49</f>
         <v>0</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J49" s="15"/>
+      <c r="J49" s="11"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="4">
+      <c r="A50" s="5">
         <v>48</v>
       </c>
-      <c r="B50" s="4"/>
+      <c r="B50" s="5"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="4"/>
+      <c r="D50" s="5"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4">
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J50" s="15"/>
+      <c r="J50" s="11"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="4">
+      <c r="A51" s="5">
         <v>49</v>
       </c>
-      <c r="B51" s="4"/>
+      <c r="B51" s="5"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="4"/>
+      <c r="D51" s="5"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4">
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="15"/>
+      <c r="J51" s="11"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="4">
+      <c r="A52" s="5">
         <v>50</v>
       </c>
-      <c r="B52" s="4"/>
+      <c r="B52" s="5"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="4"/>
+      <c r="D52" s="5"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4">
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J52" s="15"/>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="4">
+      <c r="A53" s="5">
         <v>51</v>
       </c>
-      <c r="B53" s="4"/>
+      <c r="B53" s="5"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="4"/>
+      <c r="D53" s="5"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4">
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J53" s="15"/>
+      <c r="J53" s="11"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="4">
+      <c r="A54" s="5">
         <v>52</v>
       </c>
-      <c r="B54" s="4"/>
+      <c r="B54" s="5"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="4"/>
+      <c r="D54" s="5"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4">
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J54" s="15"/>
+      <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="4">
+      <c r="A55" s="5">
         <v>53</v>
       </c>
-      <c r="B55" s="4"/>
+      <c r="B55" s="5"/>
       <c r="C55" s="1"/>
-      <c r="D55" s="4"/>
+      <c r="D55" s="5"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4">
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J55" s="15"/>
+      <c r="J55" s="11"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="4">
+      <c r="A56" s="5">
         <v>54</v>
       </c>
-      <c r="B56" s="4"/>
+      <c r="B56" s="5"/>
       <c r="C56" s="1"/>
-      <c r="D56" s="4"/>
+      <c r="D56" s="5"/>
       <c r="E56" s="2"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4">
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="15"/>
+      <c r="J56" s="11"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="4">
+      <c r="A57" s="5">
         <v>55</v>
       </c>
-      <c r="B57" s="4"/>
+      <c r="B57" s="5"/>
       <c r="C57" s="1"/>
-      <c r="D57" s="4"/>
+      <c r="D57" s="5"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4">
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J57" s="15"/>
+      <c r="J57" s="11"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="4">
+      <c r="A58" s="5">
         <v>56</v>
       </c>
-      <c r="B58" s="4"/>
+      <c r="B58" s="5"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="4"/>
+      <c r="D58" s="5"/>
       <c r="E58" s="2"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4">
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="15"/>
+      <c r="J58" s="11"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="4">
+      <c r="A59" s="5">
         <v>57</v>
       </c>
-      <c r="B59" s="4"/>
+      <c r="B59" s="5"/>
       <c r="C59" s="1"/>
-      <c r="D59" s="4"/>
+      <c r="D59" s="5"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4">
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J59" s="15"/>
+      <c r="J59" s="11"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="4">
+      <c r="A60" s="5">
         <v>58</v>
       </c>
-      <c r="B60" s="4"/>
+      <c r="B60" s="5"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="4"/>
+      <c r="D60" s="5"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4">
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J60" s="15"/>
+      <c r="J60" s="11"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="4">
+      <c r="A61" s="5">
         <v>59</v>
       </c>
-      <c r="B61" s="4"/>
+      <c r="B61" s="5"/>
       <c r="C61" s="1"/>
-      <c r="D61" s="4"/>
+      <c r="D61" s="5"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4">
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J61" s="15"/>
+      <c r="J61" s="11"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="4">
+      <c r="A62" s="5">
         <v>60</v>
       </c>
-      <c r="B62" s="4"/>
+      <c r="B62" s="5"/>
       <c r="C62" s="1"/>
-      <c r="D62" s="4"/>
+      <c r="D62" s="5"/>
       <c r="E62" s="2"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4">
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J62" s="15"/>
+      <c r="J62" s="11"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="4">
+      <c r="A63" s="5">
         <v>61</v>
       </c>
-      <c r="B63" s="4"/>
+      <c r="B63" s="5"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="4"/>
+      <c r="D63" s="5"/>
       <c r="E63" s="2"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4">
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J63" s="15"/>
+      <c r="J63" s="11"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="4">
+      <c r="A64" s="5">
         <v>62</v>
       </c>
-      <c r="B64" s="4"/>
+      <c r="B64" s="5"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="4"/>
+      <c r="D64" s="5"/>
       <c r="E64" s="2"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4">
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J64" s="15"/>
+      <c r="J64" s="11"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="4">
+      <c r="A65" s="5">
         <v>63</v>
       </c>
-      <c r="B65" s="4"/>
+      <c r="B65" s="5"/>
       <c r="C65" s="1"/>
-      <c r="D65" s="4"/>
+      <c r="D65" s="5"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4">
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="15"/>
+      <c r="J65" s="11"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="4">
+      <c r="A66" s="5">
         <v>64</v>
       </c>
-      <c r="B66" s="4"/>
+      <c r="B66" s="5"/>
       <c r="C66" s="1"/>
-      <c r="D66" s="4"/>
+      <c r="D66" s="5"/>
       <c r="E66" s="2"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4">
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J66" s="15"/>
+      <c r="J66" s="11"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="4">
+      <c r="A67" s="5">
         <v>65</v>
       </c>
-      <c r="B67" s="4"/>
+      <c r="B67" s="5"/>
       <c r="C67" s="1"/>
-      <c r="D67" s="4"/>
+      <c r="D67" s="5"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4">
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J67" s="15"/>
+      <c r="J67" s="11"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="4">
+      <c r="A68" s="5">
         <v>66</v>
       </c>
-      <c r="B68" s="4"/>
+      <c r="B68" s="5"/>
       <c r="C68" s="1"/>
-      <c r="D68" s="4"/>
+      <c r="D68" s="5"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4">
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J68" s="15"/>
+      <c r="J68" s="11"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="4">
+      <c r="A69" s="5">
         <v>67</v>
       </c>
-      <c r="B69" s="4"/>
+      <c r="B69" s="5"/>
       <c r="C69" s="1"/>
-      <c r="D69" s="4"/>
+      <c r="D69" s="5"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4">
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J69" s="15"/>
+      <c r="J69" s="11"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="4">
+      <c r="A70" s="5">
         <v>68</v>
       </c>
-      <c r="B70" s="4"/>
+      <c r="B70" s="5"/>
       <c r="C70" s="1"/>
-      <c r="D70" s="4"/>
+      <c r="D70" s="5"/>
       <c r="E70" s="2"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4">
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J70" s="15"/>
+      <c r="J70" s="11"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="4">
+      <c r="A71" s="5">
         <v>69</v>
       </c>
-      <c r="B71" s="4"/>
+      <c r="B71" s="5"/>
       <c r="C71" s="1"/>
-      <c r="D71" s="4"/>
+      <c r="D71" s="5"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4">
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J71" s="15"/>
+      <c r="J71" s="11"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="4">
+      <c r="A72" s="5">
         <v>70</v>
       </c>
-      <c r="B72" s="4"/>
+      <c r="B72" s="5"/>
       <c r="C72" s="1"/>
-      <c r="D72" s="4"/>
+      <c r="D72" s="5"/>
       <c r="E72" s="2"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4">
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J72" s="15"/>
+      <c r="J72" s="11"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="4">
+      <c r="A73" s="5">
         <v>71</v>
       </c>
-      <c r="B73" s="4"/>
+      <c r="B73" s="5"/>
       <c r="C73" s="1"/>
-      <c r="D73" s="4"/>
+      <c r="D73" s="5"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4">
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J73" s="15"/>
+      <c r="J73" s="11"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="4">
+      <c r="A74" s="5">
         <v>72</v>
       </c>
-      <c r="B74" s="4"/>
+      <c r="B74" s="5"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="4"/>
+      <c r="D74" s="5"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4">
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J74" s="15"/>
+      <c r="J74" s="11"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="4">
+      <c r="A75" s="5">
         <v>73</v>
       </c>
-      <c r="B75" s="4"/>
+      <c r="B75" s="5"/>
       <c r="C75" s="1"/>
-      <c r="D75" s="4"/>
+      <c r="D75" s="5"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4">
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J75" s="15"/>
+      <c r="J75" s="11"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="4">
+      <c r="A76" s="5">
         <v>74</v>
       </c>
-      <c r="B76" s="4"/>
+      <c r="B76" s="5"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="4"/>
+      <c r="D76" s="5"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4">
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J76" s="15"/>
+      <c r="J76" s="11"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="4">
+      <c r="A77" s="5">
         <v>75</v>
       </c>
-      <c r="B77" s="4"/>
+      <c r="B77" s="5"/>
       <c r="C77" s="1"/>
-      <c r="D77" s="4"/>
+      <c r="D77" s="5"/>
       <c r="E77" s="2"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4">
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J77" s="15"/>
+      <c r="J77" s="11"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="4">
+      <c r="A78" s="5">
         <v>76</v>
       </c>
-      <c r="B78" s="4"/>
+      <c r="B78" s="5"/>
       <c r="C78" s="1"/>
-      <c r="D78" s="4"/>
+      <c r="D78" s="5"/>
       <c r="E78" s="2"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4">
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J78" s="15"/>
+      <c r="J78" s="11"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="4">
+      <c r="A79" s="5">
         <v>77</v>
       </c>
-      <c r="B79" s="4"/>
+      <c r="B79" s="5"/>
       <c r="C79" s="1"/>
-      <c r="D79" s="4"/>
+      <c r="D79" s="5"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4">
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J79" s="15"/>
+      <c r="J79" s="11"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="4">
+      <c r="A80" s="5">
         <v>78</v>
       </c>
-      <c r="B80" s="4"/>
+      <c r="B80" s="5"/>
       <c r="C80" s="1"/>
-      <c r="D80" s="4"/>
+      <c r="D80" s="5"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4">
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J80" s="15"/>
+      <c r="J80" s="11"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="4">
+      <c r="A81" s="5">
         <v>79</v>
       </c>
-      <c r="B81" s="4"/>
+      <c r="B81" s="5"/>
       <c r="C81" s="1"/>
-      <c r="D81" s="4"/>
+      <c r="D81" s="5"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4">
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5">
         <f t="shared" ref="H81:H101" si="3">F81*G81</f>
         <v>0</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J81" s="15"/>
+      <c r="J81" s="11"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="4">
+      <c r="A82" s="5">
         <v>80</v>
       </c>
-      <c r="B82" s="4"/>
+      <c r="B82" s="5"/>
       <c r="C82" s="1"/>
-      <c r="D82" s="4"/>
+      <c r="D82" s="5"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4">
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J82" s="15"/>
+      <c r="J82" s="11"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="4">
+      <c r="A83" s="5">
         <v>81</v>
       </c>
-      <c r="B83" s="4"/>
+      <c r="B83" s="5"/>
       <c r="C83" s="1"/>
-      <c r="D83" s="4"/>
+      <c r="D83" s="5"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4">
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J83" s="15"/>
+      <c r="J83" s="11"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="4">
+      <c r="A84" s="5">
         <v>82</v>
       </c>
-      <c r="B84" s="4"/>
+      <c r="B84" s="5"/>
       <c r="C84" s="1"/>
-      <c r="D84" s="4"/>
+      <c r="D84" s="5"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4">
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J84" s="15"/>
+      <c r="J84" s="11"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="4">
+      <c r="A85" s="5">
         <v>83</v>
       </c>
-      <c r="B85" s="4"/>
+      <c r="B85" s="5"/>
       <c r="C85" s="1"/>
-      <c r="D85" s="4"/>
+      <c r="D85" s="5"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4">
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J85" s="15"/>
+      <c r="J85" s="11"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="4">
+      <c r="A86" s="5">
         <v>84</v>
       </c>
-      <c r="B86" s="4"/>
+      <c r="B86" s="5"/>
       <c r="C86" s="1"/>
-      <c r="D86" s="4"/>
+      <c r="D86" s="5"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4">
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J86" s="15"/>
+      <c r="J86" s="11"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="4">
+      <c r="A87" s="5">
         <v>85</v>
       </c>
-      <c r="B87" s="4"/>
+      <c r="B87" s="5"/>
       <c r="C87" s="1"/>
-      <c r="D87" s="4"/>
+      <c r="D87" s="5"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4">
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J87" s="15"/>
+      <c r="J87" s="11"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="4">
+      <c r="A88" s="5">
         <v>86</v>
       </c>
-      <c r="B88" s="4"/>
+      <c r="B88" s="5"/>
       <c r="C88" s="1"/>
-      <c r="D88" s="4"/>
+      <c r="D88" s="5"/>
       <c r="E88" s="2"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4">
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J88" s="15"/>
+      <c r="J88" s="11"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="4">
+      <c r="A89" s="5">
         <v>87</v>
       </c>
-      <c r="B89" s="4"/>
+      <c r="B89" s="5"/>
       <c r="C89" s="1"/>
-      <c r="D89" s="4"/>
+      <c r="D89" s="5"/>
       <c r="E89" s="2"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4">
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J89" s="15"/>
+      <c r="J89" s="11"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="4">
+      <c r="A90" s="5">
         <v>88</v>
       </c>
-      <c r="B90" s="4"/>
+      <c r="B90" s="5"/>
       <c r="C90" s="1"/>
-      <c r="D90" s="4"/>
+      <c r="D90" s="5"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4">
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J90" s="15"/>
+      <c r="J90" s="11"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="4">
+      <c r="A91" s="5">
         <v>89</v>
       </c>
-      <c r="B91" s="4"/>
+      <c r="B91" s="5"/>
       <c r="C91" s="1"/>
-      <c r="D91" s="4"/>
+      <c r="D91" s="5"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4">
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J91" s="15"/>
+      <c r="J91" s="11"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="4">
+      <c r="A92" s="5">
         <v>90</v>
       </c>
-      <c r="B92" s="4"/>
+      <c r="B92" s="5"/>
       <c r="C92" s="1"/>
-      <c r="D92" s="4"/>
+      <c r="D92" s="5"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4">
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J92" s="15"/>
+      <c r="J92" s="11"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="4">
+      <c r="A93" s="5">
         <v>91</v>
       </c>
-      <c r="B93" s="4"/>
+      <c r="B93" s="5"/>
       <c r="C93" s="1"/>
-      <c r="D93" s="4"/>
+      <c r="D93" s="5"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4">
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J93" s="15"/>
+      <c r="J93" s="11"/>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="4">
+      <c r="A94" s="5">
         <v>92</v>
       </c>
-      <c r="B94" s="4"/>
+      <c r="B94" s="5"/>
       <c r="C94" s="1"/>
-      <c r="D94" s="4"/>
+      <c r="D94" s="5"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4">
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J94" s="15"/>
+      <c r="J94" s="11"/>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="4">
+      <c r="A95" s="5">
         <v>93</v>
       </c>
-      <c r="B95" s="4"/>
+      <c r="B95" s="5"/>
       <c r="C95" s="1"/>
-      <c r="D95" s="4"/>
+      <c r="D95" s="5"/>
       <c r="E95" s="2"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4">
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J95" s="15"/>
+      <c r="J95" s="11"/>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="4">
+      <c r="A96" s="5">
         <v>94</v>
       </c>
-      <c r="B96" s="4"/>
+      <c r="B96" s="5"/>
       <c r="C96" s="1"/>
-      <c r="D96" s="4"/>
+      <c r="D96" s="5"/>
       <c r="E96" s="2"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4">
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J96" s="15"/>
+      <c r="J96" s="11"/>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="4">
+      <c r="A97" s="5">
         <v>95</v>
       </c>
-      <c r="B97" s="4"/>
+      <c r="B97" s="5"/>
       <c r="C97" s="1"/>
-      <c r="D97" s="4"/>
+      <c r="D97" s="5"/>
       <c r="E97" s="2"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4">
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J97" s="15"/>
+      <c r="J97" s="11"/>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="4">
+      <c r="A98" s="5">
         <v>96</v>
       </c>
-      <c r="B98" s="4"/>
+      <c r="B98" s="5"/>
       <c r="C98" s="1"/>
-      <c r="D98" s="4"/>
+      <c r="D98" s="5"/>
       <c r="E98" s="2"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4">
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J98" s="15"/>
+      <c r="J98" s="11"/>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="4">
+      <c r="A99" s="5">
         <v>97</v>
       </c>
-      <c r="B99" s="4"/>
+      <c r="B99" s="5"/>
       <c r="C99" s="1"/>
-      <c r="D99" s="4"/>
+      <c r="D99" s="5"/>
       <c r="E99" s="2"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4">
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J99" s="15"/>
+      <c r="J99" s="11"/>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="4">
+      <c r="A100" s="5">
         <v>98</v>
       </c>
-      <c r="B100" s="4"/>
+      <c r="B100" s="5"/>
       <c r="C100" s="1"/>
-      <c r="D100" s="4"/>
+      <c r="D100" s="5"/>
       <c r="E100" s="2"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4">
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J100" s="15"/>
+      <c r="J100" s="11"/>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="4">
+      <c r="A101" s="5">
         <v>99</v>
       </c>
-      <c r="B101" s="4"/>
+      <c r="B101" s="5"/>
       <c r="C101" s="1"/>
-      <c r="D101" s="4"/>
+      <c r="D101" s="5"/>
       <c r="E101" s="2"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4">
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J101" s="15"/>
+      <c r="J101" s="11"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I101" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="持有"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <mergeCells count="4">
@@ -3851,7 +3883,7 @@
     <mergeCell ref="J10:J11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2 I17 I3:I16 I18:I101">
       <formula1>$K$1:$K$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3863,72 +3895,78 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.375"/>
     <col min="8" max="8" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>54</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>46188</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2">
         <v>4300</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <v>4.8581</v>
       </c>
       <c r="G2" s="2">
         <v>5.17</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I2" s="2">
         <f>E2*(G2-F2)</f>
@@ -3938,23 +3976,46 @@
         <v>1308.3</v>
       </c>
       <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="B3" s="4">
+        <v>46190</v>
+      </c>
+      <c r="C3" s="2">
+        <v>600172</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2">
+        <v>600</v>
+      </c>
+      <c r="F3" s="6">
+        <v>12.2123</v>
+      </c>
+      <c r="G3" s="2">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="2">
+        <f>E3*(G3-F3)</f>
+        <v>472.619999999999</v>
+      </c>
+      <c r="J3" s="2">
+        <v>460.95</v>
+      </c>
       <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3965,11 +4026,16 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="2">
+        <f t="shared" ref="I4:I9" si="0">E4*(G4-F4)</f>
+        <v>0</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3980,11 +4046,16 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="I5" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3995,11 +4066,16 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -4010,11 +4086,16 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="I7" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -4025,11 +4106,16 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="I8" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4040,27 +4126,34 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="I9" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="8"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
       <c r="J10" s="2">
         <f>SUM(J2:J9)</f>
-        <v>1308.3</v>
+        <v>1769.25</v>
       </c>
       <c r="K10" s="2"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D2" etc:filterBottomFollowUsedRange="0">

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -4,16 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
     <sheet name="清单" sheetId="1" r:id="rId2"/>
     <sheet name="已出售" sheetId="3" r:id="rId3"/>
+    <sheet name="自选股" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已出售!$C$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已出售!$C$1:$D$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="71">
   <si>
     <t>时间</t>
   </si>
@@ -89,9 +90,15 @@
     <t>持有</t>
   </si>
   <si>
+    <t>等待反弹出售</t>
+  </si>
+  <si>
     <t>山西焦化</t>
   </si>
   <si>
+    <t>在7月中旬等待补仓，或者低于3.3后补仓，看情况</t>
+  </si>
+  <si>
     <t>000751</t>
   </si>
   <si>
@@ -104,6 +111,9 @@
     <t>南京证券</t>
   </si>
   <si>
+    <t>长期持有不做变动</t>
+  </si>
+  <si>
     <t>古越龙山</t>
   </si>
   <si>
@@ -116,6 +126,9 @@
     <t>深粮控股</t>
   </si>
   <si>
+    <t>低于6块的时候补仓1000</t>
+  </si>
+  <si>
     <t>中国西电</t>
   </si>
   <si>
@@ -125,6 +138,9 @@
     <t>电魂网络</t>
   </si>
   <si>
+    <t>持有不做变动 等带反弹</t>
+  </si>
+  <si>
     <t>昆药集团</t>
   </si>
   <si>
@@ -134,10 +150,13 @@
     <t>航天电子</t>
   </si>
   <si>
+    <t>暂不做任何的操作，但是如果低于</t>
+  </si>
+  <si>
     <t>中信建投</t>
   </si>
   <si>
-    <t>长期持有，在30左右售出</t>
+    <t>如果低于22或者更低就购入10000块左右的，如果有余额</t>
   </si>
   <si>
     <t>002716</t>
@@ -146,13 +165,13 @@
     <t>湖南白银</t>
   </si>
   <si>
-    <t>也是在8块左右的时候进行补充，每次1000股左右</t>
+    <t>也是在8~8.5之间 如果有余额就补仓1000股左右</t>
   </si>
   <si>
     <t>江龙船艇</t>
   </si>
   <si>
-    <t>在11~12块左右的时候进行做T</t>
+    <t>不做任何的处理 长期持有</t>
   </si>
   <si>
     <t>泰胜风能</t>
@@ -170,6 +189,9 @@
     <t>ST闻泰</t>
   </si>
   <si>
+    <t>等待盈利后就出售，5%这个点吧 不过可能等不到了，那就持有</t>
+  </si>
+  <si>
     <t>出手时间</t>
   </si>
   <si>
@@ -210,6 +232,21 @@
   </si>
   <si>
     <t>总盈亏</t>
+  </si>
+  <si>
+    <t>当前股价</t>
+  </si>
+  <si>
+    <t>预测最低股价</t>
+  </si>
+  <si>
+    <t>3.5~4</t>
+  </si>
+  <si>
+    <t>工商银行</t>
+  </si>
+  <si>
+    <t>中国东航</t>
   </si>
 </sst>
 </file>
@@ -381,18 +418,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.35"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -760,7 +791,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -784,16 +815,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -802,91 +833,103 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -894,16 +937,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -933,7 +967,7 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1495,206 +1529,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="4">
+      <c r="A2" s="7">
         <v>46096</v>
       </c>
-      <c r="B2" s="2">
-        <f t="shared" ref="B2:B7" si="0">SUM(D2+C2)</f>
+      <c r="B2" s="6">
+        <f t="shared" ref="B2:B8" si="0">SUM(D2+C2)</f>
         <v>225842</v>
       </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C2" s="6">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6">
         <v>225842</v>
       </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="E2" s="6">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
         <v>11837</v>
       </c>
-      <c r="G2" s="2">
-        <f t="shared" ref="G2:G7" si="1">SUM(B2+F2-E2)</f>
+      <c r="G2" s="6">
+        <f t="shared" ref="G2:G8" si="1">SUM(B2+F2-E2)</f>
         <v>237679</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4">
+      <c r="A3" s="7">
         <v>46107</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="6">
         <f t="shared" si="0"/>
         <v>236842</v>
       </c>
-      <c r="C3" s="2">
-        <f>B2</f>
+      <c r="C3" s="6">
+        <f t="shared" ref="C3:C8" si="2">B2</f>
         <v>225842</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="6">
         <v>11000</v>
       </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
         <v>11837</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="6">
         <f t="shared" si="1"/>
         <v>248679</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="4">
+      <c r="A4" s="7">
         <v>46101</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="6">
         <f t="shared" si="0"/>
         <v>256842</v>
       </c>
-      <c r="C4" s="2">
-        <f>B3</f>
+      <c r="C4" s="6">
+        <f t="shared" si="2"/>
         <v>236842</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="6">
         <v>20000</v>
       </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
         <v>11837</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="6">
         <f t="shared" si="1"/>
         <v>268679</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="4">
+      <c r="A5" s="7">
         <v>46177</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="6">
         <f t="shared" si="0"/>
         <v>266842</v>
       </c>
-      <c r="C5" s="2">
-        <f>B4</f>
+      <c r="C5" s="6">
+        <f t="shared" si="2"/>
         <v>256842</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="6">
         <v>10000</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
         <v>11837</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="6">
         <f t="shared" si="1"/>
         <v>278679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="4">
+      <c r="A6" s="7">
         <v>46182</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="6">
         <f t="shared" si="0"/>
         <v>276842</v>
       </c>
-      <c r="C6" s="2">
-        <f>B5</f>
+      <c r="C6" s="6">
+        <f t="shared" si="2"/>
         <v>266842</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="6">
         <v>10000</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
         <v>11873</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="6">
         <f t="shared" si="1"/>
         <v>288715</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="4">
+      <c r="A7" s="7">
         <v>46184</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="6">
         <f t="shared" si="0"/>
         <v>281842</v>
       </c>
-      <c r="C7" s="2">
-        <f>B6</f>
+      <c r="C7" s="6">
+        <f t="shared" si="2"/>
         <v>276842</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="6">
         <v>5000</v>
       </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
         <v>11873</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="6">
         <f t="shared" si="1"/>
         <v>293715</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="4">
+      <c r="A8" s="7">
         <v>46190</v>
       </c>
-      <c r="B8" s="2">
-        <f>SUM(D8+C8)</f>
+      <c r="B8" s="6">
+        <f t="shared" si="0"/>
         <v>282342</v>
       </c>
-      <c r="C8" s="2">
-        <f>B7</f>
+      <c r="C8" s="6">
+        <f t="shared" si="2"/>
         <v>281842</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="6">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
         <v>11873</v>
       </c>
-      <c r="G8" s="2">
-        <f>SUM(B8+F8-E8)</f>
+      <c r="G8" s="6">
+        <f t="shared" si="1"/>
         <v>294215</v>
       </c>
     </row>
@@ -1710,2169 +1744,2183 @@
   <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="8"/>
-    <col min="2" max="2" width="9.375" style="8"/>
-    <col min="3" max="3" width="9" style="7"/>
-    <col min="4" max="4" width="9" style="8"/>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="9.375" style="9"/>
+    <col min="3" max="3" width="9" style="8"/>
+    <col min="4" max="4" width="9" style="9"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="8" width="12.875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="9" style="7"/>
-    <col min="10" max="10" width="68.625" style="9" customWidth="1"/>
+    <col min="6" max="8" width="12.875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="9" style="8"/>
+    <col min="10" max="10" width="68.625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="8" customFormat="1" spans="1:11">
+      <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="5">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="1">
         <v>300323</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="13">
         <v>46182</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="1">
         <v>16.6114</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="1">
         <v>1600</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="1">
         <f>F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="7"/>
+      <c r="I2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="5">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="1">
         <v>600740</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <v>46182</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="1">
         <v>4.1541</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="1">
         <v>1800</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="1">
         <f t="shared" ref="H3:H16" si="0">F3*G3</f>
         <v>7477.38</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="11"/>
+      <c r="I3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" hidden="1" spans="1:11">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="B4" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="14">
         <v>1</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="16">
         <v>46182</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="14">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="14">
         <v>4300</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="14">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="16"/>
+      <c r="I4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="1">
         <v>601990</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>46182</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="1">
         <v>9.9227</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="1">
         <v>500</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="1">
         <f t="shared" si="0"/>
         <v>4961.35</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="11"/>
+      <c r="I5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="5">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="1">
         <v>600059</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="C6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <v>46182</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="1">
         <v>10.9008</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="1">
         <v>1000</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="1">
         <f t="shared" si="0"/>
         <v>10900.8</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>24</v>
+      <c r="I6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="5">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="B7" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>46182</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="1">
         <v>9.6507</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="1">
         <v>1000</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="1">
         <f t="shared" si="0"/>
         <v>9650.7</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="11"/>
+      <c r="I7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="5">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="1">
         <v>601179</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <v>46182</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="1">
         <v>20.12</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="1">
         <v>700</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>14084</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>28</v>
+      <c r="I8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="5">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="1">
         <v>603258</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>46182</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="1">
         <v>20.6888</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="1">
         <v>900</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>18619.92</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="11"/>
+      <c r="I9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="5">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="1">
         <v>600422</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>46182</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="1">
         <v>21.0619</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="1">
         <v>600</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>12637.14</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>31</v>
+      <c r="I10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="5">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>46188</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="1">
         <v>8.5</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="1">
         <v>600</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="1">
         <f t="shared" si="0"/>
         <v>5100</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="18"/>
+      <c r="I11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="19"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="5">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="1">
         <v>600879</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <v>46182</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="1">
         <v>26.2661</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="1">
         <v>700</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="1">
         <f t="shared" si="0"/>
         <v>18386.27</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="11"/>
+      <c r="I12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="5">
+      <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="1">
         <v>601066</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <v>46182</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="1">
         <v>27.6302</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="1">
         <v>3400</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>93942.68</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>34</v>
+      <c r="I13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="5">
+      <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="B14" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <v>46182</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="1">
         <v>18.3681</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="1">
         <v>1000</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>18368.1</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>37</v>
+      <c r="I14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="5">
+      <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="1">
         <v>300589</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <v>46182</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="1">
         <v>22.8225</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="1">
         <v>1200</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="1">
         <f t="shared" si="0"/>
         <v>27387</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>39</v>
+      <c r="I15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="5">
+      <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="1">
         <v>300129</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <v>46182</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="1">
         <v>14.9016</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="1">
         <v>2300</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="1">
         <f t="shared" si="0"/>
         <v>34273.68</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>41</v>
+      <c r="I16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" hidden="1" spans="1:10">
-      <c r="A17" s="19">
+      <c r="A17" s="20">
         <v>15</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>600172</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="19">
+      <c r="C17" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="20">
         <v>1</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="22">
         <v>46188</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <v>12.2123</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="20">
         <v>600</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="20">
         <f t="shared" ref="H17:H48" si="1">F17*G17</f>
         <v>7327.38</v>
       </c>
-      <c r="I17" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>43</v>
+      <c r="I17" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="5">
+      <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="1">
         <v>600745</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="7">
         <v>46189</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="1">
         <v>18.6687</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="1">
         <v>800</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="1">
         <f t="shared" si="1"/>
         <v>14934.96</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="11"/>
+      <c r="I18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="5">
-        <v>17</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="11"/>
+      <c r="I19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="5">
+      <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5">
+      <c r="B20" s="1"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="11"/>
+      <c r="I20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="5">
+      <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5">
+      <c r="B21" s="1"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="11"/>
+      <c r="I21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="12"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="5">
+      <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5">
+      <c r="B22" s="1"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="11"/>
+      <c r="I22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="5">
+      <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5">
+      <c r="B23" s="1"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="11"/>
+      <c r="I23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="5">
+      <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5">
+      <c r="B24" s="1"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="11"/>
+      <c r="I24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="5">
+      <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5">
+      <c r="B25" s="1"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="11"/>
+      <c r="I25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="5">
+      <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5">
+      <c r="B26" s="1"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="11"/>
+      <c r="I26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="5">
+      <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5">
+      <c r="B27" s="1"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="11"/>
+      <c r="I27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="5">
+      <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5">
+      <c r="B28" s="1"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="11"/>
+      <c r="I28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="5">
+      <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5">
+      <c r="B29" s="1"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="11"/>
+      <c r="I29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="5">
+      <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5">
+      <c r="B30" s="1"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="11"/>
+      <c r="I30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="5">
+      <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5">
+      <c r="B31" s="1"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="11"/>
+      <c r="I31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="5">
+      <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5">
+      <c r="B32" s="1"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="11"/>
+      <c r="I32" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="5">
+      <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5">
+      <c r="B33" s="1"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="11"/>
+      <c r="I33" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="5">
+      <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5">
+      <c r="B34" s="1"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="11"/>
+      <c r="I34" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="5">
+      <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5">
+      <c r="B35" s="1"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="11"/>
+      <c r="I35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="5">
+      <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5">
+      <c r="B36" s="1"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="11"/>
+      <c r="I36" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="12"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="5">
+      <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5">
+      <c r="B37" s="1"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="11"/>
+      <c r="I37" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="12"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="5">
+      <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5">
+      <c r="B38" s="1"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="11"/>
+      <c r="I38" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="12"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="5">
+      <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5">
+      <c r="B39" s="1"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="11"/>
+      <c r="I39" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="12"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="5">
+      <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5">
+      <c r="B40" s="1"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="11"/>
+      <c r="I40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="5">
+      <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5">
+      <c r="B41" s="1"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="11"/>
+      <c r="I41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="12"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="5">
+      <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5">
+      <c r="B42" s="1"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="11"/>
+      <c r="I42" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="12"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="5">
+      <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5">
+      <c r="B43" s="1"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="11"/>
+      <c r="I43" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="12"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="5">
+      <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5">
+      <c r="B44" s="1"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="11"/>
+      <c r="I44" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="12"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="5">
+      <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5">
+      <c r="B45" s="1"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="11"/>
+      <c r="I45" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="12"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="5">
+      <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5">
+      <c r="B46" s="1"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="11"/>
+      <c r="I46" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="12"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="5">
+      <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5">
+      <c r="B47" s="1"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="11"/>
+      <c r="I47" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="12"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="5">
+      <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5">
+      <c r="B48" s="1"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="11"/>
+      <c r="I48" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="12"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="5">
+      <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5">
+      <c r="B49" s="1"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1">
         <f t="shared" ref="H49:H80" si="2">F49*G49</f>
         <v>0</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="11"/>
+      <c r="I49" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="5">
+      <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5">
+      <c r="B50" s="1"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="11"/>
+      <c r="I50" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="12"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="5">
+      <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5">
+      <c r="B51" s="1"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="11"/>
+      <c r="I51" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="12"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="5">
+      <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5">
+      <c r="B52" s="1"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="11"/>
+      <c r="I52" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="12"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="5">
+      <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5">
+      <c r="B53" s="1"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="11"/>
+      <c r="I53" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="12"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="5">
+      <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5">
+      <c r="B54" s="1"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="11"/>
+      <c r="I54" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="12"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="5">
+      <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5">
+      <c r="B55" s="1"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="11"/>
+      <c r="I55" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="12"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="5">
+      <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5">
+      <c r="B56" s="1"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="11"/>
+      <c r="I56" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="12"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="5">
+      <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5">
+      <c r="B57" s="1"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="11"/>
+      <c r="I57" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="12"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="5">
+      <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5">
+      <c r="B58" s="1"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="11"/>
+      <c r="I58" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="12"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="5">
+      <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5">
+      <c r="B59" s="1"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="11"/>
+      <c r="I59" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="12"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="5">
+      <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5">
+      <c r="B60" s="1"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="11"/>
+      <c r="I60" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="12"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="5">
+      <c r="A61" s="1">
         <v>59</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5">
+      <c r="B61" s="1"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="11"/>
+      <c r="I61" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="12"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="5">
+      <c r="A62" s="1">
         <v>60</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5">
+      <c r="B62" s="1"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="11"/>
+      <c r="I62" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="12"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="5">
+      <c r="A63" s="1">
         <v>61</v>
       </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5">
+      <c r="B63" s="1"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="11"/>
+      <c r="I63" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="12"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="5">
+      <c r="A64" s="1">
         <v>62</v>
       </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5">
+      <c r="B64" s="1"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="11"/>
+      <c r="I64" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="12"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="5">
+      <c r="A65" s="1">
         <v>63</v>
       </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5">
+      <c r="B65" s="1"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="11"/>
+      <c r="I65" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="12"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="5">
+      <c r="A66" s="1">
         <v>64</v>
       </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5">
+      <c r="B66" s="1"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="11"/>
+      <c r="I66" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="12"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="5">
+      <c r="A67" s="1">
         <v>65</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5">
+      <c r="B67" s="1"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="11"/>
+      <c r="I67" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="12"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="5">
+      <c r="A68" s="1">
         <v>66</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5">
+      <c r="B68" s="1"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="11"/>
+      <c r="I68" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="12"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="5">
+      <c r="A69" s="1">
         <v>67</v>
       </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5">
+      <c r="B69" s="1"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="11"/>
+      <c r="I69" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="12"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="5">
+      <c r="A70" s="1">
         <v>68</v>
       </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5">
+      <c r="B70" s="1"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="11"/>
+      <c r="I70" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="12"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="5">
+      <c r="A71" s="1">
         <v>69</v>
       </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5">
+      <c r="B71" s="1"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="11"/>
+      <c r="I71" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="12"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="5">
+      <c r="A72" s="1">
         <v>70</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5">
+      <c r="B72" s="1"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="11"/>
+      <c r="I72" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="12"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="5">
+      <c r="A73" s="1">
         <v>71</v>
       </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5">
+      <c r="B73" s="1"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="11"/>
+      <c r="I73" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="12"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="5">
+      <c r="A74" s="1">
         <v>72</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5">
+      <c r="B74" s="1"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="11"/>
+      <c r="I74" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="12"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="5">
+      <c r="A75" s="1">
         <v>73</v>
       </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5">
+      <c r="B75" s="1"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="11"/>
+      <c r="I75" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="12"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="5">
+      <c r="A76" s="1">
         <v>74</v>
       </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5">
+      <c r="B76" s="1"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="11"/>
+      <c r="I76" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="12"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="5">
+      <c r="A77" s="1">
         <v>75</v>
       </c>
-      <c r="B77" s="5"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5">
+      <c r="B77" s="1"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="11"/>
+      <c r="I77" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="12"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="5">
+      <c r="A78" s="1">
         <v>76</v>
       </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5">
+      <c r="B78" s="1"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="11"/>
+      <c r="I78" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="12"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="5">
+      <c r="A79" s="1">
         <v>77</v>
       </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5">
+      <c r="B79" s="1"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="11"/>
+      <c r="I79" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="12"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="5">
+      <c r="A80" s="1">
         <v>78</v>
       </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5">
+      <c r="B80" s="1"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I80" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="11"/>
+      <c r="I80" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="12"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="5">
+      <c r="A81" s="1">
         <v>79</v>
       </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5">
+      <c r="B81" s="1"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1">
         <f t="shared" ref="H81:H101" si="3">F81*G81</f>
         <v>0</v>
       </c>
-      <c r="I81" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="11"/>
+      <c r="I81" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="12"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="5">
+      <c r="A82" s="1">
         <v>80</v>
       </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
-      <c r="H82" s="5">
+      <c r="B82" s="1"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I82" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="11"/>
+      <c r="I82" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="12"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="5">
+      <c r="A83" s="1">
         <v>81</v>
       </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
-      <c r="H83" s="5">
+      <c r="B83" s="1"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I83" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="11"/>
+      <c r="I83" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="12"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="5">
+      <c r="A84" s="1">
         <v>82</v>
       </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5">
+      <c r="B84" s="1"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="11"/>
+      <c r="I84" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="12"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="5">
+      <c r="A85" s="1">
         <v>83</v>
       </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
-      <c r="H85" s="5">
+      <c r="B85" s="1"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I85" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="11"/>
+      <c r="I85" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="12"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="5">
+      <c r="A86" s="1">
         <v>84</v>
       </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
-      <c r="H86" s="5">
+      <c r="B86" s="1"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I86" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="11"/>
+      <c r="I86" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="12"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="5">
+      <c r="A87" s="1">
         <v>85</v>
       </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
-      <c r="H87" s="5">
+      <c r="B87" s="1"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="11"/>
+      <c r="I87" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="12"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="5">
+      <c r="A88" s="1">
         <v>86</v>
       </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
-      <c r="H88" s="5">
+      <c r="B88" s="1"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I88" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="11"/>
+      <c r="I88" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="12"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="5">
+      <c r="A89" s="1">
         <v>87</v>
       </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
-      <c r="H89" s="5">
+      <c r="B89" s="1"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I89" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="11"/>
+      <c r="I89" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="12"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="5">
+      <c r="A90" s="1">
         <v>88</v>
       </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5">
+      <c r="B90" s="1"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I90" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="11"/>
+      <c r="I90" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="12"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="5">
+      <c r="A91" s="1">
         <v>89</v>
       </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-      <c r="H91" s="5">
+      <c r="B91" s="1"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="11"/>
+      <c r="I91" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="12"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="5">
+      <c r="A92" s="1">
         <v>90</v>
       </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5">
+      <c r="B92" s="1"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I92" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="11"/>
+      <c r="I92" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="12"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="5">
+      <c r="A93" s="1">
         <v>91</v>
       </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5">
+      <c r="B93" s="1"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I93" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="11"/>
+      <c r="I93" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="12"/>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="5">
+      <c r="A94" s="1">
         <v>92</v>
       </c>
-      <c r="B94" s="5"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5">
+      <c r="B94" s="1"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="11"/>
+      <c r="I94" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="12"/>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="5">
+      <c r="A95" s="1">
         <v>93</v>
       </c>
-      <c r="B95" s="5"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5">
+      <c r="B95" s="1"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I95" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="11"/>
+      <c r="I95" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="12"/>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="5">
+      <c r="A96" s="1">
         <v>94</v>
       </c>
-      <c r="B96" s="5"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5">
+      <c r="B96" s="1"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I96" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="11"/>
+      <c r="I96" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="12"/>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="5">
+      <c r="A97" s="1">
         <v>95</v>
       </c>
-      <c r="B97" s="5"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5">
+      <c r="B97" s="1"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I97" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="11"/>
+      <c r="I97" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="12"/>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="5">
+      <c r="A98" s="1">
         <v>96</v>
       </c>
-      <c r="B98" s="5"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5">
+      <c r="B98" s="1"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="11"/>
+      <c r="I98" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="12"/>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="5">
+      <c r="A99" s="1">
         <v>97</v>
       </c>
-      <c r="B99" s="5"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5">
+      <c r="B99" s="1"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I99" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="11"/>
+      <c r="I99" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="12"/>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="5">
+      <c r="A100" s="1">
         <v>98</v>
       </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5">
+      <c r="B100" s="1"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I100" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="11"/>
+      <c r="I100" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="12"/>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="5">
+      <c r="A101" s="1">
         <v>99</v>
       </c>
-      <c r="B101" s="5"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5">
+      <c r="B101" s="1"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="11"/>
+      <c r="I101" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="12"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I101" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="7">
-      <filters>
-        <filter val="持有"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="持有"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>
@@ -3883,7 +3931,7 @@
     <mergeCell ref="J10:J11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2 I17 I3:I16 I18:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I101">
       <formula1>$K$1:$K$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3903,260 +3951,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>56</v>
       </c>
+      <c r="G1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="1">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="7">
         <v>46188</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="C2" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="6">
         <v>4300</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="2">
         <v>4.8581</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="6">
         <v>5.17</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="H2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="6">
         <f>E2*(G2-F2)</f>
         <v>1341.17</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="6">
         <v>1308.3</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="1">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="7">
         <v>46190</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="6">
         <v>600172</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="6">
         <v>600</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="2">
         <v>12.2123</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="6">
         <v>13</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="H3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="6">
         <f>E3*(G3-F3)</f>
         <v>472.619999999999</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="6">
         <v>460.95</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="1">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6">
         <f t="shared" ref="I4:I9" si="0">E4*(G4-F4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="1">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="1">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="1">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="1">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="1">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="2">
+      <c r="A10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="6">
         <f>SUM(J2:J9)</f>
         <v>1769.25</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D2" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D3" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
@@ -4165,4 +4213,137 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>601398</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="3">
+        <v>7.16</v>
+      </c>
+      <c r="E3">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>600115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4">
+        <v>3.93</v>
+      </c>
+      <c r="E4">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
@@ -915,7 +915,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -928,9 +928,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -942,9 +939,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1529,205 +1523,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>46096</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <f t="shared" ref="B2:B8" si="0">SUM(D2+C2)</f>
         <v>225842</v>
       </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
         <v>225842</v>
       </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
         <v>11837</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <f t="shared" ref="G2:G8" si="1">SUM(B2+F2-E2)</f>
         <v>237679</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>46107</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <f t="shared" si="0"/>
         <v>236842</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <f t="shared" ref="C3:C8" si="2">B2</f>
         <v>225842</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>11000</v>
       </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
         <v>11837</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <f t="shared" si="1"/>
         <v>248679</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>46101</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>256842</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <f t="shared" si="2"/>
         <v>236842</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>20000</v>
       </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
         <v>11837</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <f t="shared" si="1"/>
         <v>268679</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>46177</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>266842</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <f t="shared" si="2"/>
         <v>256842</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>10000</v>
       </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
         <v>11837</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f t="shared" si="1"/>
         <v>278679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>46182</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>276842</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <f t="shared" si="2"/>
         <v>266842</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>10000</v>
       </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
         <v>11873</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <f t="shared" si="1"/>
         <v>288715</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>46184</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f t="shared" si="0"/>
         <v>281842</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <f t="shared" si="2"/>
         <v>276842</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>5000</v>
       </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
         <v>11873</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <f t="shared" si="1"/>
         <v>293715</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>46190</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>282342</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f t="shared" si="2"/>
         <v>281842</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>500</v>
       </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
         <v>11873</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <f t="shared" si="1"/>
         <v>294215</v>
       </c>
@@ -1744,45 +1738,45 @@
   <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="9"/>
-    <col min="2" max="2" width="9.375" style="9"/>
-    <col min="3" max="3" width="9" style="8"/>
-    <col min="4" max="4" width="9" style="9"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="9.375" style="3"/>
+    <col min="3" max="3" width="9" style="7"/>
+    <col min="4" max="4" width="9" style="3"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="8" width="12.875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="9" style="8"/>
-    <col min="10" max="10" width="68.625" style="10" customWidth="1"/>
+    <col min="6" max="8" width="12.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9" style="7"/>
+    <col min="10" max="10" width="68.625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="7" customFormat="1" spans="1:11">
+      <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1793,13 +1787,13 @@
       <c r="B2" s="1">
         <v>300323</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="11">
         <v>46182</v>
       </c>
       <c r="F2" s="1">
@@ -1812,13 +1806,13 @@
         <f>F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="12" t="s">
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="8"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
@@ -1827,13 +1821,13 @@
       <c r="B3" s="1">
         <v>600740</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="11">
         <v>46182</v>
       </c>
       <c r="F3" s="1">
@@ -1846,43 +1840,43 @@
         <f t="shared" ref="H3:H16" si="0">F3*G3</f>
         <v>7477.38</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="12" t="s">
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="1" spans="1:11">
-      <c r="A4" s="14">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="14">
         <v>46182</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="12">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="12">
         <v>4300</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="12">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="17"/>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
@@ -1891,13 +1885,13 @@
       <c r="B5" s="1">
         <v>601990</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="11">
         <v>46182</v>
       </c>
       <c r="F5" s="1">
@@ -1910,10 +1904,10 @@
         <f t="shared" si="0"/>
         <v>4961.35</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="12" t="s">
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1924,13 +1918,13 @@
       <c r="B6" s="1">
         <v>600059</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <v>46182</v>
       </c>
       <c r="F6" s="1">
@@ -1943,10 +1937,10 @@
         <f t="shared" si="0"/>
         <v>10900.8</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="12" t="s">
+      <c r="I6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1954,16 +1948,16 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11">
         <v>46182</v>
       </c>
       <c r="F7" s="1">
@@ -1976,10 +1970,10 @@
         <f t="shared" si="0"/>
         <v>9650.7</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="12" t="s">
+      <c r="I7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1990,13 +1984,13 @@
       <c r="B8" s="1">
         <v>601179</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <v>46182</v>
       </c>
       <c r="F8" s="1">
@@ -2009,10 +2003,10 @@
         <f t="shared" si="0"/>
         <v>14084</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="12" t="s">
+      <c r="I8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2023,13 +2017,13 @@
       <c r="B9" s="1">
         <v>603258</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11">
         <v>46182</v>
       </c>
       <c r="F9" s="1">
@@ -2042,10 +2036,10 @@
         <f t="shared" si="0"/>
         <v>18619.92</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="12" t="s">
+      <c r="I9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2056,13 +2050,13 @@
       <c r="B10" s="1">
         <v>600422</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <v>46182</v>
       </c>
       <c r="F10" s="1">
@@ -2075,21 +2069,21 @@
         <f t="shared" si="0"/>
         <v>12637.14</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="18" t="s">
+      <c r="I10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="16" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="5"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="11">
         <v>46188</v>
       </c>
       <c r="F11" s="1">
@@ -2102,10 +2096,10 @@
         <f t="shared" si="0"/>
         <v>5100</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="19"/>
+      <c r="I11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
@@ -2114,13 +2108,13 @@
       <c r="B12" s="1">
         <v>600879</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="11">
         <v>46182</v>
       </c>
       <c r="F12" s="1">
@@ -2133,10 +2127,10 @@
         <f t="shared" si="0"/>
         <v>18386.27</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="12" t="s">
+      <c r="I12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="10" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2147,13 +2141,13 @@
       <c r="B13" s="1">
         <v>601066</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="11">
         <v>46182</v>
       </c>
       <c r="F13" s="1">
@@ -2166,10 +2160,10 @@
         <f t="shared" si="0"/>
         <v>93942.68</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="12" t="s">
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="10" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2177,16 +2171,16 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="11">
         <v>46182</v>
       </c>
       <c r="F14" s="1">
@@ -2199,10 +2193,10 @@
         <f t="shared" si="0"/>
         <v>18368.1</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="12" t="s">
+      <c r="I14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="10" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2213,13 +2207,13 @@
       <c r="B15" s="1">
         <v>300589</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="11">
         <v>46182</v>
       </c>
       <c r="F15" s="1">
@@ -2232,10 +2226,10 @@
         <f t="shared" si="0"/>
         <v>27387</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="12" t="s">
+      <c r="I15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="10" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2246,13 +2240,13 @@
       <c r="B16" s="1">
         <v>300129</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="11">
         <v>46182</v>
       </c>
       <c r="F16" s="1">
@@ -2265,43 +2259,43 @@
         <f t="shared" si="0"/>
         <v>34273.68</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="12" t="s">
+      <c r="I16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" hidden="1" spans="1:10">
-      <c r="A17" s="20">
+      <c r="A17" s="18">
         <v>15</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="18">
         <v>600172</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="18">
         <v>1</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="20">
         <v>46188</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="18">
         <v>12.2123</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="18">
         <v>600</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="18">
         <f t="shared" ref="H17:H48" si="1">F17*G17</f>
         <v>7327.38</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="23" t="s">
+      <c r="J17" s="21" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2312,13 +2306,13 @@
       <c r="B18" s="1">
         <v>600745</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>46189</v>
       </c>
       <c r="F18" s="1">
@@ -2331,10 +2325,10 @@
         <f t="shared" si="1"/>
         <v>14934.96</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="12" t="s">
+      <c r="I18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2343,1577 +2337,1577 @@
         <v>17</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" s="5"/>
+      <c r="C19" s="4"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="6"/>
+      <c r="E19" s="5"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="12"/>
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1"/>
-      <c r="C20" s="5"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="6"/>
+      <c r="E20" s="5"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="12"/>
+      <c r="I20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="10"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1"/>
-      <c r="C21" s="5"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="6"/>
+      <c r="E21" s="5"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="12"/>
+      <c r="I21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1"/>
-      <c r="C22" s="5"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="6"/>
+      <c r="E22" s="5"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="12"/>
+      <c r="I22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="5"/>
+      <c r="C23" s="4"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="6"/>
+      <c r="E23" s="5"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="12"/>
+      <c r="I23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1"/>
-      <c r="C24" s="5"/>
+      <c r="C24" s="4"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="6"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="12"/>
+      <c r="I24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="10"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1"/>
-      <c r="C25" s="5"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="6"/>
+      <c r="E25" s="5"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="12"/>
+      <c r="I25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1"/>
-      <c r="C26" s="5"/>
+      <c r="C26" s="4"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="6"/>
+      <c r="E26" s="5"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="12"/>
+      <c r="I26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1"/>
-      <c r="C27" s="5"/>
+      <c r="C27" s="4"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="6"/>
+      <c r="E27" s="5"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="12"/>
+      <c r="I27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="5"/>
+      <c r="C28" s="4"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="6"/>
+      <c r="E28" s="5"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="12"/>
+      <c r="I28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="10"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="1"/>
-      <c r="C29" s="5"/>
+      <c r="C29" s="4"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="6"/>
+      <c r="E29" s="5"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="12"/>
+      <c r="I29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1"/>
-      <c r="C30" s="5"/>
+      <c r="C30" s="4"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="6"/>
+      <c r="E30" s="5"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="12"/>
+      <c r="I30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="10"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1"/>
-      <c r="C31" s="5"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="6"/>
+      <c r="E31" s="5"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="12"/>
+      <c r="I31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1"/>
-      <c r="C32" s="5"/>
+      <c r="C32" s="4"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="6"/>
+      <c r="E32" s="5"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="12"/>
+      <c r="I32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="10"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="B33" s="1"/>
-      <c r="C33" s="5"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="6"/>
+      <c r="E33" s="5"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="12"/>
+      <c r="I33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="10"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34" s="1"/>
-      <c r="C34" s="5"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="6"/>
+      <c r="E34" s="5"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="12"/>
+      <c r="I34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="10"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35" s="1"/>
-      <c r="C35" s="5"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="6"/>
+      <c r="E35" s="5"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="12"/>
+      <c r="I35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36" s="1"/>
-      <c r="C36" s="5"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="6"/>
+      <c r="E36" s="5"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="12"/>
+      <c r="I36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="10"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37" s="1"/>
-      <c r="C37" s="5"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="6"/>
+      <c r="E37" s="5"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="12"/>
+      <c r="I37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="5"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="6"/>
+      <c r="E38" s="5"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="12"/>
+      <c r="I38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="10"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="B39" s="1"/>
-      <c r="C39" s="5"/>
+      <c r="C39" s="4"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="6"/>
+      <c r="E39" s="5"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="12"/>
+      <c r="I39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="10"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="B40" s="1"/>
-      <c r="C40" s="5"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="6"/>
+      <c r="E40" s="5"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="12"/>
+      <c r="I40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="10"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="5"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="6"/>
+      <c r="E41" s="5"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="12"/>
+      <c r="I41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="10"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="5"/>
+      <c r="C42" s="4"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="6"/>
+      <c r="E42" s="5"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="12"/>
+      <c r="I42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="10"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="5"/>
+      <c r="C43" s="4"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="6"/>
+      <c r="E43" s="5"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="12"/>
+      <c r="I43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="10"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
         <v>42</v>
       </c>
       <c r="B44" s="1"/>
-      <c r="C44" s="5"/>
+      <c r="C44" s="4"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="6"/>
+      <c r="E44" s="5"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="12"/>
+      <c r="I44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="10"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1">
         <v>43</v>
       </c>
       <c r="B45" s="1"/>
-      <c r="C45" s="5"/>
+      <c r="C45" s="4"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="6"/>
+      <c r="E45" s="5"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="12"/>
+      <c r="I45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="10"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1">
         <v>44</v>
       </c>
       <c r="B46" s="1"/>
-      <c r="C46" s="5"/>
+      <c r="C46" s="4"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="6"/>
+      <c r="E46" s="5"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I46" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="12"/>
+      <c r="I46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="10"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1">
         <v>45</v>
       </c>
       <c r="B47" s="1"/>
-      <c r="C47" s="5"/>
+      <c r="C47" s="4"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="6"/>
+      <c r="E47" s="5"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="12"/>
+      <c r="I47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="10"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1">
         <v>46</v>
       </c>
       <c r="B48" s="1"/>
-      <c r="C48" s="5"/>
+      <c r="C48" s="4"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="6"/>
+      <c r="E48" s="5"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="12"/>
+      <c r="I48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="10"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1">
         <v>47</v>
       </c>
       <c r="B49" s="1"/>
-      <c r="C49" s="5"/>
+      <c r="C49" s="4"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="6"/>
+      <c r="E49" s="5"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1">
         <f t="shared" ref="H49:H80" si="2">F49*G49</f>
         <v>0</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="12"/>
+      <c r="I49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="10"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1">
         <v>48</v>
       </c>
       <c r="B50" s="1"/>
-      <c r="C50" s="5"/>
+      <c r="C50" s="4"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="6"/>
+      <c r="E50" s="5"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="12"/>
+      <c r="I50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="10"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1">
         <v>49</v>
       </c>
       <c r="B51" s="1"/>
-      <c r="C51" s="5"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="6"/>
+      <c r="E51" s="5"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="12"/>
+      <c r="I51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="10"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1">
         <v>50</v>
       </c>
       <c r="B52" s="1"/>
-      <c r="C52" s="5"/>
+      <c r="C52" s="4"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="6"/>
+      <c r="E52" s="5"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="12"/>
+      <c r="I52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="10"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="1">
         <v>51</v>
       </c>
       <c r="B53" s="1"/>
-      <c r="C53" s="5"/>
+      <c r="C53" s="4"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="6"/>
+      <c r="E53" s="5"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="12"/>
+      <c r="I53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="10"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1">
         <v>52</v>
       </c>
       <c r="B54" s="1"/>
-      <c r="C54" s="5"/>
+      <c r="C54" s="4"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="6"/>
+      <c r="E54" s="5"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I54" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="12"/>
+      <c r="I54" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="10"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="1">
         <v>53</v>
       </c>
       <c r="B55" s="1"/>
-      <c r="C55" s="5"/>
+      <c r="C55" s="4"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="6"/>
+      <c r="E55" s="5"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I55" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="12"/>
+      <c r="I55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="10"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="1">
         <v>54</v>
       </c>
       <c r="B56" s="1"/>
-      <c r="C56" s="5"/>
+      <c r="C56" s="4"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="6"/>
+      <c r="E56" s="5"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I56" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="12"/>
+      <c r="I56" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="10"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1">
         <v>55</v>
       </c>
       <c r="B57" s="1"/>
-      <c r="C57" s="5"/>
+      <c r="C57" s="4"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="6"/>
+      <c r="E57" s="5"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I57" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="12"/>
+      <c r="I57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="10"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1">
         <v>56</v>
       </c>
       <c r="B58" s="1"/>
-      <c r="C58" s="5"/>
+      <c r="C58" s="4"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="6"/>
+      <c r="E58" s="5"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I58" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="12"/>
+      <c r="I58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="10"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="1">
         <v>57</v>
       </c>
       <c r="B59" s="1"/>
-      <c r="C59" s="5"/>
+      <c r="C59" s="4"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="6"/>
+      <c r="E59" s="5"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I59" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="12"/>
+      <c r="I59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="10"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="1">
         <v>58</v>
       </c>
       <c r="B60" s="1"/>
-      <c r="C60" s="5"/>
+      <c r="C60" s="4"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="6"/>
+      <c r="E60" s="5"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I60" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="12"/>
+      <c r="I60" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="10"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="1">
         <v>59</v>
       </c>
       <c r="B61" s="1"/>
-      <c r="C61" s="5"/>
+      <c r="C61" s="4"/>
       <c r="D61" s="1"/>
-      <c r="E61" s="6"/>
+      <c r="E61" s="5"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I61" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="12"/>
+      <c r="I61" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="10"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="1">
         <v>60</v>
       </c>
       <c r="B62" s="1"/>
-      <c r="C62" s="5"/>
+      <c r="C62" s="4"/>
       <c r="D62" s="1"/>
-      <c r="E62" s="6"/>
+      <c r="E62" s="5"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="12"/>
+      <c r="I62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="10"/>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="1">
         <v>61</v>
       </c>
       <c r="B63" s="1"/>
-      <c r="C63" s="5"/>
+      <c r="C63" s="4"/>
       <c r="D63" s="1"/>
-      <c r="E63" s="6"/>
+      <c r="E63" s="5"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I63" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="12"/>
+      <c r="I63" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="10"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="1">
         <v>62</v>
       </c>
       <c r="B64" s="1"/>
-      <c r="C64" s="5"/>
+      <c r="C64" s="4"/>
       <c r="D64" s="1"/>
-      <c r="E64" s="6"/>
+      <c r="E64" s="5"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="12"/>
+      <c r="I64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="10"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="1">
         <v>63</v>
       </c>
       <c r="B65" s="1"/>
-      <c r="C65" s="5"/>
+      <c r="C65" s="4"/>
       <c r="D65" s="1"/>
-      <c r="E65" s="6"/>
+      <c r="E65" s="5"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I65" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="12"/>
+      <c r="I65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="10"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="1">
         <v>64</v>
       </c>
       <c r="B66" s="1"/>
-      <c r="C66" s="5"/>
+      <c r="C66" s="4"/>
       <c r="D66" s="1"/>
-      <c r="E66" s="6"/>
+      <c r="E66" s="5"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I66" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="12"/>
+      <c r="I66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="10"/>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="1">
         <v>65</v>
       </c>
       <c r="B67" s="1"/>
-      <c r="C67" s="5"/>
+      <c r="C67" s="4"/>
       <c r="D67" s="1"/>
-      <c r="E67" s="6"/>
+      <c r="E67" s="5"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I67" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="12"/>
+      <c r="I67" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="10"/>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="1">
         <v>66</v>
       </c>
       <c r="B68" s="1"/>
-      <c r="C68" s="5"/>
+      <c r="C68" s="4"/>
       <c r="D68" s="1"/>
-      <c r="E68" s="6"/>
+      <c r="E68" s="5"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I68" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="12"/>
+      <c r="I68" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="10"/>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="1">
         <v>67</v>
       </c>
       <c r="B69" s="1"/>
-      <c r="C69" s="5"/>
+      <c r="C69" s="4"/>
       <c r="D69" s="1"/>
-      <c r="E69" s="6"/>
+      <c r="E69" s="5"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I69" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="12"/>
+      <c r="I69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="10"/>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="1">
         <v>68</v>
       </c>
       <c r="B70" s="1"/>
-      <c r="C70" s="5"/>
+      <c r="C70" s="4"/>
       <c r="D70" s="1"/>
-      <c r="E70" s="6"/>
+      <c r="E70" s="5"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I70" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="12"/>
+      <c r="I70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="10"/>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="1">
         <v>69</v>
       </c>
       <c r="B71" s="1"/>
-      <c r="C71" s="5"/>
+      <c r="C71" s="4"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="6"/>
+      <c r="E71" s="5"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I71" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="12"/>
+      <c r="I71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="10"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="1">
         <v>70</v>
       </c>
       <c r="B72" s="1"/>
-      <c r="C72" s="5"/>
+      <c r="C72" s="4"/>
       <c r="D72" s="1"/>
-      <c r="E72" s="6"/>
+      <c r="E72" s="5"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I72" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="12"/>
+      <c r="I72" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="10"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="1">
         <v>71</v>
       </c>
       <c r="B73" s="1"/>
-      <c r="C73" s="5"/>
+      <c r="C73" s="4"/>
       <c r="D73" s="1"/>
-      <c r="E73" s="6"/>
+      <c r="E73" s="5"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I73" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="12"/>
+      <c r="I73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="10"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="1">
         <v>72</v>
       </c>
       <c r="B74" s="1"/>
-      <c r="C74" s="5"/>
+      <c r="C74" s="4"/>
       <c r="D74" s="1"/>
-      <c r="E74" s="6"/>
+      <c r="E74" s="5"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I74" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="12"/>
+      <c r="I74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="10"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="1">
         <v>73</v>
       </c>
       <c r="B75" s="1"/>
-      <c r="C75" s="5"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="1"/>
-      <c r="E75" s="6"/>
+      <c r="E75" s="5"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I75" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="12"/>
+      <c r="I75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="10"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="1">
         <v>74</v>
       </c>
       <c r="B76" s="1"/>
-      <c r="C76" s="5"/>
+      <c r="C76" s="4"/>
       <c r="D76" s="1"/>
-      <c r="E76" s="6"/>
+      <c r="E76" s="5"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I76" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="12"/>
+      <c r="I76" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="10"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="1">
         <v>75</v>
       </c>
       <c r="B77" s="1"/>
-      <c r="C77" s="5"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1"/>
-      <c r="E77" s="6"/>
+      <c r="E77" s="5"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I77" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="12"/>
+      <c r="I77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="10"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="1">
         <v>76</v>
       </c>
       <c r="B78" s="1"/>
-      <c r="C78" s="5"/>
+      <c r="C78" s="4"/>
       <c r="D78" s="1"/>
-      <c r="E78" s="6"/>
+      <c r="E78" s="5"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I78" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="12"/>
+      <c r="I78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="10"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="1">
         <v>77</v>
       </c>
       <c r="B79" s="1"/>
-      <c r="C79" s="5"/>
+      <c r="C79" s="4"/>
       <c r="D79" s="1"/>
-      <c r="E79" s="6"/>
+      <c r="E79" s="5"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I79" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="12"/>
+      <c r="I79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="10"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="1">
         <v>78</v>
       </c>
       <c r="B80" s="1"/>
-      <c r="C80" s="5"/>
+      <c r="C80" s="4"/>
       <c r="D80" s="1"/>
-      <c r="E80" s="6"/>
+      <c r="E80" s="5"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I80" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="12"/>
+      <c r="I80" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="10"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="1">
         <v>79</v>
       </c>
       <c r="B81" s="1"/>
-      <c r="C81" s="5"/>
+      <c r="C81" s="4"/>
       <c r="D81" s="1"/>
-      <c r="E81" s="6"/>
+      <c r="E81" s="5"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1">
         <f t="shared" ref="H81:H101" si="3">F81*G81</f>
         <v>0</v>
       </c>
-      <c r="I81" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="12"/>
+      <c r="I81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="10"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="1">
         <v>80</v>
       </c>
       <c r="B82" s="1"/>
-      <c r="C82" s="5"/>
+      <c r="C82" s="4"/>
       <c r="D82" s="1"/>
-      <c r="E82" s="6"/>
+      <c r="E82" s="5"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I82" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="12"/>
+      <c r="I82" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="10"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="1">
         <v>81</v>
       </c>
       <c r="B83" s="1"/>
-      <c r="C83" s="5"/>
+      <c r="C83" s="4"/>
       <c r="D83" s="1"/>
-      <c r="E83" s="6"/>
+      <c r="E83" s="5"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I83" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="12"/>
+      <c r="I83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="10"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="1">
         <v>82</v>
       </c>
       <c r="B84" s="1"/>
-      <c r="C84" s="5"/>
+      <c r="C84" s="4"/>
       <c r="D84" s="1"/>
-      <c r="E84" s="6"/>
+      <c r="E84" s="5"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I84" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="12"/>
+      <c r="I84" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="10"/>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="1">
         <v>83</v>
       </c>
       <c r="B85" s="1"/>
-      <c r="C85" s="5"/>
+      <c r="C85" s="4"/>
       <c r="D85" s="1"/>
-      <c r="E85" s="6"/>
+      <c r="E85" s="5"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I85" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="12"/>
+      <c r="I85" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="10"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="1">
         <v>84</v>
       </c>
       <c r="B86" s="1"/>
-      <c r="C86" s="5"/>
+      <c r="C86" s="4"/>
       <c r="D86" s="1"/>
-      <c r="E86" s="6"/>
+      <c r="E86" s="5"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I86" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="12"/>
+      <c r="I86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="10"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="1">
         <v>85</v>
       </c>
       <c r="B87" s="1"/>
-      <c r="C87" s="5"/>
+      <c r="C87" s="4"/>
       <c r="D87" s="1"/>
-      <c r="E87" s="6"/>
+      <c r="E87" s="5"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I87" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="12"/>
+      <c r="I87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="10"/>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="1">
         <v>86</v>
       </c>
       <c r="B88" s="1"/>
-      <c r="C88" s="5"/>
+      <c r="C88" s="4"/>
       <c r="D88" s="1"/>
-      <c r="E88" s="6"/>
+      <c r="E88" s="5"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I88" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="12"/>
+      <c r="I88" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="10"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="1">
         <v>87</v>
       </c>
       <c r="B89" s="1"/>
-      <c r="C89" s="5"/>
+      <c r="C89" s="4"/>
       <c r="D89" s="1"/>
-      <c r="E89" s="6"/>
+      <c r="E89" s="5"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I89" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="12"/>
+      <c r="I89" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="10"/>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1">
         <v>88</v>
       </c>
       <c r="B90" s="1"/>
-      <c r="C90" s="5"/>
+      <c r="C90" s="4"/>
       <c r="D90" s="1"/>
-      <c r="E90" s="6"/>
+      <c r="E90" s="5"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I90" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="12"/>
+      <c r="I90" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="10"/>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1">
         <v>89</v>
       </c>
       <c r="B91" s="1"/>
-      <c r="C91" s="5"/>
+      <c r="C91" s="4"/>
       <c r="D91" s="1"/>
-      <c r="E91" s="6"/>
+      <c r="E91" s="5"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I91" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="12"/>
+      <c r="I91" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="10"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1">
         <v>90</v>
       </c>
       <c r="B92" s="1"/>
-      <c r="C92" s="5"/>
+      <c r="C92" s="4"/>
       <c r="D92" s="1"/>
-      <c r="E92" s="6"/>
+      <c r="E92" s="5"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I92" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="12"/>
+      <c r="I92" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="10"/>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="1">
         <v>91</v>
       </c>
       <c r="B93" s="1"/>
-      <c r="C93" s="5"/>
+      <c r="C93" s="4"/>
       <c r="D93" s="1"/>
-      <c r="E93" s="6"/>
+      <c r="E93" s="5"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I93" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="12"/>
+      <c r="I93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="10"/>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="1">
         <v>92</v>
       </c>
       <c r="B94" s="1"/>
-      <c r="C94" s="5"/>
+      <c r="C94" s="4"/>
       <c r="D94" s="1"/>
-      <c r="E94" s="6"/>
+      <c r="E94" s="5"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I94" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="12"/>
+      <c r="I94" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="10"/>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="1">
         <v>93</v>
       </c>
       <c r="B95" s="1"/>
-      <c r="C95" s="5"/>
+      <c r="C95" s="4"/>
       <c r="D95" s="1"/>
-      <c r="E95" s="6"/>
+      <c r="E95" s="5"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I95" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="12"/>
+      <c r="I95" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="10"/>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="1">
         <v>94</v>
       </c>
       <c r="B96" s="1"/>
-      <c r="C96" s="5"/>
+      <c r="C96" s="4"/>
       <c r="D96" s="1"/>
-      <c r="E96" s="6"/>
+      <c r="E96" s="5"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I96" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="12"/>
+      <c r="I96" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="10"/>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="1">
         <v>95</v>
       </c>
       <c r="B97" s="1"/>
-      <c r="C97" s="5"/>
+      <c r="C97" s="4"/>
       <c r="D97" s="1"/>
-      <c r="E97" s="6"/>
+      <c r="E97" s="5"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I97" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="12"/>
+      <c r="I97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="10"/>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="1">
         <v>96</v>
       </c>
       <c r="B98" s="1"/>
-      <c r="C98" s="5"/>
+      <c r="C98" s="4"/>
       <c r="D98" s="1"/>
-      <c r="E98" s="6"/>
+      <c r="E98" s="5"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I98" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="12"/>
+      <c r="I98" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="10"/>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="1">
         <v>97</v>
       </c>
       <c r="B99" s="1"/>
-      <c r="C99" s="5"/>
+      <c r="C99" s="4"/>
       <c r="D99" s="1"/>
-      <c r="E99" s="6"/>
+      <c r="E99" s="5"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I99" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="12"/>
+      <c r="I99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="10"/>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="1">
         <v>98</v>
       </c>
       <c r="B100" s="1"/>
-      <c r="C100" s="5"/>
+      <c r="C100" s="4"/>
       <c r="D100" s="1"/>
-      <c r="E100" s="6"/>
+      <c r="E100" s="5"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I100" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="12"/>
+      <c r="I100" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="10"/>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="1">
         <v>99</v>
       </c>
       <c r="B101" s="1"/>
-      <c r="C101" s="5"/>
+      <c r="C101" s="4"/>
       <c r="D101" s="1"/>
-      <c r="E101" s="6"/>
+      <c r="E101" s="5"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I101" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="12"/>
+      <c r="I101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="10"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I101" etc:filterBottomFollowUsedRange="0">
@@ -3951,257 +3945,257 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>46188</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>4300</v>
       </c>
       <c r="F2" s="2">
         <v>4.8581</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>5.17</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <f>E2*(G2-F2)</f>
         <v>1341.17</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <v>1308.3</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>46190</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>600172</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>600</v>
       </c>
       <c r="F3" s="2">
         <v>12.2123</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>13</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <f>E3*(G3-F3)</f>
         <v>472.619999999999</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>460.95</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5">
         <f t="shared" ref="I4:I9" si="0">E4*(G4-F4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="6">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5">
         <f>SUM(J2:J9)</f>
         <v>1769.25</v>
       </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D3" etc:filterBottomFollowUsedRange="0">
@@ -4245,7 +4239,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="23" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -4254,7 +4248,7 @@
       <c r="D2" s="3">
         <v>5.13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>68</v>
       </c>
     </row>

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="71">
   <si>
     <t>时间</t>
   </si>
@@ -222,13 +222,13 @@
     <t>月度盈亏</t>
   </si>
   <si>
-    <t>月份盈亏</t>
-  </si>
-  <si>
     <t>季度盈亏</t>
   </si>
   <si>
     <t>单次购入单次售出</t>
+  </si>
+  <si>
+    <t>6.09购入3400售出2400</t>
   </si>
   <si>
     <t>总盈亏</t>
@@ -3937,14 +3937,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.375"/>
-    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="22.125" customWidth="1"/>
+    <col min="10" max="10" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -3981,11 +3982,8 @@
       <c r="L1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -4008,7 +4006,7 @@
         <v>5.17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I2" s="5">
         <f>E2*(G2-F2)</f>
@@ -4019,9 +4017,8 @@
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -4044,7 +4041,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I3" s="5">
         <f>E3*(G3-F3)</f>
@@ -4055,29 +4052,43 @@
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="B4" s="6">
+        <v>46199</v>
+      </c>
+      <c r="C4" s="1">
+        <v>601066</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2400</v>
+      </c>
+      <c r="F4" s="5">
+        <v>27.6302</v>
+      </c>
+      <c r="G4" s="5">
+        <v>31</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="I4" s="5">
         <f t="shared" ref="I4:I9" si="0">E4*(G4-F4)</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="5"/>
+        <v>8087.52</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8087.52</v>
+      </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -4095,9 +4106,8 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -4115,9 +4125,8 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -4135,9 +4144,8 @@
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" spans="1:13">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -4155,9 +4163,8 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-    </row>
-    <row r="9" spans="1:13">
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -4175,9 +4182,8 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:13">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="4" t="s">
         <v>65</v>
       </c>
@@ -4191,11 +4197,10 @@
       <c r="I10" s="4"/>
       <c r="J10" s="5">
         <f>SUM(J2:J9)</f>
-        <v>1769.25</v>
+        <v>9856.77</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D3" etc:filterBottomFollowUsedRange="0">

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -13,8 +13,8 @@
     <sheet name="自选股" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已出售!$C$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已出售!$C$1:$D$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="73">
   <si>
     <t>时间</t>
   </si>
@@ -66,7 +66,7 @@
     <t>名称</t>
   </si>
   <si>
-    <t>购入时间</t>
+    <t>购入/出售时间</t>
   </si>
   <si>
     <t>股价</t>
@@ -156,7 +156,8 @@
     <t>中信建投</t>
   </si>
   <si>
-    <t>如果低于22或者更低就购入10000块左右的，如果有余额</t>
+    <t>1、6.19出售2400,31元每股
+2、6.29买入1000股，29.3</t>
   </si>
   <si>
     <t>002716</t>
@@ -192,6 +193,12 @@
     <t>等待盈利后就出售，5%这个点吧 不过可能等不到了，那就持有</t>
   </si>
   <si>
+    <t>中国东航</t>
+  </si>
+  <si>
+    <t>华微电子</t>
+  </si>
+  <si>
     <t>出手时间</t>
   </si>
   <si>
@@ -213,6 +220,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>手续费</t>
+  </si>
+  <si>
     <t>盈亏</t>
   </si>
   <si>
@@ -244,9 +254,6 @@
   </si>
   <si>
     <t>工商银行</t>
-  </si>
-  <si>
-    <t>中国东航</t>
   </si>
 </sst>
 </file>
@@ -618,7 +625,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -651,6 +658,17 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -791,7 +809,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -803,34 +821,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -915,7 +933,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -937,6 +955,15 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -967,13 +994,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
@@ -1734,21 +1779,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K101"/>
+  <sheetPr/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="9.375" style="3"/>
-    <col min="3" max="3" width="9" style="7"/>
+    <col min="3" max="3" width="9" style="10"/>
     <col min="4" max="4" width="9" style="3"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
     <col min="6" max="8" width="12.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="7"/>
-    <col min="10" max="10" width="68.625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="9" style="10"/>
+    <col min="10" max="10" width="68.625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:11">
+    <row r="1" s="10" customFormat="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -1761,22 +1806,22 @@
       <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="13" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1793,7 +1838,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="14">
         <v>46182</v>
       </c>
       <c r="F2" s="1">
@@ -1803,16 +1848,16 @@
         <v>1600</v>
       </c>
       <c r="H2" s="1">
-        <f>F2*G2</f>
+        <f t="shared" ref="H2:H8" si="0">F2*G2</f>
         <v>26578.24</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="7"/>
+      <c r="K2" s="10"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
@@ -1827,7 +1872,7 @@
       <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="14">
         <v>46182</v>
       </c>
       <c r="F3" s="1">
@@ -1837,46 +1882,46 @@
         <v>1800</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H16" si="0">F3*G3</f>
+        <f t="shared" si="0"/>
         <v>7477.38</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:11">
-      <c r="A4" s="12">
+    <row r="4" spans="1:11">
+      <c r="A4" s="15">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="15">
         <v>1</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="17">
         <v>46182</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="15">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="15">
         <v>4300</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="15">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="15"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
@@ -1891,7 +1936,7 @@
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="14">
         <v>46182</v>
       </c>
       <c r="F5" s="1">
@@ -1907,7 +1952,7 @@
       <c r="I5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="13" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1924,7 +1969,7 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="14">
         <v>46182</v>
       </c>
       <c r="F6" s="1">
@@ -1940,7 +1985,7 @@
       <c r="I6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="13" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1948,7 +1993,7 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="32" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1957,7 +2002,7 @@
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="14">
         <v>46182</v>
       </c>
       <c r="F7" s="1">
@@ -1973,7 +2018,7 @@
       <c r="I7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1990,7 +2035,7 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="14">
         <v>46182</v>
       </c>
       <c r="F8" s="1">
@@ -2006,7 +2051,7 @@
       <c r="I8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="13" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2023,7 +2068,7 @@
       <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="14">
         <v>46182</v>
       </c>
       <c r="F9" s="1">
@@ -2033,13 +2078,13 @@
         <v>900</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H9:H18" si="1">F9*G9</f>
         <v>18619.92</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2056,7 +2101,7 @@
       <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="14">
         <v>46182</v>
       </c>
       <c r="F10" s="1">
@@ -2066,13 +2111,13 @@
         <v>600</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12637.14</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="19" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2083,7 +2128,7 @@
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="14">
         <v>46188</v>
       </c>
       <c r="F11" s="1">
@@ -2093,13 +2138,13 @@
         <v>600</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5100</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="17"/>
+      <c r="J11" s="20"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
@@ -2114,7 +2159,7 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="14">
         <v>46182</v>
       </c>
       <c r="F12" s="1">
@@ -2124,30 +2169,30 @@
         <v>700</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18386.27</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1">
+      <c r="A13" s="21">
         <v>11</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="21">
         <v>601066</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="14">
         <v>46182</v>
       </c>
       <c r="F13" s="1">
@@ -2157,260 +2202,296 @@
         <v>3400</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>93942.68</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="22" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="11">
-        <v>46182</v>
-      </c>
-      <c r="F14" s="1">
-        <v>18.3681</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="24">
+        <v>2</v>
+      </c>
+      <c r="E14" s="25">
+        <v>46192</v>
+      </c>
+      <c r="F14" s="24">
+        <v>31</v>
+      </c>
+      <c r="G14" s="24">
+        <v>-2400</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="1"/>
+        <v>-74400</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="27"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="14">
+        <v>46202</v>
+      </c>
+      <c r="F15" s="1">
+        <v>29.3</v>
+      </c>
+      <c r="G15" s="1">
         <v>1000</v>
       </c>
-      <c r="H14" s="1">
-        <f t="shared" si="0"/>
-        <v>18368.1</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1">
-        <v>300589</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11">
-        <v>46182</v>
-      </c>
-      <c r="F15" s="1">
-        <v>22.8225</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1200</v>
-      </c>
       <c r="H15" s="1">
-        <f t="shared" si="0"/>
-        <v>27387</v>
+        <f t="shared" si="1"/>
+        <v>29300</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="10" t="s">
-        <v>45</v>
-      </c>
+      <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1">
-        <v>300129</v>
+        <v>12</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>41</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="14">
         <v>46182</v>
       </c>
       <c r="F16" s="1">
-        <v>14.9016</v>
+        <v>18.3681</v>
       </c>
       <c r="G16" s="1">
-        <v>2300</v>
+        <v>1000</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="0"/>
-        <v>34273.68</v>
+        <f t="shared" si="1"/>
+        <v>18368.1</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" hidden="1" spans="1:10">
-      <c r="A17" s="18">
-        <v>15</v>
-      </c>
-      <c r="B17" s="18">
-        <v>600172</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="18">
+      <c r="J16" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
+        <v>300589</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="1">
         <v>1</v>
       </c>
-      <c r="E17" s="20">
-        <v>46188</v>
-      </c>
-      <c r="F17" s="18">
-        <v>12.2123</v>
-      </c>
-      <c r="G17" s="18">
-        <v>600</v>
-      </c>
-      <c r="H17" s="18">
-        <f t="shared" ref="H17:H48" si="1">F17*G17</f>
-        <v>7327.38</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>49</v>
+      <c r="E17" s="14">
+        <v>46182</v>
+      </c>
+      <c r="F17" s="1">
+        <v>22.8225</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1200</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
+        <v>27387</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1">
-        <v>600745</v>
+        <v>300129</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E18" s="6">
-        <v>46189</v>
+      <c r="E18" s="14">
+        <v>46182</v>
       </c>
       <c r="F18" s="1">
-        <v>18.6687</v>
+        <v>14.9016</v>
       </c>
       <c r="G18" s="1">
-        <v>800</v>
+        <v>2300</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
-        <v>14934.96</v>
+        <v>34273.68</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="10" t="s">
-        <v>51</v>
+      <c r="J18" s="13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="10"/>
+      <c r="A19" s="24">
+        <v>15</v>
+      </c>
+      <c r="B19" s="24">
+        <v>600172</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="24">
+        <v>1</v>
+      </c>
+      <c r="E19" s="29">
+        <v>46188</v>
+      </c>
+      <c r="F19" s="24">
+        <v>12.2123</v>
+      </c>
+      <c r="G19" s="24">
+        <v>600</v>
+      </c>
+      <c r="H19" s="24">
+        <f t="shared" ref="H19:H50" si="2">F19*G19</f>
+        <v>7327.38</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="1">
+        <v>600745</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6">
+        <v>46189</v>
+      </c>
+      <c r="F20" s="1">
+        <v>18.6687</v>
+      </c>
+      <c r="G20" s="1">
+        <v>800</v>
+      </c>
       <c r="H20" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>14934.96</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J20" s="10"/>
+      <c r="J20" s="13" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="B21">
+        <v>600115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6">
+        <v>46203</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3.7838</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3200</v>
+      </c>
       <c r="H21" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>12108.16</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J21" s="10"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="1">
+        <v>600360</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6">
+        <v>46203</v>
+      </c>
+      <c r="F22" s="1">
+        <v>14.6146</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2000</v>
+      </c>
       <c r="H22" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>29229.2</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="10"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="4"/>
@@ -2419,17 +2500,17 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J23" s="10"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="4"/>
@@ -2438,17 +2519,17 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J24" s="10"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="4"/>
@@ -2457,17 +2538,17 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J25" s="10"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="4"/>
@@ -2476,17 +2557,17 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="10"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="4"/>
@@ -2495,17 +2576,17 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="10"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="4"/>
@@ -2514,17 +2595,17 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J28" s="10"/>
+      <c r="J28" s="13"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="4"/>
@@ -2533,17 +2614,17 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="10"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="4"/>
@@ -2552,17 +2633,17 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J30" s="10"/>
+      <c r="J30" s="13"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4"/>
@@ -2571,17 +2652,17 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="10"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="4"/>
@@ -2590,17 +2671,17 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="10"/>
+      <c r="J32" s="13"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="4"/>
@@ -2609,17 +2690,17 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="10"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4"/>
@@ -2628,17 +2709,17 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J34" s="10"/>
+      <c r="J34" s="13"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="4"/>
@@ -2647,17 +2728,17 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="10"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="4"/>
@@ -2666,17 +2747,17 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="10"/>
+      <c r="J36" s="13"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="4"/>
@@ -2685,17 +2766,17 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="10"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="4"/>
@@ -2704,17 +2785,17 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J38" s="10"/>
+      <c r="J38" s="13"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="4"/>
@@ -2723,17 +2804,17 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J39" s="10"/>
+      <c r="J39" s="13"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="4"/>
@@ -2742,17 +2823,17 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="10"/>
+      <c r="J40" s="13"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="4"/>
@@ -2761,17 +2842,17 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J41" s="10"/>
+      <c r="J41" s="13"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="4"/>
@@ -2780,17 +2861,17 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="10"/>
+      <c r="J42" s="13"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4"/>
@@ -2799,17 +2880,17 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J43" s="10"/>
+      <c r="J43" s="13"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4"/>
@@ -2818,17 +2899,17 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="10"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="4"/>
@@ -2837,17 +2918,17 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="10"/>
+      <c r="J45" s="13"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="4"/>
@@ -2856,17 +2937,17 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J46" s="10"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="4"/>
@@ -2875,17 +2956,17 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="10"/>
+      <c r="J47" s="13"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="4"/>
@@ -2894,17 +2975,17 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J48" s="10"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4"/>
@@ -2913,17 +2994,17 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1">
-        <f t="shared" ref="H49:H80" si="2">F49*G49</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J49" s="10"/>
+      <c r="J49" s="13"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4"/>
@@ -2938,11 +3019,11 @@
       <c r="I50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J50" s="10"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4"/>
@@ -2951,17 +3032,17 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H51:H82" si="3">F51*G51</f>
         <v>0</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="10"/>
+      <c r="J51" s="13"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="4"/>
@@ -2970,17 +3051,17 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J52" s="10"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="4"/>
@@ -2989,17 +3070,17 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J53" s="10"/>
+      <c r="J53" s="13"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4"/>
@@ -3008,17 +3089,17 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J54" s="10"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="4"/>
@@ -3027,17 +3108,17 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J55" s="10"/>
+      <c r="J55" s="13"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="4"/>
@@ -3046,17 +3127,17 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="10"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="4"/>
@@ -3065,17 +3146,17 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J57" s="10"/>
+      <c r="J57" s="13"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="4"/>
@@ -3084,17 +3165,17 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="10"/>
+      <c r="J58" s="13"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="1">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="4"/>
@@ -3103,17 +3184,17 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J59" s="10"/>
+      <c r="J59" s="13"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="1">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="4"/>
@@ -3122,17 +3203,17 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J60" s="10"/>
+      <c r="J60" s="13"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="1">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="4"/>
@@ -3141,17 +3222,17 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J61" s="10"/>
+      <c r="J61" s="13"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4"/>
@@ -3160,17 +3241,17 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J62" s="10"/>
+      <c r="J62" s="13"/>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="1">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="4"/>
@@ -3179,17 +3260,17 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J63" s="10"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4"/>
@@ -3198,17 +3279,17 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J64" s="10"/>
+      <c r="J64" s="13"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="1">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4"/>
@@ -3217,17 +3298,17 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="10"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="1">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4"/>
@@ -3236,17 +3317,17 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J66" s="10"/>
+      <c r="J66" s="13"/>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="1">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="4"/>
@@ -3255,17 +3336,17 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J67" s="10"/>
+      <c r="J67" s="13"/>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="1">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="4"/>
@@ -3274,17 +3355,17 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J68" s="10"/>
+      <c r="J68" s="13"/>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="1">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4"/>
@@ -3293,17 +3374,17 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J69" s="10"/>
+      <c r="J69" s="13"/>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="4"/>
@@ -3312,17 +3393,17 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J70" s="10"/>
+      <c r="J70" s="13"/>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="4"/>
@@ -3331,17 +3412,17 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J71" s="10"/>
+      <c r="J71" s="13"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="1">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="4"/>
@@ -3350,17 +3431,17 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J72" s="10"/>
+      <c r="J72" s="13"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="1">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="4"/>
@@ -3369,17 +3450,17 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J73" s="10"/>
+      <c r="J73" s="13"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="1">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="4"/>
@@ -3388,17 +3469,17 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J74" s="10"/>
+      <c r="J74" s="13"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="1">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="4"/>
@@ -3407,17 +3488,17 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J75" s="10"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="1">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4"/>
@@ -3426,17 +3507,17 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J76" s="10"/>
+      <c r="J76" s="13"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="1">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4"/>
@@ -3445,17 +3526,17 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J77" s="10"/>
+      <c r="J77" s="13"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="1">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4"/>
@@ -3464,17 +3545,17 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J78" s="10"/>
+      <c r="J78" s="13"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="1">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="4"/>
@@ -3483,17 +3564,17 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J79" s="10"/>
+      <c r="J79" s="13"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="4"/>
@@ -3502,17 +3583,17 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J80" s="10"/>
+      <c r="J80" s="13"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="1">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4"/>
@@ -3521,17 +3602,17 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1">
-        <f t="shared" ref="H81:H101" si="3">F81*G81</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J81" s="10"/>
+      <c r="J81" s="13"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="1">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="4"/>
@@ -3546,11 +3627,11 @@
       <c r="I82" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J82" s="10"/>
+      <c r="J82" s="13"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="1">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4"/>
@@ -3559,17 +3640,17 @@
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H83:H103" si="4">F83*G83</f>
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J83" s="10"/>
+      <c r="J83" s="13"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="1">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="4"/>
@@ -3578,17 +3659,17 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J84" s="10"/>
+      <c r="J84" s="13"/>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="1">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="4"/>
@@ -3597,17 +3678,17 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J85" s="10"/>
+      <c r="J85" s="13"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="1">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="4"/>
@@ -3616,17 +3697,17 @@
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J86" s="10"/>
+      <c r="J86" s="13"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="1">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4"/>
@@ -3635,17 +3716,17 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J87" s="10"/>
+      <c r="J87" s="13"/>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="1">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="4"/>
@@ -3654,17 +3735,17 @@
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J88" s="10"/>
+      <c r="J88" s="13"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="1">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="4"/>
@@ -3673,17 +3754,17 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J89" s="10"/>
+      <c r="J89" s="13"/>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="4"/>
@@ -3692,17 +3773,17 @@
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J90" s="10"/>
+      <c r="J90" s="13"/>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="4"/>
@@ -3711,17 +3792,17 @@
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J91" s="10"/>
+      <c r="J91" s="13"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="4"/>
@@ -3730,17 +3811,17 @@
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J92" s="10"/>
+      <c r="J92" s="13"/>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4"/>
@@ -3749,17 +3830,17 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J93" s="10"/>
+      <c r="J93" s="13"/>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="1">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="4"/>
@@ -3768,17 +3849,17 @@
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J94" s="10"/>
+      <c r="J94" s="13"/>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="1">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="4"/>
@@ -3787,17 +3868,17 @@
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J95" s="10"/>
+      <c r="J95" s="13"/>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4"/>
@@ -3806,17 +3887,17 @@
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J96" s="10"/>
+      <c r="J96" s="13"/>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="1">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4"/>
@@ -3825,17 +3906,17 @@
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J97" s="10"/>
+      <c r="J97" s="13"/>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="4"/>
@@ -3844,17 +3925,17 @@
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J98" s="10"/>
+      <c r="J98" s="13"/>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="1">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="4"/>
@@ -3863,17 +3944,17 @@
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J99" s="10"/>
+      <c r="J99" s="13"/>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="1">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="4"/>
@@ -3882,17 +3963,17 @@
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J100" s="10"/>
+      <c r="J100" s="13"/>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="1">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4"/>
@@ -3901,32 +3982,69 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J101" s="10"/>
+      <c r="J101" s="13"/>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="1">
+        <v>98</v>
+      </c>
+      <c r="B102" s="1"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="13"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="1">
+        <v>99</v>
+      </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="13"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I101" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="equal" val="持有"/>
-      </customFilters>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I103" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
     <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B13:B15"/>
     <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C13:C15"/>
     <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J13:J15"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I101">
-      <formula1>$K$1:$K$2</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+      <formula1>$I$2:$I$20</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3937,60 +4055,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.375"/>
     <col min="8" max="8" width="22.125" customWidth="1"/>
-    <col min="10" max="10" width="10.875" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>64</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="6">
         <v>46188</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="32" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -4006,19 +4128,28 @@
         <v>5.17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="5">
-        <f>E2*(G2-F2)</f>
+        <v>66</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <f>E2*(G2-F2)-I2</f>
         <v>1341.17</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="5">
         <v>1308.3</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" s="7">
+        <f>SUM(K2:K4)</f>
+        <v>9745.52</v>
+      </c>
+      <c r="M2" s="7">
+        <f>SUM(L2)</f>
+        <v>9745.52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -4041,19 +4172,22 @@
         <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="5">
-        <f>E3*(G3-F3)</f>
+        <v>66</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <f t="shared" ref="J3:J9" si="0">E3*(G3-F3)-I3</f>
         <v>472.619999999999</v>
       </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
         <v>460.95</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -4076,19 +4210,22 @@
         <v>31</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" ref="I4:I9" si="0">E4*(G4-F4)</f>
-        <v>8087.52</v>
+        <v>67</v>
+      </c>
+      <c r="I4" s="1">
+        <v>111.25</v>
       </c>
       <c r="J4" s="5">
-        <v>8087.52</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-    </row>
-    <row r="5" spans="1:12">
+        <f t="shared" si="0"/>
+        <v>7976.27</v>
+      </c>
+      <c r="K4" s="5">
+        <v>7976.27</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -4099,15 +4236,16 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="5">
+      <c r="I5" s="1"/>
+      <c r="J5" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -4118,15 +4256,16 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="5">
+      <c r="I6" s="1"/>
+      <c r="J6" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="5"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -4137,15 +4276,16 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5">
+      <c r="I7" s="1"/>
+      <c r="J7" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7" s="5"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -4156,15 +4296,16 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="5">
+      <c r="I8" s="1"/>
+      <c r="J8" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8" s="5"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -4175,17 +4316,18 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="5">
+      <c r="I9" s="1"/>
+      <c r="J9" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9" s="5"/>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4194,20 +4336,23 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="5">
-        <f>SUM(J2:J9)</f>
-        <v>9856.77</v>
-      </c>
-      <c r="K10" s="5"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="5">
+        <f>SUM(K2:K9)</f>
+        <v>9745.52</v>
+      </c>
       <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D3" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D4" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="A10:I10"/>
+  <mergeCells count="3">
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="M2:M4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4234,17 +4379,17 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="32" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -4254,7 +4399,7 @@
         <v>5.13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4265,7 +4410,7 @@
         <v>601398</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D3" s="3">
         <v>7.16</v>
@@ -4282,7 +4427,7 @@
         <v>600115</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>3.93</v>

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="75">
   <si>
     <t>时间</t>
   </si>
@@ -197,6 +197,12 @@
   </si>
   <si>
     <t>华微电子</t>
+  </si>
+  <si>
+    <t>000725</t>
+  </si>
+  <si>
+    <t>京东方Ａ</t>
   </si>
   <si>
     <t>出手时间</t>
@@ -933,7 +939,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -998,13 +1004,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1017,9 +1017,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1896,7 +1893,7 @@
       <c r="A4" s="15">
         <v>3</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="28" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="16" t="s">
@@ -1993,7 +1990,7 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="29" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -2180,13 +2177,13 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="21">
+      <c r="A13" s="7">
         <v>11</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="7">
         <v>601066</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="1">
@@ -2208,39 +2205,39 @@
       <c r="I13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="24">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="22">
         <v>2</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="23">
         <v>46192</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <v>31</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <v>-2400</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="22">
         <f t="shared" si="1"/>
         <v>-74400</v>
       </c>
-      <c r="I14" s="26" t="s">
+      <c r="I14" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="27"/>
+      <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="1">
         <v>3</v>
       </c>
@@ -2266,7 +2263,7 @@
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="29" t="s">
         <v>41</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2362,35 +2359,35 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="24">
+      <c r="A19" s="22">
         <v>15</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="22">
         <v>600172</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="22">
         <v>1</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="26">
         <v>46188</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="22">
         <v>12.2123</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="22">
         <v>600</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="22">
         <f t="shared" ref="H19:H50" si="2">F19*G19</f>
         <v>7327.38</v>
       </c>
       <c r="I19" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J19" s="30" t="s">
+      <c r="J19" s="27" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2493,15 +2490,27 @@
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+      <c r="B23" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>46204</v>
+      </c>
+      <c r="F23" s="1">
+        <v>8.5585</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1700</v>
+      </c>
       <c r="H23" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14549.45</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>17</v>
@@ -4069,40 +4078,40 @@
         <v>7</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4112,7 +4121,7 @@
       <c r="B2" s="6">
         <v>46188</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="29" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -4128,7 +4137,7 @@
         <v>5.17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -4172,7 +4181,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -4210,7 +4219,7 @@
         <v>31</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I4" s="1">
         <v>111.25</v>
@@ -4327,7 +4336,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4379,17 +4388,17 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="29" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -4399,7 +4408,7 @@
         <v>5.13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4410,7 +4419,7 @@
         <v>601398</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3" s="3">
         <v>7.16</v>

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="76">
   <si>
     <t>时间</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>6.09购入3400售出2400</t>
+  </si>
+  <si>
+    <t>6.30购入1800股卖出1300</t>
   </si>
   <si>
     <t>总盈亏</t>
@@ -2475,11 +2478,11 @@
         <v>14.6146</v>
       </c>
       <c r="G22" s="1">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="2"/>
-        <v>29229.2</v>
+        <v>26306.28</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>17</v>
@@ -4238,19 +4241,35 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="B5" s="6">
+        <v>46213</v>
+      </c>
+      <c r="C5" s="5">
+        <v>600360</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1300</v>
+      </c>
+      <c r="F5" s="1">
+        <v>14.6146</v>
+      </c>
+      <c r="G5" s="5">
+        <v>17.59</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="5"/>
+        <v>3868.02</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3868.02</v>
+      </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
     </row>
@@ -4336,7 +4355,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4349,7 +4368,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="5">
         <f>SUM(K2:K9)</f>
-        <v>9745.52</v>
+        <v>13613.54</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -4388,10 +4407,10 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4408,7 +4427,7 @@
         <v>5.13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4419,7 +4438,7 @@
         <v>601398</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="3">
         <v>7.16</v>

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -4,17 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
     <sheet name="清单" sheetId="1" r:id="rId2"/>
-    <sheet name="已出售" sheetId="3" r:id="rId3"/>
-    <sheet name="自选股" sheetId="4" r:id="rId4"/>
+    <sheet name="定投股票" sheetId="6" r:id="rId3"/>
+    <sheet name="已出售" sheetId="3" r:id="rId4"/>
+    <sheet name="自选股" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已出售!$C$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">定投股票!$B$1:$I$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已出售!$C$1:$D$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="76">
   <si>
     <t>时间</t>
   </si>
@@ -205,6 +207,9 @@
     <t>京东方Ａ</t>
   </si>
   <si>
+    <t>工商银行</t>
+  </si>
+  <si>
     <t>出手时间</t>
   </si>
   <si>
@@ -260,9 +265,6 @@
   </si>
   <si>
     <t>3.5~4</t>
-  </si>
-  <si>
-    <t>工商银行</t>
   </si>
 </sst>
 </file>
@@ -942,7 +944,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1000,6 +1002,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1013,7 +1027,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1021,11 +1035,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1780,7 +1806,2322 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="9.375" style="3"/>
+    <col min="3" max="3" width="9" style="10"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="5" width="12.875" style="19" customWidth="1"/>
+    <col min="6" max="8" width="12.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9" style="10"/>
+    <col min="10" max="10" width="68.625" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="10" customFormat="1" spans="1:11">
+      <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>300323</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F2" s="1">
+        <v>16.6114</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H2" s="1">
+        <f t="shared" ref="H2:H8" si="0">F2*G2</f>
+        <v>26578.24</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="10"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>600740</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4.1541</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1800</v>
+      </c>
+      <c r="H3" s="1">
+        <f t="shared" si="0"/>
+        <v>7477.38</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="15">
+        <v>1</v>
+      </c>
+      <c r="E4" s="22">
+        <v>46182</v>
+      </c>
+      <c r="F4" s="15">
+        <v>4.8581</v>
+      </c>
+      <c r="G4" s="15">
+        <v>4300</v>
+      </c>
+      <c r="H4" s="15">
+        <f t="shared" si="0"/>
+        <v>20889.83</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>601990</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F5" s="1">
+        <v>9.9227</v>
+      </c>
+      <c r="G5" s="1">
+        <v>500</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>4961.35</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>600059</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10.9008</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>10900.8</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F7" s="1">
+        <v>9.6507</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="0"/>
+        <v>9650.7</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>601179</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F8" s="1">
+        <v>20.12</v>
+      </c>
+      <c r="G8" s="1">
+        <v>700</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>14084</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>603258</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F9" s="1">
+        <v>20.6888</v>
+      </c>
+      <c r="G9" s="1">
+        <v>900</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" ref="H9:H18" si="1">F9*G9</f>
+        <v>18619.92</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>600422</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F10" s="1">
+        <v>21.0619</v>
+      </c>
+      <c r="G10" s="1">
+        <v>600</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
+        <v>12637.14</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="21">
+        <v>46188</v>
+      </c>
+      <c r="F11" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>600</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
+        <v>5100</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="24"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
+        <v>600879</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F12" s="1">
+        <v>26.2661</v>
+      </c>
+      <c r="G12" s="1">
+        <v>700</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
+        <v>18386.27</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="7">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7">
+        <v>601066</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F13" s="1">
+        <v>27.6302</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3400</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
+        <v>93942.68</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="26">
+        <v>2</v>
+      </c>
+      <c r="E14" s="27">
+        <v>46192</v>
+      </c>
+      <c r="F14" s="26">
+        <v>31</v>
+      </c>
+      <c r="G14" s="26">
+        <v>-2400</v>
+      </c>
+      <c r="H14" s="26">
+        <f t="shared" si="1"/>
+        <v>-74400</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="29"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="21">
+        <v>46202</v>
+      </c>
+      <c r="F15" s="1">
+        <v>29.3</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
+        <v>29300</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F16" s="1">
+        <v>18.3681</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
+        <v>18368.1</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
+        <v>300589</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F17" s="1">
+        <v>22.8225</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1200</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
+        <v>27387</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="30">
+        <v>14</v>
+      </c>
+      <c r="B18" s="30">
+        <v>300129</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F18" s="1">
+        <v>14.9016</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2300</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
+        <v>34273.68</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="21">
+        <v>46223</v>
+      </c>
+      <c r="F19" s="1">
+        <v>7.35</v>
+      </c>
+      <c r="G19" s="1">
+        <v>700</v>
+      </c>
+      <c r="H19" s="1">
+        <f>F19*G19</f>
+        <v>5145</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="13"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="26">
+        <v>15</v>
+      </c>
+      <c r="B20" s="26">
+        <v>600172</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="26">
+        <v>1</v>
+      </c>
+      <c r="E20" s="32">
+        <v>46188</v>
+      </c>
+      <c r="F20" s="26">
+        <v>12.2123</v>
+      </c>
+      <c r="G20" s="26">
+        <v>600</v>
+      </c>
+      <c r="H20" s="26">
+        <f t="shared" ref="H20:H51" si="2">F20*G20</f>
+        <v>7327.38</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="1">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1">
+        <v>600745</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="34">
+        <v>46189</v>
+      </c>
+      <c r="F21" s="1">
+        <v>18.6687</v>
+      </c>
+      <c r="G21" s="1">
+        <v>800</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="2"/>
+        <v>14934.96</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="1">
+        <v>17</v>
+      </c>
+      <c r="B22">
+        <v>600115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="34">
+        <v>46203</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3.7838</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3200</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="2"/>
+        <v>12108.16</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="13"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="1">
+        <v>18</v>
+      </c>
+      <c r="B23" s="1">
+        <v>600360</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="34">
+        <v>46203</v>
+      </c>
+      <c r="F23" s="1">
+        <v>14.6146</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1800</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="2"/>
+        <v>26306.28</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="1">
+        <v>19</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="34">
+        <v>46204</v>
+      </c>
+      <c r="F24" s="1">
+        <v>8.5585</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1700</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="2"/>
+        <v>14549.45</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="1">
+        <v>20</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="1">
+        <v>21</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="13"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="1">
+        <v>22</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="1">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="1">
+        <v>24</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="13"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="1">
+        <v>25</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="13"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="1">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="13"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="1">
+        <v>27</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="1">
+        <v>28</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="13"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="1">
+        <v>29</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="13"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="1">
+        <v>30</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="1">
+        <v>31</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="13"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="1">
+        <v>32</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="1">
+        <v>33</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="1">
+        <v>34</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="1">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="1">
+        <v>36</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="1">
+        <v>37</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="1">
+        <v>38</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="13"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="1">
+        <v>39</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="1">
+        <v>40</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="1">
+        <v>41</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="1">
+        <v>42</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="1">
+        <v>43</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="1">
+        <v>44</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="13"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="1">
+        <v>45</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="13"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="1">
+        <v>46</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="1">
+        <v>47</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1">
+        <f t="shared" ref="H52:H83" si="3">F52*G52</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="1">
+        <v>48</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="13"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="1">
+        <v>49</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1">
+        <v>50</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="1">
+        <v>51</v>
+      </c>
+      <c r="B56" s="1"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="13"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="1">
+        <v>52</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="13"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="1">
+        <v>53</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="13"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="1">
+        <v>54</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="13"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="1">
+        <v>55</v>
+      </c>
+      <c r="B60" s="1"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="1">
+        <v>56</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="13"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="1">
+        <v>57</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="13"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="1">
+        <v>58</v>
+      </c>
+      <c r="B63" s="1"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="13"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="1">
+        <v>59</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="13"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="1">
+        <v>60</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="13"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="1">
+        <v>61</v>
+      </c>
+      <c r="B66" s="1"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="13"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="1">
+        <v>62</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="35"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="1">
+        <v>63</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="1">
+        <v>64</v>
+      </c>
+      <c r="B69" s="1"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="1">
+        <v>65</v>
+      </c>
+      <c r="B70" s="1"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="13"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="1">
+        <v>66</v>
+      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="35"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="13"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="1">
+        <v>67</v>
+      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="13"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="1">
+        <v>68</v>
+      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="13"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="1">
+        <v>69</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="35"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="13"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="1">
+        <v>70</v>
+      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="13"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="1">
+        <v>71</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="35"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="13"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="1">
+        <v>72</v>
+      </c>
+      <c r="B77" s="1"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="35"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="1">
+        <v>73</v>
+      </c>
+      <c r="B78" s="1"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="35"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="13"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="1">
+        <v>74</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="35"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="1">
+        <v>75</v>
+      </c>
+      <c r="B80" s="1"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="35"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="13"/>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="1">
+        <v>76</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="35"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="13"/>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="1">
+        <v>77</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="35"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="13"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="1">
+        <v>78</v>
+      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="35"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="13"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="1">
+        <v>79</v>
+      </c>
+      <c r="B84" s="1"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="35"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1">
+        <f t="shared" ref="H84:H104" si="4">F84*G84</f>
+        <v>0</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="13"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="1">
+        <v>80</v>
+      </c>
+      <c r="B85" s="1"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="35"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="13"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="1">
+        <v>81</v>
+      </c>
+      <c r="B86" s="1"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="35"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="13"/>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="1">
+        <v>82</v>
+      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="35"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="13"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="1">
+        <v>83</v>
+      </c>
+      <c r="B88" s="1"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="35"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="13"/>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="1">
+        <v>84</v>
+      </c>
+      <c r="B89" s="1"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="35"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="13"/>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="1">
+        <v>85</v>
+      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="35"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="13"/>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="1">
+        <v>86</v>
+      </c>
+      <c r="B91" s="1"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="35"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="13"/>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="1">
+        <v>87</v>
+      </c>
+      <c r="B92" s="1"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="35"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="13"/>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="1">
+        <v>88</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="35"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="13"/>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="1">
+        <v>89</v>
+      </c>
+      <c r="B94" s="1"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="35"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="13"/>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="1">
+        <v>90</v>
+      </c>
+      <c r="B95" s="1"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="35"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="13"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="1">
+        <v>91</v>
+      </c>
+      <c r="B96" s="1"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="35"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="13"/>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" s="1">
+        <v>92</v>
+      </c>
+      <c r="B97" s="1"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="35"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="13"/>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="1">
+        <v>93</v>
+      </c>
+      <c r="B98" s="1"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="35"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="13"/>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="1">
+        <v>94</v>
+      </c>
+      <c r="B99" s="1"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="35"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="13"/>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="1">
+        <v>95</v>
+      </c>
+      <c r="B100" s="1"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="35"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="13"/>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="1">
+        <v>96</v>
+      </c>
+      <c r="B101" s="1"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="35"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="13"/>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="1">
+        <v>97</v>
+      </c>
+      <c r="B102" s="1"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="35"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="13"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="1">
+        <v>98</v>
+      </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="35"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="13"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="1">
+        <v>99</v>
+      </c>
+      <c r="B104" s="1"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="35"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="13"/>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I104" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <mergeCells count="11">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J13:J15"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I19 I1:I18 I20:I1048576">
+      <formula1>$I$2:$I$21</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1830,10 +4171,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>300323</v>
+        <v>601398</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -1848,78 +4189,50 @@
         <v>1600</v>
       </c>
       <c r="H2" s="1">
-        <f t="shared" ref="H2:H8" si="0">F2*G2</f>
+        <f>F2*G2</f>
         <v>26578.24</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>18</v>
-      </c>
+      <c r="J2" s="13"/>
       <c r="K2" s="10"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>600740</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F3" s="1">
-        <v>4.1541</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1800</v>
-      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="1">
+        <f t="shared" ref="H3:H13" si="0">F3*G3</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="1">
         <f t="shared" si="0"/>
-        <v>7477.38</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="15">
-        <v>3</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="15">
-        <v>1</v>
-      </c>
-      <c r="E4" s="17">
-        <v>46182</v>
-      </c>
-      <c r="F4" s="15">
-        <v>4.8581</v>
-      </c>
-      <c r="G4" s="15">
-        <v>4300</v>
-      </c>
-      <c r="H4" s="15">
-        <f t="shared" si="0"/>
-        <v>20889.83</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>23</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="J4" s="18"/>
     </row>
@@ -1927,531 +4240,319 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>601990</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F5" s="1">
-        <v>9.9227</v>
-      </c>
-      <c r="G5" s="1">
-        <v>500</v>
-      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="1">
         <f t="shared" si="0"/>
-        <v>4961.35</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>600059</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F6" s="1">
-        <v>10.9008</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1000</v>
-      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="1">
         <f t="shared" si="0"/>
-        <v>10900.8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F7" s="1">
-        <v>9.6507</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1000</v>
-      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="1">
         <f t="shared" si="0"/>
-        <v>9650.7</v>
+        <v>0</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>601179</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F8" s="1">
-        <v>20.12</v>
-      </c>
-      <c r="G8" s="1">
-        <v>700</v>
-      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>14084</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="13" t="s">
-        <v>32</v>
-      </c>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>603258</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F9" s="1">
-        <v>20.6888</v>
-      </c>
-      <c r="G9" s="1">
-        <v>900</v>
-      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="1">
-        <f t="shared" ref="H9:H18" si="1">F9*G9</f>
-        <v>18619.92</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>34</v>
-      </c>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>600422</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F10" s="1">
-        <v>21.0619</v>
-      </c>
-      <c r="G10" s="1">
-        <v>600</v>
-      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
       <c r="H10" s="1">
-        <f t="shared" si="1"/>
-        <v>12637.14</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="19" t="s">
-        <v>36</v>
-      </c>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="14">
-        <v>46188</v>
-      </c>
-      <c r="F11" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="G11" s="1">
-        <v>600</v>
-      </c>
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
       <c r="H11" s="1">
-        <f t="shared" si="1"/>
-        <v>5100</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="20"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1">
-        <v>600879</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F12" s="1">
-        <v>26.2661</v>
-      </c>
-      <c r="G12" s="1">
-        <v>700</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
       <c r="H12" s="1">
-        <f t="shared" si="1"/>
-        <v>18386.27</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="13" t="s">
-        <v>38</v>
-      </c>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="7">
-        <v>11</v>
-      </c>
-      <c r="B13" s="7">
-        <v>601066</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F13" s="1">
-        <v>27.6302</v>
-      </c>
-      <c r="G13" s="1">
-        <v>3400</v>
-      </c>
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
       <c r="H13" s="1">
-        <f t="shared" si="1"/>
-        <v>93942.68</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="21" t="s">
-        <v>40</v>
-      </c>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="22">
-        <v>2</v>
-      </c>
-      <c r="E14" s="23">
-        <v>46192</v>
-      </c>
-      <c r="F14" s="22">
-        <v>31</v>
-      </c>
-      <c r="G14" s="22">
-        <v>-2400</v>
-      </c>
-      <c r="H14" s="22">
-        <f t="shared" si="1"/>
-        <v>-74400</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="25"/>
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <f t="shared" ref="H10:H55" si="1">F14*G14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="1">
-        <v>3</v>
-      </c>
-      <c r="E15" s="14">
-        <v>46202</v>
-      </c>
-      <c r="F15" s="1">
-        <v>29.3</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1000</v>
-      </c>
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
       <c r="H15" s="1">
         <f t="shared" si="1"/>
-        <v>29300</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="20"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>12</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F16" s="1">
-        <v>18.3681</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1000</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
       <c r="H16" s="1">
         <f t="shared" si="1"/>
-        <v>18368.1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="13" t="s">
-        <v>43</v>
-      </c>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1">
-        <v>13</v>
-      </c>
-      <c r="B17" s="1">
-        <v>300589</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F17" s="1">
-        <v>22.8225</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1200</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
       <c r="H17" s="1">
         <f t="shared" si="1"/>
-        <v>27387</v>
+        <v>0</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="13" t="s">
-        <v>45</v>
-      </c>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1">
-        <v>14</v>
-      </c>
-      <c r="B18" s="1">
-        <v>300129</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>46182</v>
-      </c>
-      <c r="F18" s="1">
-        <v>14.9016</v>
-      </c>
-      <c r="G18" s="1">
-        <v>2300</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
-        <v>34273.68</v>
+        <v>0</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="22">
-        <v>15</v>
-      </c>
-      <c r="B19" s="22">
-        <v>600172</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="22">
-        <v>1</v>
-      </c>
-      <c r="E19" s="26">
-        <v>46188</v>
-      </c>
-      <c r="F19" s="22">
-        <v>12.2123</v>
-      </c>
-      <c r="G19" s="22">
-        <v>600</v>
-      </c>
-      <c r="H19" s="22">
-        <f t="shared" ref="H19:H50" si="2">F19*G19</f>
-        <v>7327.38</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" s="27" t="s">
-        <v>49</v>
-      </c>
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1">
-        <v>16</v>
-      </c>
-      <c r="B20" s="1">
-        <v>600745</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6">
-        <v>46189</v>
-      </c>
-      <c r="F20" s="1">
-        <v>18.6687</v>
-      </c>
-      <c r="G20" s="1">
-        <v>800</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
       <c r="H20" s="1">
-        <f t="shared" si="2"/>
-        <v>14934.96</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J20" s="13" t="s">
-        <v>51</v>
-      </c>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1">
-        <v>17</v>
-      </c>
-      <c r="B21">
-        <v>600115</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6">
-        <v>46203</v>
-      </c>
-      <c r="F21" s="1">
-        <v>3.7838</v>
-      </c>
-      <c r="G21" s="1">
-        <v>3200</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
       <c r="H21" s="1">
-        <f t="shared" si="2"/>
-        <v>12108.16</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>17</v>
@@ -2460,29 +4561,17 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1">
-        <v>18</v>
-      </c>
-      <c r="B22" s="1">
-        <v>600360</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6">
-        <v>46203</v>
-      </c>
-      <c r="F22" s="1">
-        <v>14.6146</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1800</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
       <c r="H22" s="1">
-        <f t="shared" si="2"/>
-        <v>26306.28</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>17</v>
@@ -2491,29 +4580,17 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1">
-        <v>19</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6">
-        <v>46204</v>
-      </c>
-      <c r="F23" s="1">
-        <v>8.5585</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1700</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
       <c r="H23" s="1">
-        <f t="shared" si="2"/>
-        <v>14549.45</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>17</v>
@@ -2522,7 +4599,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="4"/>
@@ -2531,7 +4608,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I24" s="4" t="s">
@@ -2541,7 +4618,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="4"/>
@@ -2550,7 +4627,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I25" s="4" t="s">
@@ -2560,7 +4637,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="4"/>
@@ -2569,7 +4646,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I26" s="4" t="s">
@@ -2579,7 +4656,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="4"/>
@@ -2588,7 +4665,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I27" s="4" t="s">
@@ -2598,7 +4675,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="4"/>
@@ -2607,7 +4684,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I28" s="4" t="s">
@@ -2617,7 +4694,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="4"/>
@@ -2626,7 +4703,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I29" s="4" t="s">
@@ -2636,7 +4713,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="4"/>
@@ -2645,7 +4722,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -2655,7 +4732,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4"/>
@@ -2664,7 +4741,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I31" s="4" t="s">
@@ -2674,7 +4751,7 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="4"/>
@@ -2683,7 +4760,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
@@ -2693,7 +4770,7 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="4"/>
@@ -2702,7 +4779,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I33" s="4" t="s">
@@ -2712,7 +4789,7 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4"/>
@@ -2721,7 +4798,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I34" s="4" t="s">
@@ -2731,7 +4808,7 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="4"/>
@@ -2740,7 +4817,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I35" s="4" t="s">
@@ -2750,7 +4827,7 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="4"/>
@@ -2759,7 +4836,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I36" s="4" t="s">
@@ -2769,7 +4846,7 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="4"/>
@@ -2778,7 +4855,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I37" s="4" t="s">
@@ -2788,7 +4865,7 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="4"/>
@@ -2797,7 +4874,7 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I38" s="4" t="s">
@@ -2807,7 +4884,7 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="4"/>
@@ -2816,7 +4893,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I39" s="4" t="s">
@@ -2826,7 +4903,7 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="4"/>
@@ -2835,7 +4912,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I40" s="4" t="s">
@@ -2845,7 +4922,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="4"/>
@@ -2854,7 +4931,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I41" s="4" t="s">
@@ -2864,7 +4941,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="4"/>
@@ -2873,7 +4950,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I42" s="4" t="s">
@@ -2883,7 +4960,7 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4"/>
@@ -2892,7 +4969,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I43" s="4" t="s">
@@ -2902,7 +4979,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4"/>
@@ -2911,7 +4988,7 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I44" s="4" t="s">
@@ -2921,7 +4998,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="4"/>
@@ -2930,7 +5007,7 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I45" s="4" t="s">
@@ -2940,7 +5017,7 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="4"/>
@@ -2949,7 +5026,7 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I46" s="4" t="s">
@@ -2959,7 +5036,7 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="4"/>
@@ -2968,7 +5045,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I47" s="4" t="s">
@@ -2978,7 +5055,7 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="4"/>
@@ -2987,7 +5064,7 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I48" s="4" t="s">
@@ -2997,7 +5074,7 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4"/>
@@ -3006,7 +5083,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I49" s="4" t="s">
@@ -3016,7 +5093,7 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4"/>
@@ -3025,7 +5102,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I50" s="4" t="s">
@@ -3035,7 +5112,7 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4"/>
@@ -3044,7 +5121,7 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1">
-        <f t="shared" ref="H51:H82" si="3">F51*G51</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I51" s="4" t="s">
@@ -3054,7 +5131,7 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="4"/>
@@ -3063,7 +5140,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
@@ -3073,7 +5150,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="1">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="4"/>
@@ -3082,7 +5159,7 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I53" s="4" t="s">
@@ -3092,7 +5169,7 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4"/>
@@ -3101,7 +5178,7 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I54" s="4" t="s">
@@ -3111,7 +5188,7 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="1">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="4"/>
@@ -3120,7 +5197,7 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I55" s="4" t="s">
@@ -3130,7 +5207,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="1">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="4"/>
@@ -3139,7 +5216,7 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H56:H93" si="2">F56*G56</f>
         <v>0</v>
       </c>
       <c r="I56" s="4" t="s">
@@ -3149,7 +5226,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="4"/>
@@ -3158,7 +5235,7 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I57" s="4" t="s">
@@ -3168,7 +5245,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="4"/>
@@ -3177,7 +5254,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I58" s="4" t="s">
@@ -3187,7 +5264,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="1">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="4"/>
@@ -3196,7 +5273,7 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I59" s="4" t="s">
@@ -3206,7 +5283,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="1">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="4"/>
@@ -3215,7 +5292,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I60" s="4" t="s">
@@ -3225,7 +5302,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="1">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="4"/>
@@ -3234,7 +5311,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I61" s="4" t="s">
@@ -3244,7 +5321,7 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="1">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4"/>
@@ -3253,7 +5330,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
@@ -3263,7 +5340,7 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="1">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="4"/>
@@ -3272,7 +5349,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
@@ -3282,7 +5359,7 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="1">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4"/>
@@ -3291,7 +5368,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
@@ -3301,7 +5378,7 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="1">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4"/>
@@ -3310,7 +5387,7 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I65" s="4" t="s">
@@ -3320,7 +5397,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="1">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4"/>
@@ -3329,7 +5406,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I66" s="4" t="s">
@@ -3339,7 +5416,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="1">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="4"/>
@@ -3348,7 +5425,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
@@ -3358,7 +5435,7 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="1">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="4"/>
@@ -3367,7 +5444,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
@@ -3377,7 +5454,7 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="1">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4"/>
@@ -3386,7 +5463,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I69" s="4" t="s">
@@ -3396,7 +5473,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="1">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="4"/>
@@ -3405,7 +5482,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I70" s="4" t="s">
@@ -3415,7 +5492,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="1">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="4"/>
@@ -3424,7 +5501,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I71" s="4" t="s">
@@ -3434,7 +5511,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="1">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="4"/>
@@ -3443,7 +5520,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I72" s="4" t="s">
@@ -3453,7 +5530,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="1">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="4"/>
@@ -3462,7 +5539,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I73" s="4" t="s">
@@ -3472,7 +5549,7 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="1">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="4"/>
@@ -3481,7 +5558,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I74" s="4" t="s">
@@ -3491,7 +5568,7 @@
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="1">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="4"/>
@@ -3500,7 +5577,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
@@ -3510,7 +5587,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="1">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4"/>
@@ -3519,7 +5596,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
@@ -3529,7 +5606,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="1">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4"/>
@@ -3538,7 +5615,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
@@ -3548,7 +5625,7 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="1">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4"/>
@@ -3557,7 +5634,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
@@ -3567,7 +5644,7 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="1">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="4"/>
@@ -3576,7 +5653,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
@@ -3586,7 +5663,7 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="1">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="4"/>
@@ -3595,7 +5672,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
@@ -3605,7 +5682,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="1">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4"/>
@@ -3614,7 +5691,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I81" s="4" t="s">
@@ -3624,7 +5701,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="1">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="4"/>
@@ -3633,7 +5710,7 @@
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I82" s="4" t="s">
@@ -3643,7 +5720,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="1">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4"/>
@@ -3652,7 +5729,7 @@
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1">
-        <f t="shared" ref="H83:H103" si="4">F83*G83</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
@@ -3662,7 +5739,7 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="1">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="4"/>
@@ -3671,7 +5748,7 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
@@ -3681,7 +5758,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="1">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="4"/>
@@ -3690,7 +5767,7 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
@@ -3700,7 +5777,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="1">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="4"/>
@@ -3709,7 +5786,7 @@
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I86" s="4" t="s">
@@ -3719,7 +5796,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="1">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4"/>
@@ -3728,7 +5805,7 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I87" s="4" t="s">
@@ -3738,7 +5815,7 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="1">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="4"/>
@@ -3747,7 +5824,7 @@
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I88" s="4" t="s">
@@ -3757,7 +5834,7 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="1">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="4"/>
@@ -3766,7 +5843,7 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
@@ -3776,7 +5853,7 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="4"/>
@@ -3785,7 +5862,7 @@
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
@@ -3795,7 +5872,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="4"/>
@@ -3804,7 +5881,7 @@
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I91" s="4" t="s">
@@ -3814,7 +5891,7 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="4"/>
@@ -3823,7 +5900,7 @@
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I92" s="4" t="s">
@@ -3833,7 +5910,7 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="1">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4"/>
@@ -3842,7 +5919,7 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I93" s="4" t="s">
@@ -3850,213 +5927,13 @@
       </c>
       <c r="J93" s="13"/>
     </row>
-    <row r="94" spans="1:10">
-      <c r="A94" s="1">
-        <v>90</v>
-      </c>
-      <c r="B94" s="1"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="13"/>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="A95" s="1">
-        <v>91</v>
-      </c>
-      <c r="B95" s="1"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="13"/>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="A96" s="1">
-        <v>92</v>
-      </c>
-      <c r="B96" s="1"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="13"/>
-    </row>
-    <row r="97" spans="1:10">
-      <c r="A97" s="1">
-        <v>93</v>
-      </c>
-      <c r="B97" s="1"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="13"/>
-    </row>
-    <row r="98" spans="1:10">
-      <c r="A98" s="1">
-        <v>94</v>
-      </c>
-      <c r="B98" s="1"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I98" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="13"/>
-    </row>
-    <row r="99" spans="1:10">
-      <c r="A99" s="1">
-        <v>95</v>
-      </c>
-      <c r="B99" s="1"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I99" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="13"/>
-    </row>
-    <row r="100" spans="1:10">
-      <c r="A100" s="1">
-        <v>96</v>
-      </c>
-      <c r="B100" s="1"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="13"/>
-    </row>
-    <row r="101" spans="1:10">
-      <c r="A101" s="1">
-        <v>97</v>
-      </c>
-      <c r="B101" s="1"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I101" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="13"/>
-    </row>
-    <row r="102" spans="1:10">
-      <c r="A102" s="1">
-        <v>98</v>
-      </c>
-      <c r="B102" s="1"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I102" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" s="13"/>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" s="1">
-        <v>99</v>
-      </c>
-      <c r="B103" s="1"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" s="13"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I103" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I93" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="8">
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J13:J15"/>
-  </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
-      <formula1>$I$2:$I$20</formula1>
+      <formula1>$I$2:$I$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4064,13 +5941,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.375"/>
+    <col min="4" max="4" width="9" style="3"/>
     <col min="8" max="8" width="22.125" customWidth="1"/>
     <col min="9" max="9" width="11.875" style="3" customWidth="1"/>
     <col min="11" max="11" width="10.875" customWidth="1"/>
@@ -4081,40 +5959,40 @@
         <v>7</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="5" t="s">
         <v>58</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="E1" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4124,10 +6002,10 @@
       <c r="B2" s="6">
         <v>46188</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="5">
@@ -4140,7 +6018,7 @@
         <v>5.17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -4171,7 +6049,7 @@
       <c r="C3" s="5">
         <v>600172</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E3" s="5">
@@ -4184,7 +6062,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -4209,7 +6087,7 @@
       <c r="C4" s="1">
         <v>601066</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E4" s="5">
@@ -4222,7 +6100,7 @@
         <v>31</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I4" s="1">
         <v>111.25</v>
@@ -4247,7 +6125,7 @@
       <c r="C5" s="5">
         <v>600360</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E5" s="5">
@@ -4260,7 +6138,7 @@
         <v>17.59</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="5">
@@ -4279,7 +6157,7 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="1"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -4299,7 +6177,7 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="D7" s="1"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -4319,7 +6197,7 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="D8" s="1"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -4339,7 +6217,7 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="D9" s="1"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -4355,11 +6233,11 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -4374,7 +6252,7 @@
       <c r="M10" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D5" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="3">
@@ -4387,7 +6265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E14"/>
@@ -4407,17 +6285,17 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="37" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -4427,7 +6305,7 @@
         <v>5.13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4438,7 +6316,7 @@
         <v>601398</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D3" s="3">
         <v>7.16</v>

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
@@ -14,9 +14,9 @@
     <sheet name="自选股" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">定投股票!$B$1:$I$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已出售!$C$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已出售!$C$1:$D$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="77">
   <si>
     <t>时间</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>6.30购入1800股卖出1300</t>
+  </si>
+  <si>
+    <t>6.16购入800股，卖出600股</t>
   </si>
   <si>
     <t>总盈亏</t>
@@ -944,7 +947,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -975,6 +978,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1002,9 +1008,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1020,9 +1023,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1035,23 +1047,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1585,12 +1591,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="1"/>
-    <col min="2" max="2" width="8.875" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="6" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="10.3727272727273" customWidth="1"/>
+    <col min="2" max="2" width="8.87272727272727" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="6" width="8.87272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1806,21 +1812,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K107"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="9.375" style="3"/>
-    <col min="3" max="3" width="9" style="10"/>
+    <col min="2" max="2" width="9.37272727272727" style="3"/>
+    <col min="3" max="3" width="9" style="11"/>
     <col min="4" max="4" width="9" style="3"/>
-    <col min="5" max="5" width="12.875" style="19" customWidth="1"/>
-    <col min="6" max="8" width="12.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="10"/>
-    <col min="10" max="10" width="68.625" style="11" customWidth="1"/>
+    <col min="5" max="8" width="12.8727272727273" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9" style="11"/>
+    <col min="10" max="10" width="68.6272727272727" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" spans="1:11">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="11" customFormat="1" ht="28" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -1847,7 +1852,7 @@
       <c r="I1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="14" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1880,10 +1885,10 @@
       <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="10"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
@@ -1914,40 +1919,40 @@
       <c r="I3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="15">
+      <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="16">
         <v>1</v>
       </c>
       <c r="E4" s="22">
         <v>46182</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="16">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="16">
         <v>4300</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="16">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="19"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
@@ -1978,7 +1983,7 @@
       <c r="I5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="14" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2011,7 +2016,7 @@
       <c r="I6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="14" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2019,7 +2024,7 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -2044,7 +2049,7 @@
       <c r="I7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2077,7 +2082,7 @@
       <c r="I8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2104,13 +2109,13 @@
         <v>900</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" ref="H9:H18" si="1">F9*G9</f>
+        <f>F9*G9</f>
         <v>18619.92</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="14" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2137,7 +2142,7 @@
         <v>600</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="1"/>
+        <f>F10*G10</f>
         <v>12637.14</v>
       </c>
       <c r="I10" s="4" t="s">
@@ -2164,7 +2169,7 @@
         <v>600</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="1"/>
+        <f>F11*G11</f>
         <v>5100</v>
       </c>
       <c r="I11" s="4" t="s">
@@ -2173,47 +2178,39 @@
       <c r="J11" s="24"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="21">
+        <v>46226</v>
+      </c>
+      <c r="F12" s="1">
+        <v>9</v>
+      </c>
+      <c r="G12" s="1">
+        <v>600</v>
+      </c>
+      <c r="H12" s="1">
+        <f>F12*G12</f>
+        <v>5400</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="25"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B13" s="1">
         <v>600879</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="21">
-        <v>46182</v>
-      </c>
-      <c r="F12" s="1">
-        <v>26.2661</v>
-      </c>
-      <c r="G12" s="1">
-        <v>700</v>
-      </c>
-      <c r="H12" s="1">
-        <f t="shared" si="1"/>
-        <v>18386.27</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="7">
-        <v>11</v>
-      </c>
-      <c r="B13" s="7">
-        <v>601066</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -2222,420 +2219,446 @@
         <v>46182</v>
       </c>
       <c r="F13" s="1">
+        <v>26.2661</v>
+      </c>
+      <c r="G13" s="1">
+        <v>700</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" ref="H13:H25" si="1">F13*G13</f>
+        <v>18386.27</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="26">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7">
+        <v>601066</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F14" s="1">
         <v>27.6302</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G14" s="1">
         <v>3400</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H14" s="1">
         <f t="shared" si="1"/>
         <v>93942.68</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="25" t="s">
+      <c r="I14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="26">
+    <row r="15" spans="1:11">
+      <c r="A15" s="28"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="29">
         <v>2</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E15" s="30">
         <v>46192</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F15" s="29">
         <v>31</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G15" s="29">
         <v>-2400</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H15" s="29">
         <f t="shared" si="1"/>
         <v>-74400</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I15" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="29"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="1">
+      <c r="J15" s="32"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="33"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="1">
         <v>3</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E16" s="21">
         <v>46202</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F16" s="1">
         <v>29.3</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G16" s="1">
         <v>1000</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H16" s="1">
         <f t="shared" si="1"/>
         <v>29300</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="24"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="1">
+      <c r="I16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="24"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B17" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D17" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E17" s="21">
         <v>46182</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F17" s="1">
         <v>18.3681</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G17" s="1">
         <v>1000</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H17" s="1">
         <f t="shared" si="1"/>
         <v>18368.1</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="13" t="s">
+      <c r="I17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="1">
+    <row r="18" spans="1:10">
+      <c r="A18" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B18" s="1">
         <v>300589</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E18" s="21">
         <v>46182</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F18" s="1">
         <v>22.8225</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G18" s="1">
         <v>1200</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H18" s="1">
         <f t="shared" si="1"/>
         <v>27387</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="13" t="s">
+      <c r="I18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="30">
+    <row r="19" spans="1:10">
+      <c r="A19" s="26">
         <v>14</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B19" s="7">
         <v>300129</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E19" s="21">
         <v>46182</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F19" s="1">
         <v>14.9016</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G19" s="1">
         <v>2300</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H19" s="1">
         <f t="shared" si="1"/>
         <v>34273.68</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="13" t="s">
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="1">
+    <row r="20" spans="1:10">
+      <c r="A20" s="34"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="1">
         <v>2</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E20" s="21">
         <v>46223</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F20" s="1">
         <v>7.35</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G20" s="1">
         <v>700</v>
       </c>
-      <c r="H19" s="1">
-        <f>F19*G19</f>
+      <c r="H20" s="1">
+        <f t="shared" si="1"/>
         <v>5145</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="13"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="26">
+      <c r="I20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="29">
         <v>15</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B21" s="29">
         <v>600172</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C21" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D21" s="29">
         <v>1</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E21" s="30">
         <v>46188</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F21" s="29">
         <v>12.2123</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G21" s="29">
         <v>600</v>
       </c>
-      <c r="H20" s="26">
-        <f t="shared" ref="H20:H51" si="2">F20*G20</f>
+      <c r="H21" s="29">
+        <f t="shared" si="1"/>
         <v>7327.38</v>
       </c>
-      <c r="I20" s="16" t="s">
+      <c r="I21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J20" s="33" t="s">
+      <c r="J21" s="36" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="1">
-        <v>16</v>
-      </c>
-      <c r="B21" s="1">
-        <v>600745</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="34">
-        <v>46189</v>
-      </c>
-      <c r="F21" s="1">
-        <v>18.6687</v>
-      </c>
-      <c r="G21" s="1">
-        <v>800</v>
-      </c>
-      <c r="H21" s="1">
-        <f t="shared" si="2"/>
-        <v>14934.96</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1">
-        <v>17</v>
-      </c>
-      <c r="B22">
-        <v>600115</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
+        <v>16</v>
+      </c>
+      <c r="B22" s="1">
+        <v>600745</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
-      <c r="E22" s="34">
-        <v>46203</v>
+      <c r="E22" s="21">
+        <v>46189</v>
       </c>
       <c r="F22" s="1">
-        <v>3.7838</v>
+        <v>18.6687</v>
       </c>
       <c r="G22" s="1">
-        <v>3200</v>
+        <v>800</v>
       </c>
       <c r="H22" s="1">
-        <f t="shared" si="2"/>
-        <v>12108.16</v>
+        <f t="shared" si="1"/>
+        <v>14934.96</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="13"/>
+      <c r="J22" s="14" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1">
-        <v>18</v>
-      </c>
-      <c r="B23" s="1">
-        <v>600360</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>53</v>
+        <v>17</v>
+      </c>
+      <c r="B23">
+        <v>600115</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="21">
         <v>46203</v>
       </c>
       <c r="F23" s="1">
-        <v>14.6146</v>
+        <v>3.7838</v>
       </c>
       <c r="G23" s="1">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="2"/>
-        <v>26306.28</v>
+        <f t="shared" si="1"/>
+        <v>12108.16</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J23" s="13"/>
+      <c r="J23" s="14"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="1">
-        <v>19</v>
-      </c>
-      <c r="B24" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>55</v>
+      <c r="A24" s="26">
+        <v>18</v>
+      </c>
+      <c r="B24" s="7">
+        <v>600360</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
-      <c r="E24" s="34">
-        <v>46204</v>
+      <c r="E24" s="21">
+        <v>46203</v>
       </c>
       <c r="F24" s="1">
-        <v>8.5585</v>
+        <v>14.6146</v>
       </c>
       <c r="G24" s="1">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="2"/>
-        <v>14549.45</v>
+        <f t="shared" si="1"/>
+        <v>26306.28</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J24" s="13"/>
+      <c r="J24" s="14"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="1">
-        <v>20</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="6">
+        <v>46213</v>
+      </c>
+      <c r="F25" s="5">
+        <v>17.59</v>
+      </c>
+      <c r="G25" s="1">
+        <v>-1300</v>
+      </c>
       <c r="H25" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>-22867</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="J25" s="14"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="1">
-        <v>21</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="21">
+        <v>46226</v>
+      </c>
+      <c r="F26" s="1">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1">
+        <v>500</v>
+      </c>
       <c r="H26" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>F26*G26</f>
+        <v>5000</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="13"/>
+      <c r="J26" s="14"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1">
-        <v>22</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="21">
+        <v>46204</v>
+      </c>
+      <c r="F27" s="1">
+        <v>8.5585</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1700</v>
+      </c>
       <c r="H27" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" ref="H27:H54" si="2">F27*G27</f>
+        <v>14549.45</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="13"/>
+      <c r="J27" s="14"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="4"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="35"/>
+      <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1">
@@ -2645,16 +2668,16 @@
       <c r="I28" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J28" s="13"/>
+      <c r="J28" s="14"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="4"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="35"/>
+      <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1">
@@ -2664,16 +2687,16 @@
       <c r="I29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="13"/>
+      <c r="J29" s="14"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="4"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="35"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1">
@@ -2683,16 +2706,16 @@
       <c r="I30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J30" s="13"/>
+      <c r="J30" s="14"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="4"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="35"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1">
@@ -2702,16 +2725,16 @@
       <c r="I31" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="13"/>
+      <c r="J31" s="14"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="4"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="35"/>
+      <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1">
@@ -2721,16 +2744,16 @@
       <c r="I32" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="13"/>
+      <c r="J32" s="14"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="4"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="35"/>
+      <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1">
@@ -2740,16 +2763,16 @@
       <c r="I33" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="13"/>
+      <c r="J33" s="14"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="35"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1">
@@ -2759,16 +2782,16 @@
       <c r="I34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J34" s="13"/>
+      <c r="J34" s="14"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="4"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="35"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1">
@@ -2778,16 +2801,16 @@
       <c r="I35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="13"/>
+      <c r="J35" s="14"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="4"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="35"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1">
@@ -2797,16 +2820,16 @@
       <c r="I36" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="13"/>
+      <c r="J36" s="14"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="4"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="35"/>
+      <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1">
@@ -2816,16 +2839,16 @@
       <c r="I37" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="13"/>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="4"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="35"/>
+      <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1">
@@ -2835,16 +2858,16 @@
       <c r="I38" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J38" s="13"/>
+      <c r="J38" s="14"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="4"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="35"/>
+      <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
@@ -2854,16 +2877,16 @@
       <c r="I39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J39" s="13"/>
+      <c r="J39" s="14"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="4"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="35"/>
+      <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1">
@@ -2873,16 +2896,16 @@
       <c r="I40" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="13"/>
+      <c r="J40" s="14"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="4"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="35"/>
+      <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1">
@@ -2892,16 +2915,16 @@
       <c r="I41" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J41" s="13"/>
+      <c r="J41" s="14"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="4"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="35"/>
+      <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1">
@@ -2911,16 +2934,16 @@
       <c r="I42" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="13"/>
+      <c r="J42" s="14"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="35"/>
+      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1">
@@ -2930,16 +2953,16 @@
       <c r="I43" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J43" s="13"/>
+      <c r="J43" s="14"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="35"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1">
@@ -2949,16 +2972,16 @@
       <c r="I44" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="13"/>
+      <c r="J44" s="14"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="4"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="35"/>
+      <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1">
@@ -2968,16 +2991,16 @@
       <c r="I45" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="13"/>
+      <c r="J45" s="14"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="4"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="35"/>
+      <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1">
@@ -2987,16 +3010,16 @@
       <c r="I46" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J46" s="13"/>
+      <c r="J46" s="14"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="4"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="35"/>
+      <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1">
@@ -3006,16 +3029,16 @@
       <c r="I47" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="13"/>
+      <c r="J47" s="14"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="4"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="35"/>
+      <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1">
@@ -3025,16 +3048,16 @@
       <c r="I48" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J48" s="13"/>
+      <c r="J48" s="14"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="35"/>
+      <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1">
@@ -3044,16 +3067,16 @@
       <c r="I49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J49" s="13"/>
+      <c r="J49" s="14"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="35"/>
+      <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1">
@@ -3063,16 +3086,16 @@
       <c r="I50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J50" s="13"/>
+      <c r="J50" s="14"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="35"/>
+      <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1">
@@ -3082,92 +3105,92 @@
       <c r="I51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="13"/>
+      <c r="J51" s="14"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="4"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="35"/>
+      <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1">
-        <f t="shared" ref="H52:H83" si="3">F52*G52</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J52" s="13"/>
+      <c r="J52" s="14"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="1">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="4"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="35"/>
+      <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J53" s="13"/>
+      <c r="J53" s="14"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="35"/>
+      <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J54" s="13"/>
+      <c r="J54" s="14"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="1">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="4"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="35"/>
+      <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H55:H86" si="3">F55*G55</f>
         <v>0</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J55" s="13"/>
+      <c r="J55" s="14"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="4"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="35"/>
+      <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1">
@@ -3177,16 +3200,16 @@
       <c r="I56" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="13"/>
+      <c r="J56" s="14"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="4"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="35"/>
+      <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1">
@@ -3196,16 +3219,16 @@
       <c r="I57" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J57" s="13"/>
+      <c r="J57" s="14"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="4"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="35"/>
+      <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1">
@@ -3215,16 +3238,16 @@
       <c r="I58" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="13"/>
+      <c r="J58" s="14"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="1">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="4"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="35"/>
+      <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1">
@@ -3234,16 +3257,16 @@
       <c r="I59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J59" s="13"/>
+      <c r="J59" s="14"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="1">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="4"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="35"/>
+      <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1">
@@ -3253,16 +3276,16 @@
       <c r="I60" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J60" s="13"/>
+      <c r="J60" s="14"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="1">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="4"/>
       <c r="D61" s="1"/>
-      <c r="E61" s="35"/>
+      <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1">
@@ -3272,16 +3295,16 @@
       <c r="I61" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J61" s="13"/>
+      <c r="J61" s="14"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="1">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4"/>
       <c r="D62" s="1"/>
-      <c r="E62" s="35"/>
+      <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1">
@@ -3291,16 +3314,16 @@
       <c r="I62" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J62" s="13"/>
+      <c r="J62" s="14"/>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="1">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="4"/>
       <c r="D63" s="1"/>
-      <c r="E63" s="35"/>
+      <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1">
@@ -3310,16 +3333,16 @@
       <c r="I63" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J63" s="13"/>
+      <c r="J63" s="14"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="1">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4"/>
       <c r="D64" s="1"/>
-      <c r="E64" s="35"/>
+      <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1">
@@ -3329,16 +3352,16 @@
       <c r="I64" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J64" s="13"/>
+      <c r="J64" s="14"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="1">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4"/>
       <c r="D65" s="1"/>
-      <c r="E65" s="35"/>
+      <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1">
@@ -3348,16 +3371,16 @@
       <c r="I65" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="13"/>
+      <c r="J65" s="14"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="1">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4"/>
       <c r="D66" s="1"/>
-      <c r="E66" s="35"/>
+      <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1">
@@ -3367,16 +3390,16 @@
       <c r="I66" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J66" s="13"/>
+      <c r="J66" s="14"/>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="1">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="4"/>
       <c r="D67" s="1"/>
-      <c r="E67" s="35"/>
+      <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1">
@@ -3386,16 +3409,16 @@
       <c r="I67" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J67" s="13"/>
+      <c r="J67" s="14"/>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="1">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="4"/>
       <c r="D68" s="1"/>
-      <c r="E68" s="35"/>
+      <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1">
@@ -3405,16 +3428,16 @@
       <c r="I68" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J68" s="13"/>
+      <c r="J68" s="14"/>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="1">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4"/>
       <c r="D69" s="1"/>
-      <c r="E69" s="35"/>
+      <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1">
@@ -3424,16 +3447,16 @@
       <c r="I69" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J69" s="13"/>
+      <c r="J69" s="14"/>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="1">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="4"/>
       <c r="D70" s="1"/>
-      <c r="E70" s="35"/>
+      <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1">
@@ -3443,16 +3466,16 @@
       <c r="I70" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J70" s="13"/>
+      <c r="J70" s="14"/>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="1">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="4"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="35"/>
+      <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1">
@@ -3462,16 +3485,16 @@
       <c r="I71" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J71" s="13"/>
+      <c r="J71" s="14"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="1">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="4"/>
       <c r="D72" s="1"/>
-      <c r="E72" s="35"/>
+      <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1">
@@ -3481,16 +3504,16 @@
       <c r="I72" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J72" s="13"/>
+      <c r="J72" s="14"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="1">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="4"/>
       <c r="D73" s="1"/>
-      <c r="E73" s="35"/>
+      <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1">
@@ -3500,16 +3523,16 @@
       <c r="I73" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J73" s="13"/>
+      <c r="J73" s="14"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="1">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="4"/>
       <c r="D74" s="1"/>
-      <c r="E74" s="35"/>
+      <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1">
@@ -3519,16 +3542,16 @@
       <c r="I74" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J74" s="13"/>
+      <c r="J74" s="14"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="1">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="4"/>
       <c r="D75" s="1"/>
-      <c r="E75" s="35"/>
+      <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1">
@@ -3538,16 +3561,16 @@
       <c r="I75" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J75" s="13"/>
+      <c r="J75" s="14"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="1">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4"/>
       <c r="D76" s="1"/>
-      <c r="E76" s="35"/>
+      <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1">
@@ -3557,16 +3580,16 @@
       <c r="I76" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J76" s="13"/>
+      <c r="J76" s="14"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="1">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4"/>
       <c r="D77" s="1"/>
-      <c r="E77" s="35"/>
+      <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1">
@@ -3576,16 +3599,16 @@
       <c r="I77" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J77" s="13"/>
+      <c r="J77" s="14"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="1">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4"/>
       <c r="D78" s="1"/>
-      <c r="E78" s="35"/>
+      <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1">
@@ -3595,16 +3618,16 @@
       <c r="I78" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J78" s="13"/>
+      <c r="J78" s="14"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="1">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="4"/>
       <c r="D79" s="1"/>
-      <c r="E79" s="35"/>
+      <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1">
@@ -3614,16 +3637,16 @@
       <c r="I79" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J79" s="13"/>
+      <c r="J79" s="14"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="1">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="4"/>
       <c r="D80" s="1"/>
-      <c r="E80" s="35"/>
+      <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1">
@@ -3633,16 +3656,16 @@
       <c r="I80" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J80" s="13"/>
+      <c r="J80" s="14"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="1">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4"/>
       <c r="D81" s="1"/>
-      <c r="E81" s="35"/>
+      <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1">
@@ -3652,16 +3675,16 @@
       <c r="I81" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J81" s="13"/>
+      <c r="J81" s="14"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="1">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="4"/>
       <c r="D82" s="1"/>
-      <c r="E82" s="35"/>
+      <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1">
@@ -3671,16 +3694,16 @@
       <c r="I82" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J82" s="13"/>
+      <c r="J82" s="14"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="1">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4"/>
       <c r="D83" s="1"/>
-      <c r="E83" s="35"/>
+      <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1">
@@ -3690,92 +3713,92 @@
       <c r="I83" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J83" s="13"/>
+      <c r="J83" s="14"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="1">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="4"/>
       <c r="D84" s="1"/>
-      <c r="E84" s="35"/>
+      <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1">
-        <f t="shared" ref="H84:H104" si="4">F84*G84</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J84" s="13"/>
+      <c r="J84" s="14"/>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="1">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="4"/>
       <c r="D85" s="1"/>
-      <c r="E85" s="35"/>
+      <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J85" s="13"/>
+      <c r="J85" s="14"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="1">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="4"/>
       <c r="D86" s="1"/>
-      <c r="E86" s="35"/>
+      <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J86" s="13"/>
+      <c r="J86" s="14"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="1">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4"/>
       <c r="D87" s="1"/>
-      <c r="E87" s="35"/>
+      <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H87:H107" si="4">F87*G87</f>
         <v>0</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J87" s="13"/>
+      <c r="J87" s="14"/>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="1">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="4"/>
       <c r="D88" s="1"/>
-      <c r="E88" s="35"/>
+      <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1">
@@ -3785,16 +3808,16 @@
       <c r="I88" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J88" s="13"/>
+      <c r="J88" s="14"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="1">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="4"/>
       <c r="D89" s="1"/>
-      <c r="E89" s="35"/>
+      <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1">
@@ -3804,16 +3827,16 @@
       <c r="I89" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J89" s="13"/>
+      <c r="J89" s="14"/>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="4"/>
       <c r="D90" s="1"/>
-      <c r="E90" s="35"/>
+      <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1">
@@ -3823,16 +3846,16 @@
       <c r="I90" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J90" s="13"/>
+      <c r="J90" s="14"/>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="4"/>
       <c r="D91" s="1"/>
-      <c r="E91" s="35"/>
+      <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1">
@@ -3842,16 +3865,16 @@
       <c r="I91" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J91" s="13"/>
+      <c r="J91" s="14"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="4"/>
       <c r="D92" s="1"/>
-      <c r="E92" s="35"/>
+      <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1">
@@ -3861,16 +3884,16 @@
       <c r="I92" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J92" s="13"/>
+      <c r="J92" s="14"/>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4"/>
       <c r="D93" s="1"/>
-      <c r="E93" s="35"/>
+      <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1">
@@ -3880,16 +3903,16 @@
       <c r="I93" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J93" s="13"/>
+      <c r="J93" s="14"/>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="1">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="4"/>
       <c r="D94" s="1"/>
-      <c r="E94" s="35"/>
+      <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1">
@@ -3899,16 +3922,16 @@
       <c r="I94" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J94" s="13"/>
+      <c r="J94" s="14"/>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="1">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="4"/>
       <c r="D95" s="1"/>
-      <c r="E95" s="35"/>
+      <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1">
@@ -3918,16 +3941,16 @@
       <c r="I95" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J95" s="13"/>
+      <c r="J95" s="14"/>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="1">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4"/>
       <c r="D96" s="1"/>
-      <c r="E96" s="35"/>
+      <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1">
@@ -3937,16 +3960,16 @@
       <c r="I96" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J96" s="13"/>
+      <c r="J96" s="14"/>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="1">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4"/>
       <c r="D97" s="1"/>
-      <c r="E97" s="35"/>
+      <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1">
@@ -3956,16 +3979,16 @@
       <c r="I97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J97" s="13"/>
+      <c r="J97" s="14"/>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="1">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="4"/>
       <c r="D98" s="1"/>
-      <c r="E98" s="35"/>
+      <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1">
@@ -3975,16 +3998,16 @@
       <c r="I98" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J98" s="13"/>
+      <c r="J98" s="14"/>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="4"/>
       <c r="D99" s="1"/>
-      <c r="E99" s="35"/>
+      <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1">
@@ -3994,16 +4017,16 @@
       <c r="I99" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J99" s="13"/>
+      <c r="J99" s="14"/>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="1">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="4"/>
       <c r="D100" s="1"/>
-      <c r="E100" s="35"/>
+      <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1">
@@ -4013,16 +4036,16 @@
       <c r="I100" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J100" s="13"/>
+      <c r="J100" s="14"/>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4"/>
       <c r="D101" s="1"/>
-      <c r="E101" s="35"/>
+      <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1">
@@ -4032,16 +4055,16 @@
       <c r="I101" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J101" s="13"/>
+      <c r="J101" s="14"/>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="1">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="4"/>
       <c r="D102" s="1"/>
-      <c r="E102" s="35"/>
+      <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
       <c r="H102" s="1">
@@ -4051,16 +4074,16 @@
       <c r="I102" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J102" s="13"/>
+      <c r="J102" s="14"/>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="1">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4"/>
       <c r="D103" s="1"/>
-      <c r="E103" s="35"/>
+      <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
       <c r="H103" s="1">
@@ -4070,16 +4093,16 @@
       <c r="I103" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J103" s="13"/>
+      <c r="J103" s="14"/>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="1">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="4"/>
       <c r="D104" s="1"/>
-      <c r="E104" s="35"/>
+      <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
       <c r="H104" s="1">
@@ -4089,28 +4112,88 @@
       <c r="I104" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J104" s="13"/>
+      <c r="J104" s="14"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="1">
+        <v>97</v>
+      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="14"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="1">
+        <v>98</v>
+      </c>
+      <c r="B106" s="1"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="14"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="1">
+        <v>99</v>
+      </c>
+      <c r="B107" s="1"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="14"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I104" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I107" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A24:A26"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B24:B26"/>
     <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C24:C26"/>
     <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="J14:J16"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I19 I1:I18 I20:I1048576">
-      <formula1>$I$2:$I$21</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I12 I1:I11 I13:I1048576">
+      <formula1>$I$2:$I$22</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4122,19 +4205,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K93"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="9.375" style="3"/>
-    <col min="3" max="3" width="9" style="10"/>
+    <col min="2" max="2" width="9.37272727272727" style="3"/>
+    <col min="3" max="3" width="9" style="11"/>
     <col min="4" max="4" width="9" style="3"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="8" width="12.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="10"/>
-    <col min="10" max="10" width="68.625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="12.8727272727273" customWidth="1"/>
+    <col min="6" max="8" width="12.8727272727273" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9" style="11"/>
+    <col min="10" max="10" width="68.6272727272727" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" spans="1:11">
+    <row r="1" s="11" customFormat="1" ht="28" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4147,22 +4230,22 @@
       <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="14" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4179,7 +4262,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="15">
         <v>46182</v>
       </c>
       <c r="F2" s="1">
@@ -4195,8 +4278,8 @@
       <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="10"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
@@ -4205,7 +4288,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="14"/>
+      <c r="E3" s="15"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1">
@@ -4215,18 +4298,18 @@
       <c r="I3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="13"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
       <c r="H4" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4234,7 +4317,7 @@
       <c r="I4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="19"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
@@ -4243,7 +4326,7 @@
       <c r="B5" s="1"/>
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="14"/>
+      <c r="E5" s="15"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1">
@@ -4253,7 +4336,7 @@
       <c r="I5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="13"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
@@ -4262,7 +4345,7 @@
       <c r="B6" s="1"/>
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="14"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
@@ -4272,7 +4355,7 @@
       <c r="I6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="13"/>
+      <c r="J6" s="14"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
@@ -4281,7 +4364,7 @@
       <c r="B7" s="1"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="14"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1">
@@ -4291,7 +4374,7 @@
       <c r="I7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="13"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
@@ -4300,7 +4383,7 @@
       <c r="B8" s="1"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="14"/>
+      <c r="E8" s="15"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1">
@@ -4310,7 +4393,7 @@
       <c r="I8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="13"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
@@ -4319,7 +4402,7 @@
       <c r="B9" s="1"/>
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="14"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1">
@@ -4329,7 +4412,7 @@
       <c r="I9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="13"/>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
@@ -4348,7 +4431,7 @@
       <c r="I10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="13"/>
+      <c r="J10" s="14"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
@@ -4367,7 +4450,7 @@
       <c r="I11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="13"/>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
@@ -4386,7 +4469,7 @@
       <c r="I12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="13"/>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
@@ -4405,7 +4488,7 @@
       <c r="I13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="13"/>
+      <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
@@ -4424,7 +4507,7 @@
       <c r="I14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="13"/>
+      <c r="J14" s="14"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
@@ -4443,7 +4526,7 @@
       <c r="I15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="13"/>
+      <c r="J15" s="14"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
@@ -4462,7 +4545,7 @@
       <c r="I16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="13"/>
+      <c r="J16" s="14"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1">
@@ -4481,7 +4564,7 @@
       <c r="I17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="13"/>
+      <c r="J17" s="14"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1">
@@ -4500,7 +4583,7 @@
       <c r="I18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="13"/>
+      <c r="J18" s="14"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1">
@@ -4519,7 +4602,7 @@
       <c r="I19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="13"/>
+      <c r="J19" s="14"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1">
@@ -4538,7 +4621,7 @@
       <c r="I20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J20" s="13"/>
+      <c r="J20" s="14"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1">
@@ -4557,7 +4640,7 @@
       <c r="I21" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J21" s="13"/>
+      <c r="J21" s="14"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1">
@@ -4576,7 +4659,7 @@
       <c r="I22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="13"/>
+      <c r="J22" s="14"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1">
@@ -4595,7 +4678,7 @@
       <c r="I23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J23" s="13"/>
+      <c r="J23" s="14"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="1">
@@ -4614,7 +4697,7 @@
       <c r="I24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J24" s="13"/>
+      <c r="J24" s="14"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1">
@@ -4633,7 +4716,7 @@
       <c r="I25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J25" s="13"/>
+      <c r="J25" s="14"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="1">
@@ -4652,7 +4735,7 @@
       <c r="I26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="13"/>
+      <c r="J26" s="14"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1">
@@ -4671,7 +4754,7 @@
       <c r="I27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="13"/>
+      <c r="J27" s="14"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1">
@@ -4690,7 +4773,7 @@
       <c r="I28" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J28" s="13"/>
+      <c r="J28" s="14"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1">
@@ -4709,7 +4792,7 @@
       <c r="I29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="13"/>
+      <c r="J29" s="14"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1">
@@ -4728,7 +4811,7 @@
       <c r="I30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J30" s="13"/>
+      <c r="J30" s="14"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1">
@@ -4747,7 +4830,7 @@
       <c r="I31" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="13"/>
+      <c r="J31" s="14"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1">
@@ -4766,7 +4849,7 @@
       <c r="I32" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="13"/>
+      <c r="J32" s="14"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1">
@@ -4785,7 +4868,7 @@
       <c r="I33" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="13"/>
+      <c r="J33" s="14"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1">
@@ -4804,7 +4887,7 @@
       <c r="I34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J34" s="13"/>
+      <c r="J34" s="14"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1">
@@ -4823,7 +4906,7 @@
       <c r="I35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="13"/>
+      <c r="J35" s="14"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1">
@@ -4842,7 +4925,7 @@
       <c r="I36" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="13"/>
+      <c r="J36" s="14"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1">
@@ -4861,7 +4944,7 @@
       <c r="I37" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="13"/>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1">
@@ -4880,7 +4963,7 @@
       <c r="I38" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J38" s="13"/>
+      <c r="J38" s="14"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1">
@@ -4899,7 +4982,7 @@
       <c r="I39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J39" s="13"/>
+      <c r="J39" s="14"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1">
@@ -4918,7 +5001,7 @@
       <c r="I40" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="13"/>
+      <c r="J40" s="14"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1">
@@ -4937,7 +5020,7 @@
       <c r="I41" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J41" s="13"/>
+      <c r="J41" s="14"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1">
@@ -4956,7 +5039,7 @@
       <c r="I42" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="13"/>
+      <c r="J42" s="14"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1">
@@ -4975,7 +5058,7 @@
       <c r="I43" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J43" s="13"/>
+      <c r="J43" s="14"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
@@ -4994,7 +5077,7 @@
       <c r="I44" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="13"/>
+      <c r="J44" s="14"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1">
@@ -5013,7 +5096,7 @@
       <c r="I45" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="13"/>
+      <c r="J45" s="14"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1">
@@ -5032,7 +5115,7 @@
       <c r="I46" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J46" s="13"/>
+      <c r="J46" s="14"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1">
@@ -5051,7 +5134,7 @@
       <c r="I47" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="13"/>
+      <c r="J47" s="14"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1">
@@ -5070,7 +5153,7 @@
       <c r="I48" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J48" s="13"/>
+      <c r="J48" s="14"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1">
@@ -5089,7 +5172,7 @@
       <c r="I49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J49" s="13"/>
+      <c r="J49" s="14"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1">
@@ -5108,7 +5191,7 @@
       <c r="I50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J50" s="13"/>
+      <c r="J50" s="14"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1">
@@ -5127,7 +5210,7 @@
       <c r="I51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="13"/>
+      <c r="J51" s="14"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1">
@@ -5146,7 +5229,7 @@
       <c r="I52" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J52" s="13"/>
+      <c r="J52" s="14"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="1">
@@ -5165,7 +5248,7 @@
       <c r="I53" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J53" s="13"/>
+      <c r="J53" s="14"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1">
@@ -5184,7 +5267,7 @@
       <c r="I54" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J54" s="13"/>
+      <c r="J54" s="14"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="1">
@@ -5203,7 +5286,7 @@
       <c r="I55" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J55" s="13"/>
+      <c r="J55" s="14"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="1">
@@ -5222,7 +5305,7 @@
       <c r="I56" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="13"/>
+      <c r="J56" s="14"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1">
@@ -5241,7 +5324,7 @@
       <c r="I57" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J57" s="13"/>
+      <c r="J57" s="14"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1">
@@ -5260,7 +5343,7 @@
       <c r="I58" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="13"/>
+      <c r="J58" s="14"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="1">
@@ -5279,7 +5362,7 @@
       <c r="I59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J59" s="13"/>
+      <c r="J59" s="14"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="1">
@@ -5298,7 +5381,7 @@
       <c r="I60" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J60" s="13"/>
+      <c r="J60" s="14"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="1">
@@ -5317,7 +5400,7 @@
       <c r="I61" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J61" s="13"/>
+      <c r="J61" s="14"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="1">
@@ -5336,7 +5419,7 @@
       <c r="I62" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J62" s="13"/>
+      <c r="J62" s="14"/>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="1">
@@ -5355,7 +5438,7 @@
       <c r="I63" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J63" s="13"/>
+      <c r="J63" s="14"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="1">
@@ -5374,7 +5457,7 @@
       <c r="I64" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J64" s="13"/>
+      <c r="J64" s="14"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="1">
@@ -5393,7 +5476,7 @@
       <c r="I65" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="13"/>
+      <c r="J65" s="14"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="1">
@@ -5412,7 +5495,7 @@
       <c r="I66" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J66" s="13"/>
+      <c r="J66" s="14"/>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="1">
@@ -5431,7 +5514,7 @@
       <c r="I67" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J67" s="13"/>
+      <c r="J67" s="14"/>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="1">
@@ -5450,7 +5533,7 @@
       <c r="I68" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J68" s="13"/>
+      <c r="J68" s="14"/>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="1">
@@ -5469,7 +5552,7 @@
       <c r="I69" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J69" s="13"/>
+      <c r="J69" s="14"/>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="1">
@@ -5488,7 +5571,7 @@
       <c r="I70" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J70" s="13"/>
+      <c r="J70" s="14"/>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="1">
@@ -5507,7 +5590,7 @@
       <c r="I71" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J71" s="13"/>
+      <c r="J71" s="14"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="1">
@@ -5526,7 +5609,7 @@
       <c r="I72" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J72" s="13"/>
+      <c r="J72" s="14"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="1">
@@ -5545,7 +5628,7 @@
       <c r="I73" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J73" s="13"/>
+      <c r="J73" s="14"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="1">
@@ -5564,7 +5647,7 @@
       <c r="I74" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J74" s="13"/>
+      <c r="J74" s="14"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="1">
@@ -5583,7 +5666,7 @@
       <c r="I75" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J75" s="13"/>
+      <c r="J75" s="14"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="1">
@@ -5602,7 +5685,7 @@
       <c r="I76" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J76" s="13"/>
+      <c r="J76" s="14"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="1">
@@ -5621,7 +5704,7 @@
       <c r="I77" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J77" s="13"/>
+      <c r="J77" s="14"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="1">
@@ -5640,7 +5723,7 @@
       <c r="I78" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J78" s="13"/>
+      <c r="J78" s="14"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="1">
@@ -5659,7 +5742,7 @@
       <c r="I79" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J79" s="13"/>
+      <c r="J79" s="14"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="1">
@@ -5678,7 +5761,7 @@
       <c r="I80" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J80" s="13"/>
+      <c r="J80" s="14"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="1">
@@ -5697,7 +5780,7 @@
       <c r="I81" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J81" s="13"/>
+      <c r="J81" s="14"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="1">
@@ -5716,7 +5799,7 @@
       <c r="I82" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J82" s="13"/>
+      <c r="J82" s="14"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="1">
@@ -5735,7 +5818,7 @@
       <c r="I83" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J83" s="13"/>
+      <c r="J83" s="14"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="1">
@@ -5754,7 +5837,7 @@
       <c r="I84" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J84" s="13"/>
+      <c r="J84" s="14"/>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="1">
@@ -5773,7 +5856,7 @@
       <c r="I85" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J85" s="13"/>
+      <c r="J85" s="14"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="1">
@@ -5792,7 +5875,7 @@
       <c r="I86" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J86" s="13"/>
+      <c r="J86" s="14"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="1">
@@ -5811,7 +5894,7 @@
       <c r="I87" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J87" s="13"/>
+      <c r="J87" s="14"/>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="1">
@@ -5830,7 +5913,7 @@
       <c r="I88" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J88" s="13"/>
+      <c r="J88" s="14"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="1">
@@ -5849,7 +5932,7 @@
       <c r="I89" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J89" s="13"/>
+      <c r="J89" s="14"/>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1">
@@ -5868,7 +5951,7 @@
       <c r="I90" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J90" s="13"/>
+      <c r="J90" s="14"/>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1">
@@ -5887,7 +5970,7 @@
       <c r="I91" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J91" s="13"/>
+      <c r="J91" s="14"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1">
@@ -5906,7 +5989,7 @@
       <c r="I92" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J92" s="13"/>
+      <c r="J92" s="14"/>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="1">
@@ -5925,7 +6008,7 @@
       <c r="I93" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J93" s="13"/>
+      <c r="J93" s="14"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I93" etc:filterBottomFollowUsedRange="0">
@@ -5945,13 +6028,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="10.375"/>
+    <col min="2" max="2" width="10.6363636363636"/>
     <col min="4" max="4" width="9" style="3"/>
-    <col min="8" max="8" width="22.125" customWidth="1"/>
-    <col min="9" max="9" width="11.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="22.1272727272727" customWidth="1"/>
+    <col min="9" max="9" width="11.8727272727273" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -6002,7 +6085,7 @@
       <c r="B2" s="6">
         <v>46188</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -6155,19 +6238,37 @@
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="1"/>
+      <c r="B6" s="6">
+        <v>46213</v>
+      </c>
+      <c r="C6" s="5">
+        <v>600745</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="5">
+        <v>600</v>
+      </c>
+      <c r="F6" s="5">
+        <v>18.65</v>
+      </c>
+      <c r="G6" s="5">
+        <v>21.24</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="1">
+        <v>19.06</v>
+      </c>
       <c r="J6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="5"/>
+        <v>1534.94</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1534.94</v>
+      </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
     </row>
@@ -6233,7 +6334,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -6246,13 +6347,13 @@
       <c r="J10" s="4"/>
       <c r="K10" s="5">
         <f>SUM(K2:K9)</f>
-        <v>13613.54</v>
+        <v>15148.48</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D5" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D6" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="3">
@@ -6269,9 +6370,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="12.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6285,17 +6386,17 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -6305,7 +6406,7 @@
         <v>5.13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:5">

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="80">
   <si>
     <t>时间</t>
   </si>
@@ -110,6 +110,9 @@
     <t>售出</t>
   </si>
   <si>
+    <t>股票在4.2附近的时候增持1000股到2000股，盈利大于300元就可以抛出</t>
+  </si>
+  <si>
     <t>南京证券</t>
   </si>
   <si>
@@ -134,7 +137,7 @@
     <t>中国西电</t>
   </si>
   <si>
-    <t>低于14补仓</t>
+    <t>低于12可以考虑补仓，每次补仓500股</t>
   </si>
   <si>
     <t>电魂网络</t>
@@ -146,7 +149,7 @@
     <t>昆药集团</t>
   </si>
   <si>
-    <t>在8.5左右的时候进行补仓，9块左右进行售出做T，每次600股</t>
+    <t>在8左右的时候进行补仓，9块左右进行售出做T，每次600股</t>
   </si>
   <si>
     <t>航天电子</t>
@@ -186,7 +189,7 @@
     <t>黄河旋风</t>
   </si>
   <si>
-    <t>短期持有，升值5%以上可以考虑售出</t>
+    <t>在10元附件增持500股</t>
   </si>
   <si>
     <t>ST闻泰</t>
@@ -268,6 +271,12 @@
   </si>
   <si>
     <t>3.5~4</t>
+  </si>
+  <si>
+    <t>宁波能源</t>
+  </si>
+  <si>
+    <t>4.5~4.8</t>
   </si>
 </sst>
 </file>
@@ -947,10 +956,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1014,18 +1026,33 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1035,15 +1062,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1056,11 +1074,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1600,205 +1630,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>46096</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="6">
         <f t="shared" ref="B2:B8" si="0">SUM(D2+C2)</f>
         <v>225842</v>
       </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="C2" s="6">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6">
         <v>225842</v>
       </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" s="6">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
         <v>11837</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f t="shared" ref="G2:G8" si="1">SUM(B2+F2-E2)</f>
         <v>237679</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="7">
         <v>46107</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <f t="shared" si="0"/>
         <v>236842</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="6">
         <f t="shared" ref="C3:C8" si="2">B2</f>
         <v>225842</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="6">
         <v>11000</v>
       </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
         <v>11837</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="6">
         <f t="shared" si="1"/>
         <v>248679</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>46101</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <f t="shared" si="0"/>
         <v>256842</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <f t="shared" si="2"/>
         <v>236842</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>20000</v>
       </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
         <v>11837</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <f t="shared" si="1"/>
         <v>268679</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>46177</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <f t="shared" si="0"/>
         <v>266842</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <f t="shared" si="2"/>
         <v>256842</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>10000</v>
       </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
         <v>11837</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <f t="shared" si="1"/>
         <v>278679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>46182</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <f t="shared" si="0"/>
         <v>276842</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <f t="shared" si="2"/>
         <v>266842</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <v>10000</v>
       </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
         <v>11873</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <f t="shared" si="1"/>
         <v>288715</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>46184</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <f t="shared" si="0"/>
         <v>281842</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <f t="shared" si="2"/>
         <v>276842</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>5000</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
         <v>11873</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <f t="shared" si="1"/>
         <v>293715</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>46190</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="6">
         <f t="shared" si="0"/>
         <v>282342</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <f t="shared" si="2"/>
         <v>281842</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6">
         <v>500</v>
       </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
         <v>11873</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <f t="shared" si="1"/>
         <v>294215</v>
       </c>
@@ -1815,2376 +1845,2378 @@
   <dimension ref="A1:K107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="9.37272727272727" style="3"/>
-    <col min="3" max="3" width="9" style="11"/>
-    <col min="4" max="4" width="9" style="3"/>
-    <col min="5" max="8" width="12.8727272727273" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="11"/>
-    <col min="10" max="10" width="68.6272727272727" style="12" customWidth="1"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="9.37272727272727" style="12"/>
+    <col min="3" max="3" width="9" style="12"/>
+    <col min="4" max="4" width="9" style="4"/>
+    <col min="5" max="8" width="12.8727272727273" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9" style="12"/>
+    <col min="10" max="10" width="68.6272727272727" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" ht="28" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="12" customFormat="1" ht="28" spans="1:11">
+      <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="5">
         <v>300323</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="22">
         <v>46182</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>16.6114</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>1600</v>
       </c>
-      <c r="H2" s="1">
-        <f t="shared" ref="H2:H8" si="0">F2*G2</f>
+      <c r="H2" s="2">
+        <f t="shared" ref="H2:H12" si="0">F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="14" t="s">
+      <c r="I2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="11"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="5">
         <v>600740</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="22">
         <v>46182</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>4.1541</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>1800</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <f t="shared" si="0"/>
         <v>7477.38</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="14" t="s">
+      <c r="I3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="16">
+      <c r="A4" s="23">
         <v>3</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="17">
         <v>1</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <v>46182</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="17">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="17">
         <v>4300</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="17">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="19"/>
+      <c r="J4" s="26" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="5">
         <v>601990</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="22">
         <v>46182</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>9.9227</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>500</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <f t="shared" si="0"/>
         <v>4961.35</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>25</v>
+      <c r="I5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="5">
         <v>600059</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="22">
         <v>46182</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>10.9008</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>1000</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <f t="shared" si="0"/>
         <v>10900.8</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>27</v>
+      <c r="I6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1">
+      <c r="C7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <v>46182</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>9.6507</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="2">
         <v>1000</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <f t="shared" si="0"/>
         <v>9650.7</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>30</v>
+      <c r="I7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="5">
         <v>601179</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="C8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="22">
         <v>46182</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>20.12</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="2">
         <v>700</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <f t="shared" si="0"/>
         <v>14084</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>32</v>
+      <c r="I8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="5">
         <v>603258</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="22">
         <v>46182</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>20.6888</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="2">
         <v>900</v>
       </c>
-      <c r="H9" s="1">
-        <f>F9*G9</f>
+      <c r="H9" s="2">
+        <f t="shared" si="0"/>
         <v>18619.92</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>34</v>
+      <c r="I9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="8">
         <v>600422</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="22">
         <v>46182</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>21.0619</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
         <v>600</v>
       </c>
-      <c r="H10" s="1">
-        <f>F10*G10</f>
+      <c r="H10" s="2">
+        <f t="shared" si="0"/>
         <v>12637.14</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>36</v>
+      <c r="I10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="27" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="28">
         <v>2</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="29">
         <v>46188</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="28">
         <v>8.5</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="28">
         <v>600</v>
       </c>
-      <c r="H11" s="1">
-        <f>F11*G11</f>
+      <c r="H11" s="28">
+        <f t="shared" si="0"/>
         <v>5100</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="24"/>
+      <c r="I11" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="28">
         <v>3</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="29">
         <v>46226</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="28">
         <v>9</v>
       </c>
-      <c r="G12" s="1">
-        <v>600</v>
-      </c>
-      <c r="H12" s="1">
-        <f>F12*G12</f>
-        <v>5400</v>
-      </c>
-      <c r="I12" s="4" t="s">
+      <c r="G12" s="28">
+        <v>-600</v>
+      </c>
+      <c r="H12" s="28">
+        <f t="shared" si="0"/>
+        <v>-5400</v>
+      </c>
+      <c r="I12" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="25"/>
+      <c r="J12" s="31"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="5">
         <v>600879</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="C13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="22">
         <v>46182</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>26.2661</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="2">
         <v>700</v>
       </c>
-      <c r="H13" s="1">
-        <f t="shared" ref="H13:H25" si="1">F13*G13</f>
+      <c r="H13" s="2">
+        <f t="shared" ref="H13:H26" si="1">F13*G13</f>
         <v>18386.27</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>38</v>
+      <c r="I13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="26">
+      <c r="A14" s="32">
         <v>11</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="8">
         <v>601066</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="C14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <v>46182</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <v>27.6302</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="2">
         <v>3400</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="2">
         <f t="shared" si="1"/>
         <v>93942.68</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="27" t="s">
-        <v>40</v>
+      <c r="I14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="28"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="29">
+      <c r="A15" s="34"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="28">
         <v>2</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>46192</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <v>31</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28">
         <v>-2400</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="28">
         <f t="shared" si="1"/>
         <v>-74400</v>
       </c>
-      <c r="I15" s="31" t="s">
+      <c r="I15" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="J15" s="32"/>
+      <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="33"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="1">
+      <c r="A16" s="36"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="2">
         <v>3</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="22">
         <v>46202</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>29.3</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="2">
         <v>1000</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="2">
         <f t="shared" si="1"/>
         <v>29300</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="24"/>
+      <c r="I16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="31"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>12</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="1">
+      <c r="C17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="22">
         <v>46182</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <v>18.3681</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="2">
         <v>1000</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="2">
         <f t="shared" si="1"/>
         <v>18368.1</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>43</v>
+      <c r="I17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>13</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="5">
         <v>300589</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="C18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="22">
         <v>46182</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>22.8225</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="2">
         <v>1200</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="2">
         <f t="shared" si="1"/>
         <v>27387</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>45</v>
+      <c r="I18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="26">
+      <c r="A19" s="32">
         <v>14</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>300129</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="C19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="22">
         <v>46182</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <v>14.9016</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="2">
         <v>2300</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="2">
         <f t="shared" si="1"/>
         <v>34273.68</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>47</v>
+      <c r="I19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="34"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="1">
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="2">
         <v>2</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="22">
         <v>46223</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <v>7.35</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="2">
         <v>700</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="2">
         <f t="shared" si="1"/>
         <v>5145</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="14"/>
+      <c r="I20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="29">
+      <c r="A21" s="39">
         <v>15</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="40">
         <v>600172</v>
       </c>
-      <c r="C21" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="29">
+      <c r="C21" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="28">
         <v>1</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>46188</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <v>12.2123</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28">
         <v>600</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="28">
         <f t="shared" si="1"/>
         <v>7327.38</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="36" t="s">
-        <v>49</v>
+      <c r="J21" s="41" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>16</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="5">
         <v>600745</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="1">
+      <c r="C22" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="22">
         <v>46189</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <v>18.6687</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="2">
         <v>800</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="2">
         <f t="shared" si="1"/>
         <v>14934.96</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>51</v>
+      <c r="I22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="1">
-        <v>17</v>
-      </c>
-      <c r="B23">
+      <c r="A23" s="2">
+        <v>17</v>
+      </c>
+      <c r="B23" s="12">
         <v>600115</v>
       </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="1">
+      <c r="C23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="2">
         <v>1</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="22">
         <v>46203</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>3.7838</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="2">
         <v>3200</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="2">
         <f t="shared" si="1"/>
         <v>12108.16</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="14"/>
+      <c r="I23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="15"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="26">
+      <c r="A24" s="32">
         <v>18</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <v>600360</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="1">
+      <c r="C24" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="22">
         <v>46203</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <v>14.6146</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="2">
         <v>1800</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="2">
         <f t="shared" si="1"/>
         <v>26306.28</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="14"/>
+      <c r="I24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="15"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="28"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="1">
+      <c r="A25" s="34"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="28">
         <v>2</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="42">
         <v>46213</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="20">
         <v>17.59</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="28">
         <v>-1300</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="28">
         <f t="shared" si="1"/>
         <v>-22867</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="J25" s="14"/>
+      <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="33"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="1">
+      <c r="A26" s="36"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="2">
         <v>3</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="22">
         <v>46226</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <v>10</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="2">
         <v>500</v>
       </c>
-      <c r="H26" s="1">
-        <f>F26*G26</f>
+      <c r="H26" s="2">
+        <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="14"/>
+      <c r="I26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="15"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>19</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="B27" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="1">
+      <c r="C27" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="2">
         <v>1</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="22">
         <v>46204</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <v>8.5585</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="2">
         <v>1700</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="2">
         <f t="shared" ref="H27:H54" si="2">F27*G27</f>
         <v>14549.45</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="14"/>
+      <c r="I27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="15"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>20</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="14"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>21</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="14"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>22</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="14"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>23</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="14"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>24</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="14"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="15"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>25</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="14"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="15"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>26</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="14"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="15"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>27</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="14"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>28</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="14"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="15"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>29</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="14"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="15"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>30</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="14"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>31</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="14"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="15"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>32</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="14"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="15"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>33</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="14"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="15"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>34</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="14"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="15"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>35</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="14"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="15"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>36</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="14"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="15"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>37</v>
       </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="14"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="15"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>38</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="14"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="15"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>39</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="14"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="15"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>40</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="14"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="15"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>41</v>
       </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="14"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="15"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>42</v>
       </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="14"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="15"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>43</v>
       </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="14"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="15"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>44</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="14"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="15"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>45</v>
       </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="14"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="15"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>46</v>
       </c>
-      <c r="B54" s="1"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="14"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="15"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>47</v>
       </c>
-      <c r="B55" s="1"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1">
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2">
         <f t="shared" ref="H55:H86" si="3">F55*G55</f>
         <v>0</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="14"/>
+      <c r="I55" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="15"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>48</v>
       </c>
-      <c r="B56" s="1"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1">
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="14"/>
+      <c r="I56" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="15"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>49</v>
       </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1">
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="14"/>
+      <c r="I57" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="15"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>50</v>
       </c>
-      <c r="B58" s="1"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1">
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="14"/>
+      <c r="I58" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="15"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>51</v>
       </c>
-      <c r="B59" s="1"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1">
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="14"/>
+      <c r="I59" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="15"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>52</v>
       </c>
-      <c r="B60" s="1"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1">
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="14"/>
+      <c r="I60" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="15"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>53</v>
       </c>
-      <c r="B61" s="1"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="14"/>
+      <c r="I61" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="15"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>54</v>
       </c>
-      <c r="B62" s="1"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1">
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I62" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="14"/>
+      <c r="I62" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="15"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>55</v>
       </c>
-      <c r="B63" s="1"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1">
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="14"/>
+      <c r="I63" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="15"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>56</v>
       </c>
-      <c r="B64" s="1"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1">
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="14"/>
+      <c r="I64" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="15"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>57</v>
       </c>
-      <c r="B65" s="1"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1">
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I65" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="14"/>
+      <c r="I65" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="15"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>58</v>
       </c>
-      <c r="B66" s="1"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1">
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I66" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="14"/>
+      <c r="I66" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="15"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>59</v>
       </c>
-      <c r="B67" s="1"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1">
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I67" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="14"/>
+      <c r="I67" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="15"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>60</v>
       </c>
-      <c r="B68" s="1"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1">
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="14"/>
+      <c r="I68" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="15"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>61</v>
       </c>
-      <c r="B69" s="1"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1">
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I69" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="14"/>
+      <c r="I69" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="15"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>62</v>
       </c>
-      <c r="B70" s="1"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1">
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I70" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="14"/>
+      <c r="I70" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="15"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <v>63</v>
       </c>
-      <c r="B71" s="1"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1">
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I71" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="14"/>
+      <c r="I71" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="15"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="1">
+      <c r="A72" s="2">
         <v>64</v>
       </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1">
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="14"/>
+      <c r="I72" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="15"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="1">
+      <c r="A73" s="2">
         <v>65</v>
       </c>
-      <c r="B73" s="1"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1">
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I73" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="14"/>
+      <c r="I73" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="15"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="1">
+      <c r="A74" s="2">
         <v>66</v>
       </c>
-      <c r="B74" s="1"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1">
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I74" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="14"/>
+      <c r="I74" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="15"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>67</v>
       </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1">
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="14"/>
+      <c r="I75" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="15"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>68</v>
       </c>
-      <c r="B76" s="1"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1">
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I76" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="14"/>
+      <c r="I76" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="15"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="1">
+      <c r="A77" s="2">
         <v>69</v>
       </c>
-      <c r="B77" s="1"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1">
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="14"/>
+      <c r="I77" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="15"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="1">
+      <c r="A78" s="2">
         <v>70</v>
       </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1">
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I78" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="14"/>
+      <c r="I78" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="15"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>71</v>
       </c>
-      <c r="B79" s="1"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1">
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I79" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="14"/>
+      <c r="I79" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="15"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>72</v>
       </c>
-      <c r="B80" s="1"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1">
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="14"/>
+      <c r="I80" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="15"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>73</v>
       </c>
-      <c r="B81" s="1"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1">
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I81" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="14"/>
+      <c r="I81" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="15"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>74</v>
       </c>
-      <c r="B82" s="1"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1">
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I82" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="14"/>
+      <c r="I82" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="15"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>75</v>
       </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1">
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I83" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="14"/>
+      <c r="I83" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="15"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>76</v>
       </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1">
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I84" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="14"/>
+      <c r="I84" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="15"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>77</v>
       </c>
-      <c r="B85" s="1"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1">
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I85" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="14"/>
+      <c r="I85" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="15"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>78</v>
       </c>
-      <c r="B86" s="1"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1">
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I86" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="14"/>
+      <c r="I86" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="15"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>79</v>
       </c>
-      <c r="B87" s="1"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1">
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2">
         <f t="shared" ref="H87:H107" si="4">F87*G87</f>
         <v>0</v>
       </c>
-      <c r="I87" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="14"/>
+      <c r="I87" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="15"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>80</v>
       </c>
-      <c r="B88" s="1"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1">
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I88" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="14"/>
+      <c r="I88" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="15"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>81</v>
       </c>
-      <c r="B89" s="1"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1">
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I89" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="14"/>
+      <c r="I89" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="15"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>82</v>
       </c>
-      <c r="B90" s="1"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1">
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I90" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="14"/>
+      <c r="I90" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="15"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>83</v>
       </c>
-      <c r="B91" s="1"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1">
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="14"/>
+      <c r="I91" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="15"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>84</v>
       </c>
-      <c r="B92" s="1"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1">
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I92" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="14"/>
+      <c r="I92" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="15"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>85</v>
       </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1">
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I93" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="14"/>
+      <c r="I93" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="15"/>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <v>86</v>
       </c>
-      <c r="B94" s="1"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1">
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I94" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="14"/>
+      <c r="I94" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="15"/>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <v>87</v>
       </c>
-      <c r="B95" s="1"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1">
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I95" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="14"/>
+      <c r="I95" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="15"/>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <v>88</v>
       </c>
-      <c r="B96" s="1"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1">
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I96" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="14"/>
+      <c r="I96" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="15"/>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <v>89</v>
       </c>
-      <c r="B97" s="1"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1">
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I97" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="14"/>
+      <c r="I97" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="15"/>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>90</v>
       </c>
-      <c r="B98" s="1"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1">
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I98" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="14"/>
+      <c r="I98" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="15"/>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <v>91</v>
       </c>
-      <c r="B99" s="1"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1">
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I99" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="14"/>
+      <c r="I99" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="15"/>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <v>92</v>
       </c>
-      <c r="B100" s="1"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1">
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I100" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="14"/>
+      <c r="I100" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="15"/>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <v>93</v>
       </c>
-      <c r="B101" s="1"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1">
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I101" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="14"/>
+      <c r="I101" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="15"/>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="1">
+      <c r="A102" s="2">
         <v>94</v>
       </c>
-      <c r="B102" s="1"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1">
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I102" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" s="14"/>
+      <c r="I102" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="15"/>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>95</v>
       </c>
-      <c r="B103" s="1"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1">
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I103" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" s="14"/>
+      <c r="I103" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="15"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="1">
+      <c r="A104" s="2">
         <v>96</v>
       </c>
-      <c r="B104" s="1"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1">
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I104" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J104" s="14"/>
+      <c r="I104" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="15"/>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="1">
+      <c r="A105" s="2">
         <v>97</v>
       </c>
-      <c r="B105" s="1"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1">
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I105" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J105" s="14"/>
+      <c r="I105" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="15"/>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="1">
+      <c r="A106" s="2">
         <v>98</v>
       </c>
-      <c r="B106" s="1"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1">
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I106" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J106" s="14"/>
+      <c r="I106" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="15"/>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="1">
+      <c r="A107" s="2">
         <v>99</v>
       </c>
-      <c r="B107" s="1"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1">
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I107" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="14"/>
+      <c r="I107" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="15"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I107" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="14">
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C10:C12"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C24:C26"/>
@@ -4192,7 +4224,7 @@
     <mergeCell ref="J14:J16"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I12 I1:I11 I13:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
       <formula1>$I$2:$I$22</formula1>
     </dataValidation>
   </dataValidations>
@@ -4207,1808 +4239,1808 @@
   <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="9.37272727272727" style="3"/>
-    <col min="3" max="3" width="9" style="11"/>
-    <col min="4" max="4" width="9" style="3"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="9.37272727272727" style="4"/>
+    <col min="3" max="3" width="9" style="12"/>
+    <col min="4" max="4" width="9" style="4"/>
     <col min="5" max="5" width="12.8727272727273" customWidth="1"/>
-    <col min="6" max="8" width="12.8727272727273" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="11"/>
-    <col min="10" max="10" width="68.6272727272727" style="12" customWidth="1"/>
+    <col min="6" max="8" width="12.8727272727273" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9" style="12"/>
+    <col min="10" max="10" width="68.6272727272727" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" ht="28" spans="1:11">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="12" customFormat="1" ht="28" spans="1:11">
+      <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>601398</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="16">
         <v>46182</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>16.6114</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>1600</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <f>F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="11"/>
+      <c r="I2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="15"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1">
+      <c r="B3" s="2"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2">
         <f t="shared" ref="H3:H13" si="0">F3*G3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="14"/>
+      <c r="I3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="1">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="19"/>
+      <c r="I4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="20"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1">
+      <c r="B5" s="2"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="14"/>
+      <c r="I5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="15"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1">
+      <c r="B6" s="2"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="14"/>
+      <c r="I6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="15"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1">
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="14"/>
+      <c r="I7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="15"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1">
+      <c r="B8" s="2"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="14"/>
+      <c r="I8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="15"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1">
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="14"/>
+      <c r="I9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="15"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1">
+      <c r="B10" s="2"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="14"/>
+      <c r="I10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="15"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1">
+      <c r="D11" s="2"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="14"/>
+      <c r="I11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="15"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1">
+      <c r="B12" s="2"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="14"/>
+      <c r="I12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1">
+      <c r="B13" s="2"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="14"/>
+      <c r="I13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1">
+      <c r="B14" s="2"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2">
         <f t="shared" ref="H10:H55" si="1">F14*G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="14"/>
+      <c r="I14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1">
+      <c r="B15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="14"/>
+      <c r="I15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1">
+      <c r="B16" s="2"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="14"/>
+      <c r="I16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="15"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1">
+      <c r="B17" s="2"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="14"/>
+      <c r="I17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="15"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="14"/>
+      <c r="I18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1">
+      <c r="B19" s="2"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="14"/>
+      <c r="I19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="15"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1">
+      <c r="B20" s="2"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="14"/>
+      <c r="I20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1">
+      <c r="B21" s="2"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="14"/>
+      <c r="I21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1">
+      <c r="B22" s="2"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="14"/>
+      <c r="I22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1">
+      <c r="B23" s="2"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="14"/>
+      <c r="I23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="15"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1">
+      <c r="B24" s="2"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="14"/>
+      <c r="I24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="15"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1">
+      <c r="B25" s="2"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="14"/>
+      <c r="I25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1">
+      <c r="B26" s="2"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="14"/>
+      <c r="I26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="15"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1">
+      <c r="B27" s="2"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="14"/>
+      <c r="I27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="15"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1">
+      <c r="B28" s="2"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="14"/>
+      <c r="I28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1">
+      <c r="B29" s="2"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="14"/>
+      <c r="I29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1">
+      <c r="B30" s="2"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="14"/>
+      <c r="I30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1">
+      <c r="B31" s="2"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="14"/>
+      <c r="I31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1">
+      <c r="B32" s="2"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="14"/>
+      <c r="I32" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="15"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1">
+      <c r="B33" s="2"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="14"/>
+      <c r="I33" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="15"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1">
+      <c r="B34" s="2"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="14"/>
+      <c r="I34" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="15"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1">
+      <c r="B35" s="2"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="14"/>
+      <c r="I35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1">
+      <c r="B36" s="2"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="14"/>
+      <c r="I36" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="15"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1">
+      <c r="B37" s="2"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="14"/>
+      <c r="I37" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="15"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1">
+      <c r="B38" s="2"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="14"/>
+      <c r="I38" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1">
+      <c r="B39" s="2"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="14"/>
+      <c r="I39" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="15"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1">
+      <c r="B40" s="2"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="14"/>
+      <c r="I40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="15"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1">
+      <c r="B41" s="2"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="14"/>
+      <c r="I41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="15"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1">
+      <c r="B42" s="2"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="14"/>
+      <c r="I42" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="15"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1">
+      <c r="B43" s="2"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="14"/>
+      <c r="I43" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="15"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1">
+      <c r="B44" s="2"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="14"/>
+      <c r="I44" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="15"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1">
+      <c r="B45" s="2"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="14"/>
+      <c r="I45" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="15"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1">
+      <c r="B46" s="2"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="14"/>
+      <c r="I46" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="15"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1">
+      <c r="B47" s="2"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="14"/>
+      <c r="I47" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="15"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1">
+      <c r="B48" s="2"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I48" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="14"/>
+      <c r="I48" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="15"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1">
+      <c r="B49" s="2"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="14"/>
+      <c r="I49" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="15"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1">
+      <c r="B50" s="2"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="14"/>
+      <c r="I50" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="15"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1">
+      <c r="B51" s="2"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="14"/>
+      <c r="I51" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="15"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1">
+      <c r="B52" s="2"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="14"/>
+      <c r="I52" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="15"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1">
+      <c r="B53" s="2"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="14"/>
+      <c r="I53" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="15"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="1"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1">
+      <c r="B54" s="2"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="14"/>
+      <c r="I54" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="15"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="1"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1">
+      <c r="B55" s="2"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="14"/>
+      <c r="I55" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="15"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="1"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1">
+      <c r="B56" s="2"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2">
         <f t="shared" ref="H56:H93" si="2">F56*G56</f>
         <v>0</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="14"/>
+      <c r="I56" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="15"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="14"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="15"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="1"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="14"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="15"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="1"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="14"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="15"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="1"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="14"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="15"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="1"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="14"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="15"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="1"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="14"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="15"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="1"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="14"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="15"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="1"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="14"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="15"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" s="1"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="14"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="15"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" s="1"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="14"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="15"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" s="1"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="14"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="15"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" s="1"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="14"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="15"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" s="1"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="14"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="15"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" s="1"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="14"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="15"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" s="1"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="14"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="15"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="1">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="14"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="15"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="1">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B73" s="1"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="14"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="15"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="1">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="1"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="14"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="15"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="14"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="15"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" s="1"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="14"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="15"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="1">
+      <c r="A77" s="2">
         <v>76</v>
       </c>
-      <c r="B77" s="1"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="14"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="15"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="1">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="14"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="15"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="B79" s="1"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="14"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="15"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" s="1"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="14"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="15"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" s="1"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="14"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="15"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" s="1"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="14"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="15"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="14"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="15"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="14"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="15"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" s="1"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="14"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="15"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" s="1"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="14"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="15"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" s="1"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="14"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="15"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" s="1"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="14"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="15"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" s="1"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="14"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="15"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" s="1"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="14"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="15"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" s="1"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="14"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="15"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="1"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="14"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="15"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>92</v>
       </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="14"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="15"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I93" etc:filterBottomFollowUsedRange="0">
@@ -6031,326 +6063,326 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="10.6363636363636"/>
-    <col min="4" max="4" width="9" style="3"/>
+    <col min="4" max="4" width="9" style="4"/>
     <col min="8" max="8" width="22.1272727272727" customWidth="1"/>
-    <col min="9" max="9" width="11.8727272727273" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.8727272727273" style="4" customWidth="1"/>
     <col min="11" max="11" width="10.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>68</v>
       </c>
+      <c r="M1" s="6" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>46188</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="6">
         <v>4300</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>4.8581</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>5.17</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
+      <c r="H2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
         <f>E2*(G2-F2)-I2</f>
         <v>1341.17</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="6">
         <v>1308.3</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="8">
         <f>SUM(K2:K4)</f>
         <v>9745.52</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="8">
         <f>SUM(L2)</f>
         <v>9745.52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="4">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>46190</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="6">
         <v>600172</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="6">
         <v>600</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>12.2123</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="6">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="H3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
         <f t="shared" ref="J3:J9" si="0">E3*(G3-F3)-I3</f>
         <v>472.619999999999</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="6">
         <v>460.95</v>
       </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="4">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>46199</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>601066</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="6">
         <v>2400</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <v>27.6302</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <v>31</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="H4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="2">
         <v>111.25</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="6">
         <f t="shared" si="0"/>
         <v>7976.27</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="6">
         <v>7976.27</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>46213</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>600360</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="6">
         <v>1300</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>14.6146</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <v>17.59</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="5">
+      <c r="H5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="6">
         <f t="shared" si="0"/>
         <v>3868.02</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="6">
         <v>3868.02</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>46213</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>600745</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="6">
         <v>600</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="6">
         <v>18.65</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <v>21.24</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="H6" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="2">
         <v>19.06</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="6">
         <f t="shared" si="0"/>
         <v>1534.94</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="6">
         <v>1534.94</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="5">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="5">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="5">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="5">
+      <c r="A10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="6">
         <f>SUM(K2:K9)</f>
         <v>15148.48</v>
       </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D6" etc:filterBottomFollowUsedRange="0">
@@ -6372,7 +6404,7 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="5" max="5" width="12.8727272727273" customWidth="1"/>
+    <col min="5" max="5" width="12.8727272727273" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6386,27 +6418,27 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" t="s">
         <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>5.13</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>76</v>
+      <c r="E2" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6417,13 +6449,13 @@
         <v>601398</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="3">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4">
         <v>7.16</v>
       </c>
-      <c r="E3">
-        <v>6.6</v>
+      <c r="E3" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6434,18 +6466,30 @@
         <v>600115</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>3.93</v>
       </c>
-      <c r="E4">
-        <v>3.8</v>
+      <c r="E4" s="1">
+        <v>3.5</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
+      </c>
+      <c r="B5">
+        <v>600982</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5">
+        <v>5.02</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5">

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -14,7 +14,7 @@
     <sheet name="自选股" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">定投股票!$B$1:$I$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已出售!$C$1:$D$6</definedName>
   </definedNames>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="82">
   <si>
     <t>时间</t>
   </si>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>京东方Ａ</t>
+  </si>
+  <si>
+    <t>002858</t>
+  </si>
+  <si>
+    <t>力盛体育</t>
   </si>
   <si>
     <t>工商银行</t>
@@ -956,7 +962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -969,9 +975,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1039,7 +1042,28 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1053,20 +1077,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1630,205 +1648,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>46096</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <f t="shared" ref="B2:B8" si="0">SUM(D2+C2)</f>
         <v>225842</v>
       </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
         <v>225842</v>
       </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
         <v>11837</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <f t="shared" ref="G2:G8" si="1">SUM(B2+F2-E2)</f>
         <v>237679</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>46107</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <f t="shared" si="0"/>
         <v>236842</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <f t="shared" ref="C3:C8" si="2">B2</f>
         <v>225842</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>11000</v>
       </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
         <v>11837</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <f t="shared" si="1"/>
         <v>248679</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>46101</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>256842</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <f t="shared" si="2"/>
         <v>236842</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>20000</v>
       </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
         <v>11837</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <f t="shared" si="1"/>
         <v>268679</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>46177</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>266842</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <f t="shared" si="2"/>
         <v>256842</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>10000</v>
       </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
         <v>11837</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f t="shared" si="1"/>
         <v>278679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>46182</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>276842</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <f t="shared" si="2"/>
         <v>266842</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>10000</v>
       </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
         <v>11873</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <f t="shared" si="1"/>
         <v>288715</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>46184</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f t="shared" si="0"/>
         <v>281842</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <f t="shared" si="2"/>
         <v>276842</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>5000</v>
       </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
         <v>11873</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <f t="shared" si="1"/>
         <v>293715</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>46190</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>282342</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f t="shared" si="2"/>
         <v>281842</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>500</v>
       </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
         <v>11873</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <f t="shared" si="1"/>
         <v>294215</v>
       </c>
@@ -1842,47 +1860,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="9.37272727272727" style="12"/>
-    <col min="3" max="3" width="9" style="12"/>
-    <col min="4" max="4" width="9" style="4"/>
-    <col min="5" max="8" width="12.8727272727273" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9" style="12"/>
-    <col min="10" max="10" width="68.6272727272727" style="13" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="9.37272727272727" style="11"/>
+    <col min="3" max="3" width="9" style="11"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="8" width="12.8727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="11"/>
+    <col min="10" max="10" width="68.6272727272727" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" ht="28" spans="1:11">
+    <row r="1" s="11" customFormat="1" ht="28" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1890,16 +1908,16 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>300323</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="21">
         <v>46182</v>
       </c>
       <c r="F2" s="2">
@@ -1912,28 +1930,28 @@
         <f t="shared" ref="H2:H12" si="0">F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="15" t="s">
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="12"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>600740</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="21">
         <v>46182</v>
       </c>
       <c r="F3" s="2">
@@ -1946,43 +1964,43 @@
         <f t="shared" si="0"/>
         <v>7477.38</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="15" t="s">
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="23">
+      <c r="A4" s="22">
         <v>3</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>1</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="24">
         <v>46182</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="16">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="16">
         <v>4300</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="16">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="J4" s="25" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1990,16 +2008,16 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>601990</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="21">
         <v>46182</v>
       </c>
       <c r="F5" s="2">
@@ -2012,10 +2030,10 @@
         <f t="shared" si="0"/>
         <v>4961.35</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2023,16 +2041,16 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>600059</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="21">
         <v>46182</v>
       </c>
       <c r="F6" s="2">
@@ -2045,10 +2063,10 @@
         <f t="shared" si="0"/>
         <v>10900.8</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="15" t="s">
+      <c r="I6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2056,16 +2074,16 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>46182</v>
       </c>
       <c r="F7" s="2">
@@ -2078,10 +2096,10 @@
         <f t="shared" si="0"/>
         <v>9650.7</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="15" t="s">
+      <c r="I7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2089,16 +2107,16 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>601179</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="21">
         <v>46182</v>
       </c>
       <c r="F8" s="2">
@@ -2111,27 +2129,27 @@
         <f t="shared" si="0"/>
         <v>14084</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="15" t="s">
+      <c r="I8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="2">
+      <c r="A9" s="26">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="27">
         <v>603258</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="21">
         <v>46182</v>
       </c>
       <c r="F9" s="2">
@@ -2144,608 +2162,632 @@
         <f t="shared" si="0"/>
         <v>18619.92</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="15" t="s">
+      <c r="I9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="8">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="21">
+        <v>46233</v>
+      </c>
+      <c r="F10" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="G10" s="2">
+        <v>500</v>
+      </c>
+      <c r="H10" s="2">
+        <f>F10*G10</f>
+        <v>6450</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="30"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B11" s="7">
         <v>600422</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E11" s="21">
         <v>46182</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F11" s="2">
         <v>21.0619</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G11" s="2">
         <v>600</v>
       </c>
-      <c r="H10" s="2">
-        <f t="shared" si="0"/>
+      <c r="H11" s="2">
+        <f>F11*G11</f>
         <v>12637.14</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="27" t="s">
+      <c r="I11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="32" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="28">
+    <row r="12" spans="1:11">
+      <c r="A12" s="33"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="34">
         <v>2</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E12" s="35">
         <v>46188</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F12" s="34">
         <v>8.5</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G12" s="34">
         <v>600</v>
       </c>
-      <c r="H11" s="28">
-        <f t="shared" si="0"/>
+      <c r="H12" s="34">
+        <f>F12*G12</f>
         <v>5100</v>
       </c>
-      <c r="I11" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="31"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="28">
+      <c r="I12" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="37"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="38"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="34">
         <v>3</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E13" s="35">
         <v>46226</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F13" s="34">
         <v>9</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G13" s="34">
         <v>-600</v>
       </c>
-      <c r="H12" s="28">
-        <f t="shared" si="0"/>
+      <c r="H13" s="34">
+        <f>F13*G13</f>
         <v>-5400</v>
       </c>
-      <c r="I12" s="30" t="s">
+      <c r="I13" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="31"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="2">
+      <c r="J13" s="37"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B14" s="4">
         <v>600879</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="22">
-        <v>46182</v>
-      </c>
-      <c r="F13" s="2">
-        <v>26.2661</v>
-      </c>
-      <c r="G13" s="2">
-        <v>700</v>
-      </c>
-      <c r="H13" s="2">
-        <f t="shared" ref="H13:H26" si="1">F13*G13</f>
-        <v>18386.27</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="32">
-        <v>11</v>
-      </c>
-      <c r="B14" s="8">
-        <v>601066</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <v>46182</v>
       </c>
       <c r="F14" s="2">
+        <v>26.2661</v>
+      </c>
+      <c r="G14" s="2">
+        <v>700</v>
+      </c>
+      <c r="H14" s="2">
+        <f>F14*G14</f>
+        <v>18386.27</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="31">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7">
+        <v>601066</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F15" s="2">
         <v>27.6302</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G15" s="2">
         <v>3400</v>
       </c>
-      <c r="H14" s="2">
-        <f t="shared" si="1"/>
+      <c r="H15" s="2">
+        <f>F15*G15</f>
         <v>93942.68</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="33" t="s">
+      <c r="I15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="39" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="34"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="28">
+    <row r="16" spans="1:11">
+      <c r="A16" s="33"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="34">
         <v>2</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E16" s="35">
         <v>46192</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F16" s="34">
         <v>31</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G16" s="34">
         <v>-2400</v>
       </c>
-      <c r="H15" s="28">
-        <f t="shared" si="1"/>
+      <c r="H16" s="34">
+        <f>F16*G16</f>
         <v>-74400</v>
       </c>
-      <c r="I15" s="30" t="s">
+      <c r="I16" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="J15" s="35"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="36"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="2">
+      <c r="J16" s="40"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="38"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="2">
         <v>3</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E17" s="21">
         <v>46202</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F17" s="2">
         <v>29.3</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1000</v>
-      </c>
-      <c r="H16" s="2">
-        <f t="shared" si="1"/>
-        <v>29300</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="31"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2">
-        <v>12</v>
-      </c>
-      <c r="B17" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="22">
-        <v>46182</v>
-      </c>
-      <c r="F17" s="2">
-        <v>18.3681</v>
       </c>
       <c r="G17" s="2">
         <v>1000</v>
       </c>
       <c r="H17" s="2">
-        <f t="shared" si="1"/>
-        <v>18368.1</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="15" t="s">
-        <v>44</v>
-      </c>
+        <f>F17*G17</f>
+        <v>29300</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="37"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2">
-        <v>13</v>
-      </c>
-      <c r="B18" s="5">
-        <v>300589</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="21">
         <v>46182</v>
       </c>
       <c r="F18" s="2">
-        <v>22.8225</v>
+        <v>18.3681</v>
       </c>
       <c r="G18" s="2">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="1"/>
-        <v>27387</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>46</v>
+        <f>F18*G18</f>
+        <v>18368.1</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="32">
-        <v>14</v>
-      </c>
-      <c r="B19" s="8">
-        <v>300129</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>47</v>
+      <c r="A19" s="26">
+        <v>13</v>
+      </c>
+      <c r="B19" s="27">
+        <v>300589</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="21">
         <v>46182</v>
       </c>
       <c r="F19" s="2">
-        <v>14.9016</v>
+        <v>22.8225</v>
       </c>
       <c r="G19" s="2">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="1"/>
-        <v>34273.68</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="15" t="s">
-        <v>48</v>
+        <f>F19*G19</f>
+        <v>27387</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="2">
         <v>2</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="21">
+        <v>46233</v>
+      </c>
+      <c r="F20" s="2">
+        <v>12.55</v>
+      </c>
+      <c r="G20" s="2">
+        <v>600</v>
+      </c>
+      <c r="H20" s="2">
+        <f>F20*G20</f>
+        <v>7530</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="31">
+        <v>14</v>
+      </c>
+      <c r="B21" s="7">
+        <v>300129</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="21">
+        <v>46182</v>
+      </c>
+      <c r="F21" s="2">
+        <v>14.9016</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2300</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" ref="H21:H28" si="1">F21*G21</f>
+        <v>34273.68</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="21">
         <v>46223</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F22" s="2">
         <v>7.35</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G22" s="2">
         <v>700</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H22" s="2">
         <f t="shared" si="1"/>
         <v>5145</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="39">
+      <c r="I22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="43">
         <v>15</v>
       </c>
-      <c r="B21" s="40">
+      <c r="B23" s="44">
         <v>600172</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C23" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D23" s="34">
         <v>1</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E23" s="35">
         <v>46188</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F23" s="34">
         <v>12.2123</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G23" s="34">
         <v>600</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H23" s="34">
         <f t="shared" si="1"/>
         <v>7327.38</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="41" t="s">
+      <c r="J23" s="45" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2">
+    <row r="24" spans="1:10">
+      <c r="A24" s="2">
         <v>16</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B24" s="4">
         <v>600745</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E24" s="21">
         <v>46189</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F24" s="2">
         <v>18.6687</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G24" s="2">
         <v>800</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H24" s="2">
         <f t="shared" si="1"/>
         <v>14934.96</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="15" t="s">
+      <c r="I24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2">
-        <v>17</v>
-      </c>
-      <c r="B23" s="12">
+    <row r="25" spans="1:10">
+      <c r="A25" s="2">
+        <v>17</v>
+      </c>
+      <c r="B25" s="11">
         <v>600115</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D25" s="2">
         <v>1</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E25" s="21">
         <v>46203</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F25" s="2">
         <v>3.7838</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G25" s="2">
         <v>3200</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H25" s="2">
         <f t="shared" si="1"/>
         <v>12108.16</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="32">
+      <c r="I25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="31">
         <v>18</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B26" s="7">
         <v>600360</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D26" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E26" s="21">
         <v>46203</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F26" s="2">
         <v>14.6146</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G26" s="2">
         <v>1800</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H26" s="2">
         <f t="shared" si="1"/>
         <v>26306.28</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="34"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="28">
+      <c r="I26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="33"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="34">
         <v>2</v>
       </c>
-      <c r="E25" s="42">
+      <c r="E27" s="46">
         <v>46213</v>
       </c>
-      <c r="F25" s="20">
+      <c r="F27" s="19">
         <v>17.59</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G27" s="34">
         <v>-1300</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H27" s="34">
         <f t="shared" si="1"/>
         <v>-22867</v>
       </c>
-      <c r="I25" s="30" t="s">
+      <c r="I27" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="36"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="2">
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="38"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="2">
         <v>3</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E28" s="21">
         <v>46226</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F28" s="2">
         <v>10</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G28" s="2">
         <v>500</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H28" s="2">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="15"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2">
-        <v>19</v>
-      </c>
-      <c r="B27" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1</v>
-      </c>
-      <c r="E27" s="22">
-        <v>46204</v>
-      </c>
-      <c r="F27" s="2">
-        <v>8.5585</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1700</v>
-      </c>
-      <c r="H27" s="2">
-        <f t="shared" ref="H27:H54" si="2">F27*G27</f>
-        <v>14549.45</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2">
-        <v>20</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="15"/>
+      <c r="I28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="14"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2">
-        <v>21</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="B29" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="21">
+        <v>46204</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8.5585</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1700</v>
+      </c>
       <c r="H29" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="15"/>
+        <f t="shared" ref="H29:H56" si="2">F29*G29</f>
+        <v>14549.45</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="14"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2">
-        <v>22</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="B30" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="21">
+        <v>46227</v>
+      </c>
+      <c r="F30" s="2">
+        <v>10.2102</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1000</v>
+      </c>
       <c r="H30" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="15"/>
+        <v>10210.2</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="14"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2">
-        <v>23</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -2754,17 +2796,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="15"/>
+      <c r="I31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="14"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2">
-        <v>24</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2773,17 +2815,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="15"/>
+      <c r="I32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="14"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2">
-        <v>25</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2792,17 +2834,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="15"/>
+      <c r="I33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="14"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2">
-        <v>26</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -2811,17 +2853,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="15"/>
+      <c r="I34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="14"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2">
-        <v>27</v>
-      </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
+        <v>25</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -2830,17 +2872,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="15"/>
+      <c r="I35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="14"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2">
-        <v>28</v>
-      </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -2849,17 +2891,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="15"/>
+      <c r="I36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="14"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2">
-        <v>29</v>
-      </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -2868,17 +2910,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="15"/>
+      <c r="I37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2">
-        <v>30</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -2887,17 +2929,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="15"/>
+      <c r="I38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="14"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2">
-        <v>31</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -2906,17 +2948,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="15"/>
+      <c r="I39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="14"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2">
-        <v>32</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -2925,17 +2967,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="15"/>
+      <c r="I40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="14"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="2">
-        <v>33</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -2944,17 +2986,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="15"/>
+      <c r="I41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="14"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2">
-        <v>34</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -2963,17 +3005,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="15"/>
+      <c r="I42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="14"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2">
-        <v>35</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -2982,17 +3024,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="15"/>
+      <c r="I43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="14"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2">
-        <v>36</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -3001,17 +3043,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="15"/>
+      <c r="I44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="14"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -3020,17 +3062,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="15"/>
+      <c r="I45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="14"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="2">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -3039,17 +3081,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I46" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="15"/>
+      <c r="I46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="14"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -3058,17 +3100,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="15"/>
+      <c r="I47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="14"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
+        <v>38</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3077,17 +3119,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="15"/>
+      <c r="I48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="14"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -3096,17 +3138,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="15"/>
+      <c r="I49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="14"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -3115,17 +3157,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="15"/>
+      <c r="I50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="14"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -3134,17 +3176,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="15"/>
+      <c r="I51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="14"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2">
-        <v>44</v>
-      </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
+        <v>42</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -3153,17 +3195,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="15"/>
+      <c r="I52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="14"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
@@ -3172,17 +3214,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="15"/>
+      <c r="I53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="14"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2">
-        <v>46</v>
-      </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -3191,74 +3233,74 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I54" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="15"/>
+      <c r="I54" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="14"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2">
-        <f t="shared" ref="H55:H86" si="3">F55*G55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="15"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="14"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2">
-        <v>48</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
+        <v>46</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="15"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="14"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="2">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="15"/>
+        <f t="shared" ref="H57:H88" si="3">F57*G57</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="14"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="2">
-        <v>50</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
@@ -3267,17 +3309,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I58" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="15"/>
+      <c r="I58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="14"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="2">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
+        <v>49</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
@@ -3286,17 +3328,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I59" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="15"/>
+      <c r="I59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="14"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="2">
-        <v>52</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -3305,17 +3347,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I60" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="15"/>
+      <c r="I60" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="14"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="2">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
+        <v>51</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
@@ -3324,17 +3366,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I61" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="15"/>
+      <c r="I61" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="14"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="2">
-        <v>54</v>
-      </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
@@ -3343,17 +3385,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="15"/>
+      <c r="I62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="14"/>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="2">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
+        <v>53</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
@@ -3362,17 +3404,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I63" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="15"/>
+      <c r="I63" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="14"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="2">
-        <v>56</v>
-      </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
@@ -3381,17 +3423,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="15"/>
+      <c r="I64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="14"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="2">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -3400,17 +3442,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I65" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="15"/>
+      <c r="I65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="14"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="2">
-        <v>58</v>
-      </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
@@ -3419,17 +3461,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I66" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="15"/>
+      <c r="I66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="14"/>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="2">
-        <v>59</v>
-      </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
@@ -3438,17 +3480,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I67" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="15"/>
+      <c r="I67" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="14"/>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="2">
-        <v>60</v>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
@@ -3457,17 +3499,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I68" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="15"/>
+      <c r="I68" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="14"/>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="2">
-        <v>61</v>
-      </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
@@ -3476,17 +3518,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I69" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="15"/>
+      <c r="I69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="14"/>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="2">
-        <v>62</v>
-      </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
@@ -3495,17 +3537,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I70" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="15"/>
+      <c r="I70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="14"/>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="2">
-        <v>63</v>
-      </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
+        <v>61</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
@@ -3514,17 +3556,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I71" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="15"/>
+      <c r="I71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="14"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="2">
-        <v>64</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
@@ -3533,17 +3575,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I72" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="15"/>
+      <c r="I72" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="14"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="2">
-        <v>65</v>
-      </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
+        <v>63</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
@@ -3552,17 +3594,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I73" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="15"/>
+      <c r="I73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="14"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="2">
-        <v>66</v>
-      </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
@@ -3571,17 +3613,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I74" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="15"/>
+      <c r="I74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="14"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="2">
-        <v>67</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
@@ -3590,17 +3632,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I75" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="15"/>
+      <c r="I75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="14"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="2">
-        <v>68</v>
-      </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
@@ -3609,17 +3651,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I76" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="15"/>
+      <c r="I76" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="14"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="2">
-        <v>69</v>
-      </c>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
@@ -3628,17 +3670,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I77" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="15"/>
+      <c r="I77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="14"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="2">
-        <v>70</v>
-      </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
@@ -3647,17 +3689,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I78" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="15"/>
+      <c r="I78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="14"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="2">
-        <v>71</v>
-      </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
+        <v>69</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
@@ -3666,17 +3708,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I79" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="15"/>
+      <c r="I79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="14"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="2">
-        <v>72</v>
-      </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
@@ -3685,17 +3727,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I80" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="15"/>
+      <c r="I80" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="14"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="2">
-        <v>73</v>
-      </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
+        <v>71</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
@@ -3704,17 +3746,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I81" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="15"/>
+      <c r="I81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="14"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="2">
-        <v>74</v>
-      </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
+        <v>72</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
@@ -3723,17 +3765,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I82" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="15"/>
+      <c r="I82" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="14"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="2">
-        <v>75</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
@@ -3742,17 +3784,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I83" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="15"/>
+      <c r="I83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="14"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="2">
-        <v>76</v>
-      </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
+        <v>74</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
@@ -3761,17 +3803,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I84" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="15"/>
+      <c r="I84" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="14"/>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="2">
-        <v>77</v>
-      </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
@@ -3780,17 +3822,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I85" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="15"/>
+      <c r="I85" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="14"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="2">
-        <v>78</v>
-      </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
+        <v>76</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
@@ -3799,74 +3841,74 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I86" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="15"/>
+      <c r="I86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="14"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="2">
-        <v>79</v>
-      </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2">
-        <f t="shared" ref="H87:H107" si="4">F87*G87</f>
-        <v>0</v>
-      </c>
-      <c r="I87" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="15"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="14"/>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2">
-        <v>80</v>
-      </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
+        <v>78</v>
+      </c>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="15"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="14"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2">
-        <v>81</v>
-      </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
+        <v>79</v>
+      </c>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="15"/>
+        <f t="shared" ref="H89:H109" si="4">F89*G89</f>
+        <v>0</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="14"/>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2">
-        <v>82</v>
-      </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
@@ -3875,17 +3917,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I90" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="15"/>
+      <c r="I90" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="14"/>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2">
-        <v>83</v>
-      </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
+        <v>81</v>
+      </c>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
@@ -3894,17 +3936,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I91" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="15"/>
+      <c r="I91" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="14"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2">
-        <v>84</v>
-      </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
@@ -3913,17 +3955,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I92" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="15"/>
+      <c r="I92" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="14"/>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2">
-        <v>85</v>
-      </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
@@ -3932,17 +3974,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I93" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="15"/>
+      <c r="I93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="14"/>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="2">
-        <v>86</v>
-      </c>
-      <c r="B94" s="5"/>
-      <c r="C94" s="5"/>
+        <v>84</v>
+      </c>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
@@ -3951,17 +3993,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I94" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="15"/>
+      <c r="I94" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="14"/>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="2">
-        <v>87</v>
-      </c>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
+        <v>85</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
@@ -3970,17 +4012,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I95" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="15"/>
+      <c r="I95" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="14"/>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2">
-        <v>88</v>
-      </c>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
@@ -3989,17 +4031,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I96" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="15"/>
+      <c r="I96" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="14"/>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2">
-        <v>89</v>
-      </c>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
@@ -4008,17 +4050,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I97" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="15"/>
+      <c r="I97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="14"/>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2">
-        <v>90</v>
-      </c>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
@@ -4027,17 +4069,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I98" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="15"/>
+      <c r="I98" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="14"/>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2">
-        <v>91</v>
-      </c>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
+        <v>89</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
@@ -4046,17 +4088,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I99" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="15"/>
+      <c r="I99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="14"/>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="2">
-        <v>92</v>
-      </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
@@ -4065,17 +4107,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I100" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="15"/>
+      <c r="I100" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="14"/>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2">
-        <v>93</v>
-      </c>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
@@ -4084,17 +4126,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I101" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="15"/>
+      <c r="I101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="14"/>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2">
-        <v>94</v>
-      </c>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
@@ -4103,17 +4145,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I102" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" s="15"/>
+      <c r="I102" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="14"/>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2">
-        <v>95</v>
-      </c>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
+        <v>93</v>
+      </c>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
@@ -4122,17 +4164,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I103" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" s="15"/>
+      <c r="I103" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="14"/>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2">
-        <v>96</v>
-      </c>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
+        <v>94</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
@@ -4141,17 +4183,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I104" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J104" s="15"/>
+      <c r="I104" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="14"/>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2">
-        <v>97</v>
-      </c>
-      <c r="B105" s="5"/>
-      <c r="C105" s="5"/>
+        <v>95</v>
+      </c>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
@@ -4160,17 +4202,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I105" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J105" s="15"/>
+      <c r="I105" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="14"/>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2">
-        <v>98</v>
-      </c>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
+        <v>96</v>
+      </c>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
@@ -4179,17 +4221,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I106" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J106" s="15"/>
+      <c r="I106" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="14"/>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2">
-        <v>99</v>
-      </c>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
+        <v>97</v>
+      </c>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
@@ -4198,34 +4240,78 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I107" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="15"/>
+      <c r="I107" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="14"/>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="2">
+        <v>98</v>
+      </c>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="14"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="2">
+        <v>99</v>
+      </c>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" s="14"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I107" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I109" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="14">
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A14:A16"/>
+  <mergeCells count="20">
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A15:A17"/>
     <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B15:B17"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C15:C17"/>
     <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J15:J17"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
-      <formula1>$I$2:$I$22</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10 I20 I1:I9 I11:I19 I21:I1048576">
+      <formula1>$I$2:$I$24</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4239,45 +4325,45 @@
   <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="9.37272727272727" style="4"/>
-    <col min="3" max="3" width="9" style="12"/>
-    <col min="4" max="4" width="9" style="4"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="9.37272727272727" style="1"/>
+    <col min="3" max="3" width="9" style="11"/>
+    <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="12.8727272727273" customWidth="1"/>
-    <col min="6" max="8" width="12.8727272727273" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9" style="12"/>
-    <col min="10" max="10" width="68.6272727272727" style="13" customWidth="1"/>
+    <col min="6" max="8" width="12.8727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="11"/>
+    <col min="10" max="10" width="68.6272727272727" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" ht="28" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="11" customFormat="1" ht="28" spans="1:11">
+      <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4288,13 +4374,13 @@
       <c r="B2" s="2">
         <v>601398</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>57</v>
+      <c r="C2" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="15">
         <v>46182</v>
       </c>
       <c r="F2" s="2">
@@ -4307,163 +4393,163 @@
         <f>F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="12"/>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="14"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="5"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="16"/>
+      <c r="E3" s="15"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2">
         <f t="shared" ref="H3:H13" si="0">F3*G3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="15"/>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
       <c r="H4" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="20"/>
+      <c r="I4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="19"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="16"/>
+      <c r="E5" s="15"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="15"/>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="5"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="16"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="15"/>
+      <c r="I6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="14"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="16"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="15"/>
+      <c r="I7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="5"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="16"/>
+      <c r="E8" s="15"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="15"/>
+      <c r="I8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="16"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="15"/>
+      <c r="I9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="15"/>
+      <c r="I10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="14"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2">
@@ -4472,1575 +4558,1575 @@
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="7"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="15"/>
+      <c r="I11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="5"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="7"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="15"/>
+      <c r="I12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="5"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="15"/>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="5"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="6"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2">
         <f t="shared" ref="H10:H55" si="1">F14*G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="15"/>
+      <c r="I14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="14"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="5"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="6"/>
+      <c r="E15" s="5"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="15"/>
+      <c r="I15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="14"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="5"/>
+      <c r="C16" s="4"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="6"/>
+      <c r="E16" s="5"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="15"/>
+      <c r="I16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="14"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="5"/>
+      <c r="C17" s="4"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="6"/>
+      <c r="E17" s="5"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="15"/>
+      <c r="I17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="14"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="6"/>
+      <c r="E18" s="5"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="15"/>
+      <c r="I18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="14"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="5"/>
+      <c r="C19" s="4"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="6"/>
+      <c r="E19" s="5"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="15"/>
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="14"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="5"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="6"/>
+      <c r="E20" s="5"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="15"/>
+      <c r="I20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="14"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="5"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="6"/>
+      <c r="E21" s="5"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="15"/>
+      <c r="I21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="14"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="5"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="6"/>
+      <c r="E22" s="5"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="15"/>
+      <c r="I22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="14"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="5"/>
+      <c r="C23" s="4"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="6"/>
+      <c r="E23" s="5"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="15"/>
+      <c r="I23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="14"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="5"/>
+      <c r="C24" s="4"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="6"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="15"/>
+      <c r="I24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="14"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="5"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="6"/>
+      <c r="E25" s="5"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="15"/>
+      <c r="I25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="14"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="5"/>
+      <c r="C26" s="4"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="6"/>
+      <c r="E26" s="5"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="15"/>
+      <c r="I26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="14"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="5"/>
+      <c r="C27" s="4"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="6"/>
+      <c r="E27" s="5"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="15"/>
+      <c r="I27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="14"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="5"/>
+      <c r="C28" s="4"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="6"/>
+      <c r="E28" s="5"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="15"/>
+      <c r="I28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="14"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="5"/>
+      <c r="C29" s="4"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="6"/>
+      <c r="E29" s="5"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="15"/>
+      <c r="I29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="14"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="5"/>
+      <c r="C30" s="4"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="6"/>
+      <c r="E30" s="5"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="15"/>
+      <c r="I30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="14"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2"/>
-      <c r="C31" s="5"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="6"/>
+      <c r="E31" s="5"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="15"/>
+      <c r="I31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="14"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="5"/>
+      <c r="C32" s="4"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="6"/>
+      <c r="E32" s="5"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="15"/>
+      <c r="I32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="14"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="5"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="6"/>
+      <c r="E33" s="5"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="15"/>
+      <c r="I33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="14"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2"/>
-      <c r="C34" s="5"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="6"/>
+      <c r="E34" s="5"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="15"/>
+      <c r="I34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="14"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="5"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="6"/>
+      <c r="E35" s="5"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="15"/>
+      <c r="I35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="14"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2"/>
-      <c r="C36" s="5"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="6"/>
+      <c r="E36" s="5"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="15"/>
+      <c r="I36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="14"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2"/>
-      <c r="C37" s="5"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="6"/>
+      <c r="E37" s="5"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="15"/>
+      <c r="I37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2"/>
-      <c r="C38" s="5"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="6"/>
+      <c r="E38" s="5"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="15"/>
+      <c r="I38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="14"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2"/>
-      <c r="C39" s="5"/>
+      <c r="C39" s="4"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="6"/>
+      <c r="E39" s="5"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="15"/>
+      <c r="I39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="14"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2"/>
-      <c r="C40" s="5"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="6"/>
+      <c r="E40" s="5"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="15"/>
+      <c r="I40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="14"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2"/>
-      <c r="C41" s="5"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="6"/>
+      <c r="E41" s="5"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="15"/>
+      <c r="I41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="14"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="5"/>
+      <c r="C42" s="4"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="6"/>
+      <c r="E42" s="5"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="15"/>
+      <c r="I42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="14"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="2"/>
-      <c r="C43" s="5"/>
+      <c r="C43" s="4"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="6"/>
+      <c r="E43" s="5"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="15"/>
+      <c r="I43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="14"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="5"/>
+      <c r="C44" s="4"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="6"/>
+      <c r="E44" s="5"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="15"/>
+      <c r="I44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="14"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="2"/>
-      <c r="C45" s="5"/>
+      <c r="C45" s="4"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="6"/>
+      <c r="E45" s="5"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="15"/>
+      <c r="I45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="14"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="2"/>
-      <c r="C46" s="5"/>
+      <c r="C46" s="4"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="6"/>
+      <c r="E46" s="5"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I46" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="15"/>
+      <c r="I46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="14"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="2"/>
-      <c r="C47" s="5"/>
+      <c r="C47" s="4"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="6"/>
+      <c r="E47" s="5"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="15"/>
+      <c r="I47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="14"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="2"/>
-      <c r="C48" s="5"/>
+      <c r="C48" s="4"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="6"/>
+      <c r="E48" s="5"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="15"/>
+      <c r="I48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="14"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="2"/>
-      <c r="C49" s="5"/>
+      <c r="C49" s="4"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="6"/>
+      <c r="E49" s="5"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="15"/>
+      <c r="I49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="14"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="2"/>
-      <c r="C50" s="5"/>
+      <c r="C50" s="4"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="6"/>
+      <c r="E50" s="5"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="15"/>
+      <c r="I50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="14"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="2"/>
-      <c r="C51" s="5"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="6"/>
+      <c r="E51" s="5"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="15"/>
+      <c r="I51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="14"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="2"/>
-      <c r="C52" s="5"/>
+      <c r="C52" s="4"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="6"/>
+      <c r="E52" s="5"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="15"/>
+      <c r="I52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="14"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="2"/>
-      <c r="C53" s="5"/>
+      <c r="C53" s="4"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="6"/>
+      <c r="E53" s="5"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="15"/>
+      <c r="I53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="14"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="2"/>
-      <c r="C54" s="5"/>
+      <c r="C54" s="4"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="6"/>
+      <c r="E54" s="5"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I54" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="15"/>
+      <c r="I54" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="14"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="2"/>
-      <c r="C55" s="5"/>
+      <c r="C55" s="4"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="6"/>
+      <c r="E55" s="5"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I55" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="15"/>
+      <c r="I55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="14"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="2"/>
-      <c r="C56" s="5"/>
+      <c r="C56" s="4"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="6"/>
+      <c r="E56" s="5"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2">
         <f t="shared" ref="H56:H93" si="2">F56*G56</f>
         <v>0</v>
       </c>
-      <c r="I56" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="15"/>
+      <c r="I56" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="14"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="2"/>
-      <c r="C57" s="5"/>
+      <c r="C57" s="4"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="6"/>
+      <c r="E57" s="5"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I57" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="15"/>
+      <c r="I57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="14"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="2"/>
-      <c r="C58" s="5"/>
+      <c r="C58" s="4"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="6"/>
+      <c r="E58" s="5"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I58" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="15"/>
+      <c r="I58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="14"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="2"/>
-      <c r="C59" s="5"/>
+      <c r="C59" s="4"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="6"/>
+      <c r="E59" s="5"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I59" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="15"/>
+      <c r="I59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="14"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="2"/>
-      <c r="C60" s="5"/>
+      <c r="C60" s="4"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="6"/>
+      <c r="E60" s="5"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I60" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="15"/>
+      <c r="I60" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="14"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="2"/>
-      <c r="C61" s="5"/>
+      <c r="C61" s="4"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="6"/>
+      <c r="E61" s="5"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I61" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="15"/>
+      <c r="I61" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="14"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="2"/>
-      <c r="C62" s="5"/>
+      <c r="C62" s="4"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="6"/>
+      <c r="E62" s="5"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="15"/>
+      <c r="I62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="14"/>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="2"/>
-      <c r="C63" s="5"/>
+      <c r="C63" s="4"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="6"/>
+      <c r="E63" s="5"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I63" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="15"/>
+      <c r="I63" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="14"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="2"/>
-      <c r="C64" s="5"/>
+      <c r="C64" s="4"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="6"/>
+      <c r="E64" s="5"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="15"/>
+      <c r="I64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="14"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="2">
         <v>64</v>
       </c>
       <c r="B65" s="2"/>
-      <c r="C65" s="5"/>
+      <c r="C65" s="4"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="6"/>
+      <c r="E65" s="5"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I65" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="15"/>
+      <c r="I65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="14"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="2"/>
-      <c r="C66" s="5"/>
+      <c r="C66" s="4"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="6"/>
+      <c r="E66" s="5"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I66" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="15"/>
+      <c r="I66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="14"/>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" s="2"/>
-      <c r="C67" s="5"/>
+      <c r="C67" s="4"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="6"/>
+      <c r="E67" s="5"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I67" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="15"/>
+      <c r="I67" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="14"/>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" s="2"/>
-      <c r="C68" s="5"/>
+      <c r="C68" s="4"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="6"/>
+      <c r="E68" s="5"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I68" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="15"/>
+      <c r="I68" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="14"/>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="2">
         <v>68</v>
       </c>
       <c r="B69" s="2"/>
-      <c r="C69" s="5"/>
+      <c r="C69" s="4"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="6"/>
+      <c r="E69" s="5"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I69" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="15"/>
+      <c r="I69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="14"/>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" s="2"/>
-      <c r="C70" s="5"/>
+      <c r="C70" s="4"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="6"/>
+      <c r="E70" s="5"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I70" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="15"/>
+      <c r="I70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="14"/>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="2">
         <v>70</v>
       </c>
       <c r="B71" s="2"/>
-      <c r="C71" s="5"/>
+      <c r="C71" s="4"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="6"/>
+      <c r="E71" s="5"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I71" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="15"/>
+      <c r="I71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="14"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" s="2"/>
-      <c r="C72" s="5"/>
+      <c r="C72" s="4"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="6"/>
+      <c r="E72" s="5"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I72" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="15"/>
+      <c r="I72" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="14"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="2">
         <v>72</v>
       </c>
       <c r="B73" s="2"/>
-      <c r="C73" s="5"/>
+      <c r="C73" s="4"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="6"/>
+      <c r="E73" s="5"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I73" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="15"/>
+      <c r="I73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="14"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" s="2"/>
-      <c r="C74" s="5"/>
+      <c r="C74" s="4"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="6"/>
+      <c r="E74" s="5"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I74" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="15"/>
+      <c r="I74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="14"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="2">
         <v>74</v>
       </c>
       <c r="B75" s="2"/>
-      <c r="C75" s="5"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="6"/>
+      <c r="E75" s="5"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I75" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="15"/>
+      <c r="I75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="14"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" s="2"/>
-      <c r="C76" s="5"/>
+      <c r="C76" s="4"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="6"/>
+      <c r="E76" s="5"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I76" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="15"/>
+      <c r="I76" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="14"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="2">
         <v>76</v>
       </c>
       <c r="B77" s="2"/>
-      <c r="C77" s="5"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="6"/>
+      <c r="E77" s="5"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I77" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="15"/>
+      <c r="I77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="14"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="2"/>
-      <c r="C78" s="5"/>
+      <c r="C78" s="4"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="6"/>
+      <c r="E78" s="5"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I78" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="15"/>
+      <c r="I78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="14"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="2"/>
-      <c r="C79" s="5"/>
+      <c r="C79" s="4"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="6"/>
+      <c r="E79" s="5"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I79" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="15"/>
+      <c r="I79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="14"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="2"/>
-      <c r="C80" s="5"/>
+      <c r="C80" s="4"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="6"/>
+      <c r="E80" s="5"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I80" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="15"/>
+      <c r="I80" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="14"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="2"/>
-      <c r="C81" s="5"/>
+      <c r="C81" s="4"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="6"/>
+      <c r="E81" s="5"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I81" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="15"/>
+      <c r="I81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="14"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="2"/>
-      <c r="C82" s="5"/>
+      <c r="C82" s="4"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="6"/>
+      <c r="E82" s="5"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I82" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="15"/>
+      <c r="I82" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="14"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="2"/>
-      <c r="C83" s="5"/>
+      <c r="C83" s="4"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="6"/>
+      <c r="E83" s="5"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I83" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="15"/>
+      <c r="I83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="14"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="2"/>
-      <c r="C84" s="5"/>
+      <c r="C84" s="4"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="6"/>
+      <c r="E84" s="5"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I84" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="15"/>
+      <c r="I84" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="14"/>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="2"/>
-      <c r="C85" s="5"/>
+      <c r="C85" s="4"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="6"/>
+      <c r="E85" s="5"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I85" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="15"/>
+      <c r="I85" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="14"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="2"/>
-      <c r="C86" s="5"/>
+      <c r="C86" s="4"/>
       <c r="D86" s="2"/>
-      <c r="E86" s="6"/>
+      <c r="E86" s="5"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I86" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="15"/>
+      <c r="I86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="14"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="2"/>
-      <c r="C87" s="5"/>
+      <c r="C87" s="4"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="6"/>
+      <c r="E87" s="5"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I87" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="15"/>
+      <c r="I87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="14"/>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="2"/>
-      <c r="C88" s="5"/>
+      <c r="C88" s="4"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="6"/>
+      <c r="E88" s="5"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I88" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="15"/>
+      <c r="I88" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="14"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="2"/>
-      <c r="C89" s="5"/>
+      <c r="C89" s="4"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="6"/>
+      <c r="E89" s="5"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I89" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="15"/>
+      <c r="I89" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="14"/>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" s="2"/>
-      <c r="C90" s="5"/>
+      <c r="C90" s="4"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="6"/>
+      <c r="E90" s="5"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I90" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="15"/>
+      <c r="I90" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="14"/>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" s="2"/>
-      <c r="C91" s="5"/>
+      <c r="C91" s="4"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="6"/>
+      <c r="E91" s="5"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I91" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="15"/>
+      <c r="I91" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="14"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="5"/>
+      <c r="C92" s="4"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="6"/>
+      <c r="E92" s="5"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I92" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="15"/>
+      <c r="I92" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="14"/>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" s="2"/>
-      <c r="C93" s="5"/>
+      <c r="C93" s="4"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="6"/>
+      <c r="E93" s="5"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I93" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="15"/>
+      <c r="I93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="14"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I93" etc:filterBottomFollowUsedRange="0">
@@ -6063,140 +6149,140 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="10.6363636363636"/>
-    <col min="4" max="4" width="9" style="4"/>
+    <col min="4" max="4" width="9" style="1"/>
     <col min="8" max="8" width="22.1272727272727" customWidth="1"/>
-    <col min="9" max="9" width="11.8727272727273" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.8727272727273" style="1" customWidth="1"/>
     <col min="11" max="11" width="10.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>59</v>
+      <c r="B1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>64</v>
       </c>
+      <c r="G1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="I1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="L1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>46188</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="49" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>4300</v>
       </c>
       <c r="F2" s="3">
         <v>4.8581</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>5.17</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>70</v>
+      <c r="H2" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <f>E2*(G2-F2)-I2</f>
         <v>1341.17</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>1308.3</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="7">
         <f>SUM(K2:K4)</f>
         <v>9745.52</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="7">
         <f>SUM(L2)</f>
         <v>9745.52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>46190</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>600172</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>600</v>
       </c>
       <c r="F3" s="3">
         <v>12.2123</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>13</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>70</v>
+      <c r="H3" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <f t="shared" ref="J3:J9" si="0">E3*(G3-F3)-I3</f>
         <v>472.619999999999</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>460.95</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>46199</v>
       </c>
       <c r="C4" s="2">
@@ -6205,184 +6291,184 @@
       <c r="D4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>2400</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>27.6302</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>31</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>71</v>
+      <c r="H4" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="I4" s="2">
         <v>111.25</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <f t="shared" si="0"/>
         <v>7976.27</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>7976.27</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>46213</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>600360</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>1300</v>
       </c>
       <c r="F5" s="2">
         <v>14.6146</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>17.59</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>72</v>
+      <c r="H5" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <f t="shared" si="0"/>
         <v>3868.02</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>3868.02</v>
       </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>46213</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>600745</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>600</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>18.65</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>21.24</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>73</v>
+      <c r="H6" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="I6" s="2">
         <v>19.06</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <f t="shared" si="0"/>
         <v>1534.94</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>1534.94</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="6">
+      <c r="J10" s="4"/>
+      <c r="K10" s="5">
         <f>SUM(K2:K9)</f>
         <v>15148.48</v>
       </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D6" etc:filterBottomFollowUsedRange="0">
@@ -6418,27 +6504,27 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="49" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="1">
         <v>5.13</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>77</v>
+      <c r="E2" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6449,9 +6535,9 @@
         <v>601398</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4">
+        <v>59</v>
+      </c>
+      <c r="D3" s="1">
         <v>7.16</v>
       </c>
       <c r="E3" s="1">
@@ -6483,13 +6569,13 @@
         <v>600982</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5">
         <v>5.02</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:5">

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="定投股票" sheetId="6" r:id="rId3"/>
     <sheet name="已出售" sheetId="3" r:id="rId4"/>
     <sheet name="自选股" sheetId="4" r:id="rId5"/>
+    <sheet name="做T的股票" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$109</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="87">
   <si>
     <t>时间</t>
   </si>
@@ -283,6 +284,21 @@
   </si>
   <si>
     <t>4.5~4.8</t>
+  </si>
+  <si>
+    <t>002716 湖南白银</t>
+  </si>
+  <si>
+    <t>操作时间</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>京东方A</t>
   </si>
 </sst>
 </file>
@@ -962,10 +978,37 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1044,26 +1087,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1648,205 +1676,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6">
+      <c r="A2" s="15">
         <v>46096</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="14">
         <f t="shared" ref="B2:B8" si="0">SUM(D2+C2)</f>
         <v>225842</v>
       </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="C2" s="14">
+        <v>0</v>
+      </c>
+      <c r="D2" s="14">
         <v>225842</v>
       </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" s="14">
+        <v>0</v>
+      </c>
+      <c r="F2" s="14">
         <v>11837</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="14">
         <f t="shared" ref="G2:G8" si="1">SUM(B2+F2-E2)</f>
         <v>237679</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="15">
         <v>46107</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="14">
         <f t="shared" si="0"/>
         <v>236842</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="14">
         <f t="shared" ref="C3:C8" si="2">B2</f>
         <v>225842</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="14">
         <v>11000</v>
       </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="E3" s="14">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14">
         <v>11837</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="14">
         <f t="shared" si="1"/>
         <v>248679</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="6">
+      <c r="A4" s="15">
         <v>46101</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="14">
         <f t="shared" si="0"/>
         <v>256842</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="14">
         <f t="shared" si="2"/>
         <v>236842</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="14">
         <v>20000</v>
       </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="14">
+        <v>0</v>
+      </c>
+      <c r="F4" s="14">
         <v>11837</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="14">
         <f t="shared" si="1"/>
         <v>268679</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="6">
+      <c r="A5" s="15">
         <v>46177</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="14">
         <f t="shared" si="0"/>
         <v>266842</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="14">
         <f t="shared" si="2"/>
         <v>256842</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="14">
         <v>10000</v>
       </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5" s="14">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14">
         <v>11837</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="14">
         <f t="shared" si="1"/>
         <v>278679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="6">
+      <c r="A6" s="15">
         <v>46182</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="14">
         <f t="shared" si="0"/>
         <v>276842</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="14">
         <f t="shared" si="2"/>
         <v>266842</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="14">
         <v>10000</v>
       </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="14">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14">
         <v>11873</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="14">
         <f t="shared" si="1"/>
         <v>288715</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="6">
+      <c r="A7" s="15">
         <v>46184</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="14">
         <f t="shared" si="0"/>
         <v>281842</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="14">
         <f t="shared" si="2"/>
         <v>276842</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="14">
         <v>5000</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
         <v>11873</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="14">
         <f t="shared" si="1"/>
         <v>293715</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="6">
+      <c r="A8" s="15">
         <v>46190</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="14">
         <f t="shared" si="0"/>
         <v>282342</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="14">
         <f t="shared" si="2"/>
         <v>281842</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="14">
         <v>500</v>
       </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="14">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14">
         <v>11873</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="14">
         <f t="shared" si="1"/>
         <v>294215</v>
       </c>
@@ -1863,2425 +1891,2425 @@
   <dimension ref="A1:K109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="9.37272727272727" style="11"/>
-    <col min="3" max="3" width="9" style="11"/>
-    <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="8" width="12.8727272727273" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="11"/>
-    <col min="10" max="10" width="68.6272727272727" style="12" customWidth="1"/>
+    <col min="1" max="1" width="9" style="10"/>
+    <col min="2" max="2" width="9.37272727272727" style="20"/>
+    <col min="3" max="3" width="9" style="20"/>
+    <col min="4" max="4" width="9" style="10"/>
+    <col min="5" max="8" width="12.8727272727273" style="10" customWidth="1"/>
+    <col min="9" max="9" width="9" style="20"/>
+    <col min="10" max="10" width="68.6272727272727" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" ht="28" spans="1:11">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="20" customFormat="1" ht="28" spans="1:11">
+      <c r="A1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="23" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="2">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="13">
         <v>300323</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="11">
         <v>1</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="30">
         <v>46182</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="11">
         <v>16.6114</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="11">
         <v>1600</v>
       </c>
-      <c r="H2" s="2">
-        <f t="shared" ref="H2:H12" si="0">F2*G2</f>
+      <c r="H2" s="11">
+        <f t="shared" ref="H2:H20" si="0">F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="14" t="s">
+      <c r="I2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="11"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="2">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="13">
         <v>600740</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="11">
         <v>1</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="30">
         <v>46182</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="11">
         <v>4.1541</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="11">
         <v>1800</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="11">
         <f t="shared" si="0"/>
         <v>7477.38</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="14" t="s">
+      <c r="I3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="23" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="22">
+      <c r="A4" s="31">
         <v>3</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="25">
         <v>1</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="33">
         <v>46182</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="25">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="25">
         <v>4300</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="25">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="34" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="2">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="13">
         <v>601990</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="30">
         <v>46182</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="11">
         <v>9.9227</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="11">
         <v>500</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="11">
         <f t="shared" si="0"/>
         <v>4961.35</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="I5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="23" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="2">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="13">
         <v>600059</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="11">
         <v>1</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="30">
         <v>46182</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="11">
         <v>10.9008</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="11">
         <v>1000</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="11">
         <f t="shared" si="0"/>
         <v>10900.8</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="14" t="s">
+      <c r="I6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="23" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="2">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="11">
         <v>1</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="30">
         <v>46182</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="11">
         <v>9.6507</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="11">
         <v>1000</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="11">
         <f t="shared" si="0"/>
         <v>9650.7</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="14" t="s">
+      <c r="I7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="23" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="2">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="13">
         <v>601179</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="30">
         <v>46182</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="11">
         <v>20.12</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="11">
         <v>700</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="11">
         <f t="shared" si="0"/>
         <v>14084</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="14" t="s">
+      <c r="I8" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="23" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="26">
+      <c r="A9" s="35">
         <v>8</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="16">
         <v>603258</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="11">
         <v>1</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="30">
         <v>46182</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="11">
         <v>20.6888</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="11">
         <v>900</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="11">
         <f t="shared" si="0"/>
         <v>18619.92</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="14" t="s">
+      <c r="I9" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="2">
+      <c r="A10" s="36"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="11">
         <v>2</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="30">
         <v>46233</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="11">
         <v>12.9</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="11">
         <v>500</v>
       </c>
-      <c r="H10" s="2">
-        <f>F10*G10</f>
+      <c r="H10" s="11">
+        <f t="shared" si="0"/>
         <v>6450</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="30"/>
+      <c r="I10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="37"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="31">
+      <c r="A11" s="35">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="16">
         <v>600422</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="11">
         <v>1</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="30">
         <v>46182</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="11">
         <v>21.0619</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="11">
         <v>600</v>
       </c>
-      <c r="H11" s="2">
-        <f>F11*G11</f>
+      <c r="H11" s="11">
+        <f t="shared" si="0"/>
         <v>12637.14</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="32" t="s">
+      <c r="I11" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="37" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="33"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="34">
+      <c r="A12" s="36"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="38">
         <v>2</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="39">
         <v>46188</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="38">
         <v>8.5</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="38">
         <v>600</v>
       </c>
-      <c r="H12" s="34">
-        <f>F12*G12</f>
+      <c r="H12" s="38">
+        <f t="shared" si="0"/>
         <v>5100</v>
       </c>
-      <c r="I12" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="37"/>
+      <c r="I12" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="41"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="38"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="34">
+      <c r="A13" s="42"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="38">
         <v>3</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="39">
         <v>46226</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="38">
         <v>9</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="38">
         <v>-600</v>
       </c>
-      <c r="H13" s="34">
-        <f>F13*G13</f>
+      <c r="H13" s="38">
+        <f t="shared" si="0"/>
         <v>-5400</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="I13" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="37"/>
+      <c r="J13" s="41"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="2">
+      <c r="A14" s="11">
         <v>10</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="13">
         <v>600879</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="11">
         <v>1</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="30">
         <v>46182</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="11">
         <v>26.2661</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="11">
         <v>700</v>
       </c>
-      <c r="H14" s="2">
-        <f>F14*G14</f>
+      <c r="H14" s="11">
+        <f t="shared" si="0"/>
         <v>18386.27</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="14" t="s">
+      <c r="I14" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="23" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="31">
+      <c r="A15" s="35">
         <v>11</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="16">
         <v>601066</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="11">
         <v>1</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="30">
         <v>46182</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="11">
         <v>27.6302</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="11">
         <v>3400</v>
       </c>
-      <c r="H15" s="2">
-        <f>F15*G15</f>
+      <c r="H15" s="11">
+        <f t="shared" si="0"/>
         <v>93942.68</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="39" t="s">
+      <c r="I15" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="43" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="33"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="34">
+      <c r="A16" s="36"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="38">
         <v>2</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="39">
         <v>46192</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="38">
         <v>31</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="38">
         <v>-2400</v>
       </c>
-      <c r="H16" s="34">
-        <f>F16*G16</f>
+      <c r="H16" s="38">
+        <f t="shared" si="0"/>
         <v>-74400</v>
       </c>
-      <c r="I16" s="36" t="s">
+      <c r="I16" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="40"/>
+      <c r="J16" s="44"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="38"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="2">
+      <c r="A17" s="42"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="11">
         <v>3</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="30">
         <v>46202</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="11">
         <v>29.3</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="11">
         <v>1000</v>
       </c>
-      <c r="H17" s="2">
-        <f>F17*G17</f>
+      <c r="H17" s="11">
+        <f t="shared" si="0"/>
         <v>29300</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="37"/>
+      <c r="I17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="41"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="2">
+      <c r="A18" s="11">
         <v>12</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="11">
         <v>1</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="30">
         <v>46182</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="11">
         <v>18.3681</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="11">
         <v>1000</v>
       </c>
-      <c r="H18" s="2">
-        <f>F18*G18</f>
+      <c r="H18" s="11">
+        <f t="shared" si="0"/>
         <v>18368.1</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="14" t="s">
+      <c r="I18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="23" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="26">
+      <c r="A19" s="35">
         <v>13</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="16">
         <v>300589</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="11">
         <v>1</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="30">
         <v>46182</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="11">
         <v>22.8225</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="11">
         <v>1200</v>
       </c>
-      <c r="H19" s="2">
-        <f>F19*G19</f>
+      <c r="H19" s="11">
+        <f t="shared" si="0"/>
         <v>27387</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="14" t="s">
+      <c r="I19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="23" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="2">
+      <c r="A20" s="36"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="11">
         <v>2</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="30">
         <v>46233</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="11">
         <v>12.55</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="11">
         <v>600</v>
       </c>
-      <c r="H20" s="2">
-        <f>F20*G20</f>
+      <c r="H20" s="11">
+        <f t="shared" si="0"/>
         <v>7530</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="14"/>
+      <c r="I20" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="23"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="31">
+      <c r="A21" s="35">
         <v>14</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="16">
         <v>300129</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="11">
         <v>1</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="30">
         <v>46182</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="11">
         <v>14.9016</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="11">
         <v>2300</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="11">
         <f t="shared" ref="H21:H28" si="1">F21*G21</f>
         <v>34273.68</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="14" t="s">
+      <c r="I21" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="23" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="41"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="2">
+      <c r="A22" s="45"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="11">
         <v>2</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="30">
         <v>46223</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="11">
         <v>7.35</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="11">
         <v>700</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="11">
         <f t="shared" si="1"/>
         <v>5145</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="14"/>
+      <c r="I22" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="23"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="43">
+      <c r="A23" s="47">
         <v>15</v>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="48">
         <v>600172</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="38">
         <v>1</v>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="39">
         <v>46188</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="38">
         <v>12.2123</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="38">
         <v>600</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="38">
         <f t="shared" si="1"/>
         <v>7327.38</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="I23" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="45" t="s">
+      <c r="J23" s="49" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="2">
+      <c r="A24" s="11">
         <v>16</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="13">
         <v>600745</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="11">
         <v>1</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="30">
         <v>46189</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="11">
         <v>18.6687</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="11">
         <v>800</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="11">
         <f t="shared" si="1"/>
         <v>14934.96</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="14" t="s">
+      <c r="I24" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="2">
-        <v>17</v>
-      </c>
-      <c r="B25" s="11">
+      <c r="A25" s="11">
+        <v>17</v>
+      </c>
+      <c r="B25" s="20">
         <v>600115</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="11">
         <v>1</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="30">
         <v>46203</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="11">
         <v>3.7838</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="11">
         <v>3200</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="11">
         <f t="shared" si="1"/>
         <v>12108.16</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="14"/>
+      <c r="I25" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="23"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="31">
+      <c r="A26" s="35">
         <v>18</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="16">
         <v>600360</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="11">
         <v>1</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="30">
         <v>46203</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="11">
         <v>14.6146</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="11">
         <v>1800</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="11">
         <f t="shared" si="1"/>
         <v>26306.28</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="14"/>
+      <c r="I26" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="23"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="33"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="34">
+      <c r="A27" s="36"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="38">
         <v>2</v>
       </c>
-      <c r="E27" s="46">
+      <c r="E27" s="50">
         <v>46213</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="28">
         <v>17.59</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="38">
         <v>-1300</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="38">
         <f t="shared" si="1"/>
         <v>-22867</v>
       </c>
-      <c r="I27" s="36" t="s">
+      <c r="I27" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J27" s="14"/>
+      <c r="J27" s="23"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="38"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="2">
+      <c r="A28" s="42"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="11">
         <v>3</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="30">
         <v>46226</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="11">
         <v>10</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="11">
         <v>500</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="11">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="14"/>
+      <c r="I28" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="23"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="2">
+      <c r="A29" s="11">
         <v>19</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="11">
         <v>1</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="30">
         <v>46204</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="11">
         <v>8.5585</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="11">
         <v>1700</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="11">
         <f t="shared" ref="H29:H56" si="2">F29*G29</f>
         <v>14549.45</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="14"/>
+      <c r="I29" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="23"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="2">
+      <c r="A30" s="11">
         <v>20</v>
       </c>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="11">
         <v>1</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="30">
         <v>46227</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="11">
         <v>10.2102</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="11">
         <v>1000</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="11">
         <f t="shared" si="2"/>
         <v>10210.2</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="14"/>
+      <c r="I30" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="23"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="2">
+      <c r="A31" s="11">
         <v>21</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2">
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="14"/>
+      <c r="I31" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="23"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="2">
+      <c r="A32" s="11">
         <v>22</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2">
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="14"/>
+      <c r="I32" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="23"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="2">
+      <c r="A33" s="11">
         <v>23</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2">
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="14"/>
+      <c r="I33" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="23"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="2">
+      <c r="A34" s="11">
         <v>24</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2">
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="14"/>
+      <c r="I34" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="23"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="2">
+      <c r="A35" s="11">
         <v>25</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2">
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="14"/>
+      <c r="I35" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="23"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="2">
+      <c r="A36" s="11">
         <v>26</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="14"/>
+      <c r="I36" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="23"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="2">
+      <c r="A37" s="11">
         <v>27</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2">
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="14"/>
+      <c r="I37" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="23"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="2">
+      <c r="A38" s="11">
         <v>28</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2">
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="14"/>
+      <c r="I38" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="23"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="2">
+      <c r="A39" s="11">
         <v>29</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2">
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="14"/>
+      <c r="I39" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="23"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="2">
+      <c r="A40" s="11">
         <v>30</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2">
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="14"/>
+      <c r="I40" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="23"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="2">
+      <c r="A41" s="11">
         <v>31</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2">
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="14"/>
+      <c r="I41" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="23"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="2">
+      <c r="A42" s="11">
         <v>32</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2">
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="14"/>
+      <c r="I42" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="23"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="2">
+      <c r="A43" s="11">
         <v>33</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="14"/>
+      <c r="I43" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="23"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="2">
+      <c r="A44" s="11">
         <v>34</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2">
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="14"/>
+      <c r="I44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="23"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="2">
+      <c r="A45" s="11">
         <v>35</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2">
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="14"/>
+      <c r="I45" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="23"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="2">
+      <c r="A46" s="11">
         <v>36</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2">
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="14"/>
+      <c r="I46" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="23"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="2">
+      <c r="A47" s="11">
         <v>37</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2">
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="14"/>
+      <c r="I47" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="23"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="2">
+      <c r="A48" s="11">
         <v>38</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2">
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I48" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="14"/>
+      <c r="I48" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="23"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="2">
+      <c r="A49" s="11">
         <v>39</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2">
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="14"/>
+      <c r="I49" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="23"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="2">
+      <c r="A50" s="11">
         <v>40</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2">
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="14"/>
+      <c r="I50" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="23"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="2">
+      <c r="A51" s="11">
         <v>41</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2">
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="14"/>
+      <c r="I51" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="23"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="2">
+      <c r="A52" s="11">
         <v>42</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2">
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="14"/>
+      <c r="I52" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="23"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="2">
+      <c r="A53" s="11">
         <v>43</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2">
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="14"/>
+      <c r="I53" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="23"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="2">
+      <c r="A54" s="11">
         <v>44</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2">
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="14"/>
+      <c r="I54" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="23"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="2">
+      <c r="A55" s="11">
         <v>45</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2">
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="14"/>
+      <c r="I55" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="23"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="2">
+      <c r="A56" s="11">
         <v>46</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2">
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="14"/>
+      <c r="I56" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="23"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="2">
+      <c r="A57" s="11">
         <v>47</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2">
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11">
         <f t="shared" ref="H57:H88" si="3">F57*G57</f>
         <v>0</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="14"/>
+      <c r="I57" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="23"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="2">
+      <c r="A58" s="11">
         <v>48</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2">
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="14"/>
+      <c r="I58" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="23"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="2">
+      <c r="A59" s="11">
         <v>49</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2">
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="14"/>
+      <c r="I59" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="23"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="2">
+      <c r="A60" s="11">
         <v>50</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2">
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="14"/>
+      <c r="I60" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="23"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="2">
+      <c r="A61" s="11">
         <v>51</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2">
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="14"/>
+      <c r="I61" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="23"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="2">
+      <c r="A62" s="11">
         <v>52</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2">
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I62" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="14"/>
+      <c r="I62" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="23"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="2">
+      <c r="A63" s="11">
         <v>53</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2">
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="14"/>
+      <c r="I63" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="23"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="2">
+      <c r="A64" s="11">
         <v>54</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2">
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="14"/>
+      <c r="I64" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="23"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="2">
+      <c r="A65" s="11">
         <v>55</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2">
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I65" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="14"/>
+      <c r="I65" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="23"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="2">
+      <c r="A66" s="11">
         <v>56</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2">
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I66" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="14"/>
+      <c r="I66" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="23"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="2">
+      <c r="A67" s="11">
         <v>57</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2">
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I67" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="14"/>
+      <c r="I67" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="23"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="2">
+      <c r="A68" s="11">
         <v>58</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2">
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="14"/>
+      <c r="I68" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="23"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="2">
+      <c r="A69" s="11">
         <v>59</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2">
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I69" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="14"/>
+      <c r="I69" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="23"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="2">
+      <c r="A70" s="11">
         <v>60</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2">
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I70" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="14"/>
+      <c r="I70" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="23"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="2">
+      <c r="A71" s="11">
         <v>61</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2">
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I71" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="14"/>
+      <c r="I71" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="23"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="2">
+      <c r="A72" s="11">
         <v>62</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2">
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="14"/>
+      <c r="I72" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="23"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="2">
+      <c r="A73" s="11">
         <v>63</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2">
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I73" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="14"/>
+      <c r="I73" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="23"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="2">
+      <c r="A74" s="11">
         <v>64</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2">
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I74" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="14"/>
+      <c r="I74" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="23"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="2">
+      <c r="A75" s="11">
         <v>65</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2">
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="14"/>
+      <c r="I75" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="23"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="2">
+      <c r="A76" s="11">
         <v>66</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2">
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I76" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="14"/>
+      <c r="I76" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="23"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="2">
+      <c r="A77" s="11">
         <v>67</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2">
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="14"/>
+      <c r="I77" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="23"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="2">
+      <c r="A78" s="11">
         <v>68</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2">
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I78" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="14"/>
+      <c r="I78" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="23"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="2">
+      <c r="A79" s="11">
         <v>69</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2">
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I79" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="14"/>
+      <c r="I79" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="23"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="2">
+      <c r="A80" s="11">
         <v>70</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2">
+      <c r="B80" s="13"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="14"/>
+      <c r="I80" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="23"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="2">
+      <c r="A81" s="11">
         <v>71</v>
       </c>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2">
+      <c r="B81" s="13"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I81" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="14"/>
+      <c r="I81" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="23"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="2">
+      <c r="A82" s="11">
         <v>72</v>
       </c>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2">
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I82" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="14"/>
+      <c r="I82" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="23"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="2">
+      <c r="A83" s="11">
         <v>73</v>
       </c>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2">
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I83" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="14"/>
+      <c r="I83" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="23"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="2">
+      <c r="A84" s="11">
         <v>74</v>
       </c>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2">
+      <c r="B84" s="13"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I84" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="14"/>
+      <c r="I84" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="23"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="2">
+      <c r="A85" s="11">
         <v>75</v>
       </c>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2">
+      <c r="B85" s="13"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I85" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="14"/>
+      <c r="I85" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="23"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="2">
+      <c r="A86" s="11">
         <v>76</v>
       </c>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2">
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I86" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="14"/>
+      <c r="I86" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="23"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="2">
+      <c r="A87" s="11">
         <v>77</v>
       </c>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2">
+      <c r="B87" s="13"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I87" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="14"/>
+      <c r="I87" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="23"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="2">
+      <c r="A88" s="11">
         <v>78</v>
       </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2">
+      <c r="B88" s="13"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I88" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="14"/>
+      <c r="I88" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="23"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="2">
+      <c r="A89" s="11">
         <v>79</v>
       </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2">
+      <c r="B89" s="13"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11">
         <f t="shared" ref="H89:H109" si="4">F89*G89</f>
         <v>0</v>
       </c>
-      <c r="I89" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="14"/>
+      <c r="I89" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="23"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="2">
+      <c r="A90" s="11">
         <v>80</v>
       </c>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2">
+      <c r="B90" s="13"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I90" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="14"/>
+      <c r="I90" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="23"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="2">
+      <c r="A91" s="11">
         <v>81</v>
       </c>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2">
+      <c r="B91" s="13"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="14"/>
+      <c r="I91" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="23"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="2">
+      <c r="A92" s="11">
         <v>82</v>
       </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2">
+      <c r="B92" s="13"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I92" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="14"/>
+      <c r="I92" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="23"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="2">
+      <c r="A93" s="11">
         <v>83</v>
       </c>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2">
+      <c r="B93" s="13"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I93" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="14"/>
+      <c r="I93" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="23"/>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="2">
+      <c r="A94" s="11">
         <v>84</v>
       </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2">
+      <c r="B94" s="13"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I94" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="14"/>
+      <c r="I94" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="23"/>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="2">
+      <c r="A95" s="11">
         <v>85</v>
       </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2">
+      <c r="B95" s="13"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="11"/>
+      <c r="H95" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I95" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="14"/>
+      <c r="I95" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="23"/>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="2">
+      <c r="A96" s="11">
         <v>86</v>
       </c>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2">
+      <c r="B96" s="13"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I96" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="14"/>
+      <c r="I96" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="23"/>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="2">
+      <c r="A97" s="11">
         <v>87</v>
       </c>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2">
+      <c r="B97" s="13"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I97" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="14"/>
+      <c r="I97" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="23"/>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="2">
+      <c r="A98" s="11">
         <v>88</v>
       </c>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2">
+      <c r="B98" s="13"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I98" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="14"/>
+      <c r="I98" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="23"/>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="2">
+      <c r="A99" s="11">
         <v>89</v>
       </c>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2">
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
+      <c r="G99" s="11"/>
+      <c r="H99" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I99" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="14"/>
+      <c r="I99" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="23"/>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="2">
+      <c r="A100" s="11">
         <v>90</v>
       </c>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2">
+      <c r="B100" s="13"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="11"/>
+      <c r="H100" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I100" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="14"/>
+      <c r="I100" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="23"/>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="2">
+      <c r="A101" s="11">
         <v>91</v>
       </c>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2">
+      <c r="B101" s="13"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I101" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="14"/>
+      <c r="I101" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="23"/>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="2">
+      <c r="A102" s="11">
         <v>92</v>
       </c>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2">
+      <c r="B102" s="13"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I102" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" s="14"/>
+      <c r="I102" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="23"/>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="2">
+      <c r="A103" s="11">
         <v>93</v>
       </c>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2">
+      <c r="B103" s="13"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="11"/>
+      <c r="H103" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I103" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" s="14"/>
+      <c r="I103" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="23"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="2">
+      <c r="A104" s="11">
         <v>94</v>
       </c>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2">
+      <c r="B104" s="13"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="11"/>
+      <c r="G104" s="11"/>
+      <c r="H104" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I104" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J104" s="14"/>
+      <c r="I104" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="23"/>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="2">
+      <c r="A105" s="11">
         <v>95</v>
       </c>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2">
+      <c r="B105" s="13"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="11"/>
+      <c r="H105" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I105" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J105" s="14"/>
+      <c r="I105" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="23"/>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="2">
+      <c r="A106" s="11">
         <v>96</v>
       </c>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2">
+      <c r="B106" s="13"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
+      <c r="H106" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I106" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J106" s="14"/>
+      <c r="I106" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="23"/>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="2">
+      <c r="A107" s="11">
         <v>97</v>
       </c>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2">
+      <c r="B107" s="13"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I107" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="14"/>
+      <c r="I107" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="23"/>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="2">
+      <c r="A108" s="11">
         <v>98</v>
       </c>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2">
+      <c r="B108" s="13"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I108" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J108" s="14"/>
+      <c r="I108" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="23"/>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="2">
+      <c r="A109" s="11">
         <v>99</v>
       </c>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2">
+      <c r="B109" s="13"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
+      <c r="G109" s="11"/>
+      <c r="H109" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I109" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J109" s="14"/>
+      <c r="I109" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" s="23"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I109" etc:filterBottomFollowUsedRange="0">
@@ -4310,7 +4338,7 @@
     <mergeCell ref="J15:J17"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10 I20 I1:I9 I11:I19 I21:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
       <formula1>$I$2:$I$24</formula1>
     </dataValidation>
   </dataValidations>
@@ -4325,1808 +4353,1808 @@
   <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="9.37272727272727" style="1"/>
-    <col min="3" max="3" width="9" style="11"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="10"/>
+    <col min="2" max="2" width="9.37272727272727" style="10"/>
+    <col min="3" max="3" width="9" style="20"/>
+    <col min="4" max="4" width="9" style="10"/>
     <col min="5" max="5" width="12.8727272727273" customWidth="1"/>
-    <col min="6" max="8" width="12.8727272727273" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="11"/>
-    <col min="10" max="10" width="68.6272727272727" style="12" customWidth="1"/>
+    <col min="6" max="8" width="12.8727272727273" style="10" customWidth="1"/>
+    <col min="9" max="9" width="9" style="20"/>
+    <col min="10" max="10" width="68.6272727272727" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" ht="28" spans="1:11">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="20" customFormat="1" ht="28" spans="1:11">
+      <c r="A1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="23" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="2">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="11">
         <v>601398</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="11">
         <v>1</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="24">
         <v>46182</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="11">
         <v>16.6114</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="11">
         <v>1600</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="11">
         <f>F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="11"/>
+      <c r="I2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="2">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2">
+      <c r="B3" s="11"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11">
         <f t="shared" ref="H3:H13" si="0">F3*G3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="14"/>
+      <c r="I3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="23"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="2">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="2">
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="19"/>
+      <c r="I4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="2">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="B5" s="11"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="14"/>
+      <c r="I5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="2">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="B6" s="11"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="14"/>
+      <c r="I6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="2">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
+      <c r="B7" s="11"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="14"/>
+      <c r="I7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="23"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="2">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
+      <c r="B8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="14"/>
+      <c r="I8" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="23"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="2">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2">
+      <c r="B9" s="11"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="14"/>
+      <c r="I9" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="23"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="2">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2">
+      <c r="B10" s="11"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="14"/>
+      <c r="I10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="23"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="2">
+      <c r="A11" s="11">
         <v>10</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2">
+      <c r="D11" s="11"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="14"/>
+      <c r="I11" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="23"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="2">
+      <c r="A12" s="11">
         <v>11</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2">
+      <c r="B12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="14"/>
+      <c r="I12" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="23"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="2">
+      <c r="A13" s="11">
         <v>12</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2">
+      <c r="B13" s="11"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="14"/>
+      <c r="I13" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="2">
+      <c r="A14" s="11">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2">
+      <c r="B14" s="11"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11">
         <f t="shared" ref="H10:H55" si="1">F14*G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="14"/>
+      <c r="I14" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="23"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="2">
+      <c r="A15" s="11">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2">
+      <c r="B15" s="11"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="14"/>
+      <c r="I15" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="23"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="2">
+      <c r="A16" s="11">
         <v>15</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2">
+      <c r="B16" s="11"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="14"/>
+      <c r="I16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="2">
+      <c r="A17" s="11">
         <v>16</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2">
+      <c r="B17" s="11"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="14"/>
+      <c r="I17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="23"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="14"/>
+      <c r="I18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="23"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="2">
+      <c r="A19" s="11">
         <v>18</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2">
+      <c r="B19" s="11"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="14"/>
+      <c r="I19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="23"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="2">
+      <c r="A20" s="11">
         <v>19</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2">
+      <c r="B20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="14"/>
+      <c r="I20" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="23"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="2">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2">
+      <c r="B21" s="11"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="14"/>
+      <c r="I21" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="23"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="2">
+      <c r="A22" s="11">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2">
+      <c r="B22" s="11"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="14"/>
+      <c r="I22" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="23"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="2">
+      <c r="A23" s="11">
         <v>22</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2">
+      <c r="B23" s="11"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="14"/>
+      <c r="I23" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="23"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="2">
+      <c r="A24" s="11">
         <v>23</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2">
+      <c r="B24" s="11"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="14"/>
+      <c r="I24" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="23"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="2">
+      <c r="A25" s="11">
         <v>24</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2">
+      <c r="B25" s="11"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="14"/>
+      <c r="I25" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="23"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="2">
+      <c r="A26" s="11">
         <v>25</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2">
+      <c r="B26" s="11"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="14"/>
+      <c r="I26" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="23"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="2">
+      <c r="A27" s="11">
         <v>26</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2">
+      <c r="B27" s="11"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="14"/>
+      <c r="I27" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="23"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="2">
+      <c r="A28" s="11">
         <v>27</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2">
+      <c r="B28" s="11"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="14"/>
+      <c r="I28" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="23"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="2">
+      <c r="A29" s="11">
         <v>28</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2">
+      <c r="B29" s="11"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="14"/>
+      <c r="I29" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="23"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="2">
+      <c r="A30" s="11">
         <v>29</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2">
+      <c r="B30" s="11"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="14"/>
+      <c r="I30" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="23"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="2">
+      <c r="A31" s="11">
         <v>30</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2">
+      <c r="B31" s="11"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="14"/>
+      <c r="I31" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="23"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="2">
+      <c r="A32" s="11">
         <v>31</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2">
+      <c r="B32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="14"/>
+      <c r="I32" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="23"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="2">
+      <c r="A33" s="11">
         <v>32</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2">
+      <c r="B33" s="11"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="14"/>
+      <c r="I33" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="23"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="2">
+      <c r="A34" s="11">
         <v>33</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2">
+      <c r="B34" s="11"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="14"/>
+      <c r="I34" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="23"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="2">
+      <c r="A35" s="11">
         <v>34</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2">
+      <c r="B35" s="11"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="14"/>
+      <c r="I35" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="23"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="2">
+      <c r="A36" s="11">
         <v>35</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2">
+      <c r="B36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="14"/>
+      <c r="I36" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="23"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="2">
+      <c r="A37" s="11">
         <v>36</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2">
+      <c r="B37" s="11"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="14"/>
+      <c r="I37" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="23"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="2">
+      <c r="A38" s="11">
         <v>37</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2">
+      <c r="B38" s="11"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="14"/>
+      <c r="I38" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="23"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="2">
+      <c r="A39" s="11">
         <v>38</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2">
+      <c r="B39" s="11"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="14"/>
+      <c r="I39" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="23"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="2">
+      <c r="A40" s="11">
         <v>39</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2">
+      <c r="B40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="14"/>
+      <c r="I40" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="23"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="2">
+      <c r="A41" s="11">
         <v>40</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2">
+      <c r="B41" s="11"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="14"/>
+      <c r="I41" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="23"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="2">
+      <c r="A42" s="11">
         <v>41</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2">
+      <c r="B42" s="11"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="14"/>
+      <c r="I42" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="23"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="2">
+      <c r="A43" s="11">
         <v>42</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2">
+      <c r="B43" s="11"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="14"/>
+      <c r="I43" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="23"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="2">
+      <c r="A44" s="11">
         <v>43</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2">
+      <c r="B44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="14"/>
+      <c r="I44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="23"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="2">
+      <c r="A45" s="11">
         <v>44</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2">
+      <c r="B45" s="11"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="14"/>
+      <c r="I45" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="23"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="2">
+      <c r="A46" s="11">
         <v>45</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2">
+      <c r="B46" s="11"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="14"/>
+      <c r="I46" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="23"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="2">
+      <c r="A47" s="11">
         <v>46</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2">
+      <c r="B47" s="11"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="14"/>
+      <c r="I47" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="23"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="2">
+      <c r="A48" s="11">
         <v>47</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2">
+      <c r="B48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I48" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="14"/>
+      <c r="I48" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="23"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="2">
+      <c r="A49" s="11">
         <v>48</v>
       </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2">
+      <c r="B49" s="11"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="14"/>
+      <c r="I49" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="23"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="2">
+      <c r="A50" s="11">
         <v>49</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2">
+      <c r="B50" s="11"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="14"/>
+      <c r="I50" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="23"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="2">
+      <c r="A51" s="11">
         <v>50</v>
       </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2">
+      <c r="B51" s="11"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="14"/>
+      <c r="I51" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="23"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="2">
+      <c r="A52" s="11">
         <v>51</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2">
+      <c r="B52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="14"/>
+      <c r="I52" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="23"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="2">
+      <c r="A53" s="11">
         <v>52</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2">
+      <c r="B53" s="11"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="14"/>
+      <c r="I53" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="23"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="2">
+      <c r="A54" s="11">
         <v>53</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2">
+      <c r="B54" s="11"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="14"/>
+      <c r="I54" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="23"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="2">
+      <c r="A55" s="11">
         <v>54</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2">
+      <c r="B55" s="11"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="14"/>
+      <c r="I55" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="23"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="2">
+      <c r="A56" s="11">
         <v>55</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2">
+      <c r="B56" s="11"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11">
         <f t="shared" ref="H56:H93" si="2">F56*G56</f>
         <v>0</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="14"/>
+      <c r="I56" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="23"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="2">
+      <c r="A57" s="11">
         <v>56</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2">
+      <c r="B57" s="11"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="14"/>
+      <c r="I57" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="23"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="2">
+      <c r="A58" s="11">
         <v>57</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2">
+      <c r="B58" s="11"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="14"/>
+      <c r="I58" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="23"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="2">
+      <c r="A59" s="11">
         <v>58</v>
       </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2">
+      <c r="B59" s="11"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="14"/>
+      <c r="I59" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="23"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="2">
+      <c r="A60" s="11">
         <v>59</v>
       </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2">
+      <c r="B60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="14"/>
+      <c r="I60" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="23"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="2">
+      <c r="A61" s="11">
         <v>60</v>
       </c>
-      <c r="B61" s="2"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2">
+      <c r="B61" s="11"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="14"/>
+      <c r="I61" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="23"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="2">
+      <c r="A62" s="11">
         <v>61</v>
       </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2">
+      <c r="B62" s="11"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I62" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="14"/>
+      <c r="I62" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="23"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="2">
+      <c r="A63" s="11">
         <v>62</v>
       </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2">
+      <c r="B63" s="11"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="14"/>
+      <c r="I63" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="23"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="2">
+      <c r="A64" s="11">
         <v>63</v>
       </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2">
+      <c r="B64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="14"/>
+      <c r="I64" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="23"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="2">
+      <c r="A65" s="11">
         <v>64</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2">
+      <c r="B65" s="11"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I65" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="14"/>
+      <c r="I65" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="23"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="2">
+      <c r="A66" s="11">
         <v>65</v>
       </c>
-      <c r="B66" s="2"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2">
+      <c r="B66" s="11"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I66" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="14"/>
+      <c r="I66" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="23"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="2">
+      <c r="A67" s="11">
         <v>66</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2">
+      <c r="B67" s="11"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I67" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="14"/>
+      <c r="I67" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="23"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="2">
+      <c r="A68" s="11">
         <v>67</v>
       </c>
-      <c r="B68" s="2"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2">
+      <c r="B68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="14"/>
+      <c r="I68" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="23"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="2">
+      <c r="A69" s="11">
         <v>68</v>
       </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2">
+      <c r="B69" s="11"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I69" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="14"/>
+      <c r="I69" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="23"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="2">
+      <c r="A70" s="11">
         <v>69</v>
       </c>
-      <c r="B70" s="2"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2">
+      <c r="B70" s="11"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I70" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="14"/>
+      <c r="I70" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="23"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="2">
+      <c r="A71" s="11">
         <v>70</v>
       </c>
-      <c r="B71" s="2"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2">
+      <c r="B71" s="11"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I71" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="14"/>
+      <c r="I71" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="23"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="2">
+      <c r="A72" s="11">
         <v>71</v>
       </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2">
+      <c r="B72" s="11"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="14"/>
+      <c r="I72" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="23"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="2">
+      <c r="A73" s="11">
         <v>72</v>
       </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2">
+      <c r="B73" s="11"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I73" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="14"/>
+      <c r="I73" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="23"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="2">
+      <c r="A74" s="11">
         <v>73</v>
       </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2">
+      <c r="B74" s="11"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I74" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="14"/>
+      <c r="I74" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="23"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="2">
+      <c r="A75" s="11">
         <v>74</v>
       </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2">
+      <c r="B75" s="11"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="14"/>
+      <c r="I75" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="23"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="2">
+      <c r="A76" s="11">
         <v>75</v>
       </c>
-      <c r="B76" s="2"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2">
+      <c r="B76" s="11"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I76" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="14"/>
+      <c r="I76" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="23"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="2">
+      <c r="A77" s="11">
         <v>76</v>
       </c>
-      <c r="B77" s="2"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2">
+      <c r="B77" s="11"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="14"/>
+      <c r="I77" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="23"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="2">
+      <c r="A78" s="11">
         <v>77</v>
       </c>
-      <c r="B78" s="2"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2">
+      <c r="B78" s="11"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I78" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="14"/>
+      <c r="I78" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="23"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="2">
+      <c r="A79" s="11">
         <v>78</v>
       </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2">
+      <c r="B79" s="11"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I79" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="14"/>
+      <c r="I79" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="23"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="2">
+      <c r="A80" s="11">
         <v>79</v>
       </c>
-      <c r="B80" s="2"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2">
+      <c r="B80" s="11"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="14"/>
+      <c r="I80" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="23"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="2">
+      <c r="A81" s="11">
         <v>80</v>
       </c>
-      <c r="B81" s="2"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2">
+      <c r="B81" s="11"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I81" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="14"/>
+      <c r="I81" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="23"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="2">
+      <c r="A82" s="11">
         <v>81</v>
       </c>
-      <c r="B82" s="2"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2">
+      <c r="B82" s="11"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I82" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="14"/>
+      <c r="I82" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="23"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="2">
+      <c r="A83" s="11">
         <v>82</v>
       </c>
-      <c r="B83" s="2"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2">
+      <c r="B83" s="11"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I83" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="14"/>
+      <c r="I83" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="23"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="2">
+      <c r="A84" s="11">
         <v>83</v>
       </c>
-      <c r="B84" s="2"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2">
+      <c r="B84" s="11"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I84" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="14"/>
+      <c r="I84" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="23"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="2">
+      <c r="A85" s="11">
         <v>84</v>
       </c>
-      <c r="B85" s="2"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2">
+      <c r="B85" s="11"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I85" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="14"/>
+      <c r="I85" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="23"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="2">
+      <c r="A86" s="11">
         <v>85</v>
       </c>
-      <c r="B86" s="2"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2">
+      <c r="B86" s="11"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I86" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="14"/>
+      <c r="I86" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="23"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="2">
+      <c r="A87" s="11">
         <v>86</v>
       </c>
-      <c r="B87" s="2"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2">
+      <c r="B87" s="11"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I87" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="14"/>
+      <c r="I87" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="23"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="2">
+      <c r="A88" s="11">
         <v>87</v>
       </c>
-      <c r="B88" s="2"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2">
+      <c r="B88" s="11"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I88" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="14"/>
+      <c r="I88" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="23"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="2">
+      <c r="A89" s="11">
         <v>88</v>
       </c>
-      <c r="B89" s="2"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2">
+      <c r="B89" s="11"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I89" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="14"/>
+      <c r="I89" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="23"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="2">
+      <c r="A90" s="11">
         <v>89</v>
       </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2">
+      <c r="B90" s="11"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I90" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="14"/>
+      <c r="I90" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="23"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="2">
+      <c r="A91" s="11">
         <v>90</v>
       </c>
-      <c r="B91" s="2"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2">
+      <c r="B91" s="11"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="14"/>
+      <c r="I91" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="23"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="2">
+      <c r="A92" s="11">
         <v>91</v>
       </c>
-      <c r="B92" s="2"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2">
+      <c r="B92" s="11"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I92" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="14"/>
+      <c r="I92" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="23"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="2">
+      <c r="A93" s="11">
         <v>92</v>
       </c>
-      <c r="B93" s="2"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2">
+      <c r="B93" s="11"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I93" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="14"/>
+      <c r="I93" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="23"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I93" etc:filterBottomFollowUsedRange="0">
@@ -6149,326 +6177,326 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="10.6363636363636"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="10"/>
     <col min="8" max="8" width="22.1272727272727" customWidth="1"/>
-    <col min="9" max="9" width="11.8727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.8727272727273" style="10" customWidth="1"/>
     <col min="11" max="11" width="10.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="4">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="15">
         <v>46188</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="14">
         <v>4300</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="12">
         <v>4.8581</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="14">
         <v>5.17</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
+      <c r="I2" s="11">
+        <v>0</v>
+      </c>
+      <c r="J2" s="14">
         <f>E2*(G2-F2)-I2</f>
         <v>1341.17</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="14">
         <v>1308.3</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="16">
         <f>SUM(K2:K4)</f>
         <v>9745.52</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="16">
         <f>SUM(L2)</f>
         <v>9745.52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="4">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="15">
         <v>46190</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="14">
         <v>600172</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="14">
         <v>600</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="12">
         <v>12.2123</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="14">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="I3" s="11">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14">
         <f t="shared" ref="J3:J9" si="0">E3*(G3-F3)-I3</f>
         <v>472.619999999999</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="14">
         <v>460.95</v>
       </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="4">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="15">
         <v>46199</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="11">
         <v>601066</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="14">
         <v>2400</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="14">
         <v>27.6302</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="14">
         <v>31</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="11">
         <v>111.25</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="14">
         <f t="shared" si="0"/>
         <v>7976.27</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="14">
         <v>7976.27</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="4">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="15">
         <v>46213</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="14">
         <v>600360</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="14">
         <v>1300</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="11">
         <v>14.6146</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="14">
         <v>17.59</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="5">
+      <c r="I5" s="11"/>
+      <c r="J5" s="14">
         <f t="shared" si="0"/>
         <v>3868.02</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="14">
         <v>3868.02</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="4">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="15">
         <v>46213</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="14">
         <v>600745</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="14">
         <v>600</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="14">
         <v>18.65</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="14">
         <v>21.24</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="11">
         <v>19.06</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="14">
         <f t="shared" si="0"/>
         <v>1534.94</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="14">
         <v>1534.94</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="4">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="5">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="4">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="5">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="4">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="5">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="5">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14">
         <f>SUM(K2:K9)</f>
         <v>15148.48</v>
       </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D6" etc:filterBottomFollowUsedRange="0">
@@ -6490,7 +6518,7 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="5" max="5" width="12.8727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.8727272727273" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6506,7 +6534,7 @@
       <c r="D1" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>78</v>
       </c>
     </row>
@@ -6514,16 +6542,16 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="10">
         <v>5.13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="10" t="s">
         <v>79</v>
       </c>
     </row>
@@ -6537,10 +6565,10 @@
       <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="10">
         <v>7.16</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="10">
         <v>7</v>
       </c>
     </row>
@@ -6557,7 +6585,7 @@
       <c r="D4">
         <v>3.93</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="10">
         <v>3.5</v>
       </c>
     </row>
@@ -6574,7 +6602,7 @@
       <c r="D5">
         <v>5.02</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="10" t="s">
         <v>81</v>
       </c>
     </row>
@@ -6627,4 +6655,963 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q30"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="9.54545454545454" customWidth="1"/>
+    <col min="2" max="2" width="8.54545454545454" customWidth="1"/>
+    <col min="3" max="3" width="5.54545454545455" customWidth="1"/>
+    <col min="4" max="4" width="7.54545454545455" customWidth="1"/>
+    <col min="6" max="6" width="8.72727272727273" style="1"/>
+    <col min="7" max="7" width="10.6363636363636" customWidth="1"/>
+    <col min="12" max="12" width="8.72727272727273" style="1"/>
+    <col min="13" max="13" width="10.6363636363636" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="2">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B4" s="6">
+        <v>18.3681</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1000</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5">
+        <v>46203</v>
+      </c>
+      <c r="H4" s="6">
+        <v>3.7838</v>
+      </c>
+      <c r="I4" s="6">
+        <v>3200</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="5">
+        <v>46182</v>
+      </c>
+      <c r="N4" s="6">
+        <v>14.9016</v>
+      </c>
+      <c r="O4" s="6">
+        <v>2300</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B5" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="C5" s="4">
+        <v>500</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="7">
+        <v>46234</v>
+      </c>
+      <c r="H5" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="I5" s="4">
+        <v>2000</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="7">
+        <v>46234</v>
+      </c>
+      <c r="N5" s="4">
+        <v>14.65</v>
+      </c>
+      <c r="O5" s="4">
+        <v>400</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2">
+        <v>7</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="5">
+        <v>46202</v>
+      </c>
+      <c r="B11" s="6">
+        <v>29.3</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2000</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="5">
+        <v>46203</v>
+      </c>
+      <c r="H11" s="6">
+        <v>14.6146</v>
+      </c>
+      <c r="I11" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B12" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="7">
+        <v>46234</v>
+      </c>
+      <c r="H12" s="4">
+        <v>9.6</v>
+      </c>
+      <c r="I12" s="4">
+        <v>500</v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="2">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="2">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B17" s="6">
+        <v>10.9008</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="5">
+        <v>46204</v>
+      </c>
+      <c r="H17" s="6">
+        <v>8.5585</v>
+      </c>
+      <c r="I17" s="6">
+        <v>1700</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B18" s="4">
+        <v>8.1</v>
+      </c>
+      <c r="C18" s="4">
+        <v>500</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="7">
+        <v>46234</v>
+      </c>
+      <c r="H18" s="4">
+        <v>5.65</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="2">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="2">
+        <v>9</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B23" s="6">
+        <v>20.6888</v>
+      </c>
+      <c r="C23" s="6">
+        <v>900</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="5">
+        <v>46182</v>
+      </c>
+      <c r="H23" s="6">
+        <v>16.6114</v>
+      </c>
+      <c r="I23" s="6">
+        <v>1600</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B24" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="C24" s="4">
+        <v>700</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="7">
+        <v>46234</v>
+      </c>
+      <c r="H24" s="4">
+        <v>11</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="3"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="2">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="2">
+        <v>10</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L28" s="3"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B29" s="6">
+        <v>20.12</v>
+      </c>
+      <c r="C29" s="6">
+        <v>700</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="5">
+        <v>46182</v>
+      </c>
+      <c r="H29" s="6">
+        <v>14.9016</v>
+      </c>
+      <c r="I29" s="6">
+        <v>2300</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29" s="3"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B30" s="9">
+        <v>135</v>
+      </c>
+      <c r="C30" s="9">
+        <v>400</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="G30" s="7">
+        <v>46234</v>
+      </c>
+      <c r="H30" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="G27:K27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="87">
   <si>
     <t>时间</t>
   </si>
@@ -670,7 +670,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -682,6 +682,43 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -854,7 +891,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -866,34 +903,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -978,7 +1015,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1009,31 +1046,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1069,9 +1115,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1081,16 +1124,13 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1102,28 +1142,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1676,205 +1710,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
+      <c r="A2" s="18">
         <v>46096</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <f t="shared" ref="B2:B8" si="0">SUM(D2+C2)</f>
         <v>225842</v>
       </c>
-      <c r="C2" s="14">
-        <v>0</v>
-      </c>
-      <c r="D2" s="14">
+      <c r="C2" s="9">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9">
         <v>225842</v>
       </c>
-      <c r="E2" s="14">
-        <v>0</v>
-      </c>
-      <c r="F2" s="14">
+      <c r="E2" s="9">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9">
         <v>11837</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <f t="shared" ref="G2:G8" si="1">SUM(B2+F2-E2)</f>
         <v>237679</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="15">
+      <c r="A3" s="18">
         <v>46107</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="9">
         <f t="shared" si="0"/>
         <v>236842</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="9">
         <f t="shared" ref="C3:C8" si="2">B2</f>
         <v>225842</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="9">
         <v>11000</v>
       </c>
-      <c r="E3" s="14">
-        <v>0</v>
-      </c>
-      <c r="F3" s="14">
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9">
         <v>11837</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="9">
         <f t="shared" si="1"/>
         <v>248679</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="15">
+      <c r="A4" s="18">
         <v>46101</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <f t="shared" si="0"/>
         <v>256842</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="9">
         <f t="shared" si="2"/>
         <v>236842</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>20000</v>
       </c>
-      <c r="E4" s="14">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14">
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
         <v>11837</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="9">
         <f t="shared" si="1"/>
         <v>268679</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="15">
+      <c r="A5" s="18">
         <v>46177</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <f t="shared" si="0"/>
         <v>266842</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="9">
         <f t="shared" si="2"/>
         <v>256842</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>10000</v>
       </c>
-      <c r="E5" s="14">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
         <v>11837</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="9">
         <f t="shared" si="1"/>
         <v>278679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="15">
+      <c r="A6" s="18">
         <v>46182</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <f t="shared" si="0"/>
         <v>276842</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="9">
         <f t="shared" si="2"/>
         <v>266842</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="9">
         <v>10000</v>
       </c>
-      <c r="E6" s="14">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14">
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
         <v>11873</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="9">
         <f t="shared" si="1"/>
         <v>288715</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="15">
+      <c r="A7" s="18">
         <v>46184</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <f t="shared" si="0"/>
         <v>281842</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="9">
         <f t="shared" si="2"/>
         <v>276842</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="9">
         <v>5000</v>
       </c>
-      <c r="E7" s="14">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
         <v>11873</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="9">
         <f t="shared" si="1"/>
         <v>293715</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="15">
+      <c r="A8" s="18">
         <v>46190</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="9">
         <f t="shared" si="0"/>
         <v>282342</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="9">
         <f t="shared" si="2"/>
         <v>281842</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="9">
         <v>500</v>
       </c>
-      <c r="E8" s="14">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
         <v>11873</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="9">
         <f t="shared" si="1"/>
         <v>294215</v>
       </c>
@@ -1891,2425 +1925,2425 @@
   <dimension ref="A1:K109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
-    <col min="2" max="2" width="9.37272727272727" style="20"/>
-    <col min="3" max="3" width="9" style="20"/>
-    <col min="4" max="4" width="9" style="10"/>
-    <col min="5" max="8" width="12.8727272727273" style="10" customWidth="1"/>
-    <col min="9" max="9" width="9" style="20"/>
-    <col min="10" max="10" width="68.6272727272727" style="21" customWidth="1"/>
+    <col min="1" max="1" width="9" style="15"/>
+    <col min="2" max="2" width="9.37272727272727" style="23"/>
+    <col min="3" max="3" width="9" style="23"/>
+    <col min="4" max="4" width="9" style="15"/>
+    <col min="5" max="8" width="12.8727272727273" style="15" customWidth="1"/>
+    <col min="9" max="9" width="9" style="23"/>
+    <col min="10" max="10" width="68.6272727272727" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="20" customFormat="1" ht="28" spans="1:11">
-      <c r="A1" s="11" t="s">
+    <row r="1" s="23" customFormat="1" ht="28" spans="1:11">
+      <c r="A1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="26" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="11">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="17">
         <v>300323</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="14">
         <v>1</v>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="13">
         <v>46182</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="14">
         <v>16.6114</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="14">
         <v>1600</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="14">
         <f t="shared" ref="H2:H20" si="0">F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="23" t="s">
+      <c r="I2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="20"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="11">
+      <c r="A3" s="14">
         <v>2</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="17">
         <v>600740</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="14">
         <v>1</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="13">
         <v>46182</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="14">
         <v>4.1541</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="14">
         <v>1800</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="14">
         <f t="shared" si="0"/>
         <v>7477.38</v>
       </c>
-      <c r="I3" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="23" t="s">
+      <c r="I3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="31">
+      <c r="A4" s="33">
         <v>3</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="28">
         <v>1</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="35">
         <v>46182</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="28">
         <v>4.8581</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="28">
         <v>4300</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="28">
         <f t="shared" si="0"/>
         <v>20889.83</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="11">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="17">
         <v>601990</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="14">
         <v>1</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="13">
         <v>46182</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="14">
         <v>9.9227</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="14">
         <v>500</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="14">
         <f t="shared" si="0"/>
         <v>4961.35</v>
       </c>
-      <c r="I5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="23" t="s">
+      <c r="I5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="11">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="17">
         <v>600059</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="14">
         <v>1</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="13">
         <v>46182</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="14">
         <v>10.9008</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="14">
         <v>1000</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="14">
         <f t="shared" si="0"/>
         <v>10900.8</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="23" t="s">
+      <c r="I6" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="26" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="11">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="14">
         <v>1</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="13">
         <v>46182</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="14">
         <v>9.6507</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="14">
         <v>1000</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="14">
         <f t="shared" si="0"/>
         <v>9650.7</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="23" t="s">
+      <c r="I7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="11">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="17">
         <v>601179</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="14">
         <v>1</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="13">
         <v>46182</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="14">
         <v>20.12</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="14">
         <v>700</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="14">
         <f t="shared" si="0"/>
         <v>14084</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="23" t="s">
+      <c r="I8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="26" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="35">
+      <c r="A9" s="36">
         <v>8</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="19">
         <v>603258</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="14">
         <v>1</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="13">
         <v>46182</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="14">
         <v>20.6888</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="14">
         <v>900</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="14">
         <f t="shared" si="0"/>
         <v>18619.92</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="23" t="s">
+      <c r="I9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="26" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="36"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="11">
+      <c r="A10" s="37"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="14">
         <v>2</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="13">
         <v>46233</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="14">
         <v>12.9</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="14">
         <v>500</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="14">
         <f t="shared" si="0"/>
         <v>6450</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="37"/>
+      <c r="I10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="38"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="35">
+      <c r="A11" s="36">
         <v>9</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="19">
         <v>600422</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="14">
         <v>1</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="13">
         <v>46182</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="14">
         <v>21.0619</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="14">
         <v>600</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="14">
         <f t="shared" si="0"/>
         <v>12637.14</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="37" t="s">
+      <c r="I11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="36"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="38">
+      <c r="A12" s="37"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="39">
         <v>2</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="40">
         <v>46188</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="39">
         <v>8.5</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="39">
         <v>600</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="39">
         <f t="shared" si="0"/>
         <v>5100</v>
       </c>
-      <c r="I12" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="41"/>
+      <c r="I12" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="42"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="42"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="38">
+      <c r="A13" s="43"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="39">
         <v>3</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="40">
         <v>46226</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="39">
         <v>9</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="39">
         <v>-600</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="39">
         <f t="shared" si="0"/>
         <v>-5400</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="41"/>
+      <c r="J13" s="42"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="11">
+      <c r="A14" s="14">
         <v>10</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="17">
         <v>600879</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="13">
         <v>46182</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="14">
         <v>26.2661</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="14">
         <v>700</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="14">
         <f t="shared" si="0"/>
         <v>18386.27</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="23" t="s">
+      <c r="I14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="26" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="35">
+      <c r="A15" s="36">
         <v>11</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="19">
         <v>601066</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="13">
         <v>46182</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="14">
         <v>27.6302</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="14">
         <v>3400</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="14">
         <f t="shared" si="0"/>
         <v>93942.68</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="43" t="s">
+      <c r="I15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="44" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="36"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="38">
+      <c r="A16" s="37"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="39">
         <v>2</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="40">
         <v>46192</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="39">
         <v>31</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="39">
         <v>-2400</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="39">
         <f t="shared" si="0"/>
         <v>-74400</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="44"/>
+      <c r="J16" s="45"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="42"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="11">
+      <c r="A17" s="43"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="13">
         <v>46202</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="14">
         <v>29.3</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="14">
         <v>1000</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="14">
         <f t="shared" si="0"/>
         <v>29300</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="41"/>
+      <c r="I17" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="11">
+      <c r="A18" s="14">
         <v>12</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="13">
         <v>46182</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="14">
         <v>18.3681</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="14">
         <v>1000</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="14">
         <f t="shared" si="0"/>
         <v>18368.1</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="23" t="s">
+      <c r="I18" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="26" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="35">
+      <c r="A19" s="36">
         <v>13</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="19">
         <v>300589</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="14">
         <v>1</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="13">
         <v>46182</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="14">
         <v>22.8225</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="14">
         <v>1200</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="14">
         <f t="shared" si="0"/>
         <v>27387</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="23" t="s">
+      <c r="I19" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="26" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="36"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="11">
+      <c r="A20" s="37"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="13">
         <v>46233</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="14">
         <v>12.55</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="14">
         <v>600</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="14">
         <f t="shared" si="0"/>
         <v>7530</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="23"/>
+      <c r="I20" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="26"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="35">
+      <c r="A21" s="36">
         <v>14</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="19">
         <v>300129</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="14">
         <v>1</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="13">
         <v>46182</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="14">
         <v>14.9016</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="14">
         <v>2300</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="14">
         <f t="shared" ref="H21:H28" si="1">F21*G21</f>
         <v>34273.68</v>
       </c>
-      <c r="I21" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="23" t="s">
+      <c r="I21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="26" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="45"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="11">
+      <c r="A22" s="46"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="14">
         <v>2</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="13">
         <v>46223</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="14">
         <v>7.35</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="14">
         <v>700</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="14">
         <f t="shared" si="1"/>
         <v>5145</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="23"/>
+      <c r="I22" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="26"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="47">
+      <c r="A23" s="6">
         <v>15</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="2">
         <v>600172</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="39">
         <v>1</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="40">
         <v>46188</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="39">
         <v>12.2123</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="39">
         <v>600</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="39">
         <f t="shared" si="1"/>
         <v>7327.38</v>
       </c>
-      <c r="I23" s="26" t="s">
+      <c r="I23" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="49" t="s">
+      <c r="J23" s="48" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="11">
+      <c r="A24" s="14">
         <v>16</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="17">
         <v>600745</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="14">
         <v>1</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="13">
         <v>46189</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="14">
         <v>18.6687</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="14">
         <v>800</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="14">
         <f t="shared" si="1"/>
         <v>14934.96</v>
       </c>
-      <c r="I24" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="23" t="s">
+      <c r="I24" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="26" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="11">
-        <v>17</v>
-      </c>
-      <c r="B25" s="20">
+      <c r="A25" s="14">
+        <v>17</v>
+      </c>
+      <c r="B25" s="23">
         <v>600115</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="14">
         <v>1</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="13">
         <v>46203</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="14">
         <v>3.7838</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="14">
         <v>3200</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="14">
         <f t="shared" si="1"/>
         <v>12108.16</v>
       </c>
-      <c r="I25" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="23"/>
+      <c r="I25" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="26"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="35">
+      <c r="A26" s="36">
         <v>18</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="19">
         <v>600360</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="14">
         <v>1</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="13">
         <v>46203</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="14">
         <v>14.6146</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="14">
         <v>1800</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="14">
         <f t="shared" si="1"/>
         <v>26306.28</v>
       </c>
-      <c r="I26" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="23"/>
+      <c r="I26" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="26"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="36"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="38">
+      <c r="A27" s="37"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="39">
         <v>2</v>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="49">
         <v>46213</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="31">
         <v>17.59</v>
       </c>
-      <c r="G27" s="38">
+      <c r="G27" s="39">
         <v>-1300</v>
       </c>
-      <c r="H27" s="38">
+      <c r="H27" s="39">
         <f t="shared" si="1"/>
         <v>-22867</v>
       </c>
-      <c r="I27" s="40" t="s">
+      <c r="I27" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J27" s="23"/>
+      <c r="J27" s="26"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="42"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="11">
+      <c r="A28" s="43"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="13">
         <v>46226</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="14">
         <v>10</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="14">
         <v>500</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="14">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="I28" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="23"/>
+      <c r="I28" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="26"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="11">
+      <c r="A29" s="14">
         <v>19</v>
       </c>
-      <c r="B29" s="52" t="s">
+      <c r="B29" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="13">
         <v>46204</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="14">
         <v>8.5585</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="14">
         <v>1700</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="14">
         <f t="shared" ref="H29:H56" si="2">F29*G29</f>
         <v>14549.45</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="23"/>
+      <c r="I29" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="26"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="11">
+      <c r="A30" s="14">
         <v>20</v>
       </c>
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="13">
         <v>46227</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="14">
         <v>10.2102</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="14">
         <v>1000</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="14">
         <f t="shared" si="2"/>
         <v>10210.2</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="23"/>
+      <c r="I30" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="26"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="11">
+      <c r="A31" s="14">
         <v>21</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="23"/>
+      <c r="I31" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="26"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="11">
+      <c r="A32" s="14">
         <v>22</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I32" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="23"/>
+      <c r="I32" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="26"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="11">
+      <c r="A33" s="14">
         <v>23</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="23"/>
+      <c r="I33" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="26"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="11">
+      <c r="A34" s="14">
         <v>24</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11">
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I34" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="23"/>
+      <c r="I34" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="26"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="11">
+      <c r="A35" s="14">
         <v>25</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="23"/>
+      <c r="I35" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="26"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="11">
+      <c r="A36" s="14">
         <v>26</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11">
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I36" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="23"/>
+      <c r="I36" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="26"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="11">
+      <c r="A37" s="14">
         <v>27</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11">
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I37" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="23"/>
+      <c r="I37" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="11">
+      <c r="A38" s="14">
         <v>28</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11">
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I38" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="23"/>
+      <c r="I38" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="26"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="11">
+      <c r="A39" s="14">
         <v>29</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I39" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="23"/>
+      <c r="I39" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="26"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="11">
+      <c r="A40" s="14">
         <v>30</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11">
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I40" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="23"/>
+      <c r="I40" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="26"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="11">
+      <c r="A41" s="14">
         <v>31</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11">
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I41" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="23"/>
+      <c r="I41" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="26"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="11">
+      <c r="A42" s="14">
         <v>32</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I42" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="23"/>
+      <c r="I42" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="26"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="11">
+      <c r="A43" s="14">
         <v>33</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11">
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I43" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="23"/>
+      <c r="I43" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="26"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="11">
+      <c r="A44" s="14">
         <v>34</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11">
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I44" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="23"/>
+      <c r="I44" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="26"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="11">
+      <c r="A45" s="14">
         <v>35</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11">
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I45" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="23"/>
+      <c r="I45" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="26"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="11">
+      <c r="A46" s="14">
         <v>36</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11">
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I46" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="23"/>
+      <c r="I46" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="26"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="11">
+      <c r="A47" s="14">
         <v>37</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11">
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I47" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="23"/>
+      <c r="I47" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="26"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="11">
+      <c r="A48" s="14">
         <v>38</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11">
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I48" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="23"/>
+      <c r="I48" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="26"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="11">
+      <c r="A49" s="14">
         <v>39</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11">
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I49" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="23"/>
+      <c r="I49" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="26"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="11">
+      <c r="A50" s="14">
         <v>40</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11">
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I50" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="23"/>
+      <c r="I50" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="26"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="11">
+      <c r="A51" s="14">
         <v>41</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11">
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I51" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="23"/>
+      <c r="I51" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="26"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="11">
+      <c r="A52" s="14">
         <v>42</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11">
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="23"/>
+      <c r="I52" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="26"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="11">
+      <c r="A53" s="14">
         <v>43</v>
       </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11">
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I53" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="23"/>
+      <c r="I53" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="26"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="11">
+      <c r="A54" s="14">
         <v>44</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11">
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I54" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="23"/>
+      <c r="I54" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="26"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="11">
+      <c r="A55" s="14">
         <v>45</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11">
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I55" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="23"/>
+      <c r="I55" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="26"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="11">
+      <c r="A56" s="14">
         <v>46</v>
       </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11">
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I56" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="23"/>
+      <c r="I56" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="26"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="11">
+      <c r="A57" s="14">
         <v>47</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11">
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14">
         <f t="shared" ref="H57:H88" si="3">F57*G57</f>
         <v>0</v>
       </c>
-      <c r="I57" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="23"/>
+      <c r="I57" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="26"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="11">
+      <c r="A58" s="14">
         <v>48</v>
       </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11">
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I58" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="23"/>
+      <c r="I58" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="26"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="11">
+      <c r="A59" s="14">
         <v>49</v>
       </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11">
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I59" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="23"/>
+      <c r="I59" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="26"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="11">
+      <c r="A60" s="14">
         <v>50</v>
       </c>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11">
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I60" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="23"/>
+      <c r="I60" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="26"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="11">
+      <c r="A61" s="14">
         <v>51</v>
       </c>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11">
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I61" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="23"/>
+      <c r="I61" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="26"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="11">
+      <c r="A62" s="14">
         <v>52</v>
       </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11">
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I62" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="23"/>
+      <c r="I62" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="26"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="11">
+      <c r="A63" s="14">
         <v>53</v>
       </c>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11">
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I63" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="23"/>
+      <c r="I63" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="26"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="11">
+      <c r="A64" s="14">
         <v>54</v>
       </c>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11">
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I64" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="23"/>
+      <c r="I64" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="26"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="11">
+      <c r="A65" s="14">
         <v>55</v>
       </c>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11">
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I65" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="23"/>
+      <c r="I65" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="26"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="11">
+      <c r="A66" s="14">
         <v>56</v>
       </c>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11">
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I66" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="23"/>
+      <c r="I66" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="26"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="11">
+      <c r="A67" s="14">
         <v>57</v>
       </c>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11">
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I67" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="23"/>
+      <c r="I67" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="26"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="11">
+      <c r="A68" s="14">
         <v>58</v>
       </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11">
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I68" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="23"/>
+      <c r="I68" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="26"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="11">
+      <c r="A69" s="14">
         <v>59</v>
       </c>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11">
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I69" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="23"/>
+      <c r="I69" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="26"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="11">
+      <c r="A70" s="14">
         <v>60</v>
       </c>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11">
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I70" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="23"/>
+      <c r="I70" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="26"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="11">
+      <c r="A71" s="14">
         <v>61</v>
       </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11">
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I71" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="23"/>
+      <c r="I71" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="26"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="11">
+      <c r="A72" s="14">
         <v>62</v>
       </c>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11">
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I72" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="23"/>
+      <c r="I72" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="26"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="11">
+      <c r="A73" s="14">
         <v>63</v>
       </c>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11">
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I73" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="23"/>
+      <c r="I73" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="26"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="11">
+      <c r="A74" s="14">
         <v>64</v>
       </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11">
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I74" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="23"/>
+      <c r="I74" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="26"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="11">
+      <c r="A75" s="14">
         <v>65</v>
       </c>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11">
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I75" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="23"/>
+      <c r="I75" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="26"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="11">
+      <c r="A76" s="14">
         <v>66</v>
       </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11">
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I76" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="23"/>
+      <c r="I76" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="26"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="11">
+      <c r="A77" s="14">
         <v>67</v>
       </c>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11">
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I77" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="23"/>
+      <c r="I77" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="26"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="11">
+      <c r="A78" s="14">
         <v>68</v>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11">
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I78" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="23"/>
+      <c r="I78" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="26"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="11">
+      <c r="A79" s="14">
         <v>69</v>
       </c>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11">
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I79" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="23"/>
+      <c r="I79" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="26"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="11">
+      <c r="A80" s="14">
         <v>70</v>
       </c>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="11">
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I80" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="23"/>
+      <c r="I80" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="26"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="11">
+      <c r="A81" s="14">
         <v>71</v>
       </c>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11">
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I81" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="23"/>
+      <c r="I81" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="26"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="11">
+      <c r="A82" s="14">
         <v>72</v>
       </c>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="11">
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I82" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="23"/>
+      <c r="I82" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="26"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="11">
+      <c r="A83" s="14">
         <v>73</v>
       </c>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="11">
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I83" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="23"/>
+      <c r="I83" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="26"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="11">
+      <c r="A84" s="14">
         <v>74</v>
       </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="11">
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I84" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="23"/>
+      <c r="I84" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="26"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="11">
+      <c r="A85" s="14">
         <v>75</v>
       </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="11">
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I85" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="23"/>
+      <c r="I85" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="26"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="11">
+      <c r="A86" s="14">
         <v>76</v>
       </c>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="11">
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I86" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="23"/>
+      <c r="I86" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="26"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="11">
+      <c r="A87" s="14">
         <v>77</v>
       </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="11">
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I87" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="23"/>
+      <c r="I87" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="26"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="11">
+      <c r="A88" s="14">
         <v>78</v>
       </c>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="11"/>
-      <c r="H88" s="11">
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I88" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="23"/>
+      <c r="I88" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="26"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="11">
+      <c r="A89" s="14">
         <v>79</v>
       </c>
-      <c r="B89" s="13"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="11"/>
-      <c r="H89" s="11">
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14">
         <f t="shared" ref="H89:H109" si="4">F89*G89</f>
         <v>0</v>
       </c>
-      <c r="I89" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="23"/>
+      <c r="I89" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="26"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="11">
+      <c r="A90" s="14">
         <v>80</v>
       </c>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
-      <c r="H90" s="11">
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I90" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="23"/>
+      <c r="I90" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="26"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="11">
+      <c r="A91" s="14">
         <v>81</v>
       </c>
-      <c r="B91" s="13"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
-      <c r="H91" s="11">
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I91" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="23"/>
+      <c r="I91" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="26"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="11">
+      <c r="A92" s="14">
         <v>82</v>
       </c>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
-      <c r="H92" s="11">
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I92" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="23"/>
+      <c r="I92" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="26"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="11">
+      <c r="A93" s="14">
         <v>83</v>
       </c>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="11"/>
-      <c r="H93" s="11">
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I93" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="23"/>
+      <c r="I93" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="26"/>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="11">
+      <c r="A94" s="14">
         <v>84</v>
       </c>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11"/>
-      <c r="H94" s="11">
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
+      <c r="H94" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I94" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="23"/>
+      <c r="I94" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="26"/>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="11">
+      <c r="A95" s="14">
         <v>85</v>
       </c>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="11"/>
-      <c r="H95" s="11">
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="14"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I95" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="23"/>
+      <c r="I95" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="26"/>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="11">
+      <c r="A96" s="14">
         <v>86</v>
       </c>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="11"/>
-      <c r="H96" s="11">
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I96" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="23"/>
+      <c r="I96" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="26"/>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="11">
+      <c r="A97" s="14">
         <v>87</v>
       </c>
-      <c r="B97" s="13"/>
-      <c r="C97" s="13"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="11"/>
-      <c r="H97" s="11">
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I97" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="23"/>
+      <c r="I97" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="26"/>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="11">
+      <c r="A98" s="14">
         <v>88</v>
       </c>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="11"/>
-      <c r="H98" s="11">
+      <c r="B98" s="17"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
+      <c r="H98" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I98" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="23"/>
+      <c r="I98" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="26"/>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="11">
+      <c r="A99" s="14">
         <v>89</v>
       </c>
-      <c r="B99" s="13"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="11"/>
-      <c r="G99" s="11"/>
-      <c r="H99" s="11">
+      <c r="B99" s="17"/>
+      <c r="C99" s="17"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I99" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="23"/>
+      <c r="I99" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="26"/>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="11">
+      <c r="A100" s="14">
         <v>90</v>
       </c>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11"/>
-      <c r="H100" s="11">
+      <c r="B100" s="17"/>
+      <c r="C100" s="17"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
+      <c r="H100" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I100" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="23"/>
+      <c r="I100" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="26"/>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="11">
+      <c r="A101" s="14">
         <v>91</v>
       </c>
-      <c r="B101" s="13"/>
-      <c r="C101" s="13"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11"/>
-      <c r="H101" s="11">
+      <c r="B101" s="17"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="14"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I101" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="23"/>
+      <c r="I101" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="26"/>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="11">
+      <c r="A102" s="14">
         <v>92</v>
       </c>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
-      <c r="G102" s="11"/>
-      <c r="H102" s="11">
+      <c r="B102" s="17"/>
+      <c r="C102" s="17"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="14"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
+      <c r="H102" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I102" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" s="23"/>
+      <c r="I102" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="26"/>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="11">
+      <c r="A103" s="14">
         <v>93</v>
       </c>
-      <c r="B103" s="13"/>
-      <c r="C103" s="13"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
-      <c r="G103" s="11"/>
-      <c r="H103" s="11">
+      <c r="B103" s="17"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I103" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" s="23"/>
+      <c r="I103" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="26"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="11">
+      <c r="A104" s="14">
         <v>94</v>
       </c>
-      <c r="B104" s="13"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="11"/>
-      <c r="G104" s="11"/>
-      <c r="H104" s="11">
+      <c r="B104" s="17"/>
+      <c r="C104" s="17"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
+      <c r="H104" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I104" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J104" s="23"/>
+      <c r="I104" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="26"/>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="11">
+      <c r="A105" s="14">
         <v>95</v>
       </c>
-      <c r="B105" s="13"/>
-      <c r="C105" s="13"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="11"/>
-      <c r="G105" s="11"/>
-      <c r="H105" s="11">
+      <c r="B105" s="17"/>
+      <c r="C105" s="17"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
+      <c r="H105" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I105" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J105" s="23"/>
+      <c r="I105" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="26"/>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="11">
+      <c r="A106" s="14">
         <v>96</v>
       </c>
-      <c r="B106" s="13"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="11"/>
-      <c r="G106" s="11"/>
-      <c r="H106" s="11">
+      <c r="B106" s="17"/>
+      <c r="C106" s="17"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I106" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J106" s="23"/>
+      <c r="I106" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="26"/>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="11">
+      <c r="A107" s="14">
         <v>97</v>
       </c>
-      <c r="B107" s="13"/>
-      <c r="C107" s="13"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="11"/>
-      <c r="G107" s="11"/>
-      <c r="H107" s="11">
+      <c r="B107" s="17"/>
+      <c r="C107" s="17"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
+      <c r="H107" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I107" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="23"/>
+      <c r="I107" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="26"/>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="11">
+      <c r="A108" s="14">
         <v>98</v>
       </c>
-      <c r="B108" s="13"/>
-      <c r="C108" s="13"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="11"/>
-      <c r="H108" s="11">
+      <c r="B108" s="17"/>
+      <c r="C108" s="17"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="14"/>
+      <c r="G108" s="14"/>
+      <c r="H108" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I108" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J108" s="23"/>
+      <c r="I108" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="26"/>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="11">
+      <c r="A109" s="14">
         <v>99</v>
       </c>
-      <c r="B109" s="13"/>
-      <c r="C109" s="13"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="11"/>
-      <c r="H109" s="11">
+      <c r="B109" s="17"/>
+      <c r="C109" s="17"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I109" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J109" s="23"/>
+      <c r="I109" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" s="26"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I109" etc:filterBottomFollowUsedRange="0">
@@ -4353,1808 +4387,1808 @@
   <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
-    <col min="2" max="2" width="9.37272727272727" style="10"/>
-    <col min="3" max="3" width="9" style="20"/>
-    <col min="4" max="4" width="9" style="10"/>
+    <col min="1" max="1" width="9" style="15"/>
+    <col min="2" max="2" width="9.37272727272727" style="15"/>
+    <col min="3" max="3" width="9" style="23"/>
+    <col min="4" max="4" width="9" style="15"/>
     <col min="5" max="5" width="12.8727272727273" customWidth="1"/>
-    <col min="6" max="8" width="12.8727272727273" style="10" customWidth="1"/>
-    <col min="9" max="9" width="9" style="20"/>
-    <col min="10" max="10" width="68.6272727272727" style="21" customWidth="1"/>
+    <col min="6" max="8" width="12.8727272727273" style="15" customWidth="1"/>
+    <col min="9" max="9" width="9" style="23"/>
+    <col min="10" max="10" width="68.6272727272727" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="20" customFormat="1" ht="28" spans="1:11">
-      <c r="A1" s="13" t="s">
+    <row r="1" s="23" customFormat="1" ht="28" spans="1:11">
+      <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="26" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="11">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="14">
         <v>601398</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="14">
         <v>1</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="27">
         <v>46182</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="14">
         <v>16.6114</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="14">
         <v>1600</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="14">
         <f>F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="23"/>
-      <c r="K2" s="20"/>
+      <c r="I2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="26"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="11">
+      <c r="A3" s="14">
         <v>2</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11">
+      <c r="B3" s="14"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14">
         <f t="shared" ref="H3:H13" si="0">F3*G3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="23"/>
+      <c r="I3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="26"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="11">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="11">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="I4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="31"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="11">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11">
+      <c r="B5" s="14"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="23"/>
+      <c r="I5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="26"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="11">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11">
+      <c r="B6" s="14"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="23"/>
+      <c r="I6" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="11">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11">
+      <c r="B7" s="14"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="23"/>
+      <c r="I7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="26"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="11">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11">
+      <c r="B8" s="14"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="23"/>
+      <c r="I8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="26"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="11">
+      <c r="A9" s="14">
         <v>8</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11">
+      <c r="B9" s="14"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="23"/>
+      <c r="I9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="26"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="11">
+      <c r="A10" s="14">
         <v>9</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11">
+      <c r="B10" s="14"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="23"/>
+      <c r="I10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="26"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="11">
+      <c r="A11" s="14">
         <v>10</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11">
+      <c r="D11" s="14"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="23"/>
+      <c r="I11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="26"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="11">
+      <c r="A12" s="14">
         <v>11</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11">
+      <c r="B12" s="14"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="23"/>
+      <c r="I12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="26"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="11">
+      <c r="A13" s="14">
         <v>12</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11">
+      <c r="B13" s="14"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="23"/>
+      <c r="I13" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="26"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="11">
+      <c r="A14" s="14">
         <v>13</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11">
+      <c r="B14" s="14"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14">
         <f t="shared" ref="H10:H55" si="1">F14*G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="23"/>
+      <c r="I14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="26"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="11">
+      <c r="A15" s="14">
         <v>14</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11">
+      <c r="B15" s="14"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="23"/>
+      <c r="I15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="26"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="11">
+      <c r="A16" s="14">
         <v>15</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11">
+      <c r="B16" s="14"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="23"/>
+      <c r="I16" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="26"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="11">
+      <c r="A17" s="14">
         <v>16</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11">
+      <c r="B17" s="14"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="23"/>
+      <c r="I17" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="26"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="11">
-        <v>17</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11">
+      <c r="A18" s="14">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="23"/>
+      <c r="I18" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="26"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="11">
+      <c r="A19" s="14">
         <v>18</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11">
+      <c r="B19" s="14"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="23"/>
+      <c r="I19" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="26"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="11">
+      <c r="A20" s="14">
         <v>19</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11">
+      <c r="B20" s="14"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="23"/>
+      <c r="I20" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="26"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="11">
+      <c r="A21" s="14">
         <v>20</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11">
+      <c r="B21" s="14"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="23"/>
+      <c r="I21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="26"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="11">
+      <c r="A22" s="14">
         <v>21</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11">
+      <c r="B22" s="14"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="23"/>
+      <c r="I22" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="26"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="11">
+      <c r="A23" s="14">
         <v>22</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11">
+      <c r="B23" s="14"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="23"/>
+      <c r="I23" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="26"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="11">
+      <c r="A24" s="14">
         <v>23</v>
       </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11">
+      <c r="B24" s="14"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="23"/>
+      <c r="I24" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="26"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="11">
+      <c r="A25" s="14">
         <v>24</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11">
+      <c r="B25" s="14"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="23"/>
+      <c r="I25" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="26"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="11">
+      <c r="A26" s="14">
         <v>25</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11">
+      <c r="B26" s="14"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="23"/>
+      <c r="I26" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="26"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="11">
+      <c r="A27" s="14">
         <v>26</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11">
+      <c r="B27" s="14"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="23"/>
+      <c r="I27" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="26"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="11">
+      <c r="A28" s="14">
         <v>27</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11">
+      <c r="B28" s="14"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="23"/>
+      <c r="I28" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="26"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="11">
+      <c r="A29" s="14">
         <v>28</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11">
+      <c r="B29" s="14"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="23"/>
+      <c r="I29" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="26"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="11">
+      <c r="A30" s="14">
         <v>29</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11">
+      <c r="B30" s="14"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="23"/>
+      <c r="I30" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="26"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="11">
+      <c r="A31" s="14">
         <v>30</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11">
+      <c r="B31" s="14"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="23"/>
+      <c r="I31" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="26"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="11">
+      <c r="A32" s="14">
         <v>31</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11">
+      <c r="B32" s="14"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="23"/>
+      <c r="I32" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="26"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="11">
+      <c r="A33" s="14">
         <v>32</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11">
+      <c r="B33" s="14"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="23"/>
+      <c r="I33" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="26"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="11">
+      <c r="A34" s="14">
         <v>33</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11">
+      <c r="B34" s="14"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="23"/>
+      <c r="I34" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="26"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="11">
+      <c r="A35" s="14">
         <v>34</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11">
+      <c r="B35" s="14"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="23"/>
+      <c r="I35" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="26"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="11">
+      <c r="A36" s="14">
         <v>35</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11">
+      <c r="B36" s="14"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="23"/>
+      <c r="I36" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="26"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="11">
+      <c r="A37" s="14">
         <v>36</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11">
+      <c r="B37" s="14"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="23"/>
+      <c r="I37" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="11">
+      <c r="A38" s="14">
         <v>37</v>
       </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11">
+      <c r="B38" s="14"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I38" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="23"/>
+      <c r="I38" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="26"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="11">
+      <c r="A39" s="14">
         <v>38</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11">
+      <c r="B39" s="14"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I39" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="23"/>
+      <c r="I39" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="26"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="11">
+      <c r="A40" s="14">
         <v>39</v>
       </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11">
+      <c r="B40" s="14"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="23"/>
+      <c r="I40" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="26"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="11">
+      <c r="A41" s="14">
         <v>40</v>
       </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11">
+      <c r="B41" s="14"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="23"/>
+      <c r="I41" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="26"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="11">
+      <c r="A42" s="14">
         <v>41</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11">
+      <c r="B42" s="14"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I42" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="23"/>
+      <c r="I42" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="26"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="11">
+      <c r="A43" s="14">
         <v>42</v>
       </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11">
+      <c r="B43" s="14"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I43" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="23"/>
+      <c r="I43" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="26"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="11">
+      <c r="A44" s="14">
         <v>43</v>
       </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11">
+      <c r="B44" s="14"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I44" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="23"/>
+      <c r="I44" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="26"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="11">
+      <c r="A45" s="14">
         <v>44</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11">
+      <c r="B45" s="14"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I45" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="23"/>
+      <c r="I45" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="26"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="11">
+      <c r="A46" s="14">
         <v>45</v>
       </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11">
+      <c r="B46" s="14"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I46" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="23"/>
+      <c r="I46" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="26"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="11">
+      <c r="A47" s="14">
         <v>46</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11">
+      <c r="B47" s="14"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I47" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="23"/>
+      <c r="I47" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="26"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="11">
+      <c r="A48" s="14">
         <v>47</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11">
+      <c r="B48" s="14"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I48" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="23"/>
+      <c r="I48" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="26"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="11">
+      <c r="A49" s="14">
         <v>48</v>
       </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11">
+      <c r="B49" s="14"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I49" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="23"/>
+      <c r="I49" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="26"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="11">
+      <c r="A50" s="14">
         <v>49</v>
       </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11">
+      <c r="B50" s="14"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I50" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="23"/>
+      <c r="I50" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="26"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="11">
+      <c r="A51" s="14">
         <v>50</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11">
+      <c r="B51" s="14"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I51" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="23"/>
+      <c r="I51" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="26"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="11">
+      <c r="A52" s="14">
         <v>51</v>
       </c>
-      <c r="B52" s="11"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11">
+      <c r="B52" s="14"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I52" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="23"/>
+      <c r="I52" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="26"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="11">
+      <c r="A53" s="14">
         <v>52</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11">
+      <c r="B53" s="14"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I53" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="23"/>
+      <c r="I53" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="26"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="11">
+      <c r="A54" s="14">
         <v>53</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11">
+      <c r="B54" s="14"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I54" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="23"/>
+      <c r="I54" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="26"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="11">
+      <c r="A55" s="14">
         <v>54</v>
       </c>
-      <c r="B55" s="11"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11">
+      <c r="B55" s="14"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I55" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="23"/>
+      <c r="I55" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="26"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="11">
+      <c r="A56" s="14">
         <v>55</v>
       </c>
-      <c r="B56" s="11"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11">
+      <c r="B56" s="14"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14">
         <f t="shared" ref="H56:H93" si="2">F56*G56</f>
         <v>0</v>
       </c>
-      <c r="I56" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="23"/>
+      <c r="I56" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="26"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="11">
+      <c r="A57" s="14">
         <v>56</v>
       </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11">
+      <c r="B57" s="14"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I57" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="23"/>
+      <c r="I57" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="26"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="11">
+      <c r="A58" s="14">
         <v>57</v>
       </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11">
+      <c r="B58" s="14"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I58" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="23"/>
+      <c r="I58" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="26"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="11">
+      <c r="A59" s="14">
         <v>58</v>
       </c>
-      <c r="B59" s="11"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11">
+      <c r="B59" s="14"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I59" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="23"/>
+      <c r="I59" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="26"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="11">
+      <c r="A60" s="14">
         <v>59</v>
       </c>
-      <c r="B60" s="11"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11">
+      <c r="B60" s="14"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I60" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="23"/>
+      <c r="I60" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="26"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="11">
+      <c r="A61" s="14">
         <v>60</v>
       </c>
-      <c r="B61" s="11"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11">
+      <c r="B61" s="14"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I61" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="23"/>
+      <c r="I61" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="26"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="11">
+      <c r="A62" s="14">
         <v>61</v>
       </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11">
+      <c r="B62" s="14"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I62" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="23"/>
+      <c r="I62" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="26"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="11">
+      <c r="A63" s="14">
         <v>62</v>
       </c>
-      <c r="B63" s="11"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11">
+      <c r="B63" s="14"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I63" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="23"/>
+      <c r="I63" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="26"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="11">
+      <c r="A64" s="14">
         <v>63</v>
       </c>
-      <c r="B64" s="11"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11">
+      <c r="B64" s="14"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I64" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="23"/>
+      <c r="I64" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="26"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="11">
+      <c r="A65" s="14">
         <v>64</v>
       </c>
-      <c r="B65" s="11"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11">
+      <c r="B65" s="14"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I65" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="23"/>
+      <c r="I65" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="26"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="11">
+      <c r="A66" s="14">
         <v>65</v>
       </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11">
+      <c r="B66" s="14"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I66" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="23"/>
+      <c r="I66" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="26"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="11">
+      <c r="A67" s="14">
         <v>66</v>
       </c>
-      <c r="B67" s="11"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11">
+      <c r="B67" s="14"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I67" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="23"/>
+      <c r="I67" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="26"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="11">
+      <c r="A68" s="14">
         <v>67</v>
       </c>
-      <c r="B68" s="11"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11">
+      <c r="B68" s="14"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I68" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="23"/>
+      <c r="I68" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="26"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="11">
+      <c r="A69" s="14">
         <v>68</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11">
+      <c r="B69" s="14"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I69" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="23"/>
+      <c r="I69" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="26"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="11">
+      <c r="A70" s="14">
         <v>69</v>
       </c>
-      <c r="B70" s="11"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11">
+      <c r="B70" s="14"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I70" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="23"/>
+      <c r="I70" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="26"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="11">
+      <c r="A71" s="14">
         <v>70</v>
       </c>
-      <c r="B71" s="11"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11">
+      <c r="B71" s="14"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I71" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="23"/>
+      <c r="I71" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="26"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="11">
+      <c r="A72" s="14">
         <v>71</v>
       </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11">
+      <c r="B72" s="14"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I72" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="23"/>
+      <c r="I72" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="26"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="11">
+      <c r="A73" s="14">
         <v>72</v>
       </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11">
+      <c r="B73" s="14"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I73" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="23"/>
+      <c r="I73" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="26"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="11">
+      <c r="A74" s="14">
         <v>73</v>
       </c>
-      <c r="B74" s="11"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11">
+      <c r="B74" s="14"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I74" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="23"/>
+      <c r="I74" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="26"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="11">
+      <c r="A75" s="14">
         <v>74</v>
       </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11">
+      <c r="B75" s="14"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I75" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="23"/>
+      <c r="I75" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="26"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="11">
+      <c r="A76" s="14">
         <v>75</v>
       </c>
-      <c r="B76" s="11"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11">
+      <c r="B76" s="14"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I76" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="23"/>
+      <c r="I76" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="26"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="11">
+      <c r="A77" s="14">
         <v>76</v>
       </c>
-      <c r="B77" s="11"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11">
+      <c r="B77" s="14"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I77" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="23"/>
+      <c r="I77" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="26"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="11">
+      <c r="A78" s="14">
         <v>77</v>
       </c>
-      <c r="B78" s="11"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11">
+      <c r="B78" s="14"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I78" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="23"/>
+      <c r="I78" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="26"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="11">
+      <c r="A79" s="14">
         <v>78</v>
       </c>
-      <c r="B79" s="11"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11">
+      <c r="B79" s="14"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I79" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="23"/>
+      <c r="I79" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="26"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="11">
+      <c r="A80" s="14">
         <v>79</v>
       </c>
-      <c r="B80" s="11"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="11">
+      <c r="B80" s="14"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I80" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="23"/>
+      <c r="I80" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="26"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="11">
+      <c r="A81" s="14">
         <v>80</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11">
+      <c r="B81" s="14"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I81" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="23"/>
+      <c r="I81" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="26"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="11">
+      <c r="A82" s="14">
         <v>81</v>
       </c>
-      <c r="B82" s="11"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="11">
+      <c r="B82" s="14"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I82" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="23"/>
+      <c r="I82" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="26"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="11">
+      <c r="A83" s="14">
         <v>82</v>
       </c>
-      <c r="B83" s="11"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="11">
+      <c r="B83" s="14"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I83" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="23"/>
+      <c r="I83" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="26"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="11">
+      <c r="A84" s="14">
         <v>83</v>
       </c>
-      <c r="B84" s="11"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="11">
+      <c r="B84" s="14"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I84" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="23"/>
+      <c r="I84" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="26"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="11">
+      <c r="A85" s="14">
         <v>84</v>
       </c>
-      <c r="B85" s="11"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="11">
+      <c r="B85" s="14"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I85" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="23"/>
+      <c r="I85" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="26"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="11">
+      <c r="A86" s="14">
         <v>85</v>
       </c>
-      <c r="B86" s="11"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="11">
+      <c r="B86" s="14"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I86" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="23"/>
+      <c r="I86" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="26"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="11">
+      <c r="A87" s="14">
         <v>86</v>
       </c>
-      <c r="B87" s="11"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="11">
+      <c r="B87" s="14"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I87" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="23"/>
+      <c r="I87" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="26"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="11">
+      <c r="A88" s="14">
         <v>87</v>
       </c>
-      <c r="B88" s="11"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="11"/>
-      <c r="H88" s="11">
+      <c r="B88" s="14"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I88" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="23"/>
+      <c r="I88" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="26"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="11">
+      <c r="A89" s="14">
         <v>88</v>
       </c>
-      <c r="B89" s="11"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="11"/>
-      <c r="H89" s="11">
+      <c r="B89" s="14"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I89" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="23"/>
+      <c r="I89" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="26"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="11">
+      <c r="A90" s="14">
         <v>89</v>
       </c>
-      <c r="B90" s="11"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
-      <c r="H90" s="11">
+      <c r="B90" s="14"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I90" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="23"/>
+      <c r="I90" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="26"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="11">
+      <c r="A91" s="14">
         <v>90</v>
       </c>
-      <c r="B91" s="11"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
-      <c r="H91" s="11">
+      <c r="B91" s="14"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I91" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="23"/>
+      <c r="I91" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="26"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="11">
+      <c r="A92" s="14">
         <v>91</v>
       </c>
-      <c r="B92" s="11"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
-      <c r="H92" s="11">
+      <c r="B92" s="14"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I92" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="23"/>
+      <c r="I92" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="26"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="11">
+      <c r="A93" s="14">
         <v>92</v>
       </c>
-      <c r="B93" s="11"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="11"/>
-      <c r="H93" s="11">
+      <c r="B93" s="14"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I93" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="23"/>
+      <c r="I93" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="26"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I93" etc:filterBottomFollowUsedRange="0">
@@ -6177,326 +6211,326 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="10.6363636363636"/>
-    <col min="4" max="4" width="9" style="10"/>
+    <col min="4" max="4" width="9" style="15"/>
     <col min="8" max="8" width="22.1272727272727" customWidth="1"/>
-    <col min="9" max="9" width="11.8727272727273" style="10" customWidth="1"/>
+    <col min="9" max="9" width="11.8727272727273" style="15" customWidth="1"/>
     <col min="11" max="11" width="10.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="13">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="18">
         <v>46188</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>4300</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="16">
         <v>4.8581</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>5.17</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="11">
-        <v>0</v>
-      </c>
-      <c r="J2" s="14">
+      <c r="I2" s="14">
+        <v>0</v>
+      </c>
+      <c r="J2" s="9">
         <f>E2*(G2-F2)-I2</f>
         <v>1341.17</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="9">
         <v>1308.3</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="19">
         <f>SUM(K2:K4)</f>
         <v>9745.52</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="19">
         <f>SUM(L2)</f>
         <v>9745.52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="13">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="18">
         <v>46190</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="9">
         <v>600172</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="9">
         <v>600</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="16">
         <v>12.2123</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="9">
         <v>13</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="11">
-        <v>0</v>
-      </c>
-      <c r="J3" s="14">
+      <c r="I3" s="14">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9">
         <f t="shared" ref="J3:J9" si="0">E3*(G3-F3)-I3</f>
         <v>472.619999999999</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="9">
         <v>460.95</v>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="13">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="18">
         <v>46199</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="14">
         <v>601066</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="9">
         <v>2400</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="9">
         <v>27.6302</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="9">
         <v>31</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="14">
         <v>111.25</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="9">
         <f t="shared" si="0"/>
         <v>7976.27</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="9">
         <v>7976.27</v>
       </c>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="13">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="18">
         <v>46213</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="9">
         <v>600360</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="9">
         <v>1300</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="14">
         <v>14.6146</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="9">
         <v>17.59</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="14">
+      <c r="I5" s="14"/>
+      <c r="J5" s="9">
         <f t="shared" si="0"/>
         <v>3868.02</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="9">
         <v>3868.02</v>
       </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="13">
+      <c r="A6" s="17">
         <v>5</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="18">
         <v>46213</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="9">
         <v>600745</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="9">
         <v>600</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="9">
         <v>18.65</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="9">
         <v>21.24</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="14">
         <v>19.06</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="9">
         <f t="shared" si="0"/>
         <v>1534.94</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="9">
         <v>1534.94</v>
       </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="13">
+      <c r="A7" s="17">
         <v>6</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="14">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="13">
+      <c r="A8" s="17">
         <v>7</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="14">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="13">
+      <c r="A9" s="17">
         <v>8</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="14">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="9">
         <f>SUM(K2:K9)</f>
         <v>15148.48</v>
       </c>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D6" etc:filterBottomFollowUsedRange="0">
@@ -6518,7 +6552,7 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="5" max="5" width="12.8727272727273" style="10" customWidth="1"/>
+    <col min="5" max="5" width="12.8727272727273" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6534,7 +6568,7 @@
       <c r="D1" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="15" t="s">
         <v>78</v>
       </c>
     </row>
@@ -6542,16 +6576,16 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="15">
         <v>5.13</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="15" t="s">
         <v>79</v>
       </c>
     </row>
@@ -6565,10 +6599,10 @@
       <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="15">
         <v>7.16</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="15">
         <v>7</v>
       </c>
     </row>
@@ -6585,7 +6619,7 @@
       <c r="D4">
         <v>3.93</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="15">
         <v>3.5</v>
       </c>
     </row>
@@ -6602,7 +6636,7 @@
       <c r="D5">
         <v>5.02</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="15" t="s">
         <v>81</v>
       </c>
     </row>
@@ -6660,7 +6694,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.54545454545454" customWidth="1"/>
@@ -6673,7 +6707,7 @@
     <col min="13" max="13" width="10.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:12">
       <c r="A1" s="2">
         <v>1</v>
       </c>
@@ -6682,23 +6716,9 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="2">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="2">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-    </row>
-    <row r="2" spans="1:17">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>82</v>
       </c>
@@ -6707,23 +6727,9 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>83</v>
       </c>
@@ -6740,39 +6746,9 @@
         <v>84</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="L3" s="3"/>
-      <c r="M3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="5">
         <v>46182</v>
       </c>
@@ -6789,39 +6765,9 @@
         <v>17</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="5">
-        <v>46203</v>
-      </c>
-      <c r="H4" s="6">
-        <v>3.7838</v>
-      </c>
-      <c r="I4" s="6">
-        <v>3200</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="L4" s="3"/>
-      <c r="M4" s="5">
-        <v>46182</v>
-      </c>
-      <c r="N4" s="6">
-        <v>14.9016</v>
-      </c>
-      <c r="O4" s="6">
-        <v>2300</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="7">
         <v>46234</v>
       </c>
@@ -6836,73 +6782,27 @@
         <v>23</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="7">
-        <v>46234</v>
-      </c>
-      <c r="H5" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="I5" s="4">
-        <v>2000</v>
-      </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="L5" s="3"/>
-      <c r="M5" s="7">
-        <v>46234</v>
-      </c>
-      <c r="N5" s="4">
-        <v>14.65</v>
-      </c>
-      <c r="O5" s="4">
-        <v>400</v>
-      </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-    </row>
-    <row r="7" spans="1:17">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-    </row>
-    <row r="8" spans="1:17">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -6911,21 +6811,9 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="2">
-        <v>7</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-    </row>
-    <row r="9" spans="1:17">
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -6934,21 +6822,9 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-    </row>
-    <row r="10" spans="1:17">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="4" t="s">
         <v>83</v>
       </c>
@@ -6965,29 +6841,9 @@
         <v>84</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="L10" s="3"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-    </row>
-    <row r="11" spans="1:17">
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="5">
         <v>46202</v>
       </c>
@@ -7004,29 +6860,9 @@
         <v>17</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="5">
-        <v>46203</v>
-      </c>
-      <c r="H11" s="6">
-        <v>14.6146</v>
-      </c>
-      <c r="I11" s="6">
-        <v>1000</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="L11" s="3"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-    </row>
-    <row r="12" spans="1:17">
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="7">
         <v>46234</v>
       </c>
@@ -7041,575 +6877,997 @@
         <v>23</v>
       </c>
       <c r="F12" s="3"/>
-      <c r="G12" s="7">
-        <v>46234</v>
-      </c>
-      <c r="H12" s="4">
-        <v>9.6</v>
-      </c>
-      <c r="I12" s="4">
-        <v>500</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="L12" s="3"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-    </row>
-    <row r="13" spans="1:17">
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="2">
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="2">
         <v>3</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="2">
-        <v>8</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="4" t="s">
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="5">
+      <c r="F17" s="3"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="5">
         <v>46182</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B18" s="6">
         <v>10.9008</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="6">
         <v>1000</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="5">
-        <v>46204</v>
-      </c>
-      <c r="H17" s="6">
-        <v>8.5585</v>
-      </c>
-      <c r="I17" s="6">
-        <v>1700</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="7">
+      <c r="E18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="7">
         <v>46234</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B19" s="4">
         <v>8.1</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C19" s="4">
         <v>500</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="7">
-        <v>46234</v>
-      </c>
-      <c r="H18" s="4">
-        <v>5.65</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1000</v>
-      </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="2">
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="2">
         <v>4</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="2">
-        <v>9</v>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-    </row>
-    <row r="21" spans="1:17">
-      <c r="A21" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-    </row>
-    <row r="22" spans="1:17">
-      <c r="A22" s="4" t="s">
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3"/>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="A23" s="5">
+      <c r="F23" s="3"/>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="5">
         <v>46182</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B24" s="6">
         <v>20.6888</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C24" s="6">
         <v>900</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="5">
-        <v>46182</v>
-      </c>
-      <c r="H23" s="6">
-        <v>16.6114</v>
-      </c>
-      <c r="I23" s="6">
-        <v>1600</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" s="7">
+      <c r="E24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="7">
         <v>46234</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B25" s="4">
         <v>12.6</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C25" s="4">
         <v>700</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="7">
-        <v>46234</v>
-      </c>
-      <c r="H24" s="4">
-        <v>11</v>
-      </c>
-      <c r="I24" s="4">
-        <v>1000</v>
-      </c>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="3"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="2">
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="3"/>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="2">
         <v>5</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="2">
-        <v>10</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="2" t="s">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B30" s="6">
+        <v>20.12</v>
+      </c>
+      <c r="C30" s="6">
+        <v>700</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B31" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="C31" s="9">
+        <v>400</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="7">
+        <v>46238</v>
+      </c>
+      <c r="B32" s="9">
+        <v>14.4</v>
+      </c>
+      <c r="C32" s="9">
+        <v>700</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
+        <v>6</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5">
+        <v>46203</v>
+      </c>
+      <c r="B36" s="6">
+        <v>3.7838</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3200</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B37" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="C37" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>7</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5">
+        <v>46203</v>
+      </c>
+      <c r="B43" s="6">
+        <v>14.6146</v>
+      </c>
+      <c r="C43" s="6">
+        <v>1000</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B44" s="4">
+        <v>9.6</v>
+      </c>
+      <c r="C44" s="4">
+        <v>500</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
+        <v>8</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5">
+        <v>46204</v>
+      </c>
+      <c r="B50" s="6">
+        <v>8.5585</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1700</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B51" s="4">
+        <v>5.65</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2">
+        <v>9</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B56" s="6">
+        <v>16.6114</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1600</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B57" s="4">
+        <v>11</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2">
+        <v>10</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="4" t="s">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B61" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C61" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D61" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4" t="s">
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B62" s="6">
+        <v>14.9016</v>
+      </c>
+      <c r="C62" s="6">
+        <v>3000</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B63" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="C63" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2">
+        <v>11</v>
+      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="B67" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="C67" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="D67" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="L28" s="3"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" s="5">
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5">
         <v>46182</v>
       </c>
-      <c r="B29" s="6">
-        <v>20.12</v>
-      </c>
-      <c r="C29" s="6">
-        <v>700</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="B68" s="6">
+        <v>26.27</v>
+      </c>
+      <c r="C68" s="6">
+        <v>2300</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="5">
+      <c r="E68" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B69" s="4">
+        <v>14.65</v>
+      </c>
+      <c r="C69" s="4">
+        <v>400</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="10">
+        <v>12</v>
+      </c>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="12"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="12"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="13">
         <v>46182</v>
       </c>
-      <c r="H29" s="6">
-        <v>14.9016</v>
-      </c>
-      <c r="I29" s="6">
-        <v>2300</v>
-      </c>
-      <c r="J29" s="4" t="s">
+      <c r="B75" s="14">
+        <v>9.6507</v>
+      </c>
+      <c r="C75" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="K29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L29" s="3"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-    </row>
-    <row r="30" spans="1:17">
-      <c r="A30" s="7">
+      <c r="E75" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7">
         <v>46234</v>
       </c>
-      <c r="B30" s="9">
-        <v>135</v>
-      </c>
-      <c r="C30" s="9">
-        <v>400</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="G30" s="7">
+      <c r="B76" s="4">
+        <v>6.11</v>
+      </c>
+      <c r="C76" s="4">
+        <v>500</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2">
+        <v>13</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7">
+        <v>46189</v>
+      </c>
+      <c r="B82" s="4">
+        <v>18.65</v>
+      </c>
+      <c r="C82" s="4">
+        <v>200</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7">
         <v>46234</v>
       </c>
-      <c r="H30" s="4">
-        <v>7.8</v>
-      </c>
-      <c r="I30" s="4">
-        <v>1000</v>
-      </c>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4" t="s">
+      <c r="B83" s="4">
+        <v>16.75</v>
+      </c>
+      <c r="C83" s="4">
+        <v>100</v>
+      </c>
+      <c r="D83" s="4">
+        <v>5.86</v>
+      </c>
+      <c r="E83" s="4" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="M1:Q1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="M2:Q2"/>
     <mergeCell ref="A8:E8"/>
-    <mergeCell ref="G8:K8"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="G14:K14"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:E80"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="做T的股票" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$I$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$L$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">定投股票!$B$1:$I$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已出售!$C$1:$D$6</definedName>
   </definedNames>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="90">
   <si>
     <t>时间</t>
   </si>
@@ -81,6 +81,15 @@
     <t>成本</t>
   </si>
   <si>
+    <t>手续费</t>
+  </si>
+  <si>
+    <t>去年最低股价</t>
+  </si>
+  <si>
+    <t>今年最低股价</t>
+  </si>
+  <si>
     <t>状态</t>
   </si>
   <si>
@@ -96,6 +105,9 @@
     <t>等待反弹出售</t>
   </si>
   <si>
+    <t>售出</t>
+  </si>
+  <si>
     <t>山西焦化</t>
   </si>
   <si>
@@ -106,9 +118,6 @@
   </si>
   <si>
     <t>锌业股份</t>
-  </si>
-  <si>
-    <t>售出</t>
   </si>
   <si>
     <t>股票在4.2附近的时候增持1000股到2000股，盈利大于300元就可以抛出</t>
@@ -217,6 +226,9 @@
     <t>力盛体育</t>
   </si>
   <si>
+    <t>天下秀</t>
+  </si>
+  <si>
     <t>工商银行</t>
   </si>
   <si>
@@ -239,9 +251,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>手续费</t>
   </si>
   <si>
     <t>盈亏</t>
@@ -1015,7 +1024,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1113,10 +1122,46 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1124,49 +1169,49 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1701,12 +1746,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="10.3727272727273" customWidth="1"/>
-    <col min="2" max="2" width="8.87272727272727" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="6" width="8.87272727272727" customWidth="1"/>
+    <col min="1" max="1" width="10.3703703703704" customWidth="1"/>
+    <col min="2" max="2" width="8.87037037037037" customWidth="1"/>
+    <col min="3" max="3" width="10.8703703703704" customWidth="1"/>
+    <col min="4" max="6" width="8.87037037037037" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1922,20 +1967,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K109"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:N125"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="15"/>
-    <col min="2" max="2" width="9.37272727272727" style="23"/>
-    <col min="3" max="3" width="9" style="23"/>
-    <col min="4" max="4" width="9" style="15"/>
-    <col min="5" max="8" width="12.8727272727273" style="15" customWidth="1"/>
-    <col min="9" max="9" width="9" style="23"/>
-    <col min="10" max="10" width="68.6272727272727" style="24" customWidth="1"/>
+    <col min="1" max="1" width="9" style="32"/>
+    <col min="2" max="2" width="9.37037037037037" style="32"/>
+    <col min="3" max="3" width="9" style="32"/>
+    <col min="4" max="4" width="9" style="33"/>
+    <col min="5" max="10" width="12.8703703703704" style="33" customWidth="1"/>
+    <col min="11" max="11" width="12.8703703703704" style="34" customWidth="1"/>
+    <col min="12" max="12" width="9" style="32"/>
+    <col min="13" max="13" width="68.6296296296296" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="23" customFormat="1" ht="28" spans="1:11">
-      <c r="A1" s="14" t="s">
+    <row r="1" s="23" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="17" t="s">
@@ -1947,34 +1993,43 @@
       <c r="D1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="14">
+      <c r="K1" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:14">
+      <c r="A2" s="32">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="32">
         <v>300323</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>16</v>
+      <c r="C2" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="D2" s="14">
         <v>1</v>
@@ -1989,125 +2044,132 @@
         <v>1600</v>
       </c>
       <c r="H2" s="14">
-        <f t="shared" ref="H2:H20" si="0">F2*G2</f>
+        <f>F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="23"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="14">
+      <c r="I2" s="14"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="39">
+        <v>9.99</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="23"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:14">
+      <c r="D3" s="40">
         <v>2</v>
       </c>
-      <c r="B3" s="17">
+      <c r="E3" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F3" s="31">
+        <v>11</v>
+      </c>
+      <c r="G3" s="31">
+        <v>-1000</v>
+      </c>
+      <c r="H3" s="40">
+        <f>F3*G3</f>
+        <v>-11000</v>
+      </c>
+      <c r="I3" s="40"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="26"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:14">
+      <c r="A4" s="17">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
         <v>600740</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="14">
+      <c r="C4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="14">
         <v>1</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E4" s="13">
         <v>46182</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F4" s="14">
         <v>4.1541</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G4" s="14">
         <v>1800</v>
       </c>
-      <c r="H3" s="14">
-        <f t="shared" si="0"/>
+      <c r="H4" s="14">
+        <f>F4*G4</f>
         <v>7477.38</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="33">
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="45">
+        <v>3.15</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:14">
+      <c r="A5" s="46">
         <v>3</v>
       </c>
-      <c r="B4" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="34" t="s">
+      <c r="B5" s="61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="28">
+        <v>1</v>
+      </c>
+      <c r="E5" s="47">
+        <v>46182</v>
+      </c>
+      <c r="F5" s="28">
+        <v>4.8581</v>
+      </c>
+      <c r="G5" s="28">
+        <v>-4300</v>
+      </c>
+      <c r="H5" s="28">
+        <f>F5*G5</f>
+        <v>-20889.83</v>
+      </c>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="48">
+        <v>4.02</v>
+      </c>
+      <c r="L5" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="28">
-        <v>1</v>
-      </c>
-      <c r="E4" s="35">
-        <v>46182</v>
-      </c>
-      <c r="F4" s="28">
-        <v>4.8581</v>
-      </c>
-      <c r="G4" s="28">
-        <v>4300</v>
-      </c>
-      <c r="H4" s="28">
-        <f t="shared" si="0"/>
-        <v>20889.83</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="14">
+      <c r="M5" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:14">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B6" s="17">
         <v>601990</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="14">
-        <v>1</v>
-      </c>
-      <c r="E5" s="13">
-        <v>46182</v>
-      </c>
-      <c r="F5" s="14">
-        <v>9.9227</v>
-      </c>
-      <c r="G5" s="14">
-        <v>500</v>
-      </c>
-      <c r="H5" s="14">
-        <f t="shared" si="0"/>
-        <v>4961.35</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="14">
-        <v>5</v>
-      </c>
-      <c r="B6" s="17">
-        <v>600059</v>
-      </c>
       <c r="C6" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="14">
         <v>1</v>
@@ -2116,30 +2178,35 @@
         <v>46182</v>
       </c>
       <c r="F6" s="14">
-        <v>10.9008</v>
+        <v>9.9227</v>
       </c>
       <c r="G6" s="14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H6" s="14">
-        <f t="shared" si="0"/>
-        <v>10900.8</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="14">
-        <v>6</v>
-      </c>
-      <c r="B7" s="51" t="s">
+        <f>F6*G6</f>
+        <v>4961.35</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="45">
+        <v>6.46</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="17" t="s">
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:14">
+      <c r="A7" s="32">
+        <v>5</v>
+      </c>
+      <c r="B7" s="32">
+        <v>600059</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="14">
@@ -2149,64 +2216,61 @@
         <v>46182</v>
       </c>
       <c r="F7" s="14">
-        <v>9.6507</v>
+        <v>10.9008</v>
       </c>
       <c r="G7" s="14">
         <v>1000</v>
       </c>
       <c r="H7" s="14">
-        <f t="shared" si="0"/>
-        <v>9650.7</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="26" t="s">
+        <f>F7*G7</f>
+        <v>10900.8</v>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="39">
+        <v>7.21</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="26" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="14">
-        <v>7</v>
-      </c>
-      <c r="B8" s="17">
-        <v>601179</v>
-      </c>
-      <c r="C8" s="17" t="s">
+    <row r="8" ht="20" customHeight="1" spans="1:14">
+      <c r="D8" s="40">
+        <v>2</v>
+      </c>
+      <c r="E8" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F8" s="31">
+        <v>8.1</v>
+      </c>
+      <c r="G8" s="31">
+        <v>-500</v>
+      </c>
+      <c r="H8" s="40">
+        <f>F8*G8</f>
+        <v>-4050</v>
+      </c>
+      <c r="I8" s="40"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="26"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:14">
+      <c r="A9" s="32">
+        <v>6</v>
+      </c>
+      <c r="B9" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="14">
-        <v>1</v>
-      </c>
-      <c r="E8" s="13">
-        <v>46182</v>
-      </c>
-      <c r="F8" s="14">
-        <v>20.12</v>
-      </c>
-      <c r="G8" s="14">
-        <v>700</v>
-      </c>
-      <c r="H8" s="14">
-        <f t="shared" si="0"/>
-        <v>14084</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="26" t="s">
+      <c r="C9" s="32" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="36">
-        <v>8</v>
-      </c>
-      <c r="B9" s="19">
-        <v>603258</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>34</v>
       </c>
       <c r="D9" s="14">
         <v>1</v>
@@ -2215,56 +2279,61 @@
         <v>46182</v>
       </c>
       <c r="F9" s="14">
-        <v>20.6888</v>
+        <v>9.6507</v>
       </c>
       <c r="G9" s="14">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H9" s="14">
-        <f t="shared" si="0"/>
-        <v>18619.92</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="26" t="s">
+        <f>F9*G9</f>
+        <v>9650.7</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="49">
+        <v>5.55</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:14">
+      <c r="D10" s="40">
+        <v>2</v>
+      </c>
+      <c r="E10" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F10" s="31">
+        <v>6.11</v>
+      </c>
+      <c r="G10" s="31">
+        <v>-500</v>
+      </c>
+      <c r="H10" s="40">
+        <f>F10*G10</f>
+        <v>-3055</v>
+      </c>
+      <c r="I10" s="40"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="26"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:14">
+      <c r="A11" s="32">
+        <v>7</v>
+      </c>
+      <c r="B11" s="32">
+        <v>601179</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="37"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="14">
-        <v>2</v>
-      </c>
-      <c r="E10" s="13">
-        <v>46233</v>
-      </c>
-      <c r="F10" s="14">
-        <v>12.9</v>
-      </c>
-      <c r="G10" s="14">
-        <v>500</v>
-      </c>
-      <c r="H10" s="14">
-        <f t="shared" si="0"/>
-        <v>6450</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="38"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="36">
-        <v>9</v>
-      </c>
-      <c r="B11" s="19">
-        <v>600422</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>36</v>
       </c>
       <c r="D11" s="14">
         <v>1</v>
@@ -2273,81 +2342,86 @@
         <v>46182</v>
       </c>
       <c r="F11" s="14">
-        <v>21.0619</v>
+        <v>20.12</v>
       </c>
       <c r="G11" s="14">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H11" s="14">
-        <f t="shared" si="0"/>
-        <v>12637.14</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="38" t="s">
+        <f>F11*G11</f>
+        <v>14084</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="39">
+        <v>11.49</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:14">
+      <c r="D12" s="40">
+        <v>2</v>
+      </c>
+      <c r="E12" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F12" s="31">
+        <v>13.5</v>
+      </c>
+      <c r="G12" s="31">
+        <v>-400</v>
+      </c>
+      <c r="H12" s="40">
+        <f>F12*G12</f>
+        <v>-5400</v>
+      </c>
+      <c r="I12" s="40"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="26"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:14">
+      <c r="D13" s="14">
+        <v>3</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46238</v>
+      </c>
+      <c r="F13" s="9">
+        <v>14.4</v>
+      </c>
+      <c r="G13" s="9">
+        <v>700</v>
+      </c>
+      <c r="H13" s="14">
+        <f>F13*G13</f>
+        <v>10080</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="26"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:14">
+      <c r="A14" s="32">
+        <v>8</v>
+      </c>
+      <c r="B14" s="32">
+        <v>603258</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="37"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="39">
-        <v>2</v>
-      </c>
-      <c r="E12" s="40">
-        <v>46188</v>
-      </c>
-      <c r="F12" s="39">
-        <v>8.5</v>
-      </c>
-      <c r="G12" s="39">
-        <v>600</v>
-      </c>
-      <c r="H12" s="39">
-        <f t="shared" si="0"/>
-        <v>5100</v>
-      </c>
-      <c r="I12" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="42"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="43"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="39">
-        <v>3</v>
-      </c>
-      <c r="E13" s="40">
-        <v>46226</v>
-      </c>
-      <c r="F13" s="39">
-        <v>9</v>
-      </c>
-      <c r="G13" s="39">
-        <v>-600</v>
-      </c>
-      <c r="H13" s="39">
-        <f t="shared" si="0"/>
-        <v>-5400</v>
-      </c>
-      <c r="I13" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="42"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="14">
-        <v>10</v>
-      </c>
-      <c r="B14" s="17">
-        <v>600879</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
@@ -2356,820 +2430,1011 @@
         <v>46182</v>
       </c>
       <c r="F14" s="14">
+        <v>20.6888</v>
+      </c>
+      <c r="G14" s="14">
+        <v>900</v>
+      </c>
+      <c r="H14" s="14">
+        <f>F14*G14</f>
+        <v>18619.92</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="39">
+        <v>10.75</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:14">
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="13">
+        <v>46233</v>
+      </c>
+      <c r="F15" s="14">
+        <v>12.9</v>
+      </c>
+      <c r="G15" s="14">
+        <v>500</v>
+      </c>
+      <c r="H15" s="14">
+        <f>F15*G15</f>
+        <v>6450</v>
+      </c>
+      <c r="I15" s="14"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="26"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:14">
+      <c r="D16" s="40">
+        <v>3</v>
+      </c>
+      <c r="E16" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F16" s="31">
+        <v>12.6</v>
+      </c>
+      <c r="G16" s="31">
+        <v>-700</v>
+      </c>
+      <c r="H16" s="40">
+        <f>F16*G16</f>
+        <v>-8820</v>
+      </c>
+      <c r="I16" s="40"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="26"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:13">
+      <c r="A17" s="17">
+        <v>9</v>
+      </c>
+      <c r="B17" s="17">
+        <v>600422</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="14">
+        <v>1</v>
+      </c>
+      <c r="E17" s="13">
+        <v>46182</v>
+      </c>
+      <c r="F17" s="14">
+        <v>21.0619</v>
+      </c>
+      <c r="G17" s="14">
+        <v>600</v>
+      </c>
+      <c r="H17" s="14">
+        <f>F17*G17</f>
+        <v>12637.14</v>
+      </c>
+      <c r="I17" s="14"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="39">
+        <v>7.45</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:13">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="40">
+        <v>2</v>
+      </c>
+      <c r="E18" s="56">
+        <v>46188</v>
+      </c>
+      <c r="F18" s="40">
+        <v>8.5</v>
+      </c>
+      <c r="G18" s="40">
+        <v>600</v>
+      </c>
+      <c r="H18" s="40">
+        <f>F18*G18</f>
+        <v>5100</v>
+      </c>
+      <c r="I18" s="40"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" s="26"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:13">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="40">
+        <v>3</v>
+      </c>
+      <c r="E19" s="56">
+        <v>46226</v>
+      </c>
+      <c r="F19" s="40">
+        <v>9</v>
+      </c>
+      <c r="G19" s="40">
+        <v>-600</v>
+      </c>
+      <c r="H19" s="40">
+        <f>F19*G19</f>
+        <v>-5400</v>
+      </c>
+      <c r="I19" s="40"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" s="26"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:13">
+      <c r="A20" s="32">
+        <v>10</v>
+      </c>
+      <c r="B20" s="32">
+        <v>600879</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13">
+        <v>46182</v>
+      </c>
+      <c r="F20" s="14">
         <v>26.2661</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G20" s="14">
         <v>700</v>
       </c>
-      <c r="H14" s="14">
-        <f t="shared" si="0"/>
+      <c r="H20" s="14">
+        <f>F20*G20</f>
         <v>18386.27</v>
       </c>
-      <c r="I14" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="36">
+      <c r="I20" s="14"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="39">
+        <v>13.85</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:13">
+      <c r="D21" s="40">
+        <v>2</v>
+      </c>
+      <c r="E21" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F21" s="31">
+        <v>14.65</v>
+      </c>
+      <c r="G21" s="31">
+        <v>-400</v>
+      </c>
+      <c r="H21" s="40">
+        <f>F21*G21</f>
+        <v>-5860</v>
+      </c>
+      <c r="I21" s="40"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" s="57"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:13">
+      <c r="A22" s="32">
         <v>11</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B22" s="32">
         <v>601066</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C22" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E22" s="13">
         <v>46182</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F22" s="14">
         <v>27.6302</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G22" s="14">
         <v>3400</v>
       </c>
-      <c r="H15" s="14">
-        <f t="shared" si="0"/>
+      <c r="H22" s="14">
+        <f>F22*G22</f>
         <v>93942.68</v>
       </c>
-      <c r="I15" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="37"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="39">
+      <c r="I22" s="14"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="39">
+        <v>26.18</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M22" s="57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:13">
+      <c r="D23" s="40">
         <v>2</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E23" s="56">
         <v>46192</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F23" s="40">
         <v>31</v>
       </c>
-      <c r="G16" s="39">
+      <c r="G23" s="40">
         <v>-2400</v>
       </c>
-      <c r="H16" s="39">
-        <f t="shared" si="0"/>
+      <c r="H23" s="40">
+        <f>F23*G23</f>
         <v>-74400</v>
       </c>
-      <c r="I16" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="45"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="43"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="14">
+      <c r="I23" s="40"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="26"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:13">
+      <c r="D24" s="14">
         <v>3</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E24" s="13">
         <v>46202</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F24" s="14">
         <v>29.3</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G24" s="14">
         <v>1000</v>
       </c>
-      <c r="H17" s="14">
-        <f t="shared" si="0"/>
+      <c r="H24" s="14">
+        <f>F24*G24</f>
         <v>29300</v>
       </c>
-      <c r="I17" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="42"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="14">
+      <c r="I24" s="14"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="26"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:13">
+      <c r="D25" s="40">
+        <v>4</v>
+      </c>
+      <c r="E25" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F25" s="31">
+        <v>26.1</v>
+      </c>
+      <c r="G25" s="31">
+        <v>-1000</v>
+      </c>
+      <c r="H25" s="40">
+        <f>F25*G25</f>
+        <v>-26100</v>
+      </c>
+      <c r="I25" s="40"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" s="26"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:13">
+      <c r="A26" s="32">
         <v>12</v>
       </c>
-      <c r="B18" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="13">
-        <v>46182</v>
-      </c>
-      <c r="F18" s="14">
-        <v>18.3681</v>
-      </c>
-      <c r="G18" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H18" s="14">
-        <f t="shared" si="0"/>
-        <v>18368.1</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="36">
-        <v>13</v>
-      </c>
-      <c r="B19" s="19">
-        <v>300589</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="B26" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="14">
-        <v>1</v>
-      </c>
-      <c r="E19" s="13">
-        <v>46182</v>
-      </c>
-      <c r="F19" s="14">
-        <v>22.8225</v>
-      </c>
-      <c r="G19" s="14">
-        <v>1200</v>
-      </c>
-      <c r="H19" s="14">
-        <f t="shared" si="0"/>
-        <v>27387</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="26" t="s">
+      <c r="C26" s="32" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="37"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="13">
-        <v>46233</v>
-      </c>
-      <c r="F20" s="14">
-        <v>12.55</v>
-      </c>
-      <c r="G20" s="14">
-        <v>600</v>
-      </c>
-      <c r="H20" s="14">
-        <f t="shared" si="0"/>
-        <v>7530</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="26"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="36">
-        <v>14</v>
-      </c>
-      <c r="B21" s="19">
-        <v>300129</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="14">
-        <v>1</v>
-      </c>
-      <c r="E21" s="13">
-        <v>46182</v>
-      </c>
-      <c r="F21" s="14">
-        <v>14.9016</v>
-      </c>
-      <c r="G21" s="14">
-        <v>2300</v>
-      </c>
-      <c r="H21" s="14">
-        <f t="shared" ref="H21:H28" si="1">F21*G21</f>
-        <v>34273.68</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="46"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="13">
-        <v>46223</v>
-      </c>
-      <c r="F22" s="14">
-        <v>7.35</v>
-      </c>
-      <c r="G22" s="14">
-        <v>700</v>
-      </c>
-      <c r="H22" s="14">
-        <f t="shared" si="1"/>
-        <v>5145</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="26"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="6">
-        <v>15</v>
-      </c>
-      <c r="B23" s="2">
-        <v>600172</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="39">
-        <v>1</v>
-      </c>
-      <c r="E23" s="40">
-        <v>46188</v>
-      </c>
-      <c r="F23" s="39">
-        <v>12.2123</v>
-      </c>
-      <c r="G23" s="39">
-        <v>600</v>
-      </c>
-      <c r="H23" s="39">
-        <f t="shared" si="1"/>
-        <v>7327.38</v>
-      </c>
-      <c r="I23" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="J23" s="48" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="14">
-        <v>16</v>
-      </c>
-      <c r="B24" s="17">
-        <v>600745</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="14">
-        <v>1</v>
-      </c>
-      <c r="E24" s="13">
-        <v>46189</v>
-      </c>
-      <c r="F24" s="14">
-        <v>18.6687</v>
-      </c>
-      <c r="G24" s="14">
-        <v>800</v>
-      </c>
-      <c r="H24" s="14">
-        <f t="shared" si="1"/>
-        <v>14934.96</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="14">
-        <v>17</v>
-      </c>
-      <c r="B25" s="23">
-        <v>600115</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="14">
-        <v>1</v>
-      </c>
-      <c r="E25" s="13">
-        <v>46203</v>
-      </c>
-      <c r="F25" s="14">
-        <v>3.7838</v>
-      </c>
-      <c r="G25" s="14">
-        <v>3200</v>
-      </c>
-      <c r="H25" s="14">
-        <f t="shared" si="1"/>
-        <v>12108.16</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="26"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="36">
-        <v>18</v>
-      </c>
-      <c r="B26" s="19">
-        <v>600360</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>54</v>
       </c>
       <c r="D26" s="14">
         <v>1</v>
       </c>
       <c r="E26" s="13">
-        <v>46203</v>
+        <v>46182</v>
       </c>
       <c r="F26" s="14">
-        <v>14.6146</v>
+        <v>18.3681</v>
       </c>
       <c r="G26" s="14">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="H26" s="14">
-        <f t="shared" si="1"/>
-        <v>26306.28</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="37"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="39">
+        <f>F26*G26</f>
+        <v>18368.1</v>
+      </c>
+      <c r="I26" s="14"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="39">
+        <v>7.12</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:13">
+      <c r="D27" s="40">
         <v>2</v>
       </c>
-      <c r="E27" s="49">
-        <v>46213</v>
-      </c>
-      <c r="F27" s="31">
-        <v>17.59</v>
-      </c>
-      <c r="G27" s="39">
-        <v>-1300</v>
-      </c>
-      <c r="H27" s="39">
-        <f t="shared" si="1"/>
-        <v>-22867</v>
-      </c>
-      <c r="I27" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="43"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
+      <c r="E27" s="56">
+        <v>46234</v>
+      </c>
+      <c r="F27" s="40">
+        <v>7.9</v>
+      </c>
+      <c r="G27" s="40">
+        <v>-500</v>
+      </c>
+      <c r="H27" s="40">
+        <f>F27*G27</f>
+        <v>-3950</v>
+      </c>
+      <c r="I27" s="40"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="26"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:13">
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="13">
-        <v>46226</v>
+        <v>46239</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="G28" s="14">
         <v>500</v>
       </c>
       <c r="H28" s="14">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="I28" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="14">
-        <v>19</v>
-      </c>
-      <c r="B29" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>56</v>
+        <f>F28*G28</f>
+        <v>4300</v>
+      </c>
+      <c r="I28" s="14"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" s="26"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:13">
+      <c r="A29" s="32">
+        <v>13</v>
+      </c>
+      <c r="B29" s="32">
+        <v>300589</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>48</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="13">
-        <v>46204</v>
+        <v>46182</v>
       </c>
       <c r="F29" s="14">
-        <v>8.5585</v>
+        <v>22.8225</v>
       </c>
       <c r="G29" s="14">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="H29" s="14">
-        <f t="shared" ref="H29:H56" si="2">F29*G29</f>
-        <v>14549.45</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="14">
-        <v>20</v>
-      </c>
-      <c r="B30" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>58</v>
-      </c>
+        <f>F29*G29</f>
+        <v>27387</v>
+      </c>
+      <c r="I29" s="14"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="39">
+        <v>7.63</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M29" s="26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:13">
       <c r="D30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="13">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="F30" s="14">
-        <v>10.2102</v>
+        <v>12.55</v>
       </c>
       <c r="G30" s="14">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H30" s="14">
-        <f t="shared" si="2"/>
-        <v>10210.2</v>
-      </c>
-      <c r="I30" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="14">
-        <v>21</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+        <f>F30*G30</f>
+        <v>7530</v>
+      </c>
+      <c r="I30" s="14"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M30" s="26"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:13">
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="13"/>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
-      <c r="H31" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="17" t="s">
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="26"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="1:13">
+      <c r="A32" s="32">
+        <v>14</v>
+      </c>
+      <c r="B32" s="32">
+        <v>300129</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="14">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13">
+        <v>46182</v>
+      </c>
+      <c r="F32" s="14">
+        <v>14.9016</v>
+      </c>
+      <c r="G32" s="14">
+        <v>2300</v>
+      </c>
+      <c r="H32" s="14">
+        <f>F32*G32</f>
+        <v>34273.68</v>
+      </c>
+      <c r="I32" s="14"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="39">
+        <v>4.36</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="1:13">
+      <c r="D33" s="14">
+        <v>2</v>
+      </c>
+      <c r="E33" s="13">
+        <v>46223</v>
+      </c>
+      <c r="F33" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="G33" s="14">
+        <v>700</v>
+      </c>
+      <c r="H33" s="14">
+        <f>F33*G33</f>
+        <v>5145</v>
+      </c>
+      <c r="I33" s="14"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" s="26"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="1:13">
+      <c r="D34" s="40">
+        <v>3</v>
+      </c>
+      <c r="E34" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F34" s="31">
+        <v>7.8</v>
+      </c>
+      <c r="G34" s="31">
+        <v>-1000</v>
+      </c>
+      <c r="H34" s="40">
+        <f>F34*G34</f>
+        <v>-7800</v>
+      </c>
+      <c r="I34" s="40"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="58"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="1:13">
+      <c r="A35" s="2">
+        <v>15</v>
+      </c>
+      <c r="B35" s="2">
+        <v>600172</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="40">
+        <v>1</v>
+      </c>
+      <c r="E35" s="56">
+        <v>46188</v>
+      </c>
+      <c r="F35" s="40">
+        <v>12.2123</v>
+      </c>
+      <c r="G35" s="40">
+        <v>-600</v>
+      </c>
+      <c r="H35" s="40">
+        <f>F35*G35</f>
+        <v>-7327.38</v>
+      </c>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="59">
+        <v>3.71</v>
+      </c>
+      <c r="L35" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35" s="58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:13">
+      <c r="A36" s="32">
+        <v>16</v>
+      </c>
+      <c r="B36" s="32">
+        <v>600745</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="14">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13">
+        <v>46189</v>
+      </c>
+      <c r="F36" s="14">
+        <v>18.6687</v>
+      </c>
+      <c r="G36" s="14">
+        <v>800</v>
+      </c>
+      <c r="H36" s="14">
+        <f>F36*G36</f>
+        <v>14934.96</v>
+      </c>
+      <c r="I36" s="14"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="39">
+        <v>15.2</v>
+      </c>
+      <c r="L36" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:13">
+      <c r="D37" s="40">
+        <v>2</v>
+      </c>
+      <c r="E37" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F37" s="31">
+        <v>16.75</v>
+      </c>
+      <c r="G37" s="31">
+        <v>-100</v>
+      </c>
+      <c r="H37" s="40">
+        <f>F37*G37</f>
+        <v>-1675</v>
+      </c>
+      <c r="I37" s="31">
+        <v>5.86</v>
+      </c>
+      <c r="J37" s="60"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" s="26"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:13">
+      <c r="A38" s="32">
         <v>17</v>
       </c>
-      <c r="J31" s="26"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="14">
+      <c r="B38" s="32">
+        <v>600115</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="14">
+        <v>1</v>
+      </c>
+      <c r="E38" s="13">
+        <v>46203</v>
+      </c>
+      <c r="F38" s="14">
+        <v>3.7838</v>
+      </c>
+      <c r="G38" s="14">
+        <v>3200</v>
+      </c>
+      <c r="H38" s="14">
+        <f>F38*G38</f>
+        <v>12108.16</v>
+      </c>
+      <c r="I38" s="14"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="39">
+        <v>3.46</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="26"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:13">
+      <c r="D39" s="40">
+        <v>2</v>
+      </c>
+      <c r="E39" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F39" s="31">
+        <v>3.7</v>
+      </c>
+      <c r="G39" s="31">
+        <v>-2000</v>
+      </c>
+      <c r="H39" s="40">
+        <f>F39*G39</f>
+        <v>-7400</v>
+      </c>
+      <c r="I39" s="31"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="26"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="14">
-        <v>23</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="26"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="14">
-        <v>24</v>
-      </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="26"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="14">
-        <v>25</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="26"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="14">
-        <v>26</v>
-      </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="26"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="14">
-        <v>27</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="14">
-        <v>28</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="26"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="14">
-        <v>29</v>
-      </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="26"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="14">
-        <v>30</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="M39" s="26"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:13">
+      <c r="A40" s="32">
+        <v>18</v>
+      </c>
+      <c r="B40" s="32">
+        <v>600360</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="14">
+        <v>1</v>
+      </c>
+      <c r="E40" s="13">
+        <v>46203</v>
+      </c>
+      <c r="F40" s="14">
+        <v>14.6146</v>
+      </c>
+      <c r="G40" s="14">
+        <v>1800</v>
+      </c>
       <c r="H40" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="26"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="14">
-        <v>31</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="26"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="14">
-        <v>32</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
+        <f>F40*G40</f>
+        <v>26306.28</v>
+      </c>
+      <c r="I40" s="14"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="39">
+        <v>6.07</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" s="26"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:13">
+      <c r="D41" s="40">
+        <v>2</v>
+      </c>
+      <c r="E41" s="41">
+        <v>46213</v>
+      </c>
+      <c r="F41" s="31">
+        <v>17.59</v>
+      </c>
+      <c r="G41" s="40">
+        <v>-1300</v>
+      </c>
+      <c r="H41" s="40">
+        <f>F41*G41</f>
+        <v>-22867</v>
+      </c>
+      <c r="I41" s="40"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="51"/>
+      <c r="L41" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" s="26"/>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:13">
+      <c r="D42" s="14">
+        <v>3</v>
+      </c>
+      <c r="E42" s="13">
+        <v>46226</v>
+      </c>
+      <c r="F42" s="14">
+        <v>10</v>
+      </c>
+      <c r="G42" s="14">
+        <v>500</v>
+      </c>
       <c r="H42" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="26"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="14">
-        <v>33</v>
-      </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="26"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="14">
-        <v>34</v>
-      </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
+        <f>F42*G42</f>
+        <v>5000</v>
+      </c>
+      <c r="I42" s="14"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42" s="26"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:13">
+      <c r="D43" s="40">
+        <v>4</v>
+      </c>
+      <c r="E43" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F43" s="31">
+        <v>9.6</v>
+      </c>
+      <c r="G43" s="31">
+        <v>-500</v>
+      </c>
+      <c r="H43" s="40">
+        <f>F43*G43</f>
+        <v>-4800</v>
+      </c>
+      <c r="I43" s="40"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" s="26"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:13">
+      <c r="A44" s="32">
+        <v>19</v>
+      </c>
+      <c r="B44" s="62" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="14">
+        <v>1</v>
+      </c>
+      <c r="E44" s="13">
+        <v>46204</v>
+      </c>
+      <c r="F44" s="14">
+        <v>8.5585</v>
+      </c>
+      <c r="G44" s="14">
+        <v>1700</v>
+      </c>
       <c r="H44" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="26"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="14">
-        <v>35</v>
-      </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="26"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="14">
-        <v>36</v>
-      </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+        <f>F44*G44</f>
+        <v>14549.45</v>
+      </c>
+      <c r="I44" s="14"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="39">
+        <v>3.42</v>
+      </c>
+      <c r="L44" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="26"/>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:13">
+      <c r="D45" s="40">
+        <v>2</v>
+      </c>
+      <c r="E45" s="41">
+        <v>46234</v>
+      </c>
+      <c r="F45" s="31">
+        <v>5.65</v>
+      </c>
+      <c r="G45" s="31">
+        <v>-1000</v>
+      </c>
+      <c r="H45" s="40">
+        <f>F45*G45</f>
+        <v>-5650</v>
+      </c>
+      <c r="I45" s="40"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="26"/>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="1:13">
+      <c r="A46" s="17">
+        <v>20</v>
+      </c>
+      <c r="B46" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="14">
+        <v>1</v>
+      </c>
+      <c r="E46" s="13">
+        <v>46227</v>
+      </c>
+      <c r="F46" s="14">
+        <v>10.2102</v>
+      </c>
+      <c r="G46" s="14">
+        <v>1000</v>
+      </c>
       <c r="H46" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="26"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="14">
-        <v>37</v>
-      </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
+        <f t="shared" ref="H46:H72" si="0">F46*G46</f>
+        <v>10210.2</v>
+      </c>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="45">
+        <v>10.26</v>
+      </c>
+      <c r="L46" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="26"/>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:13">
+      <c r="A47" s="17">
+        <v>21</v>
+      </c>
+      <c r="B47" s="17">
+        <v>600556</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" s="14">
+        <v>1</v>
+      </c>
+      <c r="E47" s="13">
+        <v>46239</v>
+      </c>
+      <c r="F47" s="14">
+        <v>5.3053</v>
+      </c>
+      <c r="G47" s="14">
+        <v>2000</v>
+      </c>
       <c r="H47" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="26"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="14">
-        <v>38</v>
+        <f t="shared" si="0"/>
+        <v>10610.6</v>
+      </c>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="45">
+        <v>3.03</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="26"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="17">
+        <v>22</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -3178,17 +3443,20 @@
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
       <c r="H48" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="26"/>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="14">
-        <v>39</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M48" s="26"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="17">
+        <v>23</v>
       </c>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -3197,17 +3465,20 @@
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
       <c r="H49" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="26"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="14">
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="26"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="17">
+        <v>24</v>
       </c>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -3216,17 +3487,20 @@
       <c r="F50" s="14"/>
       <c r="G50" s="14"/>
       <c r="H50" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="26"/>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="14">
-        <v>41</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="26"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="17">
+        <v>25</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -3235,17 +3509,20 @@
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
       <c r="H51" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="26"/>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="14">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="26"/>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="17">
+        <v>26</v>
       </c>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -3254,17 +3531,20 @@
       <c r="F52" s="14"/>
       <c r="G52" s="14"/>
       <c r="H52" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="26"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="14">
-        <v>43</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="45"/>
+      <c r="L52" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M52" s="26"/>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="17">
+        <v>27</v>
       </c>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -3273,17 +3553,20 @@
       <c r="F53" s="14"/>
       <c r="G53" s="14"/>
       <c r="H53" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="26"/>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="14">
-        <v>44</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M53" s="26"/>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="17">
+        <v>28</v>
       </c>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -3292,17 +3575,20 @@
       <c r="F54" s="14"/>
       <c r="G54" s="14"/>
       <c r="H54" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="26"/>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="14">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M54" s="26"/>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="17">
+        <v>29</v>
       </c>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -3311,17 +3597,20 @@
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
       <c r="H55" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="26"/>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="14">
-        <v>46</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="45"/>
+      <c r="L55" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M55" s="26"/>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="17">
+        <v>30</v>
       </c>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -3330,17 +3619,20 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
       <c r="H56" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="26"/>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="14">
-        <v>47</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="45"/>
+      <c r="L56" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M56" s="26"/>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="17">
+        <v>31</v>
       </c>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -3349,17 +3641,20 @@
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
       <c r="H57" s="14">
-        <f t="shared" ref="H57:H88" si="3">F57*G57</f>
-        <v>0</v>
-      </c>
-      <c r="I57" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="26"/>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="14">
-        <v>48</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="45"/>
+      <c r="L57" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" s="26"/>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="17">
+        <v>32</v>
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -3368,17 +3663,20 @@
       <c r="F58" s="14"/>
       <c r="G58" s="14"/>
       <c r="H58" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="26"/>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="14">
-        <v>49</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="45"/>
+      <c r="L58" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M58" s="26"/>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="17">
+        <v>33</v>
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -3387,17 +3685,20 @@
       <c r="F59" s="14"/>
       <c r="G59" s="14"/>
       <c r="H59" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="26"/>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="14">
-        <v>50</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="45"/>
+      <c r="L59" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M59" s="26"/>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="17">
+        <v>34</v>
       </c>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -3406,17 +3707,20 @@
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
       <c r="H60" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="26"/>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="14">
-        <v>51</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="45"/>
+      <c r="L60" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M60" s="26"/>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" s="17">
+        <v>35</v>
       </c>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -3425,17 +3729,20 @@
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
       <c r="H61" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I61" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="26"/>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="14">
-        <v>52</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="45"/>
+      <c r="L61" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M61" s="26"/>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="A62" s="17">
+        <v>36</v>
       </c>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -3444,17 +3751,20 @@
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
       <c r="H62" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="26"/>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="14">
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="45"/>
+      <c r="L62" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M62" s="26"/>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" s="17">
+        <v>37</v>
       </c>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -3463,17 +3773,20 @@
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
       <c r="H63" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="26"/>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="14">
-        <v>54</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="45"/>
+      <c r="L63" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" s="26"/>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64" s="17">
+        <v>38</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -3482,17 +3795,20 @@
       <c r="F64" s="14"/>
       <c r="G64" s="14"/>
       <c r="H64" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="26"/>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65" s="14">
-        <v>55</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="45"/>
+      <c r="L64" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M64" s="26"/>
+    </row>
+    <row r="65" spans="1:13">
+      <c r="A65" s="17">
+        <v>39</v>
       </c>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -3501,17 +3817,20 @@
       <c r="F65" s="14"/>
       <c r="G65" s="14"/>
       <c r="H65" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="26"/>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66" s="14">
-        <v>56</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="45"/>
+      <c r="L65" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M65" s="26"/>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="A66" s="17">
+        <v>40</v>
       </c>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -3520,17 +3839,20 @@
       <c r="F66" s="14"/>
       <c r="G66" s="14"/>
       <c r="H66" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="26"/>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" s="14">
-        <v>57</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="45"/>
+      <c r="L66" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M66" s="26"/>
+    </row>
+    <row r="67" spans="1:13">
+      <c r="A67" s="17">
+        <v>41</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -3539,17 +3861,20 @@
       <c r="F67" s="14"/>
       <c r="G67" s="14"/>
       <c r="H67" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="26"/>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" s="14">
-        <v>58</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="45"/>
+      <c r="L67" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M67" s="26"/>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68" s="17">
+        <v>42</v>
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -3558,17 +3883,20 @@
       <c r="F68" s="14"/>
       <c r="G68" s="14"/>
       <c r="H68" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="26"/>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" s="14">
-        <v>59</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="45"/>
+      <c r="L68" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M68" s="26"/>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="A69" s="17">
+        <v>43</v>
       </c>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -3577,17 +3905,20 @@
       <c r="F69" s="14"/>
       <c r="G69" s="14"/>
       <c r="H69" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="26"/>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" s="14">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="45"/>
+      <c r="L69" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M69" s="26"/>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="A70" s="17">
+        <v>44</v>
       </c>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -3596,17 +3927,20 @@
       <c r="F70" s="14"/>
       <c r="G70" s="14"/>
       <c r="H70" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="26"/>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71" s="14">
-        <v>61</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="45"/>
+      <c r="L70" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M70" s="26"/>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71" s="17">
+        <v>45</v>
       </c>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -3615,17 +3949,20 @@
       <c r="F71" s="14"/>
       <c r="G71" s="14"/>
       <c r="H71" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="26"/>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72" s="14">
-        <v>62</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="45"/>
+      <c r="L71" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M71" s="26"/>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72" s="17">
+        <v>46</v>
       </c>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -3634,17 +3971,20 @@
       <c r="F72" s="14"/>
       <c r="G72" s="14"/>
       <c r="H72" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I72" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="26"/>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" s="14">
-        <v>63</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="45"/>
+      <c r="L72" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M72" s="26"/>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73" s="17">
+        <v>47</v>
       </c>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -3653,17 +3993,20 @@
       <c r="F73" s="14"/>
       <c r="G73" s="14"/>
       <c r="H73" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="26"/>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" s="14">
-        <v>64</v>
+        <f t="shared" ref="H73:H104" si="1">F73*G73</f>
+        <v>0</v>
+      </c>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="45"/>
+      <c r="L73" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M73" s="26"/>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="17">
+        <v>48</v>
       </c>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -3672,17 +4015,20 @@
       <c r="F74" s="14"/>
       <c r="G74" s="14"/>
       <c r="H74" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="26"/>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" s="14">
-        <v>65</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="45"/>
+      <c r="L74" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M74" s="26"/>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="17">
+        <v>49</v>
       </c>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -3691,17 +4037,20 @@
       <c r="F75" s="14"/>
       <c r="G75" s="14"/>
       <c r="H75" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="26"/>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" s="14">
-        <v>66</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="45"/>
+      <c r="L75" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M75" s="26"/>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" s="17">
+        <v>50</v>
       </c>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -3710,17 +4059,20 @@
       <c r="F76" s="14"/>
       <c r="G76" s="14"/>
       <c r="H76" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="26"/>
-    </row>
-    <row r="77" spans="1:10">
-      <c r="A77" s="14">
-        <v>67</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="45"/>
+      <c r="L76" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M76" s="26"/>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" s="17">
+        <v>51</v>
       </c>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -3729,17 +4081,20 @@
       <c r="F77" s="14"/>
       <c r="G77" s="14"/>
       <c r="H77" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="26"/>
-    </row>
-    <row r="78" spans="1:10">
-      <c r="A78" s="14">
-        <v>68</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="45"/>
+      <c r="L77" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M77" s="26"/>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" s="17">
+        <v>52</v>
       </c>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -3748,17 +4103,20 @@
       <c r="F78" s="14"/>
       <c r="G78" s="14"/>
       <c r="H78" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="26"/>
-    </row>
-    <row r="79" spans="1:10">
-      <c r="A79" s="14">
-        <v>69</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="45"/>
+      <c r="L78" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M78" s="26"/>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" s="17">
+        <v>53</v>
       </c>
       <c r="B79" s="17"/>
       <c r="C79" s="17"/>
@@ -3767,17 +4125,20 @@
       <c r="F79" s="14"/>
       <c r="G79" s="14"/>
       <c r="H79" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="26"/>
-    </row>
-    <row r="80" spans="1:10">
-      <c r="A80" s="14">
-        <v>70</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="45"/>
+      <c r="L79" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M79" s="26"/>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" s="17">
+        <v>54</v>
       </c>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -3786,17 +4147,20 @@
       <c r="F80" s="14"/>
       <c r="G80" s="14"/>
       <c r="H80" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="26"/>
-    </row>
-    <row r="81" spans="1:10">
-      <c r="A81" s="14">
-        <v>71</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+      <c r="K80" s="45"/>
+      <c r="L80" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M80" s="26"/>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="17">
+        <v>55</v>
       </c>
       <c r="B81" s="17"/>
       <c r="C81" s="17"/>
@@ -3805,17 +4169,20 @@
       <c r="F81" s="14"/>
       <c r="G81" s="14"/>
       <c r="H81" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="26"/>
-    </row>
-    <row r="82" spans="1:10">
-      <c r="A82" s="14">
-        <v>72</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="45"/>
+      <c r="L81" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81" s="26"/>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="17">
+        <v>56</v>
       </c>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -3824,17 +4191,20 @@
       <c r="F82" s="14"/>
       <c r="G82" s="14"/>
       <c r="H82" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="26"/>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" s="14">
-        <v>73</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="45"/>
+      <c r="L82" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M82" s="26"/>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="17">
+        <v>57</v>
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
@@ -3843,17 +4213,20 @@
       <c r="F83" s="14"/>
       <c r="G83" s="14"/>
       <c r="H83" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="26"/>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" s="14">
-        <v>74</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="45"/>
+      <c r="L83" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M83" s="26"/>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="17">
+        <v>58</v>
       </c>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -3862,17 +4235,20 @@
       <c r="F84" s="14"/>
       <c r="G84" s="14"/>
       <c r="H84" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="26"/>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="14">
-        <v>75</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="45"/>
+      <c r="L84" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M84" s="26"/>
+    </row>
+    <row r="85" spans="1:13">
+      <c r="A85" s="17">
+        <v>59</v>
       </c>
       <c r="B85" s="17"/>
       <c r="C85" s="17"/>
@@ -3881,17 +4257,20 @@
       <c r="F85" s="14"/>
       <c r="G85" s="14"/>
       <c r="H85" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="26"/>
-    </row>
-    <row r="86" spans="1:10">
-      <c r="A86" s="14">
-        <v>76</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="45"/>
+      <c r="L85" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M85" s="26"/>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="A86" s="17">
+        <v>60</v>
       </c>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -3900,17 +4279,20 @@
       <c r="F86" s="14"/>
       <c r="G86" s="14"/>
       <c r="H86" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="26"/>
-    </row>
-    <row r="87" spans="1:10">
-      <c r="A87" s="14">
-        <v>77</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+      <c r="K86" s="45"/>
+      <c r="L86" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M86" s="26"/>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="17">
+        <v>61</v>
       </c>
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
@@ -3919,17 +4301,20 @@
       <c r="F87" s="14"/>
       <c r="G87" s="14"/>
       <c r="H87" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="26"/>
-    </row>
-    <row r="88" spans="1:10">
-      <c r="A88" s="14">
-        <v>78</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="45"/>
+      <c r="L87" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M87" s="26"/>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" s="17">
+        <v>62</v>
       </c>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -3938,17 +4323,20 @@
       <c r="F88" s="14"/>
       <c r="G88" s="14"/>
       <c r="H88" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="26"/>
-    </row>
-    <row r="89" spans="1:10">
-      <c r="A89" s="14">
-        <v>79</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="45"/>
+      <c r="L88" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M88" s="26"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="17">
+        <v>63</v>
       </c>
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
@@ -3957,17 +4345,20 @@
       <c r="F89" s="14"/>
       <c r="G89" s="14"/>
       <c r="H89" s="14">
-        <f t="shared" ref="H89:H109" si="4">F89*G89</f>
-        <v>0</v>
-      </c>
-      <c r="I89" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="26"/>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" s="14">
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+      <c r="K89" s="45"/>
+      <c r="L89" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M89" s="26"/>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" s="17">
+        <v>64</v>
       </c>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -3976,17 +4367,20 @@
       <c r="F90" s="14"/>
       <c r="G90" s="14"/>
       <c r="H90" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="26"/>
-    </row>
-    <row r="91" spans="1:10">
-      <c r="A91" s="14">
-        <v>81</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+      <c r="K90" s="45"/>
+      <c r="L90" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M90" s="26"/>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="17">
+        <v>65</v>
       </c>
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
@@ -3995,17 +4389,20 @@
       <c r="F91" s="14"/>
       <c r="G91" s="14"/>
       <c r="H91" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="26"/>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="A92" s="14">
-        <v>82</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+      <c r="K91" s="45"/>
+      <c r="L91" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M91" s="26"/>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" s="17">
+        <v>66</v>
       </c>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -4014,17 +4411,20 @@
       <c r="F92" s="14"/>
       <c r="G92" s="14"/>
       <c r="H92" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="26"/>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="A93" s="14">
-        <v>83</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+      <c r="K92" s="45"/>
+      <c r="L92" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M92" s="26"/>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="A93" s="17">
+        <v>67</v>
       </c>
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
@@ -4033,17 +4433,20 @@
       <c r="F93" s="14"/>
       <c r="G93" s="14"/>
       <c r="H93" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I93" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="26"/>
-    </row>
-    <row r="94" spans="1:10">
-      <c r="A94" s="14">
-        <v>84</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I93" s="14"/>
+      <c r="J93" s="14"/>
+      <c r="K93" s="45"/>
+      <c r="L93" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M93" s="26"/>
+    </row>
+    <row r="94" spans="1:13">
+      <c r="A94" s="17">
+        <v>68</v>
       </c>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -4052,17 +4455,20 @@
       <c r="F94" s="14"/>
       <c r="G94" s="14"/>
       <c r="H94" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I94" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="26"/>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="A95" s="14">
-        <v>85</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I94" s="14"/>
+      <c r="J94" s="14"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M94" s="26"/>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="A95" s="17">
+        <v>69</v>
       </c>
       <c r="B95" s="17"/>
       <c r="C95" s="17"/>
@@ -4071,17 +4477,20 @@
       <c r="F95" s="14"/>
       <c r="G95" s="14"/>
       <c r="H95" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="26"/>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="A96" s="14">
-        <v>86</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I95" s="14"/>
+      <c r="J95" s="14"/>
+      <c r="K95" s="45"/>
+      <c r="L95" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M95" s="26"/>
+    </row>
+    <row r="96" spans="1:13">
+      <c r="A96" s="17">
+        <v>70</v>
       </c>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -4090,17 +4499,20 @@
       <c r="F96" s="14"/>
       <c r="G96" s="14"/>
       <c r="H96" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I96" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="26"/>
-    </row>
-    <row r="97" spans="1:10">
-      <c r="A97" s="14">
-        <v>87</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+      <c r="K96" s="45"/>
+      <c r="L96" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M96" s="26"/>
+    </row>
+    <row r="97" spans="1:13">
+      <c r="A97" s="17">
+        <v>71</v>
       </c>
       <c r="B97" s="17"/>
       <c r="C97" s="17"/>
@@ -4109,17 +4521,20 @@
       <c r="F97" s="14"/>
       <c r="G97" s="14"/>
       <c r="H97" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I97" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="26"/>
-    </row>
-    <row r="98" spans="1:10">
-      <c r="A98" s="14">
-        <v>88</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+      <c r="K97" s="45"/>
+      <c r="L97" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M97" s="26"/>
+    </row>
+    <row r="98" spans="1:13">
+      <c r="A98" s="17">
+        <v>72</v>
       </c>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -4128,17 +4543,20 @@
       <c r="F98" s="14"/>
       <c r="G98" s="14"/>
       <c r="H98" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I98" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="26"/>
-    </row>
-    <row r="99" spans="1:10">
-      <c r="A99" s="14">
-        <v>89</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I98" s="14"/>
+      <c r="J98" s="14"/>
+      <c r="K98" s="45"/>
+      <c r="L98" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M98" s="26"/>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="A99" s="17">
+        <v>73</v>
       </c>
       <c r="B99" s="17"/>
       <c r="C99" s="17"/>
@@ -4147,17 +4565,20 @@
       <c r="F99" s="14"/>
       <c r="G99" s="14"/>
       <c r="H99" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I99" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="26"/>
-    </row>
-    <row r="100" spans="1:10">
-      <c r="A100" s="14">
-        <v>90</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I99" s="14"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="45"/>
+      <c r="L99" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M99" s="26"/>
+    </row>
+    <row r="100" spans="1:13">
+      <c r="A100" s="17">
+        <v>74</v>
       </c>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -4166,17 +4587,20 @@
       <c r="F100" s="14"/>
       <c r="G100" s="14"/>
       <c r="H100" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="26"/>
-    </row>
-    <row r="101" spans="1:10">
-      <c r="A101" s="14">
-        <v>91</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I100" s="14"/>
+      <c r="J100" s="14"/>
+      <c r="K100" s="45"/>
+      <c r="L100" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M100" s="26"/>
+    </row>
+    <row r="101" spans="1:13">
+      <c r="A101" s="17">
+        <v>75</v>
       </c>
       <c r="B101" s="17"/>
       <c r="C101" s="17"/>
@@ -4185,17 +4609,20 @@
       <c r="F101" s="14"/>
       <c r="G101" s="14"/>
       <c r="H101" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I101" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="26"/>
-    </row>
-    <row r="102" spans="1:10">
-      <c r="A102" s="14">
-        <v>92</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I101" s="14"/>
+      <c r="J101" s="14"/>
+      <c r="K101" s="45"/>
+      <c r="L101" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M101" s="26"/>
+    </row>
+    <row r="102" spans="1:13">
+      <c r="A102" s="17">
+        <v>76</v>
       </c>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -4204,17 +4631,20 @@
       <c r="F102" s="14"/>
       <c r="G102" s="14"/>
       <c r="H102" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I102" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" s="26"/>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" s="14">
-        <v>93</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I102" s="14"/>
+      <c r="J102" s="14"/>
+      <c r="K102" s="45"/>
+      <c r="L102" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M102" s="26"/>
+    </row>
+    <row r="103" spans="1:13">
+      <c r="A103" s="17">
+        <v>77</v>
       </c>
       <c r="B103" s="17"/>
       <c r="C103" s="17"/>
@@ -4223,17 +4653,20 @@
       <c r="F103" s="14"/>
       <c r="G103" s="14"/>
       <c r="H103" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" s="26"/>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="A104" s="14">
-        <v>94</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="45"/>
+      <c r="L103" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M103" s="26"/>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" s="17">
+        <v>78</v>
       </c>
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
@@ -4242,17 +4675,20 @@
       <c r="F104" s="14"/>
       <c r="G104" s="14"/>
       <c r="H104" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J104" s="26"/>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" s="14">
-        <v>95</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I104" s="14"/>
+      <c r="J104" s="14"/>
+      <c r="K104" s="45"/>
+      <c r="L104" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M104" s="26"/>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="17">
+        <v>79</v>
       </c>
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
@@ -4261,17 +4697,20 @@
       <c r="F105" s="14"/>
       <c r="G105" s="14"/>
       <c r="H105" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I105" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J105" s="26"/>
-    </row>
-    <row r="106" spans="1:10">
-      <c r="A106" s="14">
-        <v>96</v>
+        <f t="shared" ref="H105:H125" si="2">F105*G105</f>
+        <v>0</v>
+      </c>
+      <c r="I105" s="14"/>
+      <c r="J105" s="14"/>
+      <c r="K105" s="45"/>
+      <c r="L105" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M105" s="26"/>
+    </row>
+    <row r="106" spans="1:13">
+      <c r="A106" s="17">
+        <v>80</v>
       </c>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
@@ -4280,17 +4719,20 @@
       <c r="F106" s="14"/>
       <c r="G106" s="14"/>
       <c r="H106" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J106" s="26"/>
-    </row>
-    <row r="107" spans="1:10">
-      <c r="A107" s="14">
-        <v>97</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I106" s="14"/>
+      <c r="J106" s="14"/>
+      <c r="K106" s="45"/>
+      <c r="L106" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M106" s="26"/>
+    </row>
+    <row r="107" spans="1:13">
+      <c r="A107" s="17">
+        <v>81</v>
       </c>
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
@@ -4299,17 +4741,20 @@
       <c r="F107" s="14"/>
       <c r="G107" s="14"/>
       <c r="H107" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I107" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="26"/>
-    </row>
-    <row r="108" spans="1:10">
-      <c r="A108" s="14">
-        <v>98</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="14"/>
+      <c r="J107" s="14"/>
+      <c r="K107" s="45"/>
+      <c r="L107" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M107" s="26"/>
+    </row>
+    <row r="108" spans="1:13">
+      <c r="A108" s="17">
+        <v>82</v>
       </c>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
@@ -4318,17 +4763,20 @@
       <c r="F108" s="14"/>
       <c r="G108" s="14"/>
       <c r="H108" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I108" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J108" s="26"/>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="A109" s="14">
-        <v>99</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I108" s="14"/>
+      <c r="J108" s="14"/>
+      <c r="K108" s="45"/>
+      <c r="L108" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M108" s="26"/>
+    </row>
+    <row r="109" spans="1:13">
+      <c r="A109" s="17">
+        <v>83</v>
       </c>
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
@@ -4337,43 +4785,440 @@
       <c r="F109" s="14"/>
       <c r="G109" s="14"/>
       <c r="H109" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I109" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J109" s="26"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I109" s="14"/>
+      <c r="J109" s="14"/>
+      <c r="K109" s="45"/>
+      <c r="L109" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M109" s="26"/>
+    </row>
+    <row r="110" spans="1:13">
+      <c r="A110" s="17">
+        <v>84</v>
+      </c>
+      <c r="B110" s="17"/>
+      <c r="C110" s="17"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="14"/>
+      <c r="F110" s="14"/>
+      <c r="G110" s="14"/>
+      <c r="H110" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I110" s="14"/>
+      <c r="J110" s="14"/>
+      <c r="K110" s="45"/>
+      <c r="L110" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M110" s="26"/>
+    </row>
+    <row r="111" spans="1:13">
+      <c r="A111" s="17">
+        <v>85</v>
+      </c>
+      <c r="B111" s="17"/>
+      <c r="C111" s="17"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
+      <c r="H111" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I111" s="14"/>
+      <c r="J111" s="14"/>
+      <c r="K111" s="45"/>
+      <c r="L111" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M111" s="26"/>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" s="17">
+        <v>86</v>
+      </c>
+      <c r="B112" s="17"/>
+      <c r="C112" s="17"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
+      <c r="H112" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I112" s="14"/>
+      <c r="J112" s="14"/>
+      <c r="K112" s="45"/>
+      <c r="L112" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M112" s="26"/>
+    </row>
+    <row r="113" spans="1:13">
+      <c r="A113" s="17">
+        <v>87</v>
+      </c>
+      <c r="B113" s="17"/>
+      <c r="C113" s="17"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
+      <c r="G113" s="14"/>
+      <c r="H113" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I113" s="14"/>
+      <c r="J113" s="14"/>
+      <c r="K113" s="45"/>
+      <c r="L113" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M113" s="26"/>
+    </row>
+    <row r="114" spans="1:13">
+      <c r="A114" s="17">
+        <v>88</v>
+      </c>
+      <c r="B114" s="17"/>
+      <c r="C114" s="17"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="14"/>
+      <c r="G114" s="14"/>
+      <c r="H114" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I114" s="14"/>
+      <c r="J114" s="14"/>
+      <c r="K114" s="45"/>
+      <c r="L114" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M114" s="26"/>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115" s="17">
+        <v>89</v>
+      </c>
+      <c r="B115" s="17"/>
+      <c r="C115" s="17"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
+      <c r="H115" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I115" s="14"/>
+      <c r="J115" s="14"/>
+      <c r="K115" s="45"/>
+      <c r="L115" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M115" s="26"/>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" s="17">
+        <v>90</v>
+      </c>
+      <c r="B116" s="17"/>
+      <c r="C116" s="17"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="14"/>
+      <c r="G116" s="14"/>
+      <c r="H116" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I116" s="14"/>
+      <c r="J116" s="14"/>
+      <c r="K116" s="45"/>
+      <c r="L116" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M116" s="26"/>
+    </row>
+    <row r="117" spans="1:13">
+      <c r="A117" s="17">
+        <v>91</v>
+      </c>
+      <c r="B117" s="17"/>
+      <c r="C117" s="17"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="14"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="14"/>
+      <c r="H117" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I117" s="14"/>
+      <c r="J117" s="14"/>
+      <c r="K117" s="45"/>
+      <c r="L117" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M117" s="26"/>
+    </row>
+    <row r="118" spans="1:13">
+      <c r="A118" s="17">
+        <v>92</v>
+      </c>
+      <c r="B118" s="17"/>
+      <c r="C118" s="17"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
+      <c r="H118" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I118" s="14"/>
+      <c r="J118" s="14"/>
+      <c r="K118" s="45"/>
+      <c r="L118" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M118" s="26"/>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="17">
+        <v>93</v>
+      </c>
+      <c r="B119" s="17"/>
+      <c r="C119" s="17"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I119" s="14"/>
+      <c r="J119" s="14"/>
+      <c r="K119" s="45"/>
+      <c r="L119" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M119" s="26"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="17">
+        <v>94</v>
+      </c>
+      <c r="B120" s="17"/>
+      <c r="C120" s="17"/>
+      <c r="D120" s="14"/>
+      <c r="E120" s="14"/>
+      <c r="F120" s="14"/>
+      <c r="G120" s="14"/>
+      <c r="H120" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I120" s="14"/>
+      <c r="J120" s="14"/>
+      <c r="K120" s="45"/>
+      <c r="L120" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M120" s="26"/>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" s="17">
+        <v>95</v>
+      </c>
+      <c r="B121" s="17"/>
+      <c r="C121" s="17"/>
+      <c r="D121" s="14"/>
+      <c r="E121" s="14"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="14"/>
+      <c r="H121" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I121" s="14"/>
+      <c r="J121" s="14"/>
+      <c r="K121" s="45"/>
+      <c r="L121" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M121" s="26"/>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122" s="17">
+        <v>96</v>
+      </c>
+      <c r="B122" s="17"/>
+      <c r="C122" s="17"/>
+      <c r="D122" s="14"/>
+      <c r="E122" s="14"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="14"/>
+      <c r="H122" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I122" s="14"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="45"/>
+      <c r="L122" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M122" s="26"/>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123" s="17">
+        <v>97</v>
+      </c>
+      <c r="B123" s="17"/>
+      <c r="C123" s="17"/>
+      <c r="D123" s="14"/>
+      <c r="E123" s="14"/>
+      <c r="F123" s="14"/>
+      <c r="G123" s="14"/>
+      <c r="H123" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I123" s="14"/>
+      <c r="J123" s="14"/>
+      <c r="K123" s="45"/>
+      <c r="L123" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M123" s="26"/>
+    </row>
+    <row r="124" spans="1:13">
+      <c r="A124" s="17">
+        <v>98</v>
+      </c>
+      <c r="B124" s="17"/>
+      <c r="C124" s="17"/>
+      <c r="D124" s="14"/>
+      <c r="E124" s="14"/>
+      <c r="F124" s="14"/>
+      <c r="G124" s="14"/>
+      <c r="H124" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I124" s="14"/>
+      <c r="J124" s="14"/>
+      <c r="K124" s="45"/>
+      <c r="L124" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M124" s="26"/>
+    </row>
+    <row r="125" spans="1:13">
+      <c r="A125" s="17">
+        <v>99</v>
+      </c>
+      <c r="B125" s="17"/>
+      <c r="C125" s="17"/>
+      <c r="D125" s="14"/>
+      <c r="E125" s="14"/>
+      <c r="F125" s="14"/>
+      <c r="G125" s="14"/>
+      <c r="H125" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I125" s="14"/>
+      <c r="J125" s="14"/>
+      <c r="K125" s="45"/>
+      <c r="L125" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M125" s="26"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I109" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L125" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="20">
+  <mergeCells count="62">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A25"/>
     <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B25"/>
     <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C25"/>
     <mergeCell ref="C26:C28"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="K17:K19"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="K29:K31"/>
+    <mergeCell ref="K32:K34"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="K40:K43"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="M22:M24"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
-      <formula1>$I$2:$I$24</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3 L8 L9 L10 L11 L12 L13 L16 L20 L21 L25 L26 L27 L28 L31 L34 L37 L38 L39 L43 L44 L45 L1:L2 L4:L7 L14:L15 L17:L19 L22:L24 L29:L30 L32:L33 L35:L36 L40:L42 L46:L1048576">
+      <formula1>$L$2:$L$36</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4385,19 +5230,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K93"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="15"/>
-    <col min="2" max="2" width="9.37272727272727" style="15"/>
+    <col min="2" max="2" width="9.37037037037037" style="15"/>
     <col min="3" max="3" width="9" style="23"/>
     <col min="4" max="4" width="9" style="15"/>
-    <col min="5" max="5" width="12.8727272727273" customWidth="1"/>
-    <col min="6" max="8" width="12.8727272727273" style="15" customWidth="1"/>
+    <col min="5" max="5" width="12.8703703703704" customWidth="1"/>
+    <col min="6" max="8" width="12.8703703703704" style="15" customWidth="1"/>
     <col min="9" max="9" width="9" style="23"/>
-    <col min="10" max="10" width="68.6272727272727" style="24" customWidth="1"/>
+    <col min="10" max="10" width="68.6296296296296" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="23" customFormat="1" ht="28" spans="1:11">
+    <row r="1" s="23" customFormat="1" ht="28.8" spans="1:11">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
@@ -4423,10 +5268,10 @@
         <v>13</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J1" s="26" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4437,7 +5282,7 @@
         <v>601398</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D2" s="14">
         <v>1</v>
@@ -4456,7 +5301,7 @@
         <v>26578.24</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J2" s="26"/>
       <c r="K2" s="23"/>
@@ -4476,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J3" s="26"/>
     </row>
@@ -4495,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J4" s="31"/>
     </row>
@@ -4514,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J5" s="26"/>
     </row>
@@ -4533,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J6" s="26"/>
     </row>
@@ -4552,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J7" s="26"/>
     </row>
@@ -4571,7 +5416,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J8" s="26"/>
     </row>
@@ -4590,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J9" s="26"/>
     </row>
@@ -4609,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J10" s="26"/>
     </row>
@@ -4628,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J11" s="26"/>
     </row>
@@ -4647,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J12" s="26"/>
     </row>
@@ -4666,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J13" s="26"/>
     </row>
@@ -4685,7 +5530,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J14" s="26"/>
     </row>
@@ -4704,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J15" s="26"/>
     </row>
@@ -4723,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J16" s="26"/>
     </row>
@@ -4742,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J17" s="26"/>
     </row>
@@ -4761,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J18" s="26"/>
     </row>
@@ -4780,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J19" s="26"/>
     </row>
@@ -4799,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J20" s="26"/>
     </row>
@@ -4818,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J21" s="26"/>
     </row>
@@ -4837,7 +5682,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J22" s="26"/>
     </row>
@@ -4856,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J23" s="26"/>
     </row>
@@ -4875,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J24" s="26"/>
     </row>
@@ -4894,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J25" s="26"/>
     </row>
@@ -4913,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J26" s="26"/>
     </row>
@@ -4932,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J27" s="26"/>
     </row>
@@ -4951,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" s="26"/>
     </row>
@@ -4970,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J29" s="26"/>
     </row>
@@ -4989,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J30" s="26"/>
     </row>
@@ -5008,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J31" s="26"/>
     </row>
@@ -5027,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J32" s="26"/>
     </row>
@@ -5046,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J33" s="26"/>
     </row>
@@ -5065,7 +5910,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J34" s="26"/>
     </row>
@@ -5084,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J35" s="26"/>
     </row>
@@ -5103,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J36" s="26"/>
     </row>
@@ -5122,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J37" s="26"/>
     </row>
@@ -5141,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J38" s="26"/>
     </row>
@@ -5160,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J39" s="26"/>
     </row>
@@ -5179,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J40" s="26"/>
     </row>
@@ -5198,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J41" s="26"/>
     </row>
@@ -5217,7 +6062,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J42" s="26"/>
     </row>
@@ -5236,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J43" s="26"/>
     </row>
@@ -5255,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J44" s="26"/>
     </row>
@@ -5274,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J45" s="26"/>
     </row>
@@ -5293,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J46" s="26"/>
     </row>
@@ -5312,7 +6157,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J47" s="26"/>
     </row>
@@ -5331,7 +6176,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J48" s="26"/>
     </row>
@@ -5350,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J49" s="26"/>
     </row>
@@ -5369,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J50" s="26"/>
     </row>
@@ -5388,7 +6233,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J51" s="26"/>
     </row>
@@ -5407,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J52" s="26"/>
     </row>
@@ -5426,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J53" s="26"/>
     </row>
@@ -5445,7 +6290,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J54" s="26"/>
     </row>
@@ -5464,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J55" s="26"/>
     </row>
@@ -5483,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J56" s="26"/>
     </row>
@@ -5502,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J57" s="26"/>
     </row>
@@ -5521,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J58" s="26"/>
     </row>
@@ -5540,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J59" s="26"/>
     </row>
@@ -5559,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J60" s="26"/>
     </row>
@@ -5578,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J61" s="26"/>
     </row>
@@ -5597,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J62" s="26"/>
     </row>
@@ -5616,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J63" s="26"/>
     </row>
@@ -5635,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J64" s="26"/>
     </row>
@@ -5654,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J65" s="26"/>
     </row>
@@ -5673,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J66" s="26"/>
     </row>
@@ -5692,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J67" s="26"/>
     </row>
@@ -5711,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J68" s="26"/>
     </row>
@@ -5730,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J69" s="26"/>
     </row>
@@ -5749,7 +6594,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J70" s="26"/>
     </row>
@@ -5768,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J71" s="26"/>
     </row>
@@ -5787,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J72" s="26"/>
     </row>
@@ -5806,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J73" s="26"/>
     </row>
@@ -5825,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J74" s="26"/>
     </row>
@@ -5844,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J75" s="26"/>
     </row>
@@ -5863,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J76" s="26"/>
     </row>
@@ -5882,7 +6727,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J77" s="26"/>
     </row>
@@ -5901,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J78" s="26"/>
     </row>
@@ -5920,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J79" s="26"/>
     </row>
@@ -5939,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J80" s="26"/>
     </row>
@@ -5958,7 +6803,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J81" s="26"/>
     </row>
@@ -5977,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J82" s="26"/>
     </row>
@@ -5996,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J83" s="26"/>
     </row>
@@ -6015,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J84" s="26"/>
     </row>
@@ -6034,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J85" s="26"/>
     </row>
@@ -6053,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J86" s="26"/>
     </row>
@@ -6072,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J87" s="26"/>
     </row>
@@ -6091,7 +6936,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J88" s="26"/>
     </row>
@@ -6110,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J89" s="26"/>
     </row>
@@ -6129,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J90" s="26"/>
     </row>
@@ -6148,7 +6993,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J91" s="26"/>
     </row>
@@ -6167,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J92" s="26"/>
     </row>
@@ -6186,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J93" s="26"/>
     </row>
@@ -6208,13 +7053,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.6363636363636"/>
+    <col min="2" max="2" width="10.6388888888889"/>
     <col min="4" max="4" width="9" style="15"/>
-    <col min="8" max="8" width="22.1272727272727" customWidth="1"/>
-    <col min="9" max="9" width="11.8727272727273" style="15" customWidth="1"/>
-    <col min="11" max="11" width="10.8727272727273" customWidth="1"/>
+    <col min="8" max="8" width="22.1296296296296" customWidth="1"/>
+    <col min="9" max="9" width="11.8703703703704" style="15" customWidth="1"/>
+    <col min="11" max="11" width="10.8703703703704" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -6222,40 +7067,40 @@
         <v>7</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -6265,11 +7110,11 @@
       <c r="B2" s="18">
         <v>46188</v>
       </c>
-      <c r="C2" s="52" t="s">
-        <v>21</v>
+      <c r="C2" s="64" t="s">
+        <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" s="9">
         <v>4300</v>
@@ -6281,7 +7126,7 @@
         <v>5.17</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I2" s="14">
         <v>0</v>
@@ -6313,7 +7158,7 @@
         <v>600172</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E3" s="9">
         <v>600</v>
@@ -6325,7 +7170,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I3" s="14">
         <v>0</v>
@@ -6351,7 +7196,7 @@
         <v>601066</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E4" s="9">
         <v>2400</v>
@@ -6363,7 +7208,7 @@
         <v>31</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I4" s="14">
         <v>111.25</v>
@@ -6389,7 +7234,7 @@
         <v>600360</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E5" s="9">
         <v>1300</v>
@@ -6401,7 +7246,7 @@
         <v>17.59</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="9">
@@ -6425,7 +7270,7 @@
         <v>600745</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E6" s="9">
         <v>600</v>
@@ -6437,7 +7282,7 @@
         <v>21.24</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I6" s="14">
         <v>19.06</v>
@@ -6514,7 +7359,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -6550,9 +7395,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="5" max="5" width="12.8727272727273" style="15" customWidth="1"/>
+    <col min="5" max="5" width="12.8703703703704" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6566,27 +7411,27 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="52" t="s">
-        <v>21</v>
+      <c r="B2" s="64" t="s">
+        <v>25</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" s="15">
         <v>5.13</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6597,7 +7442,7 @@
         <v>601398</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D3" s="15">
         <v>7.16</v>
@@ -6614,7 +7459,7 @@
         <v>600115</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D4">
         <v>3.93</v>
@@ -6631,13 +7476,13 @@
         <v>600982</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D5">
         <v>5.02</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6695,16 +7540,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L94"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.54545454545454" customWidth="1"/>
-    <col min="2" max="2" width="8.54545454545454" customWidth="1"/>
-    <col min="3" max="3" width="5.54545454545455" customWidth="1"/>
-    <col min="4" max="4" width="7.54545454545455" customWidth="1"/>
-    <col min="6" max="6" width="8.72727272727273" style="1"/>
-    <col min="7" max="7" width="10.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="8.72727272727273" style="1"/>
-    <col min="13" max="13" width="10.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="9.5462962962963" customWidth="1"/>
+    <col min="2" max="2" width="8.5462962962963" customWidth="1"/>
+    <col min="3" max="3" width="5.5462962962963" customWidth="1"/>
+    <col min="4" max="4" width="7.5462962962963" customWidth="1"/>
+    <col min="6" max="6" width="8.73148148148148" style="1"/>
+    <col min="7" max="7" width="10.6388888888889" customWidth="1"/>
+    <col min="12" max="12" width="8.73148148148148" style="1"/>
+    <col min="13" max="13" width="10.6388888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -6720,7 +7565,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6731,7 +7576,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>11</v>
@@ -6740,10 +7585,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F3" s="3"/>
       <c r="L3" s="3"/>
@@ -6759,10 +7604,10 @@
         <v>1000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3"/>
       <c r="L4" s="3"/>
@@ -6779,15 +7624,21 @@
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" s="3"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="A6" s="7">
+        <v>46239</v>
+      </c>
+      <c r="B6" s="4">
+        <v>8.6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>500</v>
+      </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="3"/>
@@ -6815,7 +7666,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6826,7 +7677,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>11</v>
@@ -6835,10 +7686,10 @@
         <v>12</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F10" s="3"/>
       <c r="L10" s="3"/>
@@ -6854,10 +7705,10 @@
         <v>2000</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F11" s="3"/>
       <c r="L11" s="3"/>
@@ -6874,7 +7725,7 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" s="3"/>
       <c r="L12" s="3"/>
@@ -6910,7 +7761,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -6921,7 +7772,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>11</v>
@@ -6930,10 +7781,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3"/>
       <c r="L17" s="3"/>
@@ -6949,10 +7800,10 @@
         <v>1000</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" s="3"/>
       <c r="L18" s="3"/>
@@ -6969,7 +7820,7 @@
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F19" s="3"/>
       <c r="L19" s="3"/>
@@ -6996,7 +7847,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -7007,7 +7858,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>11</v>
@@ -7016,10 +7867,10 @@
         <v>12</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F23" s="3"/>
       <c r="L23" s="3"/>
@@ -7035,10 +7886,10 @@
         <v>900</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3"/>
       <c r="L24" s="3"/>
@@ -7055,7 +7906,7 @@
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" s="3"/>
       <c r="L25" s="3"/>
@@ -7082,7 +7933,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -7093,7 +7944,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>11</v>
@@ -7102,10 +7953,10 @@
         <v>12</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F29" s="3"/>
       <c r="L29" s="3"/>
@@ -7121,10 +7972,10 @@
         <v>700</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3"/>
       <c r="L30" s="3"/>
@@ -7166,7 +8017,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -7175,7 +8026,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>11</v>
@@ -7184,10 +8035,10 @@
         <v>12</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7201,10 +8052,10 @@
         <v>3200</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7219,7 +8070,7 @@
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -7247,7 +8098,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -7256,7 +8107,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>11</v>
@@ -7265,10 +8116,10 @@
         <v>12</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -7282,10 +8133,10 @@
         <v>1000</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -7300,7 +8151,7 @@
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -7328,7 +8179,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -7337,7 +8188,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>11</v>
@@ -7346,10 +8197,10 @@
         <v>12</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -7363,10 +8214,10 @@
         <v>1700</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -7381,7 +8232,7 @@
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -7402,7 +8253,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -7411,7 +8262,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>11</v>
@@ -7420,10 +8271,10 @@
         <v>12</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -7437,10 +8288,10 @@
         <v>1600</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -7455,7 +8306,7 @@
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -7476,7 +8327,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -7485,7 +8336,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>11</v>
@@ -7494,10 +8345,10 @@
         <v>12</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -7511,10 +8362,10 @@
         <v>3000</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -7529,7 +8380,7 @@
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -7543,7 +8394,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -7552,7 +8403,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>11</v>
@@ -7561,10 +8412,10 @@
         <v>12</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -7578,10 +8429,10 @@
         <v>2300</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -7596,7 +8447,7 @@
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -7624,7 +8475,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
@@ -7633,7 +8484,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>11</v>
@@ -7642,10 +8493,10 @@
         <v>12</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -7659,10 +8510,10 @@
         <v>1000</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -7677,7 +8528,7 @@
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -7705,7 +8556,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -7714,7 +8565,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>11</v>
@@ -7723,10 +8574,10 @@
         <v>12</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -7740,10 +8591,10 @@
         <v>200</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -7760,7 +8611,7 @@
         <v>5.86</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:5">

--- a/stockList.xlsx
+++ b/stockList.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\py3\ShareCertificate\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17700" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="14055" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="总投入" sheetId="2" r:id="rId1"/>
@@ -15,7 +20,7 @@
     <sheet name="做T的股票" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$L$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">清单!$B$1:$L$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">定投股票!$B$1:$I$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已出售!$C$1:$D$6</definedName>
   </definedNames>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="90">
   <si>
     <t>时间</t>
   </si>
@@ -1024,7 +1029,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1122,18 +1127,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1160,21 +1153,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1184,15 +1168,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1202,16 +1180,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1746,12 +1718,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="10.3703703703704" customWidth="1"/>
-    <col min="2" max="2" width="8.87037037037037" customWidth="1"/>
-    <col min="3" max="3" width="10.8703703703704" customWidth="1"/>
-    <col min="4" max="6" width="8.87037037037037" customWidth="1"/>
+    <col min="1" max="1" width="10.3666666666667" customWidth="1"/>
+    <col min="2" max="2" width="8.86666666666667" customWidth="1"/>
+    <col min="3" max="3" width="10.8666666666667" customWidth="1"/>
+    <col min="4" max="6" width="8.86666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1967,20 +1939,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N125"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:N123"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="32"/>
-    <col min="2" max="2" width="9.37037037037037" style="32"/>
-    <col min="3" max="3" width="9" style="32"/>
-    <col min="4" max="4" width="9" style="33"/>
-    <col min="5" max="10" width="12.8703703703704" style="33" customWidth="1"/>
-    <col min="11" max="11" width="12.8703703703704" style="34" customWidth="1"/>
-    <col min="12" max="12" width="9" style="32"/>
-    <col min="13" max="13" width="68.6296296296296" style="35" customWidth="1"/>
+    <col min="1" max="1" width="9" style="17"/>
+    <col min="2" max="2" width="9.36666666666667" style="17"/>
+    <col min="3" max="3" width="9" style="17"/>
+    <col min="4" max="4" width="9" style="14"/>
+    <col min="5" max="10" width="12.8666666666667" style="14" customWidth="1"/>
+    <col min="11" max="11" width="12.8666666666667" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9" style="17"/>
+    <col min="13" max="13" width="68.6333333333333" style="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="23" customFormat="1" ht="28.8" spans="1:14">
+    <row r="1" s="23" customFormat="1" ht="27" spans="1:14">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
@@ -1993,25 +1965,25 @@
       <c r="D1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>16</v>
       </c>
       <c r="L1" s="17" t="s">
@@ -2022,13 +1994,13 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:14">
-      <c r="A2" s="32">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="17">
         <v>300323</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="14">
@@ -2044,12 +2016,11 @@
         <v>1600</v>
       </c>
       <c r="H2" s="14">
-        <f>F2*G2</f>
+        <f t="shared" ref="H2:H30" si="0">F2*G2</f>
         <v>26578.24</v>
       </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39">
+      <c r="J2" s="34"/>
+      <c r="K2" s="35">
         <v>9.99</v>
       </c>
       <c r="L2" s="17" t="s">
@@ -2061,10 +2032,10 @@
       <c r="N2" s="23"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:14">
-      <c r="D3" s="40">
+      <c r="D3" s="36">
         <v>2</v>
       </c>
-      <c r="E3" s="41">
+      <c r="E3" s="37">
         <v>46234</v>
       </c>
       <c r="F3" s="31">
@@ -2073,17 +2044,16 @@
       <c r="G3" s="31">
         <v>-1000</v>
       </c>
-      <c r="H3" s="40">
-        <f>F3*G3</f>
+      <c r="H3" s="36">
+        <f t="shared" si="0"/>
         <v>-11000</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="44" t="s">
+      <c r="I3" s="36"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="26"/>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:14">
       <c r="A4" s="17">
@@ -2108,12 +2078,10 @@
         <v>1800</v>
       </c>
       <c r="H4" s="14">
-        <f>F4*G4</f>
+        <f t="shared" si="0"/>
         <v>7477.38</v>
       </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="45">
+      <c r="K4" s="2">
         <v>3.15</v>
       </c>
       <c r="L4" s="17" t="s">
@@ -2124,19 +2092,19 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:14">
-      <c r="A5" s="46">
+      <c r="A5" s="41">
         <v>3</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="41" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="28">
         <v>1</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="42">
         <v>46182</v>
       </c>
       <c r="F5" s="28">
@@ -2146,12 +2114,12 @@
         <v>-4300</v>
       </c>
       <c r="H5" s="28">
-        <f>F5*G5</f>
+        <f t="shared" si="0"/>
         <v>-20889.83</v>
       </c>
       <c r="I5" s="28"/>
       <c r="J5" s="28"/>
-      <c r="K5" s="48">
+      <c r="K5" s="41">
         <v>4.02</v>
       </c>
       <c r="L5" s="29" t="s">
@@ -2184,12 +2152,10 @@
         <v>500</v>
       </c>
       <c r="H6" s="14">
-        <f>F6*G6</f>
+        <f t="shared" si="0"/>
         <v>4961.35</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="45">
+      <c r="K6" s="2">
         <v>6.46</v>
       </c>
       <c r="L6" s="17" t="s">
@@ -2200,13 +2166,13 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:14">
-      <c r="A7" s="32">
+      <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="17">
         <v>600059</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="17" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="14">
@@ -2222,12 +2188,11 @@
         <v>1000</v>
       </c>
       <c r="H7" s="14">
-        <f>F7*G7</f>
+        <f t="shared" si="0"/>
         <v>10900.8</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="39">
+      <c r="J7" s="34"/>
+      <c r="K7" s="35">
         <v>7.21</v>
       </c>
       <c r="L7" s="17" t="s">
@@ -2238,10 +2203,10 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:14">
-      <c r="D8" s="40">
+      <c r="D8" s="36">
         <v>2</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="37">
         <v>46234</v>
       </c>
       <c r="F8" s="31">
@@ -2250,26 +2215,25 @@
       <c r="G8" s="31">
         <v>-500</v>
       </c>
-      <c r="H8" s="40">
-        <f>F8*G8</f>
+      <c r="H8" s="36">
+        <f t="shared" si="0"/>
         <v>-4050</v>
       </c>
-      <c r="I8" s="40"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="44" t="s">
+      <c r="I8" s="36"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="26"/>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:14">
-      <c r="A9" s="32">
+      <c r="A9" s="17">
         <v>6</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="17" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="14">
@@ -2285,12 +2249,11 @@
         <v>1000</v>
       </c>
       <c r="H9" s="14">
-        <f>F9*G9</f>
+        <f t="shared" si="0"/>
         <v>9650.7</v>
       </c>
-      <c r="I9" s="14"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="49">
+      <c r="J9" s="34"/>
+      <c r="K9" s="35">
         <v>5.55</v>
       </c>
       <c r="L9" s="17" t="s">
@@ -2301,10 +2264,10 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:14">
-      <c r="D10" s="40">
+      <c r="D10" s="36">
         <v>2</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="37">
         <v>46234</v>
       </c>
       <c r="F10" s="31">
@@ -2313,26 +2276,25 @@
       <c r="G10" s="31">
         <v>-500</v>
       </c>
-      <c r="H10" s="40">
-        <f>F10*G10</f>
+      <c r="H10" s="36">
+        <f t="shared" si="0"/>
         <v>-3055</v>
       </c>
-      <c r="I10" s="40"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="44" t="s">
+      <c r="I10" s="36"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="26"/>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:14">
-      <c r="A11" s="32">
+      <c r="A11" s="17">
         <v>7</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="17">
         <v>601179</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D11" s="14">
@@ -2348,12 +2310,11 @@
         <v>700</v>
       </c>
       <c r="H11" s="14">
-        <f>F11*G11</f>
+        <f t="shared" si="0"/>
         <v>14084</v>
       </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="39">
+      <c r="J11" s="34"/>
+      <c r="K11" s="35">
         <v>11.49</v>
       </c>
       <c r="L11" s="17" t="s">
@@ -2364,10 +2325,10 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:14">
-      <c r="D12" s="40">
+      <c r="D12" s="36">
         <v>2</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="37">
         <v>46234</v>
       </c>
       <c r="F12" s="31">
@@ -2376,17 +2337,16 @@
       <c r="G12" s="31">
         <v>-400</v>
       </c>
-      <c r="H12" s="40">
-        <f>F12*G12</f>
+      <c r="H12" s="36">
+        <f t="shared" si="0"/>
         <v>-5400</v>
       </c>
-      <c r="I12" s="40"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="44" t="s">
+      <c r="I12" s="36"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="26"/>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:14">
       <c r="D13" s="14">
@@ -2402,25 +2362,23 @@
         <v>700</v>
       </c>
       <c r="H13" s="14">
-        <f>F13*G13</f>
+        <f t="shared" si="0"/>
         <v>10080</v>
       </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="53"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="39"/>
       <c r="L13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M13" s="26"/>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:14">
-      <c r="A14" s="32">
+      <c r="A14" s="17">
         <v>8</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="17">
         <v>603258</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="17" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="14">
@@ -2436,12 +2394,11 @@
         <v>900</v>
       </c>
       <c r="H14" s="14">
-        <f>F14*G14</f>
+        <f t="shared" si="0"/>
         <v>18619.92</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="39">
+      <c r="J14" s="34"/>
+      <c r="K14" s="35">
         <v>10.75</v>
       </c>
       <c r="L14" s="17" t="s">
@@ -2465,22 +2422,20 @@
         <v>500</v>
       </c>
       <c r="H15" s="14">
-        <f>F15*G15</f>
+        <f t="shared" si="0"/>
         <v>6450</v>
       </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="55"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="44"/>
       <c r="L15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="26"/>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:14">
-      <c r="D16" s="40">
+      <c r="D16" s="36">
         <v>3</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="37">
         <v>46234</v>
       </c>
       <c r="F16" s="31">
@@ -2489,17 +2444,16 @@
       <c r="G16" s="31">
         <v>-700</v>
       </c>
-      <c r="H16" s="40">
-        <f>F16*G16</f>
+      <c r="H16" s="36">
+        <f t="shared" si="0"/>
         <v>-8820</v>
       </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="44" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="26"/>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:13">
       <c r="A17" s="17">
@@ -2524,12 +2478,11 @@
         <v>600</v>
       </c>
       <c r="H17" s="14">
-        <f>F17*G17</f>
+        <f t="shared" si="0"/>
         <v>12637.14</v>
       </c>
-      <c r="I17" s="14"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39">
+      <c r="J17" s="34"/>
+      <c r="K17" s="35">
         <v>7.45</v>
       </c>
       <c r="L17" s="17" t="s">
@@ -2540,69 +2493,61 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:13">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="40">
+      <c r="D18" s="36">
         <v>2</v>
       </c>
-      <c r="E18" s="56">
+      <c r="E18" s="47">
         <v>46188</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="36">
         <v>8.5</v>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="36">
         <v>600</v>
       </c>
-      <c r="H18" s="40">
-        <f>F18*G18</f>
+      <c r="H18" s="36">
+        <f t="shared" si="0"/>
         <v>5100</v>
       </c>
-      <c r="I18" s="40"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="26"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="40" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:13">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="40">
+      <c r="D19" s="36">
         <v>3</v>
       </c>
-      <c r="E19" s="56">
+      <c r="E19" s="47">
         <v>46226</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="36">
         <v>9</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="36">
         <v>-600</v>
       </c>
-      <c r="H19" s="40">
-        <f>F19*G19</f>
+      <c r="H19" s="36">
+        <f t="shared" si="0"/>
         <v>-5400</v>
       </c>
-      <c r="I19" s="40"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="44" t="s">
+      <c r="I19" s="36"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M19" s="26"/>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:13">
-      <c r="A20" s="32">
+      <c r="A20" s="17">
         <v>10</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="17">
         <v>600879</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="17" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="14">
@@ -2618,12 +2563,11 @@
         <v>700</v>
       </c>
       <c r="H20" s="14">
-        <f>F20*G20</f>
+        <f t="shared" si="0"/>
         <v>18386.27</v>
       </c>
-      <c r="I20" s="14"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39">
+      <c r="J20" s="34"/>
+      <c r="K20" s="35">
         <v>13.85</v>
       </c>
       <c r="L20" s="17" t="s">
@@ -2634,10 +2578,10 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:13">
-      <c r="D21" s="40">
+      <c r="D21" s="36">
         <v>2</v>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="37">
         <v>46234</v>
       </c>
       <c r="F21" s="31">
@@ -2646,26 +2590,26 @@
       <c r="G21" s="31">
         <v>-400</v>
       </c>
-      <c r="H21" s="40">
-        <f>F21*G21</f>
+      <c r="H21" s="36">
+        <f t="shared" si="0"/>
         <v>-5860</v>
       </c>
-      <c r="I21" s="40"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="44" t="s">
+      <c r="I21" s="36"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="57"/>
+      <c r="M21" s="48"/>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:13">
-      <c r="A22" s="32">
+      <c r="A22" s="17">
         <v>11</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="17">
         <v>601066</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="17" t="s">
         <v>43</v>
       </c>
       <c r="D22" s="14">
@@ -2681,45 +2625,43 @@
         <v>3400</v>
       </c>
       <c r="H22" s="14">
-        <f>F22*G22</f>
+        <f t="shared" si="0"/>
         <v>93942.68</v>
       </c>
-      <c r="I22" s="14"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39">
+      <c r="J22" s="34"/>
+      <c r="K22" s="35">
         <v>26.18</v>
       </c>
       <c r="L22" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M22" s="57" t="s">
+      <c r="M22" s="48" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:13">
-      <c r="D23" s="40">
+      <c r="D23" s="36">
         <v>2</v>
       </c>
-      <c r="E23" s="56">
+      <c r="E23" s="47">
         <v>46192</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="36">
         <v>31</v>
       </c>
-      <c r="G23" s="40">
+      <c r="G23" s="36">
         <v>-2400</v>
       </c>
-      <c r="H23" s="40">
-        <f>F23*G23</f>
+      <c r="H23" s="36">
+        <f t="shared" si="0"/>
         <v>-74400</v>
       </c>
-      <c r="I23" s="40"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="44" t="s">
+      <c r="I23" s="36"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M23" s="26"/>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:13">
       <c r="D24" s="14">
@@ -2735,22 +2677,20 @@
         <v>1000</v>
       </c>
       <c r="H24" s="14">
-        <f>F24*G24</f>
+        <f t="shared" si="0"/>
         <v>29300</v>
       </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="55"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="44"/>
       <c r="L24" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M24" s="26"/>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:13">
-      <c r="D25" s="40">
+      <c r="D25" s="36">
         <v>4</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="37">
         <v>46234</v>
       </c>
       <c r="F25" s="31">
@@ -2759,26 +2699,25 @@
       <c r="G25" s="31">
         <v>-1000</v>
       </c>
-      <c r="H25" s="40">
-        <f>F25*G25</f>
+      <c r="H25" s="36">
+        <f t="shared" si="0"/>
         <v>-26100</v>
       </c>
-      <c r="I25" s="40"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="44" t="s">
+      <c r="I25" s="36"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M25" s="26"/>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:13">
-      <c r="A26" s="32">
+      <c r="A26" s="17">
         <v>12</v>
       </c>
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="17" t="s">
         <v>46</v>
       </c>
       <c r="D26" s="14">
@@ -2794,12 +2733,11 @@
         <v>1000</v>
       </c>
       <c r="H26" s="14">
-        <f>F26*G26</f>
+        <f t="shared" si="0"/>
         <v>18368.1</v>
       </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="39">
+      <c r="J26" s="34"/>
+      <c r="K26" s="35">
         <v>7.12</v>
       </c>
       <c r="L26" s="17" t="s">
@@ -2810,29 +2748,28 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:13">
-      <c r="D27" s="40">
+      <c r="D27" s="36">
         <v>2</v>
       </c>
-      <c r="E27" s="56">
+      <c r="E27" s="47">
         <v>46234</v>
       </c>
-      <c r="F27" s="40">
+      <c r="F27" s="36">
         <v>7.9</v>
       </c>
-      <c r="G27" s="40">
+      <c r="G27" s="36">
         <v>-500</v>
       </c>
-      <c r="H27" s="40">
-        <f>F27*G27</f>
+      <c r="H27" s="36">
+        <f t="shared" si="0"/>
         <v>-3950</v>
       </c>
-      <c r="I27" s="40"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="44" t="s">
+      <c r="I27" s="36"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M27" s="26"/>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:13">
       <c r="D28" s="14">
@@ -2848,25 +2785,23 @@
         <v>500</v>
       </c>
       <c r="H28" s="14">
-        <f>F28*G28</f>
+        <f t="shared" si="0"/>
         <v>4300</v>
       </c>
-      <c r="I28" s="14"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="53"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="39"/>
       <c r="L28" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M28" s="26"/>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:13">
-      <c r="A29" s="32">
+      <c r="A29" s="17">
         <v>13</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="17">
         <v>300589</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D29" s="14">
@@ -2882,12 +2817,11 @@
         <v>1200</v>
       </c>
       <c r="H29" s="14">
-        <f>F29*G29</f>
+        <f t="shared" si="0"/>
         <v>27387</v>
       </c>
-      <c r="I29" s="14"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="39">
+      <c r="J29" s="34"/>
+      <c r="K29" s="35">
         <v>7.63</v>
       </c>
       <c r="L29" s="17" t="s">
@@ -2911,39 +2845,31 @@
         <v>600</v>
       </c>
       <c r="H30" s="14">
-        <f>F30*G30</f>
+        <f t="shared" si="0"/>
         <v>7530</v>
       </c>
-      <c r="I30" s="14"/>
-      <c r="J30" s="54"/>
-      <c r="K30" s="55"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="44"/>
       <c r="L30" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M30" s="26"/>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:13">
       <c r="D31" s="14">
         <v>3</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="26"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="39"/>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:13">
-      <c r="A32" s="32">
+      <c r="A32" s="17">
         <v>14</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="17">
         <v>300129</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D32" s="14">
@@ -2959,12 +2885,11 @@
         <v>2300</v>
       </c>
       <c r="H32" s="14">
-        <f>F32*G32</f>
+        <f t="shared" ref="H32:H45" si="1">F32*G32</f>
         <v>34273.68</v>
       </c>
-      <c r="I32" s="14"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="39">
+      <c r="J32" s="34"/>
+      <c r="K32" s="35">
         <v>4.36</v>
       </c>
       <c r="L32" s="17" t="s">
@@ -2988,22 +2913,20 @@
         <v>700</v>
       </c>
       <c r="H33" s="14">
-        <f>F33*G33</f>
+        <f t="shared" si="1"/>
         <v>5145</v>
       </c>
-      <c r="I33" s="14"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="55"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="44"/>
       <c r="L33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M33" s="26"/>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:13">
-      <c r="D34" s="40">
+      <c r="D34" s="36">
         <v>3</v>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="37">
         <v>46234</v>
       </c>
       <c r="F34" s="31">
@@ -3012,17 +2935,17 @@
       <c r="G34" s="31">
         <v>-1000</v>
       </c>
-      <c r="H34" s="40">
-        <f>F34*G34</f>
+      <c r="H34" s="36">
+        <f t="shared" si="1"/>
         <v>-7800</v>
       </c>
-      <c r="I34" s="40"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="43"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="39"/>
       <c r="L34" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="M34" s="58"/>
+      <c r="M34" s="49"/>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:13">
       <c r="A35" s="2">
@@ -3034,42 +2957,42 @@
       <c r="C35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="40">
+      <c r="D35" s="36">
         <v>1</v>
       </c>
-      <c r="E35" s="56">
+      <c r="E35" s="47">
         <v>46188</v>
       </c>
-      <c r="F35" s="40">
+      <c r="F35" s="36">
         <v>12.2123</v>
       </c>
-      <c r="G35" s="40">
+      <c r="G35" s="36">
         <v>-600</v>
       </c>
-      <c r="H35" s="40">
-        <f>F35*G35</f>
+      <c r="H35" s="36">
+        <f t="shared" si="1"/>
         <v>-7327.38</v>
       </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="59">
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="2">
         <v>3.71</v>
       </c>
       <c r="L35" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="58" t="s">
+      <c r="M35" s="49" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:13">
-      <c r="A36" s="32">
+      <c r="A36" s="17">
         <v>16</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="17">
         <v>600745</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="17" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="14">
@@ -3085,12 +3008,11 @@
         <v>800</v>
       </c>
       <c r="H36" s="14">
-        <f>F36*G36</f>
+        <f t="shared" si="1"/>
         <v>14934.96</v>
       </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="39">
+      <c r="J36" s="34"/>
+      <c r="K36" s="35">
         <v>15.2</v>
       </c>
       <c r="L36" s="17" t="s">
@@ -3101,10 +3023,10 @@
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:13">
-      <c r="D37" s="40">
+      <c r="D37" s="36">
         <v>2</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="37">
         <v>46234</v>
       </c>
       <c r="F37" s="31">
@@ -3113,28 +3035,27 @@
       <c r="G37" s="31">
         <v>-100</v>
       </c>
-      <c r="H37" s="40">
-        <f>F37*G37</f>
+      <c r="H37" s="36">
+        <f t="shared" si="1"/>
         <v>-1675</v>
       </c>
       <c r="I37" s="31">
         <v>5.86</v>
       </c>
-      <c r="J37" s="60"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="44" t="s">
+      <c r="J37" s="50"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M37" s="26"/>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:13">
-      <c r="A38" s="32">
+      <c r="A38" s="17">
         <v>17</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="17">
         <v>600115</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="17" t="s">
         <v>56</v>
       </c>
       <c r="D38" s="14">
@@ -3150,24 +3071,22 @@
         <v>3200</v>
       </c>
       <c r="H38" s="14">
-        <f>F38*G38</f>
+        <f t="shared" si="1"/>
         <v>12108.16</v>
       </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="39">
+      <c r="J38" s="34"/>
+      <c r="K38" s="35">
         <v>3.46</v>
       </c>
       <c r="L38" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="26"/>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:13">
-      <c r="D39" s="40">
+      <c r="D39" s="36">
         <v>2</v>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="37">
         <v>46234</v>
       </c>
       <c r="F39" s="31">
@@ -3176,26 +3095,25 @@
       <c r="G39" s="31">
         <v>-2000</v>
       </c>
-      <c r="H39" s="40">
-        <f>F39*G39</f>
+      <c r="H39" s="36">
+        <f t="shared" si="1"/>
         <v>-7400</v>
       </c>
       <c r="I39" s="31"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="43"/>
-      <c r="L39" s="44" t="s">
+      <c r="J39" s="50"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M39" s="26"/>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:13">
-      <c r="A40" s="32">
+      <c r="A40" s="17">
         <v>18</v>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="17">
         <v>600360</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="17" t="s">
         <v>57</v>
       </c>
       <c r="D40" s="14">
@@ -3211,43 +3129,40 @@
         <v>1800</v>
       </c>
       <c r="H40" s="14">
-        <f>F40*G40</f>
+        <f t="shared" si="1"/>
         <v>26306.28</v>
       </c>
-      <c r="I40" s="14"/>
-      <c r="J40" s="38"/>
-      <c r="K40" s="39">
+      <c r="J40" s="34"/>
+      <c r="K40" s="35">
         <v>6.07</v>
       </c>
       <c r="L40" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M40" s="26"/>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:13">
-      <c r="D41" s="40">
+      <c r="D41" s="36">
         <v>2</v>
       </c>
-      <c r="E41" s="41">
+      <c r="E41" s="37">
         <v>46213</v>
       </c>
       <c r="F41" s="31">
         <v>17.59</v>
       </c>
-      <c r="G41" s="40">
+      <c r="G41" s="36">
         <v>-1300</v>
       </c>
-      <c r="H41" s="40">
-        <f>F41*G41</f>
+      <c r="H41" s="36">
+        <f t="shared" si="1"/>
         <v>-22867</v>
       </c>
-      <c r="I41" s="40"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="51"/>
-      <c r="L41" s="44" t="s">
+      <c r="I41" s="36"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="44"/>
+      <c r="L41" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M41" s="26"/>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:13">
       <c r="D42" s="14">
@@ -3263,22 +3178,20 @@
         <v>500</v>
       </c>
       <c r="H42" s="14">
-        <f>F42*G42</f>
+        <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="54"/>
-      <c r="K42" s="55"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="44"/>
       <c r="L42" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M42" s="26"/>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:13">
-      <c r="D43" s="40">
+      <c r="D43" s="36">
         <v>4</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="37">
         <v>46234</v>
       </c>
       <c r="F43" s="31">
@@ -3287,26 +3200,25 @@
       <c r="G43" s="31">
         <v>-500</v>
       </c>
-      <c r="H43" s="40">
-        <f>F43*G43</f>
+      <c r="H43" s="36">
+        <f t="shared" si="1"/>
         <v>-4800</v>
       </c>
-      <c r="I43" s="40"/>
-      <c r="J43" s="42"/>
-      <c r="K43" s="43"/>
-      <c r="L43" s="44" t="s">
+      <c r="I43" s="36"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M43" s="26"/>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:13">
-      <c r="A44" s="32">
+      <c r="A44" s="17">
         <v>19</v>
       </c>
-      <c r="B44" s="62" t="s">
+      <c r="B44" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="32" t="s">
+      <c r="C44" s="17" t="s">
         <v>59</v>
       </c>
       <c r="D44" s="14">
@@ -3322,24 +3234,22 @@
         <v>1700</v>
       </c>
       <c r="H44" s="14">
-        <f>F44*G44</f>
+        <f t="shared" si="1"/>
         <v>14549.45</v>
       </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="39">
+      <c r="J44" s="34"/>
+      <c r="K44" s="35">
         <v>3.42</v>
       </c>
       <c r="L44" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M44" s="26"/>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:13">
-      <c r="D45" s="40">
+      <c r="D45" s="36">
         <v>2</v>
       </c>
-      <c r="E45" s="41">
+      <c r="E45" s="37">
         <v>46234</v>
       </c>
       <c r="F45" s="31">
@@ -3348,23 +3258,22 @@
       <c r="G45" s="31">
         <v>-1000</v>
       </c>
-      <c r="H45" s="40">
-        <f>F45*G45</f>
+      <c r="H45" s="36">
+        <f t="shared" si="1"/>
         <v>-5650</v>
       </c>
-      <c r="I45" s="40"/>
-      <c r="J45" s="42"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="44" t="s">
+      <c r="I45" s="36"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="M45" s="26"/>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:13">
       <c r="A46" s="17">
         <v>20</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="52" t="s">
         <v>60</v>
       </c>
       <c r="C46" s="17" t="s">
@@ -3383,18 +3292,15 @@
         <v>1000</v>
       </c>
       <c r="H46" s="14">
-        <f t="shared" ref="H46:H72" si="0">F46*G46</f>
+        <f>F46*G46</f>
         <v>10210.2</v>
       </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="45">
+      <c r="K46" s="2">
         <v>10.26</v>
       </c>
       <c r="L46" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M46" s="26"/>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:13">
       <c r="A47" s="17">
@@ -3419,1737 +3325,930 @@
         <v>2000</v>
       </c>
       <c r="H47" s="14">
-        <f t="shared" si="0"/>
+        <f>F47*G47</f>
         <v>10610.6</v>
       </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="45">
+      <c r="K47" s="2">
         <v>3.03</v>
       </c>
       <c r="L47" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M47" s="26"/>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="17">
-        <v>22</v>
-      </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
+        <v>24</v>
+      </c>
       <c r="H48" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="45"/>
+        <f t="shared" ref="H48:H70" si="2">F48*G48</f>
+        <v>0</v>
+      </c>
       <c r="L48" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M48" s="26"/>
-    </row>
-    <row r="49" spans="1:13">
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" s="17">
-        <v>23</v>
-      </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
+        <v>25</v>
+      </c>
       <c r="H49" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L49" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M49" s="26"/>
-    </row>
-    <row r="50" spans="1:13">
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="17">
-        <v>24</v>
-      </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
+        <v>26</v>
+      </c>
       <c r="H50" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L50" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M50" s="26"/>
-    </row>
-    <row r="51" spans="1:13">
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" s="17">
-        <v>25</v>
-      </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
+        <v>27</v>
+      </c>
       <c r="H51" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L51" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M51" s="26"/>
-    </row>
-    <row r="52" spans="1:13">
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" s="17">
-        <v>26</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+        <v>28</v>
+      </c>
       <c r="H52" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L52" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M52" s="26"/>
-    </row>
-    <row r="53" spans="1:13">
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" s="17">
-        <v>27</v>
-      </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
+        <v>29</v>
+      </c>
       <c r="H53" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L53" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M53" s="26"/>
-    </row>
-    <row r="54" spans="1:13">
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" s="17">
-        <v>28</v>
-      </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
+        <v>30</v>
+      </c>
       <c r="H54" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L54" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M54" s="26"/>
-    </row>
-    <row r="55" spans="1:13">
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" s="17">
-        <v>29</v>
-      </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
+        <v>31</v>
+      </c>
       <c r="H55" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L55" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M55" s="26"/>
-    </row>
-    <row r="56" spans="1:13">
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" s="17">
-        <v>30</v>
-      </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
+        <v>32</v>
+      </c>
       <c r="H56" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L56" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M56" s="26"/>
-    </row>
-    <row r="57" spans="1:13">
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="17">
-        <v>31</v>
-      </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
+        <v>33</v>
+      </c>
       <c r="H57" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L57" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M57" s="26"/>
-    </row>
-    <row r="58" spans="1:13">
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" s="17">
-        <v>32</v>
-      </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
+        <v>34</v>
+      </c>
       <c r="H58" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L58" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M58" s="26"/>
-    </row>
-    <row r="59" spans="1:13">
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" s="17">
-        <v>33</v>
-      </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+        <v>35</v>
+      </c>
       <c r="H59" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L59" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M59" s="26"/>
-    </row>
-    <row r="60" spans="1:13">
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" s="17">
-        <v>34</v>
-      </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
+        <v>36</v>
+      </c>
       <c r="H60" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L60" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M60" s="26"/>
-    </row>
-    <row r="61" spans="1:13">
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" s="17">
-        <v>35</v>
-      </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
+        <v>37</v>
+      </c>
       <c r="H61" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L61" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M61" s="26"/>
-    </row>
-    <row r="62" spans="1:13">
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" s="17">
-        <v>36</v>
-      </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
+        <v>38</v>
+      </c>
       <c r="H62" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L62" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M62" s="26"/>
-    </row>
-    <row r="63" spans="1:13">
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" s="17">
-        <v>37</v>
-      </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
+        <v>39</v>
+      </c>
       <c r="H63" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L63" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M63" s="26"/>
-    </row>
-    <row r="64" spans="1:13">
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" s="17">
-        <v>38</v>
-      </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
+        <v>40</v>
+      </c>
       <c r="H64" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L64" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M64" s="26"/>
-    </row>
-    <row r="65" spans="1:13">
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" s="17">
-        <v>39</v>
-      </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
+        <v>41</v>
+      </c>
       <c r="H65" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L65" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M65" s="26"/>
-    </row>
-    <row r="66" spans="1:13">
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" s="17">
-        <v>40</v>
-      </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
+        <v>42</v>
+      </c>
       <c r="H66" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L66" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M66" s="26"/>
-    </row>
-    <row r="67" spans="1:13">
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67" s="17">
-        <v>41</v>
-      </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
+        <v>43</v>
+      </c>
       <c r="H67" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L67" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M67" s="26"/>
-    </row>
-    <row r="68" spans="1:13">
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68" s="17">
-        <v>42</v>
-      </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+        <v>44</v>
+      </c>
       <c r="H68" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L68" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M68" s="26"/>
-    </row>
-    <row r="69" spans="1:13">
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69" s="17">
-        <v>43</v>
-      </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
+        <v>45</v>
+      </c>
       <c r="H69" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L69" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M69" s="26"/>
-    </row>
-    <row r="70" spans="1:13">
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70" s="17">
-        <v>44</v>
-      </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
+        <v>46</v>
+      </c>
       <c r="H70" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="45"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L70" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M70" s="26"/>
-    </row>
-    <row r="71" spans="1:13">
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" s="17">
-        <v>45</v>
-      </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
+        <v>47</v>
+      </c>
       <c r="H71" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="45"/>
+        <f t="shared" ref="H71:H102" si="3">F71*G71</f>
+        <v>0</v>
+      </c>
       <c r="L71" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M71" s="26"/>
-    </row>
-    <row r="72" spans="1:13">
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72" s="17">
-        <v>46</v>
-      </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
+        <v>48</v>
+      </c>
       <c r="H72" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L72" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M72" s="26"/>
-    </row>
-    <row r="73" spans="1:13">
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73" s="17">
-        <v>47</v>
-      </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
+        <v>49</v>
+      </c>
       <c r="H73" s="14">
-        <f t="shared" ref="H73:H104" si="1">F73*G73</f>
-        <v>0</v>
-      </c>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L73" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M73" s="26"/>
-    </row>
-    <row r="74" spans="1:13">
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" s="17">
-        <v>48</v>
-      </c>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
+        <v>50</v>
+      </c>
       <c r="H74" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L74" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M74" s="26"/>
-    </row>
-    <row r="75" spans="1:13">
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75" s="17">
-        <v>49</v>
-      </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
+        <v>51</v>
+      </c>
       <c r="H75" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
-      <c r="K75" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L75" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M75" s="26"/>
-    </row>
-    <row r="76" spans="1:13">
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76" s="17">
-        <v>50</v>
-      </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
+        <v>52</v>
+      </c>
       <c r="H76" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L76" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M76" s="26"/>
-    </row>
-    <row r="77" spans="1:13">
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77" s="17">
-        <v>51</v>
-      </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
+        <v>53</v>
+      </c>
       <c r="H77" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L77" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M77" s="26"/>
-    </row>
-    <row r="78" spans="1:13">
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78" s="17">
-        <v>52</v>
-      </c>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
+        <v>54</v>
+      </c>
       <c r="H78" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14"/>
-      <c r="K78" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L78" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M78" s="26"/>
-    </row>
-    <row r="79" spans="1:13">
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79" s="17">
-        <v>53</v>
-      </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
+        <v>55</v>
+      </c>
       <c r="H79" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L79" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M79" s="26"/>
-    </row>
-    <row r="80" spans="1:13">
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80" s="17">
-        <v>54</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
+        <v>56</v>
+      </c>
       <c r="H80" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
-      <c r="K80" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L80" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M80" s="26"/>
-    </row>
-    <row r="81" spans="1:13">
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81" s="17">
-        <v>55</v>
-      </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
+        <v>57</v>
+      </c>
       <c r="H81" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L81" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M81" s="26"/>
-    </row>
-    <row r="82" spans="1:13">
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" s="17">
-        <v>56</v>
-      </c>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
+        <v>58</v>
+      </c>
       <c r="H82" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
-      <c r="K82" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L82" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M82" s="26"/>
-    </row>
-    <row r="83" spans="1:13">
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83" s="17">
-        <v>57</v>
-      </c>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
+        <v>59</v>
+      </c>
       <c r="H83" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14"/>
-      <c r="K83" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L83" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M83" s="26"/>
-    </row>
-    <row r="84" spans="1:13">
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84" s="17">
-        <v>58</v>
-      </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
+        <v>60</v>
+      </c>
       <c r="H84" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="14"/>
-      <c r="J84" s="14"/>
-      <c r="K84" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L84" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M84" s="26"/>
-    </row>
-    <row r="85" spans="1:13">
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85" s="17">
-        <v>59</v>
-      </c>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
+        <v>61</v>
+      </c>
       <c r="H85" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14"/>
-      <c r="K85" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L85" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M85" s="26"/>
-    </row>
-    <row r="86" spans="1:13">
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86" s="17">
-        <v>60</v>
-      </c>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
+        <v>62</v>
+      </c>
       <c r="H86" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="14"/>
-      <c r="J86" s="14"/>
-      <c r="K86" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L86" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M86" s="26"/>
-    </row>
-    <row r="87" spans="1:13">
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87" s="17">
-        <v>61</v>
-      </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
+        <v>63</v>
+      </c>
       <c r="H87" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="14"/>
-      <c r="J87" s="14"/>
-      <c r="K87" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L87" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M87" s="26"/>
-    </row>
-    <row r="88" spans="1:13">
+    </row>
+    <row r="88" spans="1:12">
       <c r="A88" s="17">
-        <v>62</v>
-      </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
+        <v>64</v>
+      </c>
       <c r="H88" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="14"/>
-      <c r="J88" s="14"/>
-      <c r="K88" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L88" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M88" s="26"/>
-    </row>
-    <row r="89" spans="1:13">
+    </row>
+    <row r="89" spans="1:12">
       <c r="A89" s="17">
-        <v>63</v>
-      </c>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14"/>
+        <v>65</v>
+      </c>
       <c r="H89" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="14"/>
-      <c r="J89" s="14"/>
-      <c r="K89" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L89" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M89" s="26"/>
-    </row>
-    <row r="90" spans="1:13">
+    </row>
+    <row r="90" spans="1:12">
       <c r="A90" s="17">
-        <v>64</v>
-      </c>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
+        <v>66</v>
+      </c>
       <c r="H90" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="14"/>
-      <c r="J90" s="14"/>
-      <c r="K90" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L90" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M90" s="26"/>
-    </row>
-    <row r="91" spans="1:13">
+    </row>
+    <row r="91" spans="1:12">
       <c r="A91" s="17">
-        <v>65</v>
-      </c>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
+        <v>67</v>
+      </c>
       <c r="H91" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="14"/>
-      <c r="J91" s="14"/>
-      <c r="K91" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L91" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M91" s="26"/>
-    </row>
-    <row r="92" spans="1:13">
+    </row>
+    <row r="92" spans="1:12">
       <c r="A92" s="17">
-        <v>66</v>
-      </c>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
+        <v>68</v>
+      </c>
       <c r="H92" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="14"/>
-      <c r="J92" s="14"/>
-      <c r="K92" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L92" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M92" s="26"/>
-    </row>
-    <row r="93" spans="1:13">
+    </row>
+    <row r="93" spans="1:12">
       <c r="A93" s="17">
-        <v>67</v>
-      </c>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="14"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
+        <v>69</v>
+      </c>
       <c r="H93" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I93" s="14"/>
-      <c r="J93" s="14"/>
-      <c r="K93" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L93" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M93" s="26"/>
-    </row>
-    <row r="94" spans="1:13">
+    </row>
+    <row r="94" spans="1:12">
       <c r="A94" s="17">
-        <v>68</v>
-      </c>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
+        <v>70</v>
+      </c>
       <c r="H94" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I94" s="14"/>
-      <c r="J94" s="14"/>
-      <c r="K94" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L94" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M94" s="26"/>
-    </row>
-    <row r="95" spans="1:13">
+    </row>
+    <row r="95" spans="1:12">
       <c r="A95" s="17">
-        <v>69</v>
-      </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
+        <v>71</v>
+      </c>
       <c r="H95" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="14"/>
-      <c r="J95" s="14"/>
-      <c r="K95" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L95" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M95" s="26"/>
-    </row>
-    <row r="96" spans="1:13">
+    </row>
+    <row r="96" spans="1:12">
       <c r="A96" s="17">
-        <v>70</v>
-      </c>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
+        <v>72</v>
+      </c>
       <c r="H96" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I96" s="14"/>
-      <c r="J96" s="14"/>
-      <c r="K96" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L96" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M96" s="26"/>
-    </row>
-    <row r="97" spans="1:13">
+    </row>
+    <row r="97" spans="1:12">
       <c r="A97" s="17">
-        <v>71</v>
-      </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="14"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
+        <v>73</v>
+      </c>
       <c r="H97" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I97" s="14"/>
-      <c r="J97" s="14"/>
-      <c r="K97" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L97" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M97" s="26"/>
-    </row>
-    <row r="98" spans="1:13">
+    </row>
+    <row r="98" spans="1:12">
       <c r="A98" s="17">
-        <v>72</v>
-      </c>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
+        <v>74</v>
+      </c>
       <c r="H98" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I98" s="14"/>
-      <c r="J98" s="14"/>
-      <c r="K98" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L98" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M98" s="26"/>
-    </row>
-    <row r="99" spans="1:13">
+    </row>
+    <row r="99" spans="1:12">
       <c r="A99" s="17">
-        <v>73</v>
-      </c>
-      <c r="B99" s="17"/>
-      <c r="C99" s="17"/>
-      <c r="D99" s="14"/>
-      <c r="E99" s="14"/>
-      <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
+        <v>75</v>
+      </c>
       <c r="H99" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I99" s="14"/>
-      <c r="J99" s="14"/>
-      <c r="K99" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L99" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M99" s="26"/>
-    </row>
-    <row r="100" spans="1:13">
+    </row>
+    <row r="100" spans="1:12">
       <c r="A100" s="17">
-        <v>74</v>
-      </c>
-      <c r="B100" s="17"/>
-      <c r="C100" s="17"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
+        <v>76</v>
+      </c>
       <c r="H100" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="14"/>
-      <c r="J100" s="14"/>
-      <c r="K100" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L100" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M100" s="26"/>
-    </row>
-    <row r="101" spans="1:13">
+    </row>
+    <row r="101" spans="1:12">
       <c r="A101" s="17">
-        <v>75</v>
-      </c>
-      <c r="B101" s="17"/>
-      <c r="C101" s="17"/>
-      <c r="D101" s="14"/>
-      <c r="E101" s="14"/>
-      <c r="F101" s="14"/>
-      <c r="G101" s="14"/>
+        <v>77</v>
+      </c>
       <c r="H101" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I101" s="14"/>
-      <c r="J101" s="14"/>
-      <c r="K101" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L101" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M101" s="26"/>
-    </row>
-    <row r="102" spans="1:13">
+    </row>
+    <row r="102" spans="1:12">
       <c r="A102" s="17">
-        <v>76</v>
-      </c>
-      <c r="B102" s="17"/>
-      <c r="C102" s="17"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="14"/>
-      <c r="F102" s="14"/>
-      <c r="G102" s="14"/>
+        <v>78</v>
+      </c>
       <c r="H102" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I102" s="14"/>
-      <c r="J102" s="14"/>
-      <c r="K102" s="45"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="L102" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M102" s="26"/>
-    </row>
-    <row r="103" spans="1:13">
+    </row>
+    <row r="103" spans="1:12">
       <c r="A103" s="17">
-        <v>77</v>
-      </c>
-      <c r="B103" s="17"/>
-      <c r="C103" s="17"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="14"/>
-      <c r="F103" s="14"/>
-      <c r="G103" s="14"/>
+        <v>79</v>
+      </c>
       <c r="H103" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="14"/>
-      <c r="J103" s="14"/>
-      <c r="K103" s="45"/>
+        <f t="shared" ref="H103:H123" si="4">F103*G103</f>
+        <v>0</v>
+      </c>
       <c r="L103" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M103" s="26"/>
-    </row>
-    <row r="104" spans="1:13">
+    </row>
+    <row r="104" spans="1:12">
       <c r="A104" s="17">
-        <v>78</v>
-      </c>
-      <c r="B104" s="17"/>
-      <c r="C104" s="17"/>
-      <c r="D104" s="14"/>
-      <c r="E104" s="14"/>
-      <c r="F104" s="14"/>
-      <c r="G104" s="14"/>
+        <v>80</v>
+      </c>
       <c r="H104" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="14"/>
-      <c r="J104" s="14"/>
-      <c r="K104" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L104" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M104" s="26"/>
-    </row>
-    <row r="105" spans="1:13">
+    </row>
+    <row r="105" spans="1:12">
       <c r="A105" s="17">
-        <v>79</v>
-      </c>
-      <c r="B105" s="17"/>
-      <c r="C105" s="17"/>
-      <c r="D105" s="14"/>
-      <c r="E105" s="14"/>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14"/>
+        <v>81</v>
+      </c>
       <c r="H105" s="14">
-        <f t="shared" ref="H105:H125" si="2">F105*G105</f>
-        <v>0</v>
-      </c>
-      <c r="I105" s="14"/>
-      <c r="J105" s="14"/>
-      <c r="K105" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L105" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M105" s="26"/>
-    </row>
-    <row r="106" spans="1:13">
+    </row>
+    <row r="106" spans="1:12">
       <c r="A106" s="17">
-        <v>80</v>
-      </c>
-      <c r="B106" s="17"/>
-      <c r="C106" s="17"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
+        <v>82</v>
+      </c>
       <c r="H106" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="14"/>
-      <c r="J106" s="14"/>
-      <c r="K106" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L106" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M106" s="26"/>
-    </row>
-    <row r="107" spans="1:13">
+    </row>
+    <row r="107" spans="1:12">
       <c r="A107" s="17">
-        <v>81</v>
-      </c>
-      <c r="B107" s="17"/>
-      <c r="C107" s="17"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="14"/>
-      <c r="G107" s="14"/>
+        <v>83</v>
+      </c>
       <c r="H107" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I107" s="14"/>
-      <c r="J107" s="14"/>
-      <c r="K107" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L107" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M107" s="26"/>
-    </row>
-    <row r="108" spans="1:13">
+    </row>
+    <row r="108" spans="1:12">
       <c r="A108" s="17">
-        <v>82</v>
-      </c>
-      <c r="B108" s="17"/>
-      <c r="C108" s="17"/>
-      <c r="D108" s="14"/>
-      <c r="E108" s="14"/>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14"/>
+        <v>84</v>
+      </c>
       <c r="H108" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I108" s="14"/>
-      <c r="J108" s="14"/>
-      <c r="K108" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L108" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M108" s="26"/>
-    </row>
-    <row r="109" spans="1:13">
+    </row>
+    <row r="109" spans="1:12">
       <c r="A109" s="17">
-        <v>83</v>
-      </c>
-      <c r="B109" s="17"/>
-      <c r="C109" s="17"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14"/>
+        <v>85</v>
+      </c>
       <c r="H109" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I109" s="14"/>
-      <c r="J109" s="14"/>
-      <c r="K109" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L109" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M109" s="26"/>
-    </row>
-    <row r="110" spans="1:13">
+    </row>
+    <row r="110" spans="1:12">
       <c r="A110" s="17">
-        <v>84</v>
-      </c>
-      <c r="B110" s="17"/>
-      <c r="C110" s="17"/>
-      <c r="D110" s="14"/>
-      <c r="E110" s="14"/>
-      <c r="F110" s="14"/>
-      <c r="G110" s="14"/>
+        <v>86</v>
+      </c>
       <c r="H110" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I110" s="14"/>
-      <c r="J110" s="14"/>
-      <c r="K110" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L110" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M110" s="26"/>
-    </row>
-    <row r="111" spans="1:13">
+    </row>
+    <row r="111" spans="1:12">
       <c r="A111" s="17">
-        <v>85</v>
-      </c>
-      <c r="B111" s="17"/>
-      <c r="C111" s="17"/>
-      <c r="D111" s="14"/>
-      <c r="E111" s="14"/>
-      <c r="F111" s="14"/>
-      <c r="G111" s="14"/>
+        <v>87</v>
+      </c>
       <c r="H111" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I111" s="14"/>
-      <c r="J111" s="14"/>
-      <c r="K111" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L111" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M111" s="26"/>
-    </row>
-    <row r="112" spans="1:13">
+    </row>
+    <row r="112" spans="1:12">
       <c r="A112" s="17">
-        <v>86</v>
-      </c>
-      <c r="B112" s="17"/>
-      <c r="C112" s="17"/>
-      <c r="D112" s="14"/>
-      <c r="E112" s="14"/>
-      <c r="F112" s="14"/>
-      <c r="G112" s="14"/>
+        <v>88</v>
+      </c>
       <c r="H112" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I112" s="14"/>
-      <c r="J112" s="14"/>
-      <c r="K112" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L112" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M112" s="26"/>
-    </row>
-    <row r="113" spans="1:13">
+    </row>
+    <row r="113" spans="1:12">
       <c r="A113" s="17">
-        <v>87</v>
-      </c>
-      <c r="B113" s="17"/>
-      <c r="C113" s="17"/>
-      <c r="D113" s="14"/>
-      <c r="E113" s="14"/>
-      <c r="F113" s="14"/>
-      <c r="G113" s="14"/>
+        <v>89</v>
+      </c>
       <c r="H113" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I113" s="14"/>
-      <c r="J113" s="14"/>
-      <c r="K113" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L113" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M113" s="26"/>
-    </row>
-    <row r="114" spans="1:13">
+    </row>
+    <row r="114" spans="1:12">
       <c r="A114" s="17">
-        <v>88</v>
-      </c>
-      <c r="B114" s="17"/>
-      <c r="C114" s="17"/>
-      <c r="D114" s="14"/>
-      <c r="E114" s="14"/>
-      <c r="F114" s="14"/>
-      <c r="G114" s="14"/>
+        <v>90</v>
+      </c>
       <c r="H114" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I114" s="14"/>
-      <c r="J114" s="14"/>
-      <c r="K114" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L114" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M114" s="26"/>
-    </row>
-    <row r="115" spans="1:13">
+    </row>
+    <row r="115" spans="1:12">
       <c r="A115" s="17">
-        <v>89</v>
-      </c>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="14"/>
-      <c r="E115" s="14"/>
-      <c r="F115" s="14"/>
-      <c r="G115" s="14"/>
+        <v>91</v>
+      </c>
       <c r="H115" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I115" s="14"/>
-      <c r="J115" s="14"/>
-      <c r="K115" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L115" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M115" s="26"/>
-    </row>
-    <row r="116" spans="1:13">
+    </row>
+    <row r="116" spans="1:12">
       <c r="A116" s="17">
-        <v>90</v>
-      </c>
-      <c r="B116" s="17"/>
-      <c r="C116" s="17"/>
-      <c r="D116" s="14"/>
-      <c r="E116" s="14"/>
-      <c r="F116" s="14"/>
-      <c r="G116" s="14"/>
+        <v>92</v>
+      </c>
       <c r="H116" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I116" s="14"/>
-      <c r="J116" s="14"/>
-      <c r="K116" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L116" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M116" s="26"/>
-    </row>
-    <row r="117" spans="1:13">
+    </row>
+    <row r="117" spans="1:12">
       <c r="A117" s="17">
-        <v>91</v>
-      </c>
-      <c r="B117" s="17"/>
-      <c r="C117" s="17"/>
-      <c r="D117" s="14"/>
-      <c r="E117" s="14"/>
-      <c r="F117" s="14"/>
-      <c r="G117" s="14"/>
+        <v>93</v>
+      </c>
       <c r="H117" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I117" s="14"/>
-      <c r="J117" s="14"/>
-      <c r="K117" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L117" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M117" s="26"/>
-    </row>
-    <row r="118" spans="1:13">
+    </row>
+    <row r="118" spans="1:12">
       <c r="A118" s="17">
-        <v>92</v>
-      </c>
-      <c r="B118" s="17"/>
-      <c r="C118" s="17"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="14"/>
-      <c r="F118" s="14"/>
-      <c r="G118" s="14"/>
+        <v>94</v>
+      </c>
       <c r="H118" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="14"/>
-      <c r="J118" s="14"/>
-      <c r="K118" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L118" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M118" s="26"/>
-    </row>
-    <row r="119" spans="1:13">
+    </row>
+    <row r="119" spans="1:12">
       <c r="A119" s="17">
-        <v>93</v>
-      </c>
-      <c r="B119" s="17"/>
-      <c r="C119" s="17"/>
-      <c r="D119" s="14"/>
-      <c r="E119" s="14"/>
-      <c r="F119" s="14"/>
-      <c r="G119" s="14"/>
+        <v>95</v>
+      </c>
       <c r="H119" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I119" s="14"/>
-      <c r="J119" s="14"/>
-      <c r="K119" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L119" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M119" s="26"/>
-    </row>
-    <row r="120" spans="1:13">
+    </row>
+    <row r="120" spans="1:12">
       <c r="A120" s="17">
-        <v>94</v>
-      </c>
-      <c r="B120" s="17"/>
-      <c r="C120" s="17"/>
-      <c r="D120" s="14"/>
-      <c r="E120" s="14"/>
-      <c r="F120" s="14"/>
-      <c r="G120" s="14"/>
+        <v>96</v>
+      </c>
       <c r="H120" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I120" s="14"/>
-      <c r="J120" s="14"/>
-      <c r="K120" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L120" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M120" s="26"/>
-    </row>
-    <row r="121" spans="1:13">
+    </row>
+    <row r="121" spans="1:12">
       <c r="A121" s="17">
-        <v>95</v>
-      </c>
-      <c r="B121" s="17"/>
-      <c r="C121" s="17"/>
-      <c r="D121" s="14"/>
-      <c r="E121" s="14"/>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
+        <v>97</v>
+      </c>
       <c r="H121" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I121" s="14"/>
-      <c r="J121" s="14"/>
-      <c r="K121" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L121" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M121" s="26"/>
-    </row>
-    <row r="122" spans="1:13">
+    </row>
+    <row r="122" spans="1:12">
       <c r="A122" s="17">
-        <v>96</v>
-      </c>
-      <c r="B122" s="17"/>
-      <c r="C122" s="17"/>
-      <c r="D122" s="14"/>
-      <c r="E122" s="14"/>
-      <c r="F122" s="14"/>
-      <c r="G122" s="14"/>
+        <v>98</v>
+      </c>
       <c r="H122" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I122" s="14"/>
-      <c r="J122" s="14"/>
-      <c r="K122" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L122" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M122" s="26"/>
-    </row>
-    <row r="123" spans="1:13">
+    </row>
+    <row r="123" spans="1:12">
       <c r="A123" s="17">
-        <v>97</v>
-      </c>
-      <c r="B123" s="17"/>
-      <c r="C123" s="17"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="14"/>
-      <c r="F123" s="14"/>
-      <c r="G123" s="14"/>
+        <v>99</v>
+      </c>
       <c r="H123" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I123" s="14"/>
-      <c r="J123" s="14"/>
-      <c r="K123" s="45"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="L123" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M123" s="26"/>
-    </row>
-    <row r="124" spans="1:13">
-      <c r="A124" s="17">
-        <v>98</v>
-      </c>
-      <c r="B124" s="17"/>
-      <c r="C124" s="17"/>
-      <c r="D124" s="14"/>
-      <c r="E124" s="14"/>
-      <c r="F124" s="14"/>
-      <c r="G124" s="14"/>
-      <c r="H124" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I124" s="14"/>
-      <c r="J124" s="14"/>
-      <c r="K124" s="45"/>
-      <c r="L124" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="M124" s="26"/>
-    </row>
-    <row r="125" spans="1:13">
-      <c r="A125" s="17">
-        <v>99</v>
-      </c>
-      <c r="B125" s="17"/>
-      <c r="C125" s="17"/>
-      <c r="D125" s="14"/>
-      <c r="E125" s="14"/>
-      <c r="F125" s="14"/>
-      <c r="G125" s="14"/>
-      <c r="H125" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I125" s="14"/>
-      <c r="J125" s="14"/>
-      <c r="K125" s="45"/>
-      <c r="L125" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="M125" s="26"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L125" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L123" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="62">
@@ -5217,7 +4316,7 @@
     <mergeCell ref="M22:M24"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3 L8 L9 L10 L11 L12 L13 L16 L20 L21 L25 L26 L27 L28 L31 L34 L37 L38 L39 L43 L44 L45 L1:L2 L4:L7 L14:L15 L17:L19 L22:L24 L29:L30 L32:L33 L35:L36 L40:L42 L46:L1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L47 L48:L1048576">
       <formula1>$L$2:$L$36</formula1>
     </dataValidation>
   </dataValidations>
@@ -5230,19 +4329,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K93"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="15"/>
-    <col min="2" max="2" width="9.37037037037037" style="15"/>
+    <col min="2" max="2" width="9.36666666666667" style="15"/>
     <col min="3" max="3" width="9" style="23"/>
     <col min="4" max="4" width="9" style="15"/>
-    <col min="5" max="5" width="12.8703703703704" customWidth="1"/>
-    <col min="6" max="8" width="12.8703703703704" style="15" customWidth="1"/>
+    <col min="5" max="5" width="12.8666666666667" customWidth="1"/>
+    <col min="6" max="8" width="12.8666666666667" style="15" customWidth="1"/>
     <col min="9" max="9" width="9" style="23"/>
-    <col min="10" max="10" width="68.6296296296296" style="24" customWidth="1"/>
+    <col min="10" max="10" width="68.6333333333333" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="23" customFormat="1" ht="28.8" spans="1:11">
+    <row r="1" s="23" customFormat="1" ht="27" spans="1:11">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
@@ -7053,13 +6152,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="10.6388888888889"/>
+    <col min="2" max="2" width="10.6416666666667"/>
     <col min="4" max="4" width="9" style="15"/>
-    <col min="8" max="8" width="22.1296296296296" customWidth="1"/>
-    <col min="9" max="9" width="11.8703703703704" style="15" customWidth="1"/>
-    <col min="11" max="11" width="10.8703703703704" customWidth="1"/>
+    <col min="8" max="8" width="22.1333333333333" customWidth="1"/>
+    <col min="9" max="9" width="11.8666666666667" style="15" customWidth="1"/>
+    <col min="11" max="11" width="10.8666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7110,7 +6209,7 @@
       <c r="B2" s="18">
         <v>46188</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="53" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
@@ -7395,9 +6494,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="5" max="5" width="12.8703703703704" style="15" customWidth="1"/>
+    <col min="5" max="5" width="12.8666666666667" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7421,7 +6520,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="53" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="16" t="s">
@@ -7540,16 +6639,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L94"/>
-  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.73333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.5462962962963" customWidth="1"/>
-    <col min="2" max="2" width="8.5462962962963" customWidth="1"/>
-    <col min="3" max="3" width="5.5462962962963" customWidth="1"/>
-    <col min="4" max="4" width="7.5462962962963" customWidth="1"/>
-    <col min="6" max="6" width="8.73148148148148" style="1"/>
-    <col min="7" max="7" width="10.6388888888889" customWidth="1"/>
-    <col min="12" max="12" width="8.73148148148148" style="1"/>
-    <col min="13" max="13" width="10.6388888888889" customWidth="1"/>
+    <col min="1" max="1" width="9.55" customWidth="1"/>
+    <col min="2" max="2" width="8.55" customWidth="1"/>
+    <col min="3" max="3" width="5.55" customWidth="1"/>
+    <col min="4" max="4" width="7.55" customWidth="1"/>
+    <col min="6" max="6" width="8.73333333333333" style="1"/>
+    <col min="7" max="7" width="10.6416666666667" customWidth="1"/>
+    <col min="12" max="12" width="8.73333333333333" style="1"/>
+    <col min="13" max="13" width="10.6416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
